--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,72 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
+    <t>Slovenian 2 SNL</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Orsomarso</t>
+  </si>
+  <si>
+    <t>NK Bilje</t>
+  </si>
+  <si>
+    <t>Club Sportivo Ameliano</t>
+  </si>
+  <si>
+    <t>Santa Fe</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Quindio</t>
+  </si>
+  <si>
+    <t>NK Jadran Dekani</t>
+  </si>
+  <si>
+    <t>Rubio Nu</t>
+  </si>
+  <si>
+    <t>2026-10-04 01:41:40</t>
   </si>
 </sst>
 </file>
@@ -585,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +894,1216 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2">
+        <v>1.93</v>
+      </c>
+      <c r="G2">
+        <v>2.04</v>
+      </c>
+      <c r="H2">
+        <v>4.1</v>
+      </c>
+      <c r="I2">
+        <v>4.5</v>
+      </c>
+      <c r="J2">
+        <v>3.6</v>
+      </c>
+      <c r="K2">
+        <v>3.9</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
+        <v>3.75</v>
+      </c>
+      <c r="O2">
+        <v>1.31</v>
+      </c>
+      <c r="P2">
+        <v>1.96</v>
+      </c>
+      <c r="Q2">
+        <v>1.84</v>
+      </c>
+      <c r="R2">
+        <v>1.36</v>
+      </c>
+      <c r="S2">
+        <v>3.3</v>
+      </c>
+      <c r="T2">
+        <v>1.8</v>
+      </c>
+      <c r="U2">
+        <v>2.1</v>
+      </c>
+      <c r="V2">
+        <v>1.28</v>
+      </c>
+      <c r="W2">
+        <v>1.96</v>
+      </c>
+      <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2">
+        <v>19</v>
+      </c>
+      <c r="Z2">
+        <v>40</v>
+      </c>
+      <c r="AA2">
+        <v>120</v>
+      </c>
+      <c r="AB2">
+        <v>11.5</v>
+      </c>
+      <c r="AC2">
+        <v>10.5</v>
+      </c>
+      <c r="AD2">
+        <v>21</v>
+      </c>
+      <c r="AE2">
+        <v>70</v>
+      </c>
+      <c r="AF2">
+        <v>15</v>
+      </c>
+      <c r="AG2">
+        <v>13</v>
+      </c>
+      <c r="AH2">
+        <v>23</v>
+      </c>
+      <c r="AI2">
+        <v>75</v>
+      </c>
+      <c r="AJ2">
+        <v>28</v>
+      </c>
+      <c r="AK2">
+        <v>26</v>
+      </c>
+      <c r="AL2">
+        <v>44</v>
+      </c>
+      <c r="AM2">
+        <v>120</v>
+      </c>
+      <c r="AN2">
+        <v>17</v>
+      </c>
+      <c r="AO2">
+        <v>75</v>
+      </c>
+      <c r="AP2">
+        <v>13</v>
+      </c>
+      <c r="AQ2">
+        <v>13.5</v>
+      </c>
+      <c r="AR2">
+        <v>4.3</v>
+      </c>
+      <c r="AS2">
+        <v>4.7</v>
+      </c>
+      <c r="AT2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
+        <v>14.5</v>
+      </c>
+      <c r="AW2">
+        <v>4.6</v>
+      </c>
+      <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>4.6</v>
+      </c>
+      <c r="BB2">
+        <v>19.5</v>
+      </c>
+      <c r="BC2">
+        <v>17.5</v>
+      </c>
+      <c r="BD2">
+        <v>4.4</v>
+      </c>
+      <c r="BE2">
+        <v>4.7</v>
+      </c>
+      <c r="BF2">
+        <v>12</v>
+      </c>
+      <c r="BG2">
+        <v>4.6</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3">
+        <v>4.2</v>
+      </c>
+      <c r="G3">
+        <v>5.2</v>
+      </c>
+      <c r="H3">
+        <v>1.84</v>
+      </c>
+      <c r="I3">
+        <v>2.16</v>
+      </c>
+      <c r="J3">
+        <v>3.1</v>
+      </c>
+      <c r="K3">
+        <v>4.3</v>
+      </c>
+      <c r="L3">
+        <v>1.44</v>
+      </c>
+      <c r="M3">
+        <v>1.09</v>
+      </c>
+      <c r="N3">
+        <v>2.9</v>
+      </c>
+      <c r="O3">
+        <v>1.4</v>
+      </c>
+      <c r="P3">
+        <v>1.76</v>
+      </c>
+      <c r="Q3">
+        <v>2.24</v>
+      </c>
+      <c r="R3">
+        <v>1.23</v>
+      </c>
+      <c r="S3">
+        <v>3.8</v>
+      </c>
+      <c r="T3">
+        <v>1.94</v>
+      </c>
+      <c r="U3">
+        <v>1.78</v>
+      </c>
+      <c r="V3">
+        <v>1.87</v>
+      </c>
+      <c r="W3">
+        <v>1.23</v>
+      </c>
+      <c r="X3">
+        <v>21</v>
+      </c>
+      <c r="Y3">
+        <v>13</v>
+      </c>
+      <c r="Z3">
+        <v>21</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>36</v>
+      </c>
+      <c r="AC3">
+        <v>13</v>
+      </c>
+      <c r="AD3">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>95</v>
+      </c>
+      <c r="AP3">
+        <v>7.6</v>
+      </c>
+      <c r="AQ3">
+        <v>5.8</v>
+      </c>
+      <c r="AR3">
+        <v>7.6</v>
+      </c>
+      <c r="AS3">
+        <v>1.54</v>
+      </c>
+      <c r="AT3">
+        <v>9</v>
+      </c>
+      <c r="AU3">
+        <v>6</v>
+      </c>
+      <c r="AV3">
+        <v>7.6</v>
+      </c>
+      <c r="AW3">
+        <v>1.54</v>
+      </c>
+      <c r="AX3">
+        <v>1.54</v>
+      </c>
+      <c r="AY3">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3">
+        <v>1.54</v>
+      </c>
+      <c r="BA3">
+        <v>1.54</v>
+      </c>
+      <c r="BB3">
+        <v>1.54</v>
+      </c>
+      <c r="BC3">
+        <v>1.54</v>
+      </c>
+      <c r="BD3">
+        <v>1.54</v>
+      </c>
+      <c r="BE3">
+        <v>1.54</v>
+      </c>
+      <c r="BF3">
+        <v>1.54</v>
+      </c>
+      <c r="BG3">
+        <v>9.4</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.36</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>2.32</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.32</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.99</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.32</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.32</v>
+      </c>
+      <c r="BT3">
+        <v>6</v>
+      </c>
+      <c r="BU3">
+        <v>3.3</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>2.32</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.32</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.32</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4">
+        <v>2.82</v>
+      </c>
+      <c r="G4">
+        <v>3.2</v>
+      </c>
+      <c r="H4">
+        <v>2.78</v>
+      </c>
+      <c r="I4">
+        <v>3.2</v>
+      </c>
+      <c r="J4">
+        <v>2.82</v>
+      </c>
+      <c r="K4">
+        <v>3.25</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>2.44</v>
+      </c>
+      <c r="O4">
+        <v>1.33</v>
+      </c>
+      <c r="P4">
+        <v>1.49</v>
+      </c>
+      <c r="Q4">
+        <v>2.62</v>
+      </c>
+      <c r="R4">
+        <v>1.08</v>
+      </c>
+      <c r="S4">
+        <v>3.15</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.45</v>
+      </c>
+      <c r="W4">
+        <v>1.45</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4">
+        <v>1.03</v>
+      </c>
+      <c r="AR4">
+        <v>1.03</v>
+      </c>
+      <c r="AS4">
+        <v>1.03</v>
+      </c>
+      <c r="AT4">
+        <v>1.03</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>1.03</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>1.03</v>
+      </c>
+      <c r="AY4">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.03</v>
+      </c>
+      <c r="BB4">
+        <v>1.03</v>
+      </c>
+      <c r="BC4">
+        <v>1.01</v>
+      </c>
+      <c r="BD4">
+        <v>1.03</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5">
+        <v>1.5</v>
+      </c>
+      <c r="G5">
+        <v>5.4</v>
+      </c>
+      <c r="H5">
+        <v>1.48</v>
+      </c>
+      <c r="I5">
+        <v>3.45</v>
+      </c>
+      <c r="J5">
+        <v>2.56</v>
+      </c>
+      <c r="K5">
+        <v>950</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>1.24</v>
+      </c>
+      <c r="O5">
+        <v>1.02</v>
+      </c>
+      <c r="P5">
+        <v>1.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.03</v>
+      </c>
+      <c r="R5">
+        <v>1.18</v>
+      </c>
+      <c r="S5">
+        <v>1.04</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>1.46</v>
+      </c>
+      <c r="W5">
+        <v>1.44</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5">
+        <v>1.03</v>
+      </c>
+      <c r="AR5">
+        <v>1.03</v>
+      </c>
+      <c r="AS5">
+        <v>1.03</v>
+      </c>
+      <c r="AT5">
+        <v>1.03</v>
+      </c>
+      <c r="AU5">
+        <v>1.03</v>
+      </c>
+      <c r="AV5">
+        <v>1.03</v>
+      </c>
+      <c r="AW5">
+        <v>1.03</v>
+      </c>
+      <c r="AX5">
+        <v>1.03</v>
+      </c>
+      <c r="AY5">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5">
+        <v>1.03</v>
+      </c>
+      <c r="BA5">
+        <v>1.03</v>
+      </c>
+      <c r="BB5">
+        <v>1.03</v>
+      </c>
+      <c r="BC5">
+        <v>1.03</v>
+      </c>
+      <c r="BD5">
+        <v>1.03</v>
+      </c>
+      <c r="BE5">
+        <v>1.03</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.07</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -319,7 +319,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 01:41:40</t>
+    <t>2026-10-04 03:53:43</t>
   </si>
 </sst>
 </file>
@@ -913,7 +913,7 @@
         <v>96</v>
       </c>
       <c r="F2">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G2">
         <v>2.04</v>
@@ -925,7 +925,7 @@
         <v>4.5</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
         <v>3.9</v>
@@ -937,28 +937,28 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
         <v>1.84</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V2">
         <v>1.28</v>
@@ -1015,7 +1015,7 @@
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO2">
         <v>75</v>
@@ -1030,7 +1030,7 @@
         <v>4.3</v>
       </c>
       <c r="AS2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1042,7 +1042,7 @@
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1054,7 +1054,7 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB2">
         <v>19.5</v>
@@ -1063,16 +1063,16 @@
         <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1397,16 +1397,16 @@
         <v>98</v>
       </c>
       <c r="F4">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
         <v>2.82</v>
@@ -1415,16 +1415,16 @@
         <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="P4">
         <v>1.49</v>
@@ -1433,121 +1433,121 @@
         <v>2.62</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW4">
         <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
         <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
         <v>1.01</v>
@@ -1562,61 +1562,61 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="CB4" t="s">
         <v>101</v>
@@ -1639,19 +1639,19 @@
         <v>99</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G5">
-        <v>5.4</v>
+        <v>600</v>
       </c>
       <c r="H5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I5">
         <v>3.45</v>
       </c>
       <c r="J5">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1687,10 +1687,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X5">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -319,7 +319,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 03:53:43</t>
+    <t>2026-10-04 06:06:38</t>
   </si>
 </sst>
 </file>
@@ -922,10 +922,10 @@
         <v>4.1</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
         <v>3.9</v>
@@ -937,22 +937,22 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q2">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
         <v>1.72</v>
@@ -979,7 +979,7 @@
         <v>120</v>
       </c>
       <c r="AB2">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1027,10 +1027,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1042,7 +1042,7 @@
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1054,7 +1054,7 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB2">
         <v>19.5</v>
@@ -1063,16 +1063,16 @@
         <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1436,7 +1436,7 @@
         <v>1.17</v>
       </c>
       <c r="S4">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="T4">
         <v>2.08</v>
@@ -1592,7 +1592,7 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BT4">
         <v>8</v>
@@ -1610,13 +1610,13 @@
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CB4" t="s">
         <v>101</v>
@@ -1639,19 +1639,19 @@
         <v>99</v>
       </c>
       <c r="F5">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="G5">
         <v>600</v>
       </c>
       <c r="H5">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="I5">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>2.64</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1687,10 +1687,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="X5">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -319,7 +319,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 06:06:38</t>
+    <t>2026-10-04 08:18:31</t>
   </si>
 </sst>
 </file>
@@ -913,7 +913,7 @@
         <v>96</v>
       </c>
       <c r="F2">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G2">
         <v>2.04</v>
@@ -922,7 +922,7 @@
         <v>4.1</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.65</v>
@@ -934,34 +934,34 @@
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
         <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S2">
         <v>3.3</v>
       </c>
       <c r="T2">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
         <v>1.96</v>
@@ -1030,7 +1030,7 @@
         <v>4.6</v>
       </c>
       <c r="AS2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1066,7 +1066,7 @@
         <v>4.7</v>
       </c>
       <c r="BE2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF2">
         <v>12</v>
@@ -1155,13 +1155,13 @@
         <v>97</v>
       </c>
       <c r="F3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G3">
         <v>5.2</v>
       </c>
       <c r="H3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="I3">
         <v>2.16</v>
@@ -1170,7 +1170,7 @@
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
         <v>1.44</v>
@@ -1197,10 +1197,10 @@
         <v>3.8</v>
       </c>
       <c r="T3">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
         <v>1.87</v>
@@ -1209,7 +1209,7 @@
         <v>1.23</v>
       </c>
       <c r="X3">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="Y3">
         <v>13</v>
@@ -1272,7 +1272,7 @@
         <v>7.6</v>
       </c>
       <c r="AS3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AT3">
         <v>9</v>
@@ -1284,34 +1284,34 @@
         <v>7.6</v>
       </c>
       <c r="AW3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AX3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AY3">
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BA3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BB3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BC3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BD3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BE3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BF3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BG3">
         <v>9.4</v>
@@ -1338,7 +1338,7 @@
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.99</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1439,16 +1439,16 @@
         <v>4.8</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V4">
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1514,7 +1514,7 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT4">
         <v>6.4</v>
@@ -1526,7 +1526,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX4">
         <v>13</v>
@@ -1538,25 +1538,25 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1645,10 +1645,10 @@
         <v>600</v>
       </c>
       <c r="H5">
-        <v>1.12</v>
+        <v>1.51</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J5">
         <v>1.12</v>
@@ -1687,10 +1687,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X5">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
   <si>
     <t>League</t>
   </si>
@@ -256,6 +256,12 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
@@ -283,12 +289,24 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
     <t>20:00:00</t>
   </si>
   <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Bermuda</t>
+  </si>
+  <si>
+    <t>Grenada</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
@@ -298,12 +316,24 @@
     <t>Orsomarso</t>
   </si>
   <si>
+    <t>Honduras</t>
+  </si>
+  <si>
     <t>NK Bilje</t>
   </si>
   <si>
     <t>Club Sportivo Ameliano</t>
   </si>
   <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>Bonaire</t>
+  </si>
+  <si>
     <t>Santa Fe</t>
   </si>
   <si>
@@ -313,13 +343,16 @@
     <t>Quindio</t>
   </si>
   <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
     <t>NK Jadran Dekani</t>
   </si>
   <si>
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 08:18:31</t>
+    <t>2026-10-04 10:31:07</t>
   </si>
 </sst>
 </file>
@@ -651,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -901,184 +934,184 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
-        <v>2.04</v>
+        <v>2.98</v>
       </c>
       <c r="H2">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>1.02</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="X2">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
+        <v>16</v>
+      </c>
+      <c r="Z2">
+        <v>26</v>
+      </c>
+      <c r="AA2">
+        <v>70</v>
+      </c>
+      <c r="AB2">
+        <v>13.5</v>
+      </c>
+      <c r="AC2">
+        <v>9.4</v>
+      </c>
+      <c r="AD2">
+        <v>16.5</v>
+      </c>
+      <c r="AE2">
+        <v>55</v>
+      </c>
+      <c r="AF2">
         <v>19</v>
       </c>
-      <c r="Z2">
-        <v>40</v>
-      </c>
-      <c r="AA2">
-        <v>120</v>
-      </c>
-      <c r="AB2">
-        <v>9.6</v>
-      </c>
-      <c r="AC2">
-        <v>10.5</v>
-      </c>
-      <c r="AD2">
+      <c r="AG2">
+        <v>14</v>
+      </c>
+      <c r="AH2">
         <v>21</v>
-      </c>
-      <c r="AE2">
-        <v>70</v>
-      </c>
-      <c r="AF2">
-        <v>15</v>
-      </c>
-      <c r="AG2">
-        <v>13</v>
-      </c>
-      <c r="AH2">
-        <v>23</v>
       </c>
       <c r="AI2">
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AK2">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AP2">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>3</v>
       </c>
       <c r="AR2">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS2">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>4.9</v>
+        <v>34</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD2">
-        <v>4.7</v>
+        <v>28</v>
       </c>
       <c r="BE2">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
@@ -1135,7 +1168,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1143,91 +1176,91 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F3">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="G3">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>1.86</v>
+        <v>1.1</v>
       </c>
       <c r="I3">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L3">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>1.12</v>
       </c>
       <c r="O3">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="P3">
-        <v>1.76</v>
+        <v>1.12</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S3">
-        <v>3.8</v>
+        <v>1.12</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
         <v>1000</v>
@@ -1260,545 +1293,545 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="AT3">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU3">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV3">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="AX3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="BA3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="BC3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="BD3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="BE3">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
         <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F4">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="G4">
-        <v>3.35</v>
+        <v>1.57</v>
       </c>
       <c r="H4">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="O4">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="Q4">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>2.74</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F5">
-        <v>1.56</v>
+        <v>1.94</v>
       </c>
       <c r="G5">
-        <v>600</v>
+        <v>2.02</v>
       </c>
       <c r="H5">
-        <v>1.51</v>
+        <v>4.2</v>
       </c>
       <c r="I5">
-        <v>2.98</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>1.24</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q5">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.28</v>
+        <v>1.98</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1861,249 +1894,1217 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6">
+        <v>4.3</v>
+      </c>
+      <c r="G6">
+        <v>5.2</v>
+      </c>
+      <c r="H6">
+        <v>1.86</v>
+      </c>
+      <c r="I6">
+        <v>2.16</v>
+      </c>
+      <c r="J6">
+        <v>3.3</v>
+      </c>
+      <c r="K6">
+        <v>3.7</v>
+      </c>
+      <c r="L6">
+        <v>1.44</v>
+      </c>
+      <c r="M6">
+        <v>1.09</v>
+      </c>
+      <c r="N6">
+        <v>2.9</v>
+      </c>
+      <c r="O6">
+        <v>1.4</v>
+      </c>
+      <c r="P6">
+        <v>1.75</v>
+      </c>
+      <c r="Q6">
+        <v>2.24</v>
+      </c>
+      <c r="R6">
+        <v>1.23</v>
+      </c>
+      <c r="S6">
+        <v>3.8</v>
+      </c>
+      <c r="T6">
+        <v>1.98</v>
+      </c>
+      <c r="U6">
+        <v>1.76</v>
+      </c>
+      <c r="V6">
+        <v>1.87</v>
+      </c>
+      <c r="W6">
+        <v>1.23</v>
+      </c>
+      <c r="X6">
+        <v>12.5</v>
+      </c>
+      <c r="Y6">
+        <v>12.5</v>
+      </c>
+      <c r="Z6">
+        <v>20</v>
+      </c>
+      <c r="AA6">
+        <v>940</v>
+      </c>
+      <c r="AB6">
+        <v>34</v>
+      </c>
+      <c r="AC6">
+        <v>12.5</v>
+      </c>
+      <c r="AD6">
+        <v>21</v>
+      </c>
+      <c r="AE6">
+        <v>940</v>
+      </c>
+      <c r="AF6">
+        <v>930</v>
+      </c>
+      <c r="AG6">
+        <v>930</v>
+      </c>
+      <c r="AH6">
+        <v>930</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>95</v>
+      </c>
+      <c r="AP6">
+        <v>8.4</v>
+      </c>
+      <c r="AQ6">
+        <v>6.4</v>
+      </c>
+      <c r="AR6">
+        <v>8.4</v>
+      </c>
+      <c r="AS6">
+        <v>6.2</v>
+      </c>
+      <c r="AT6">
+        <v>10.5</v>
+      </c>
+      <c r="AU6">
+        <v>6.6</v>
+      </c>
+      <c r="AV6">
+        <v>8.4</v>
+      </c>
+      <c r="AW6">
+        <v>6.6</v>
+      </c>
+      <c r="AX6">
+        <v>6.8</v>
+      </c>
+      <c r="AY6">
+        <v>11</v>
+      </c>
+      <c r="AZ6">
+        <v>5.8</v>
+      </c>
+      <c r="BA6">
+        <v>18.5</v>
+      </c>
+      <c r="BB6">
+        <v>1.82</v>
+      </c>
+      <c r="BC6">
+        <v>20</v>
+      </c>
+      <c r="BD6">
+        <v>1.82</v>
+      </c>
+      <c r="BE6">
+        <v>1.82</v>
+      </c>
+      <c r="BF6">
+        <v>1.82</v>
+      </c>
+      <c r="BG6">
+        <v>9.4</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.39</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>2.4</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.35</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>4.9</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.35</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.35</v>
+      </c>
+      <c r="BT6">
+        <v>6</v>
+      </c>
+      <c r="BU6">
+        <v>3.3</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>2.4</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.35</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.35</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
         <v>84</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7">
+        <v>2.82</v>
+      </c>
+      <c r="G7">
+        <v>3.35</v>
+      </c>
+      <c r="H7">
+        <v>2.78</v>
+      </c>
+      <c r="I7">
+        <v>3.2</v>
+      </c>
+      <c r="J7">
+        <v>2.82</v>
+      </c>
+      <c r="K7">
+        <v>3.25</v>
+      </c>
+      <c r="L7">
+        <v>1.4</v>
+      </c>
+      <c r="M7">
+        <v>1.11</v>
+      </c>
+      <c r="N7">
+        <v>2.48</v>
+      </c>
+      <c r="O7">
+        <v>1.54</v>
+      </c>
+      <c r="P7">
+        <v>1.49</v>
+      </c>
+      <c r="Q7">
+        <v>2.62</v>
+      </c>
+      <c r="R7">
+        <v>1.17</v>
+      </c>
+      <c r="S7">
+        <v>4.8</v>
+      </c>
+      <c r="T7">
+        <v>2.08</v>
+      </c>
+      <c r="U7">
+        <v>1.76</v>
+      </c>
+      <c r="V7">
+        <v>1.46</v>
+      </c>
+      <c r="W7">
+        <v>1.43</v>
+      </c>
+      <c r="X7">
+        <v>10</v>
+      </c>
+      <c r="Y7">
+        <v>10.5</v>
+      </c>
+      <c r="Z7">
+        <v>22</v>
+      </c>
+      <c r="AA7">
+        <v>70</v>
+      </c>
+      <c r="AB7">
+        <v>10.5</v>
+      </c>
+      <c r="AC7">
+        <v>8.4</v>
+      </c>
+      <c r="AD7">
+        <v>17</v>
+      </c>
+      <c r="AE7">
+        <v>55</v>
+      </c>
+      <c r="AF7">
+        <v>23</v>
+      </c>
+      <c r="AG7">
+        <v>17.5</v>
+      </c>
+      <c r="AH7">
+        <v>28</v>
+      </c>
+      <c r="AI7">
+        <v>90</v>
+      </c>
+      <c r="AJ7">
+        <v>70</v>
+      </c>
+      <c r="AK7">
+        <v>60</v>
+      </c>
+      <c r="AL7">
+        <v>90</v>
+      </c>
+      <c r="AM7">
+        <v>230</v>
+      </c>
+      <c r="AN7">
+        <v>75</v>
+      </c>
+      <c r="AO7">
+        <v>70</v>
+      </c>
+      <c r="AP7">
+        <v>6.2</v>
+      </c>
+      <c r="AQ7">
+        <v>6.2</v>
+      </c>
+      <c r="AR7">
+        <v>13</v>
+      </c>
+      <c r="AS7">
+        <v>4</v>
+      </c>
+      <c r="AT7">
+        <v>6.4</v>
+      </c>
+      <c r="AU7">
+        <v>5.3</v>
+      </c>
+      <c r="AV7">
+        <v>10</v>
+      </c>
+      <c r="AW7">
+        <v>3.95</v>
+      </c>
+      <c r="AX7">
+        <v>13.5</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>16.5</v>
+      </c>
+      <c r="BA7">
+        <v>4.1</v>
+      </c>
+      <c r="BB7">
+        <v>4</v>
+      </c>
+      <c r="BC7">
+        <v>4</v>
+      </c>
+      <c r="BD7">
+        <v>4.1</v>
+      </c>
+      <c r="BE7">
+        <v>4.2</v>
+      </c>
+      <c r="BF7">
+        <v>4</v>
+      </c>
+      <c r="BG7">
+        <v>4</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.67</v>
+      </c>
+      <c r="BJ7">
+        <v>16</v>
+      </c>
+      <c r="BK7">
+        <v>1.51</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.67</v>
+      </c>
+      <c r="BN7">
+        <v>8</v>
+      </c>
+      <c r="BO7">
+        <v>3.9</v>
+      </c>
+      <c r="BP7">
+        <v>40</v>
+      </c>
+      <c r="BQ7">
+        <v>1.61</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.65</v>
+      </c>
+      <c r="BT7">
+        <v>8</v>
+      </c>
+      <c r="BU7">
+        <v>3.9</v>
+      </c>
+      <c r="BV7">
+        <v>40</v>
+      </c>
+      <c r="BW7">
+        <v>1.61</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.65</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.65</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8">
+        <v>1.96</v>
+      </c>
+      <c r="G8">
+        <v>2.24</v>
+      </c>
+      <c r="H8">
+        <v>3.45</v>
+      </c>
+      <c r="I8">
+        <v>6.2</v>
+      </c>
+      <c r="J8">
+        <v>2.58</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+      <c r="L8">
+        <v>1.46</v>
+      </c>
+      <c r="M8">
+        <v>1.06</v>
+      </c>
+      <c r="N8">
+        <v>2.52</v>
+      </c>
+      <c r="O8">
+        <v>1.4</v>
+      </c>
+      <c r="P8">
+        <v>1.5</v>
+      </c>
+      <c r="Q8">
+        <v>2.06</v>
+      </c>
+      <c r="R8">
+        <v>1.2</v>
+      </c>
+      <c r="S8">
+        <v>3.55</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.19</v>
+      </c>
+      <c r="W8">
+        <v>1.8</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>2.5</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
         <v>85</v>
       </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>1.6</v>
+      </c>
+      <c r="G9">
+        <v>600</v>
+      </c>
+      <c r="H9">
+        <v>1.51</v>
+      </c>
+      <c r="I9">
+        <v>2.98</v>
+      </c>
+      <c r="J9">
+        <v>1.12</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.25</v>
+      </c>
+      <c r="O9">
+        <v>1.02</v>
+      </c>
+      <c r="P9">
+        <v>1.25</v>
+      </c>
+      <c r="Q9">
+        <v>1.03</v>
+      </c>
+      <c r="R9">
+        <v>1.18</v>
+      </c>
+      <c r="S9">
+        <v>1.04</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.52</v>
+      </c>
+      <c r="W9">
+        <v>1.28</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9">
+        <v>1.03</v>
+      </c>
+      <c r="AR9">
+        <v>1.03</v>
+      </c>
+      <c r="AS9">
+        <v>1.03</v>
+      </c>
+      <c r="AT9">
+        <v>1.03</v>
+      </c>
+      <c r="AU9">
+        <v>1.03</v>
+      </c>
+      <c r="AV9">
+        <v>1.03</v>
+      </c>
+      <c r="AW9">
+        <v>1.03</v>
+      </c>
+      <c r="AX9">
+        <v>1.03</v>
+      </c>
+      <c r="AY9">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9">
+        <v>1.03</v>
+      </c>
+      <c r="BA9">
+        <v>1.03</v>
+      </c>
+      <c r="BB9">
+        <v>1.03</v>
+      </c>
+      <c r="BC9">
+        <v>1.03</v>
+      </c>
+      <c r="BD9">
+        <v>1.03</v>
+      </c>
+      <c r="BE9">
+        <v>1.03</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>1.07</v>
       </c>
-      <c r="Q6">
-        <v>1.01</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>0</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6">
-        <v>0</v>
-      </c>
-      <c r="BE6">
-        <v>0</v>
-      </c>
-      <c r="BF6">
-        <v>0</v>
-      </c>
-      <c r="BG6">
-        <v>0</v>
-      </c>
-      <c r="BH6">
-        <v>0</v>
-      </c>
-      <c r="BI6">
-        <v>0</v>
-      </c>
-      <c r="BJ6">
-        <v>0</v>
-      </c>
-      <c r="BK6">
-        <v>0</v>
-      </c>
-      <c r="BL6">
-        <v>0</v>
-      </c>
-      <c r="BM6">
-        <v>0</v>
-      </c>
-      <c r="BN6">
-        <v>0</v>
-      </c>
-      <c r="BO6">
-        <v>0</v>
-      </c>
-      <c r="BP6">
-        <v>0</v>
-      </c>
-      <c r="BQ6">
-        <v>0</v>
-      </c>
-      <c r="BR6">
-        <v>0</v>
-      </c>
-      <c r="BS6">
-        <v>0</v>
-      </c>
-      <c r="BT6">
-        <v>0</v>
-      </c>
-      <c r="BU6">
-        <v>0</v>
-      </c>
-      <c r="BV6">
-        <v>0</v>
-      </c>
-      <c r="BW6">
-        <v>0</v>
-      </c>
-      <c r="BX6">
-        <v>0</v>
-      </c>
-      <c r="BY6">
-        <v>0</v>
-      </c>
-      <c r="BZ6">
-        <v>0</v>
-      </c>
-      <c r="CA6">
-        <v>0</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>101</v>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -352,7 +352,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 10:31:07</t>
+    <t>2026-10-04 12:43:03</t>
   </si>
 </sst>
 </file>
@@ -946,91 +946,91 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="H2">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="I2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.31</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q2">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA2">
         <v>70</v>
       </c>
       <c r="AB2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF2">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
         <v>75</v>
@@ -1039,73 +1039,73 @@
         <v>44</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AO2">
         <v>60</v>
       </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS2">
         <v>40</v>
       </c>
       <c r="AT2">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>3.45</v>
+        <v>27</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="BB2">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="BC2">
         <v>19</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="BE2">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
         <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1212,19 +1212,19 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O3">
         <v>1.11</v>
       </c>
       <c r="P3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q3">
         <v>1.11</v>
       </c>
       <c r="R3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S3">
         <v>1.12</v>
@@ -1320,7 +1320,7 @@
         <v>1.03</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AY3">
         <v>1.03</v>
@@ -1332,7 +1332,7 @@
         <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC3">
         <v>1.03</v>
@@ -1430,172 +1430,172 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="G4">
         <v>1.57</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L4">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q4">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S4">
+        <v>2.58</v>
+      </c>
+      <c r="T4">
+        <v>1.87</v>
+      </c>
+      <c r="U4">
+        <v>1.85</v>
+      </c>
+      <c r="V4">
+        <v>1.1</v>
+      </c>
+      <c r="W4">
+        <v>2.76</v>
+      </c>
+      <c r="X4">
+        <v>640</v>
+      </c>
+      <c r="Y4">
+        <v>790</v>
+      </c>
+      <c r="Z4">
+        <v>400</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>11.5</v>
+      </c>
+      <c r="AC4">
+        <v>14.5</v>
+      </c>
+      <c r="AD4">
+        <v>42</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>11.5</v>
+      </c>
+      <c r="AG4">
+        <v>13.5</v>
+      </c>
+      <c r="AH4">
+        <v>34</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>16.5</v>
+      </c>
+      <c r="AK4">
+        <v>20</v>
+      </c>
+      <c r="AL4">
+        <v>46</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>14</v>
+      </c>
+      <c r="AQ4">
+        <v>18.5</v>
+      </c>
+      <c r="AR4">
         <v>2.3</v>
       </c>
-      <c r="T4">
-        <v>1.01</v>
-      </c>
-      <c r="U4">
-        <v>1.01</v>
-      </c>
-      <c r="V4">
-        <v>1.01</v>
-      </c>
-      <c r="W4">
-        <v>2.74</v>
-      </c>
-      <c r="X4">
-        <v>1000</v>
-      </c>
-      <c r="Y4">
-        <v>1000</v>
-      </c>
-      <c r="Z4">
-        <v>1000</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>1000</v>
-      </c>
-      <c r="AC4">
-        <v>1000</v>
-      </c>
-      <c r="AD4">
-        <v>1000</v>
-      </c>
-      <c r="AE4">
-        <v>1000</v>
-      </c>
-      <c r="AF4">
-        <v>1000</v>
-      </c>
-      <c r="AG4">
-        <v>1000</v>
-      </c>
-      <c r="AH4">
-        <v>1000</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>1000</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>1.03</v>
-      </c>
-      <c r="AQ4">
-        <v>1.03</v>
-      </c>
-      <c r="AR4">
-        <v>1.03</v>
-      </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
@@ -1613,7 +1613,7 @@
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1693,19 +1693,19 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O5">
         <v>1.32</v>
       </c>
       <c r="P5">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q5">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="R5">
         <v>1.35</v>
@@ -1786,10 +1786,10 @@
         <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -1813,7 +1813,7 @@
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB5">
         <v>19.5</v>
@@ -1825,13 +1825,13 @@
         <v>5.1</v>
       </c>
       <c r="BE5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1917,19 +1917,19 @@
         <v>4.3</v>
       </c>
       <c r="G6">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H6">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="I6">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
         <v>1.44</v>
@@ -1938,10 +1938,10 @@
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P6">
         <v>1.75</v>
@@ -1950,130 +1950,130 @@
         <v>2.24</v>
       </c>
       <c r="R6">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T6">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="W6">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="Z6">
+        <v>11</v>
+      </c>
+      <c r="AA6">
+        <v>25</v>
+      </c>
+      <c r="AB6">
+        <v>14</v>
+      </c>
+      <c r="AC6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6">
+        <v>11.5</v>
+      </c>
+      <c r="AE6">
+        <v>28</v>
+      </c>
+      <c r="AF6">
+        <v>34</v>
+      </c>
+      <c r="AG6">
         <v>20</v>
       </c>
-      <c r="AA6">
-        <v>940</v>
-      </c>
-      <c r="AB6">
+      <c r="AH6">
+        <v>28</v>
+      </c>
+      <c r="AI6">
+        <v>180</v>
+      </c>
+      <c r="AJ6">
+        <v>980</v>
+      </c>
+      <c r="AK6">
+        <v>970</v>
+      </c>
+      <c r="AL6">
+        <v>970</v>
+      </c>
+      <c r="AM6">
+        <v>980</v>
+      </c>
+      <c r="AN6">
+        <v>970</v>
+      </c>
+      <c r="AO6">
+        <v>18.5</v>
+      </c>
+      <c r="AP6">
+        <v>10</v>
+      </c>
+      <c r="AQ6">
+        <v>7</v>
+      </c>
+      <c r="AR6">
+        <v>9</v>
+      </c>
+      <c r="AS6">
+        <v>16</v>
+      </c>
+      <c r="AT6">
+        <v>11</v>
+      </c>
+      <c r="AU6">
+        <v>7.2</v>
+      </c>
+      <c r="AV6">
+        <v>9.4</v>
+      </c>
+      <c r="AW6">
+        <v>16.5</v>
+      </c>
+      <c r="AX6">
+        <v>23</v>
+      </c>
+      <c r="AY6">
+        <v>16</v>
+      </c>
+      <c r="AZ6">
+        <v>16.5</v>
+      </c>
+      <c r="BA6">
+        <v>36</v>
+      </c>
+      <c r="BB6">
+        <v>38</v>
+      </c>
+      <c r="BC6">
+        <v>44</v>
+      </c>
+      <c r="BD6">
+        <v>48</v>
+      </c>
+      <c r="BE6">
+        <v>44</v>
+      </c>
+      <c r="BF6">
         <v>34</v>
       </c>
-      <c r="AC6">
-        <v>12.5</v>
-      </c>
-      <c r="AD6">
-        <v>21</v>
-      </c>
-      <c r="AE6">
-        <v>940</v>
-      </c>
-      <c r="AF6">
-        <v>930</v>
-      </c>
-      <c r="AG6">
-        <v>930</v>
-      </c>
-      <c r="AH6">
-        <v>930</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>95</v>
-      </c>
-      <c r="AP6">
-        <v>8.4</v>
-      </c>
-      <c r="AQ6">
-        <v>6.4</v>
-      </c>
-      <c r="AR6">
-        <v>8.4</v>
-      </c>
-      <c r="AS6">
-        <v>6.2</v>
-      </c>
-      <c r="AT6">
-        <v>10.5</v>
-      </c>
-      <c r="AU6">
-        <v>6.6</v>
-      </c>
-      <c r="AV6">
-        <v>8.4</v>
-      </c>
-      <c r="AW6">
-        <v>6.6</v>
-      </c>
-      <c r="AX6">
-        <v>6.8</v>
-      </c>
-      <c r="AY6">
-        <v>11</v>
-      </c>
-      <c r="AZ6">
-        <v>5.8</v>
-      </c>
-      <c r="BA6">
-        <v>18.5</v>
-      </c>
-      <c r="BB6">
-        <v>1.82</v>
-      </c>
-      <c r="BC6">
-        <v>20</v>
-      </c>
-      <c r="BD6">
-        <v>1.82</v>
-      </c>
-      <c r="BE6">
-        <v>1.82</v>
-      </c>
-      <c r="BF6">
-        <v>1.82</v>
-      </c>
       <c r="BG6">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2159,7 +2159,7 @@
         <v>2.82</v>
       </c>
       <c r="G7">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H7">
         <v>2.78</v>
@@ -2198,16 +2198,16 @@
         <v>4.8</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
         <v>1.46</v>
       </c>
       <c r="W7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -2401,22 +2401,22 @@
         <v>1.96</v>
       </c>
       <c r="G8">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H8">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.06</v>
@@ -2440,124 +2440,124 @@
         <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2640,7 +2640,7 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G9">
         <v>600</v>
@@ -2649,10 +2649,10 @@
         <v>1.51</v>
       </c>
       <c r="I9">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2688,7 +2688,7 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W9">
         <v>1.28</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -352,7 +352,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 12:43:03</t>
+    <t>2026-10-04 14:53:23</t>
   </si>
 </sst>
 </file>
@@ -946,19 +946,19 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H2">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I2">
         <v>3.35</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.65</v>
@@ -970,22 +970,22 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
         <v>1.83</v>
       </c>
       <c r="Q2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R2">
         <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T2">
         <v>1.68</v>
@@ -994,13 +994,13 @@
         <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
@@ -1024,7 +1024,7 @@
         <v>50</v>
       </c>
       <c r="AF2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1036,7 +1036,7 @@
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK2">
         <v>36</v>
@@ -1054,19 +1054,19 @@
         <v>60</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1075,10 +1075,10 @@
         <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY2">
         <v>10</v>
@@ -1087,22 +1087,22 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BD2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG2">
         <v>18.5</v>
@@ -1227,19 +1227,19 @@
         <v>1.09</v>
       </c>
       <c r="S3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1320,7 +1320,7 @@
         <v>1.03</v>
       </c>
       <c r="AX3">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AY3">
         <v>1.03</v>
@@ -1332,7 +1332,7 @@
         <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BC3">
         <v>1.03</v>
@@ -1430,172 +1430,172 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="G4">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
+        <v>4.6</v>
+      </c>
+      <c r="O4">
+        <v>1.21</v>
+      </c>
+      <c r="P4">
+        <v>2.34</v>
+      </c>
+      <c r="Q4">
+        <v>1.58</v>
+      </c>
+      <c r="R4">
+        <v>1.52</v>
+      </c>
+      <c r="S4">
+        <v>2.36</v>
+      </c>
+      <c r="T4">
+        <v>1.76</v>
+      </c>
+      <c r="U4">
+        <v>1.95</v>
+      </c>
+      <c r="V4">
+        <v>1.11</v>
+      </c>
+      <c r="W4">
         <v>3.05</v>
       </c>
-      <c r="O4">
-        <v>1.22</v>
-      </c>
-      <c r="P4">
-        <v>1.96</v>
-      </c>
-      <c r="Q4">
-        <v>1.66</v>
-      </c>
-      <c r="R4">
-        <v>1.45</v>
-      </c>
-      <c r="S4">
-        <v>2.58</v>
-      </c>
-      <c r="T4">
-        <v>1.87</v>
-      </c>
-      <c r="U4">
-        <v>1.85</v>
-      </c>
-      <c r="V4">
-        <v>1.1</v>
-      </c>
-      <c r="W4">
-        <v>2.76</v>
-      </c>
       <c r="X4">
-        <v>640</v>
+        <v>28</v>
       </c>
       <c r="Y4">
-        <v>790</v>
+        <v>36</v>
       </c>
       <c r="Z4">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD4">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
+        <v>15</v>
+      </c>
+      <c r="AK4">
+        <v>17</v>
+      </c>
+      <c r="AL4">
+        <v>38</v>
+      </c>
+      <c r="AM4">
+        <v>140</v>
+      </c>
+      <c r="AN4">
+        <v>6</v>
+      </c>
+      <c r="AO4">
+        <v>170</v>
+      </c>
+      <c r="AP4">
         <v>16.5</v>
       </c>
-      <c r="AK4">
-        <v>20</v>
-      </c>
-      <c r="AL4">
-        <v>46</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>14</v>
-      </c>
       <c r="AQ4">
-        <v>18.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR4">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS4">
-        <v>2.34</v>
+        <v>5.9</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU4">
+        <v>9.6</v>
+      </c>
+      <c r="AV4">
+        <v>5.1</v>
+      </c>
+      <c r="AW4">
+        <v>5.7</v>
+      </c>
+      <c r="AX4">
+        <v>8</v>
+      </c>
+      <c r="AY4">
         <v>8.4</v>
       </c>
-      <c r="AV4">
-        <v>2.22</v>
-      </c>
-      <c r="AW4">
-        <v>2.34</v>
-      </c>
-      <c r="AX4">
-        <v>1.95</v>
-      </c>
-      <c r="AY4">
-        <v>2</v>
-      </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>2.34</v>
+        <v>5.7</v>
       </c>
       <c r="BB4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC4">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="BD4">
-        <v>2.22</v>
+        <v>5.2</v>
       </c>
       <c r="BE4">
-        <v>2.34</v>
+        <v>5.7</v>
       </c>
       <c r="BF4">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="BG4">
-        <v>2.34</v>
+        <v>5.8</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
@@ -1613,7 +1613,7 @@
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1681,7 +1681,7 @@
         <v>4.2</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1705,7 +1705,7 @@
         <v>1.95</v>
       </c>
       <c r="Q5">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R5">
         <v>1.35</v>
@@ -1920,13 +1920,13 @@
         <v>4.8</v>
       </c>
       <c r="H6">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="I6">
         <v>2.06</v>
       </c>
       <c r="J6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
         <v>3.75</v>
@@ -1956,13 +1956,13 @@
         <v>3.85</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U6">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V6">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="W6">
         <v>1.27</v>
@@ -1977,19 +1977,19 @@
         <v>11</v>
       </c>
       <c r="AA6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB6">
         <v>14</v>
       </c>
       <c r="AC6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
         <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF6">
         <v>34</v>
@@ -2001,22 +2001,22 @@
         <v>28</v>
       </c>
       <c r="AI6">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AJ6">
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="AK6">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="AL6">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="AM6">
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="AN6">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="AO6">
         <v>18.5</v>
@@ -2049,7 +2049,7 @@
         <v>23</v>
       </c>
       <c r="AY6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ6">
         <v>16.5</v>
@@ -2073,7 +2073,7 @@
         <v>34</v>
       </c>
       <c r="BG6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2404,13 +2404,13 @@
         <v>2.16</v>
       </c>
       <c r="H8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
         <v>3.65</v>
@@ -2422,7 +2422,7 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O8">
         <v>1.4</v>
@@ -2431,7 +2431,7 @@
         <v>1.5</v>
       </c>
       <c r="Q8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
         <v>1.2</v>
@@ -2443,7 +2443,7 @@
         <v>1.72</v>
       </c>
       <c r="U8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V8">
         <v>1.25</v>
@@ -2458,7 +2458,7 @@
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AA8">
         <v>130</v>
@@ -2485,10 +2485,10 @@
         <v>23</v>
       </c>
       <c r="AI8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ8">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="AK8">
         <v>27</v>
@@ -2506,55 +2506,55 @@
         <v>120</v>
       </c>
       <c r="AP8">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AR8">
         <v>6.8</v>
       </c>
       <c r="AS8">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AU8">
         <v>4.1</v>
       </c>
       <c r="AV8">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AW8">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="AX8">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AY8">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BB8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC8">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BD8">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BE8">
         <v>8.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BG8">
         <v>8</v>
@@ -2640,10 +2640,10 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H9">
         <v>1.51</v>
@@ -2679,13 +2679,13 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.54</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -352,7 +352,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 14:53:23</t>
+    <t>2026-10-04 17:04:42</t>
   </si>
 </sst>
 </file>
@@ -952,13 +952,13 @@
         <v>2.64</v>
       </c>
       <c r="H2">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I2">
         <v>3.35</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
         <v>3.65</v>
@@ -970,7 +970,7 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
         <v>1.33</v>
@@ -994,10 +994,10 @@
         <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X2">
         <v>14</v>
@@ -1039,13 +1039,13 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AN2">
         <v>25</v>
@@ -1066,7 +1066,7 @@
         <v>8.6</v>
       </c>
       <c r="AT2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1090,7 +1090,7 @@
         <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BC2">
         <v>23</v>
@@ -1111,61 +1111,61 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1191,13 +1191,13 @@
         <v>1.1</v>
       </c>
       <c r="G3">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H3">
         <v>1.1</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J3">
         <v>1.1</v>
@@ -1236,10 +1236,10 @@
         <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1296,52 +1296,52 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -1353,61 +1353,61 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>112</v>
@@ -1463,10 +1463,10 @@
         <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S4">
         <v>2.36</v>
@@ -1595,61 +1595,61 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1681,10 +1681,10 @@
         <v>4.2</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
         <v>3.85</v>
@@ -1702,13 +1702,13 @@
         <v>1.32</v>
       </c>
       <c r="P5">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q5">
         <v>1.96</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S5">
         <v>3.3</v>
@@ -1786,7 +1786,7 @@
         <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS5">
         <v>5.5</v>
@@ -1813,7 +1813,7 @@
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB5">
         <v>19.5</v>
@@ -1831,67 +1831,67 @@
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>112</v>
@@ -1914,7 +1914,7 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G6">
         <v>4.8</v>
@@ -1956,7 +1956,7 @@
         <v>3.85</v>
       </c>
       <c r="T6">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
         <v>1.89</v>
@@ -2001,22 +2001,22 @@
         <v>28</v>
       </c>
       <c r="AI6">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AK6">
-        <v>930</v>
+        <v>890</v>
       </c>
       <c r="AL6">
-        <v>930</v>
+        <v>890</v>
       </c>
       <c r="AM6">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AN6">
-        <v>930</v>
+        <v>890</v>
       </c>
       <c r="AO6">
         <v>18.5</v>
@@ -2049,7 +2049,7 @@
         <v>23</v>
       </c>
       <c r="AY6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6">
         <v>16.5</v>
@@ -2058,7 +2058,7 @@
         <v>36</v>
       </c>
       <c r="BB6">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BC6">
         <v>44</v>
@@ -2198,10 +2198,10 @@
         <v>4.8</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V7">
         <v>1.46</v>
@@ -2401,10 +2401,10 @@
         <v>1.96</v>
       </c>
       <c r="G8">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I8">
         <v>4.9</v>
@@ -2416,7 +2416,7 @@
         <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M8">
         <v>1.06</v>
@@ -2449,7 +2449,7 @@
         <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X8">
         <v>11</v>
@@ -2563,61 +2563,61 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2649,7 +2649,7 @@
         <v>1.51</v>
       </c>
       <c r="I9">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J9">
         <v>1.1</v>
@@ -2688,7 +2688,7 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
         <v>1.28</v>
@@ -2748,52 +2748,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2805,61 +2805,61 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>112</v>
@@ -2900,208 +2900,208 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -352,7 +352,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 17:04:42</t>
+    <t>2026-10-04 19:16:20</t>
   </si>
 </sst>
 </file>
@@ -946,16 +946,16 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H2">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I2">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J2">
         <v>3.35</v>
@@ -970,16 +970,16 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O2">
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R2">
         <v>1.32</v>
@@ -994,22 +994,22 @@
         <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
       </c>
       <c r="Z2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB2">
         <v>11</v>
@@ -1024,7 +1024,7 @@
         <v>50</v>
       </c>
       <c r="AF2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1033,16 +1033,16 @@
         <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM2">
         <v>110</v>
@@ -1051,7 +1051,7 @@
         <v>25</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
@@ -1066,7 +1066,7 @@
         <v>8.6</v>
       </c>
       <c r="AT2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1090,10 +1090,10 @@
         <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1102,7 +1102,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG2">
         <v>18.5</v>
@@ -1188,22 +1188,22 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="G3">
-        <v>990</v>
+        <v>3.7</v>
       </c>
       <c r="H3">
-        <v>1.1</v>
+        <v>1.89</v>
       </c>
       <c r="I3">
-        <v>990</v>
+        <v>2.12</v>
       </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1212,22 +1212,22 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.13</v>
+        <v>2.72</v>
       </c>
       <c r="O3">
         <v>1.11</v>
       </c>
       <c r="P3">
-        <v>1.13</v>
+        <v>2.72</v>
       </c>
       <c r="Q3">
         <v>1.11</v>
       </c>
       <c r="R3">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="S3">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="T3">
         <v>1.11</v>
@@ -1236,10 +1236,10 @@
         <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1541,7 +1541,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR4">
         <v>5.7</v>
@@ -1556,7 +1556,7 @@
         <v>9.6</v>
       </c>
       <c r="AV4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW4">
         <v>5.7</v>
@@ -1580,7 +1580,7 @@
         <v>12</v>
       </c>
       <c r="BD4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE4">
         <v>5.7</v>
@@ -1684,7 +1684,7 @@
         <v>4.6</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
         <v>3.85</v>
@@ -1702,10 +1702,10 @@
         <v>1.32</v>
       </c>
       <c r="P5">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q5">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R5">
         <v>1.37</v>
@@ -1741,7 +1741,7 @@
         <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>21</v>
@@ -1810,16 +1810,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
         <v>5.3</v>
       </c>
       <c r="BB5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC5">
-        <v>17.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD5">
         <v>5.1</v>
@@ -1914,22 +1914,22 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G6">
         <v>4.8</v>
       </c>
       <c r="H6">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
         <v>1.44</v>
@@ -1941,10 +1941,10 @@
         <v>3.2</v>
       </c>
       <c r="O6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q6">
         <v>2.24</v>
@@ -1953,16 +1953,16 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V6">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="W6">
         <v>1.27</v>
@@ -1971,13 +1971,13 @@
         <v>12</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z6">
         <v>11</v>
       </c>
       <c r="AA6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB6">
         <v>14</v>
@@ -1992,37 +1992,37 @@
         <v>26</v>
       </c>
       <c r="AF6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG6">
         <v>20</v>
       </c>
       <c r="AH6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI6">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
-        <v>900</v>
+        <v>390</v>
       </c>
       <c r="AK6">
-        <v>890</v>
+        <v>270</v>
       </c>
       <c r="AL6">
-        <v>890</v>
+        <v>300</v>
       </c>
       <c r="AM6">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AN6">
-        <v>890</v>
+        <v>830</v>
       </c>
       <c r="AO6">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AP6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6">
         <v>7</v>
@@ -2031,28 +2031,28 @@
         <v>9</v>
       </c>
       <c r="AS6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6">
         <v>9.4</v>
       </c>
       <c r="AW6">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX6">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AY6">
         <v>14.5</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA6">
         <v>36</v>
@@ -2070,10 +2070,10 @@
         <v>44</v>
       </c>
       <c r="BF6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2168,7 +2168,7 @@
         <v>3.2</v>
       </c>
       <c r="J7">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K7">
         <v>3.25</v>
@@ -2398,22 +2398,22 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="G8">
         <v>2.14</v>
       </c>
       <c r="H8">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="L8">
         <v>1.46</v>
@@ -2422,16 +2422,16 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P8">
         <v>1.5</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R8">
         <v>1.2</v>
@@ -2440,13 +2440,13 @@
         <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
         <v>1.87</v>
@@ -2640,7 +2640,7 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G9">
         <v>990</v>
@@ -2664,7 +2664,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
         <v>1.02</v>
@@ -2673,7 +2673,7 @@
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2906,13 +2906,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
         <v>1.37</v>
       </c>
       <c r="P10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q10">
         <v>1.37</v>
@@ -2921,13 +2921,13 @@
         <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
         <v>1.01</v>
@@ -3047,61 +3047,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -352,7 +352,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 19:16:20</t>
+    <t>2026-10-04 21:27:43</t>
   </si>
 </sst>
 </file>
@@ -946,10 +946,10 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
         <v>3.05</v>
@@ -958,7 +958,7 @@
         <v>3.45</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
         <v>3.65</v>
@@ -970,19 +970,19 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
         <v>1.95</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
         <v>3.5</v>
@@ -994,13 +994,13 @@
         <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
@@ -1018,16 +1018,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>18.5</v>
@@ -1036,10 +1036,10 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL2">
         <v>50</v>
@@ -1075,7 +1075,7 @@
         <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1087,7 +1087,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>28</v>
@@ -1099,7 +1099,7 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
@@ -1194,16 +1194,16 @@
         <v>3.7</v>
       </c>
       <c r="H3">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I3">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>500</v>
+        <v>5.3</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1212,31 +1212,31 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.72</v>
+        <v>1.1</v>
       </c>
       <c r="O3">
         <v>1.11</v>
       </c>
       <c r="P3">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="Q3">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="R3">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="S3">
         <v>1.96</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U3">
         <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W3">
         <v>1.37</v>
@@ -1296,19 +1296,19 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AR3">
         <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AU3">
         <v>1.01</v>
@@ -1335,13 +1335,13 @@
         <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -1430,94 +1430,94 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="G4">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K4">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>4.6</v>
       </c>
       <c r="O4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="R4">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S4">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="T4">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W4">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="X4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z4">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AA4">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="AB4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC4">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>15</v>
@@ -1526,70 +1526,70 @@
         <v>17</v>
       </c>
       <c r="AL4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO4">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP4">
         <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR4">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="AS4">
+        <v>6.6</v>
+      </c>
+      <c r="AT4">
+        <v>8</v>
+      </c>
+      <c r="AU4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV4">
         <v>5.9</v>
       </c>
-      <c r="AT4">
-        <v>7.8</v>
-      </c>
-      <c r="AU4">
-        <v>9.6</v>
-      </c>
-      <c r="AV4">
-        <v>5.2</v>
-      </c>
       <c r="AW4">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX4">
         <v>8</v>
       </c>
       <c r="AY4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>5.7</v>
+        <v>38</v>
       </c>
       <c r="BB4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC4">
         <v>12</v>
       </c>
       <c r="BD4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE4">
-        <v>5.7</v>
+        <v>42</v>
       </c>
       <c r="BF4">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1675,7 +1675,7 @@
         <v>1.94</v>
       </c>
       <c r="G5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>4.2</v>
@@ -1702,10 +1702,10 @@
         <v>1.32</v>
       </c>
       <c r="P5">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q5">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R5">
         <v>1.37</v>
@@ -1723,7 +1723,7 @@
         <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X5">
         <v>18</v>
@@ -1750,7 +1750,7 @@
         <v>70</v>
       </c>
       <c r="AF5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG5">
         <v>11</v>
@@ -1786,22 +1786,22 @@
         <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AS5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1810,28 +1810,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB5">
         <v>20</v>
       </c>
       <c r="BC5">
-        <v>4.6</v>
+        <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1920,49 +1920,49 @@
         <v>4.8</v>
       </c>
       <c r="H6">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
         <v>1.44</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="P6">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
         <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="V6">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="W6">
         <v>1.27</v>
@@ -1971,16 +1971,16 @@
         <v>12</v>
       </c>
       <c r="Y6">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AB6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC6">
         <v>8.4</v>
@@ -1989,34 +1989,34 @@
         <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF6">
         <v>36</v>
       </c>
       <c r="AG6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AJ6">
-        <v>390</v>
+        <v>250</v>
       </c>
       <c r="AK6">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="AL6">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="AM6">
-        <v>840</v>
+        <v>800</v>
       </c>
       <c r="AN6">
-        <v>830</v>
+        <v>790</v>
       </c>
       <c r="AO6">
         <v>20</v>
@@ -2025,40 +2025,40 @@
         <v>9.6</v>
       </c>
       <c r="AQ6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AR6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU6">
         <v>7</v>
       </c>
       <c r="AV6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW6">
         <v>17.5</v>
       </c>
       <c r="AX6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA6">
         <v>36</v>
       </c>
       <c r="BB6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC6">
         <v>44</v>
@@ -2067,7 +2067,7 @@
         <v>48</v>
       </c>
       <c r="BE6">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BF6">
         <v>36</v>
@@ -2174,7 +2174,7 @@
         <v>3.25</v>
       </c>
       <c r="L7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
         <v>1.11</v>
@@ -2201,7 +2201,7 @@
         <v>2.08</v>
       </c>
       <c r="U7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
         <v>1.46</v>
@@ -2398,22 +2398,22 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G8">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H8">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
         <v>2.74</v>
       </c>
       <c r="K8">
-        <v>6.2</v>
+        <v>95</v>
       </c>
       <c r="L8">
         <v>1.46</v>
@@ -2446,10 +2446,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X8">
         <v>11</v>
@@ -2649,7 +2649,7 @@
         <v>1.51</v>
       </c>
       <c r="I9">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="J9">
         <v>1.1</v>
@@ -2688,7 +2688,7 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
         <v>1.28</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -352,7 +352,7 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 21:27:43</t>
+    <t>2026-10-04 23:37:12</t>
   </si>
 </sst>
 </file>
@@ -946,22 +946,22 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I2">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
         <v>1.31</v>
@@ -970,37 +970,37 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q2">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T2">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
@@ -1012,16 +1012,16 @@
         <v>65</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AF2">
         <v>16</v>
@@ -1048,34 +1048,34 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO2">
         <v>46</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR2">
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1084,10 +1084,10 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB2">
         <v>28</v>
@@ -1099,7 +1099,7 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
@@ -1188,22 +1188,22 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="G3">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="H3">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="I3">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="K3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1212,34 +1212,34 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="O3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P3">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="Q3">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="R3">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="S3">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="T3">
         <v>1.45</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>2.72</v>
       </c>
       <c r="V3">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="W3">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1296,10 +1296,10 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="AQ3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AR3">
         <v>1.01</v>
@@ -1335,13 +1335,13 @@
         <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BD3">
         <v>16</v>
       </c>
       <c r="BE3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -1430,10 +1430,10 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H4">
         <v>6.8</v>
@@ -1457,13 +1457,13 @@
         <v>4.6</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
         <v>2.28</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R4">
         <v>1.52</v>
@@ -1475,13 +1475,13 @@
         <v>1.84</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V4">
         <v>1.12</v>
       </c>
       <c r="W4">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="X4">
         <v>26</v>
@@ -1493,22 +1493,22 @@
         <v>170</v>
       </c>
       <c r="AA4">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB4">
         <v>11</v>
       </c>
       <c r="AC4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD4">
         <v>32</v>
       </c>
       <c r="AE4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
         <v>11</v>
@@ -1517,7 +1517,7 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
         <v>15</v>
@@ -1535,16 +1535,16 @@
         <v>7</v>
       </c>
       <c r="AO4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP4">
         <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS4">
         <v>6.6</v>
@@ -1556,22 +1556,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
         <v>8</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
         <v>11</v>
@@ -1583,10 +1583,10 @@
         <v>6</v>
       </c>
       <c r="BE4">
-        <v>42</v>
+        <v>6.4</v>
       </c>
       <c r="BF4">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG4">
         <v>6.4</v>
@@ -1672,16 +1672,16 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H5">
         <v>4.2</v>
       </c>
       <c r="I5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1705,13 +1705,13 @@
         <v>1.97</v>
       </c>
       <c r="Q5">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R5">
         <v>1.37</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T5">
         <v>1.82</v>
@@ -1720,34 +1720,34 @@
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X5">
         <v>18</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z5">
         <v>40</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB5">
         <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
         <v>21</v>
       </c>
       <c r="AE5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF5">
         <v>13</v>
@@ -1777,7 +1777,7 @@
         <v>17.5</v>
       </c>
       <c r="AO5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP5">
         <v>13</v>
@@ -1786,10 +1786,10 @@
         <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -1801,7 +1801,7 @@
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1810,28 +1810,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB5">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="BC5">
-        <v>17.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE5">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1929,7 +1929,7 @@
         <v>3.3</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L6">
         <v>1.44</v>
@@ -1947,19 +1947,19 @@
         <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R6">
         <v>1.25</v>
       </c>
       <c r="S6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T6">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
         <v>1.94</v>
@@ -1977,7 +1977,7 @@
         <v>11.5</v>
       </c>
       <c r="AA6">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AB6">
         <v>13</v>
@@ -1998,25 +1998,25 @@
         <v>21</v>
       </c>
       <c r="AH6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AJ6">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AK6">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AL6">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AM6">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="AN6">
-        <v>790</v>
+        <v>750</v>
       </c>
       <c r="AO6">
         <v>20</v>
@@ -2028,10 +2028,10 @@
         <v>6.6</v>
       </c>
       <c r="AR6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS6">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2043,16 +2043,16 @@
         <v>10</v>
       </c>
       <c r="AW6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX6">
         <v>20</v>
       </c>
       <c r="AY6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA6">
         <v>36</v>
@@ -2064,10 +2064,10 @@
         <v>44</v>
       </c>
       <c r="BD6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BE6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF6">
         <v>36</v>
@@ -2156,58 +2156,58 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="G7">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H7">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I7">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K7">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L7">
         <v>1.41</v>
       </c>
       <c r="M7">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N7">
         <v>2.48</v>
       </c>
       <c r="O7">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="P7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q7">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V7">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -2264,58 +2264,58 @@
         <v>70</v>
       </c>
       <c r="AP7">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR7">
         <v>13</v>
       </c>
       <c r="AS7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT7">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU7">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AV7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW7">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AX7">
         <v>13.5</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE7">
         <v>4.2</v>
       </c>
       <c r="BF7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2398,58 +2398,58 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>3.25</v>
+      </c>
+      <c r="K8">
         <v>3.6</v>
       </c>
-      <c r="I8">
-        <v>6.2</v>
-      </c>
-      <c r="J8">
-        <v>2.74</v>
-      </c>
-      <c r="K8">
-        <v>95</v>
-      </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="O8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P8">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="Q8">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S8">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X8">
         <v>11</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="AK8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL8">
         <v>55</v>
@@ -2500,64 +2500,64 @@
         <v>180</v>
       </c>
       <c r="AN8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO8">
         <v>120</v>
       </c>
       <c r="AP8">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8">
         <v>11</v>
       </c>
       <c r="AR8">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT8">
         <v>6.4</v>
       </c>
       <c r="AU8">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
         <v>15.5</v>
       </c>
       <c r="AW8">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8">
         <v>10</v>
       </c>
       <c r="AY8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8">
         <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC8">
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE8">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF8">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2640,7 +2640,7 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G9">
         <v>990</v>
@@ -2649,7 +2649,7 @@
         <v>1.51</v>
       </c>
       <c r="I9">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J9">
         <v>1.1</v>
@@ -2688,7 +2688,7 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W9">
         <v>1.28</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="123">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-10-06</t>
   </si>
   <si>
@@ -298,6 +301,15 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>22:15:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Guatemala</t>
   </si>
   <si>
@@ -325,6 +337,15 @@
     <t>Club Sportivo Ameliano</t>
   </si>
   <si>
+    <t>Olimpia</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Goias</t>
+  </si>
+  <si>
     <t>Suriname</t>
   </si>
   <si>
@@ -352,7 +373,16 @@
     <t>Rubio Nu</t>
   </si>
   <si>
-    <t>2026-10-04 23:37:12</t>
+    <t>Nacional (Par)</t>
+  </si>
+  <si>
+    <t>Sao Bernardo</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>2026-10-05 01:46:57</t>
   </si>
 </sst>
 </file>
@@ -684,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -934,28 +964,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J2">
         <v>3.6</v>
@@ -964,55 +994,55 @@
         <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
         <v>1.97</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T2">
         <v>1.76</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="X2">
         <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
         <v>23</v>
       </c>
       <c r="AA2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
@@ -1045,16 +1075,16 @@
         <v>50</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO2">
         <v>46</v>
       </c>
       <c r="AP2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
         <v>11</v>
@@ -1063,10 +1093,10 @@
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
         <v>7.2</v>
@@ -1075,7 +1105,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1084,28 +1114,28 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB2">
         <v>28</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD2">
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1168,7 +1198,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1176,70 +1206,70 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F3">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="G3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I3">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="J3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="O3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P3">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="R3">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="T3">
         <v>1.45</v>
       </c>
       <c r="U3">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V3">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="W3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1296,10 +1326,10 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="AQ3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AR3">
         <v>1.01</v>
@@ -1329,13 +1359,13 @@
         <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BB3">
         <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
         <v>16</v>
@@ -1410,7 +1440,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1418,106 +1448,106 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F4">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="G4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V4">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Z4">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AA4">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE4">
         <v>120</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
         <v>15</v>
@@ -1529,67 +1559,67 @@
         <v>36</v>
       </c>
       <c r="AM4">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO4">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP4">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AR4">
+        <v>23</v>
+      </c>
+      <c r="AS4">
+        <v>8.6</v>
+      </c>
+      <c r="AT4">
+        <v>7.2</v>
+      </c>
+      <c r="AU4">
+        <v>8.6</v>
+      </c>
+      <c r="AV4">
         <v>21</v>
       </c>
-      <c r="AS4">
-        <v>6.6</v>
-      </c>
-      <c r="AT4">
+      <c r="AW4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX4">
         <v>8</v>
       </c>
-      <c r="AU4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV4">
-        <v>6</v>
-      </c>
-      <c r="AW4">
-        <v>6.6</v>
-      </c>
-      <c r="AX4">
+      <c r="AY4">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AY4">
-        <v>8</v>
       </c>
       <c r="AZ4">
         <v>18</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BB4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE4">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF4">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1652,7 +1682,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1660,28 +1690,28 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F5">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G5">
         <v>2.04</v>
       </c>
       <c r="H5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1690,19 +1720,19 @@
         <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P5">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q5">
         <v>1.96</v>
@@ -1711,16 +1741,16 @@
         <v>1.37</v>
       </c>
       <c r="S5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T5">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U5">
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
         <v>1.96</v>
@@ -1741,7 +1771,7 @@
         <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>21</v>
@@ -1756,7 +1786,7 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5">
         <v>75</v>
@@ -1774,7 +1804,7 @@
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO5">
         <v>70</v>
@@ -1786,10 +1816,10 @@
         <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -1801,7 +1831,7 @@
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1813,25 +1843,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
+        <v>6.2</v>
+      </c>
+      <c r="BB5">
+        <v>5.6</v>
+      </c>
+      <c r="BC5">
+        <v>5.4</v>
+      </c>
+      <c r="BD5">
         <v>6</v>
       </c>
-      <c r="BB5">
-        <v>5.3</v>
-      </c>
-      <c r="BC5">
-        <v>5.1</v>
-      </c>
-      <c r="BD5">
-        <v>5.7</v>
-      </c>
       <c r="BE5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1894,7 +1924,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1902,67 +1932,67 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H6">
         <v>1.98</v>
       </c>
       <c r="I6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K6">
         <v>3.6</v>
       </c>
       <c r="L6">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M6">
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
         <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
         <v>1.25</v>
       </c>
       <c r="S6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
         <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V6">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="W6">
         <v>1.27</v>
@@ -1971,7 +2001,7 @@
         <v>12</v>
       </c>
       <c r="Y6">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z6">
         <v>11.5</v>
@@ -1980,7 +2010,7 @@
         <v>25</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC6">
         <v>8.4</v>
@@ -1998,25 +2028,25 @@
         <v>21</v>
       </c>
       <c r="AH6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="AJ6">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
         <v>95</v>
       </c>
       <c r="AL6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="AN6">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="AO6">
         <v>20</v>
@@ -2031,10 +2061,10 @@
         <v>9.6</v>
       </c>
       <c r="AS6">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
         <v>7</v>
@@ -2046,19 +2076,19 @@
         <v>18</v>
       </c>
       <c r="AX6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY6">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
         <v>36</v>
       </c>
       <c r="BB6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC6">
         <v>44</v>
@@ -2067,7 +2097,7 @@
         <v>55</v>
       </c>
       <c r="BE6">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="BF6">
         <v>36</v>
@@ -2136,7 +2166,7 @@
         <v>1.35</v>
       </c>
       <c r="CB6" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2144,70 +2174,70 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F7">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G7">
         <v>3.15</v>
       </c>
       <c r="H7">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J7">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K7">
         <v>3.15</v>
       </c>
       <c r="L7">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="M7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P7">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q7">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="T7">
         <v>2.12</v>
       </c>
       <c r="U7">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -2219,7 +2249,7 @@
         <v>22</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2252,7 +2282,7 @@
         <v>60</v>
       </c>
       <c r="AL7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM7">
         <v>230</v>
@@ -2264,7 +2294,7 @@
         <v>70</v>
       </c>
       <c r="AP7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ7">
         <v>7.2</v>
@@ -2273,7 +2303,7 @@
         <v>13</v>
       </c>
       <c r="AS7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2294,7 +2324,7 @@
         <v>12</v>
       </c>
       <c r="AZ7">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA7">
         <v>4.3</v>
@@ -2309,10 +2339,10 @@
         <v>4.3</v>
       </c>
       <c r="BE7">
+        <v>4.3</v>
+      </c>
+      <c r="BF7">
         <v>4.2</v>
-      </c>
-      <c r="BF7">
-        <v>4.3</v>
       </c>
       <c r="BG7">
         <v>4.3</v>
@@ -2378,7 +2408,7 @@
         <v>1.65</v>
       </c>
       <c r="CB7" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2386,179 +2416,179 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="G8">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
         <v>3.6</v>
       </c>
       <c r="L8">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="T8">
         <v>2</v>
       </c>
       <c r="U8">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V8">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W8">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="X8">
         <v>11</v>
       </c>
       <c r="Y8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA8">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC8">
         <v>7.8</v>
       </c>
-      <c r="AC8">
-        <v>8</v>
-      </c>
       <c r="AD8">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL8">
         <v>55</v>
       </c>
       <c r="AM8">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO8">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AP8">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AS8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8">
+        <v>6.6</v>
+      </c>
+      <c r="AU8">
         <v>6.4</v>
       </c>
-      <c r="AU8">
-        <v>6.8</v>
-      </c>
       <c r="AV8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>8.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AX8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY8">
         <v>9.6</v>
       </c>
       <c r="AZ8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BB8">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BC8">
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BE8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF8">
+        <v>17.5</v>
+      </c>
+      <c r="BG8">
         <v>8.6</v>
       </c>
-      <c r="BF8">
-        <v>18.5</v>
-      </c>
-      <c r="BG8">
-        <v>8.4</v>
-      </c>
       <c r="BH8">
         <v>1000</v>
       </c>
@@ -2620,7 +2650,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2628,19 +2658,19 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F9">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="G9">
         <v>990</v>
@@ -2649,7 +2679,7 @@
         <v>1.51</v>
       </c>
       <c r="I9">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="J9">
         <v>1.1</v>
@@ -2862,7 +2892,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2870,16 +2900,16 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -3104,7 +3134,733 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>112</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11">
+        <v>1.98</v>
+      </c>
+      <c r="G11">
+        <v>2.18</v>
+      </c>
+      <c r="H11">
+        <v>4.3</v>
+      </c>
+      <c r="I11">
+        <v>5.4</v>
+      </c>
+      <c r="J11">
+        <v>3.2</v>
+      </c>
+      <c r="K11">
+        <v>3.65</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.1</v>
+      </c>
+      <c r="N11">
+        <v>2.88</v>
+      </c>
+      <c r="O11">
+        <v>1.4</v>
+      </c>
+      <c r="P11">
+        <v>1.66</v>
+      </c>
+      <c r="Q11">
+        <v>2.08</v>
+      </c>
+      <c r="R11">
+        <v>1.24</v>
+      </c>
+      <c r="S11">
+        <v>3.55</v>
+      </c>
+      <c r="T11">
+        <v>1.87</v>
+      </c>
+      <c r="U11">
+        <v>1.87</v>
+      </c>
+      <c r="V11">
+        <v>1.23</v>
+      </c>
+      <c r="W11">
+        <v>1.85</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>17</v>
+      </c>
+      <c r="Z11">
+        <v>44</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD11">
+        <v>23</v>
+      </c>
+      <c r="AE11">
+        <v>90</v>
+      </c>
+      <c r="AF11">
+        <v>15.5</v>
+      </c>
+      <c r="AG11">
+        <v>13.5</v>
+      </c>
+      <c r="AH11">
+        <v>950</v>
+      </c>
+      <c r="AI11">
+        <v>100</v>
+      </c>
+      <c r="AJ11">
+        <v>36</v>
+      </c>
+      <c r="AK11">
+        <v>34</v>
+      </c>
+      <c r="AL11">
+        <v>65</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>25</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>8</v>
+      </c>
+      <c r="AQ11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR11">
+        <v>19</v>
+      </c>
+      <c r="AS11">
+        <v>2.9</v>
+      </c>
+      <c r="AT11">
+        <v>6</v>
+      </c>
+      <c r="AU11">
+        <v>5.4</v>
+      </c>
+      <c r="AV11">
+        <v>13</v>
+      </c>
+      <c r="AW11">
+        <v>2.8</v>
+      </c>
+      <c r="AX11">
+        <v>8.4</v>
+      </c>
+      <c r="AY11">
+        <v>7.8</v>
+      </c>
+      <c r="AZ11">
+        <v>14.5</v>
+      </c>
+      <c r="BA11">
+        <v>2.82</v>
+      </c>
+      <c r="BB11">
+        <v>16.5</v>
+      </c>
+      <c r="BC11">
+        <v>16</v>
+      </c>
+      <c r="BD11">
+        <v>2.78</v>
+      </c>
+      <c r="BE11">
+        <v>2.9</v>
+      </c>
+      <c r="BF11">
+        <v>2.6</v>
+      </c>
+      <c r="BG11">
+        <v>2.9</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.84</v>
+      </c>
+      <c r="BJ11">
+        <v>14.5</v>
+      </c>
+      <c r="BK11">
+        <v>1.64</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.84</v>
+      </c>
+      <c r="BN11">
+        <v>6</v>
+      </c>
+      <c r="BO11">
+        <v>3.2</v>
+      </c>
+      <c r="BP11">
+        <v>21</v>
+      </c>
+      <c r="BQ11">
+        <v>1.7</v>
+      </c>
+      <c r="BR11">
+        <v>48</v>
+      </c>
+      <c r="BS11">
+        <v>1.79</v>
+      </c>
+      <c r="BT11">
+        <v>10</v>
+      </c>
+      <c r="BU11">
+        <v>5</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.79</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.81</v>
+      </c>
+      <c r="BZ11">
+        <v>46</v>
+      </c>
+      <c r="CA11">
+        <v>1.78</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>1.84</v>
+      </c>
+      <c r="G12">
+        <v>1.96</v>
+      </c>
+      <c r="H12">
+        <v>4.2</v>
+      </c>
+      <c r="I12">
+        <v>5.1</v>
+      </c>
+      <c r="J12">
+        <v>3.35</v>
+      </c>
+      <c r="K12">
+        <v>4.6</v>
+      </c>
+      <c r="L12">
+        <v>1.38</v>
+      </c>
+      <c r="M12">
+        <v>1.06</v>
+      </c>
+      <c r="N12">
+        <v>3.55</v>
+      </c>
+      <c r="O12">
+        <v>1.3</v>
+      </c>
+      <c r="P12">
+        <v>1.86</v>
+      </c>
+      <c r="Q12">
+        <v>1.85</v>
+      </c>
+      <c r="R12">
+        <v>1.35</v>
+      </c>
+      <c r="S12">
+        <v>3.4</v>
+      </c>
+      <c r="T12">
+        <v>1.75</v>
+      </c>
+      <c r="U12">
+        <v>1.96</v>
+      </c>
+      <c r="V12">
+        <v>1.24</v>
+      </c>
+      <c r="W12">
+        <v>2.02</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>970</v>
+      </c>
+      <c r="AC12">
+        <v>970</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>970</v>
+      </c>
+      <c r="AG12">
+        <v>970</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>14</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.47</v>
+      </c>
+      <c r="AQ12">
+        <v>1.47</v>
+      </c>
+      <c r="AR12">
+        <v>1.47</v>
+      </c>
+      <c r="AS12">
+        <v>1.47</v>
+      </c>
+      <c r="AT12">
+        <v>6.6</v>
+      </c>
+      <c r="AU12">
+        <v>6.2</v>
+      </c>
+      <c r="AV12">
+        <v>1.47</v>
+      </c>
+      <c r="AW12">
+        <v>1.47</v>
+      </c>
+      <c r="AX12">
+        <v>7.8</v>
+      </c>
+      <c r="AY12">
+        <v>7.2</v>
+      </c>
+      <c r="AZ12">
+        <v>1.47</v>
+      </c>
+      <c r="BA12">
+        <v>1.47</v>
+      </c>
+      <c r="BB12">
+        <v>1.47</v>
+      </c>
+      <c r="BC12">
+        <v>1.47</v>
+      </c>
+      <c r="BD12">
+        <v>1.47</v>
+      </c>
+      <c r="BE12">
+        <v>1.47</v>
+      </c>
+      <c r="BF12">
+        <v>1.33</v>
+      </c>
+      <c r="BG12">
+        <v>1.47</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.23</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.04</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.04</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.36</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.04</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.04</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.82</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.04</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.04</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.04</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13">
+        <v>1.77</v>
+      </c>
+      <c r="G13">
+        <v>1.89</v>
+      </c>
+      <c r="H13">
+        <v>5.1</v>
+      </c>
+      <c r="I13">
+        <v>7</v>
+      </c>
+      <c r="J13">
+        <v>3.45</v>
+      </c>
+      <c r="K13">
+        <v>4.2</v>
+      </c>
+      <c r="L13">
+        <v>1.5</v>
+      </c>
+      <c r="M13">
+        <v>1.07</v>
+      </c>
+      <c r="N13">
+        <v>2.98</v>
+      </c>
+      <c r="O13">
+        <v>1.46</v>
+      </c>
+      <c r="P13">
+        <v>1.58</v>
+      </c>
+      <c r="Q13">
+        <v>2.34</v>
+      </c>
+      <c r="R13">
+        <v>1.21</v>
+      </c>
+      <c r="S13">
+        <v>4.3</v>
+      </c>
+      <c r="T13">
+        <v>2.18</v>
+      </c>
+      <c r="U13">
+        <v>1.66</v>
+      </c>
+      <c r="V13">
+        <v>1.17</v>
+      </c>
+      <c r="W13">
+        <v>2.12</v>
+      </c>
+      <c r="X13">
+        <v>970</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>970</v>
+      </c>
+      <c r="AC13">
+        <v>970</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>970</v>
+      </c>
+      <c r="AG13">
+        <v>950</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>40</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.48</v>
+      </c>
+      <c r="AQ13">
+        <v>1.62</v>
+      </c>
+      <c r="AR13">
+        <v>1.62</v>
+      </c>
+      <c r="AS13">
+        <v>1.62</v>
+      </c>
+      <c r="AT13">
+        <v>5.4</v>
+      </c>
+      <c r="AU13">
+        <v>5.9</v>
+      </c>
+      <c r="AV13">
+        <v>1.62</v>
+      </c>
+      <c r="AW13">
+        <v>1.62</v>
+      </c>
+      <c r="AX13">
+        <v>1.46</v>
+      </c>
+      <c r="AY13">
+        <v>1.51</v>
+      </c>
+      <c r="AZ13">
+        <v>1.62</v>
+      </c>
+      <c r="BA13">
+        <v>1.62</v>
+      </c>
+      <c r="BB13">
+        <v>1.62</v>
+      </c>
+      <c r="BC13">
+        <v>1.62</v>
+      </c>
+      <c r="BD13">
+        <v>1.62</v>
+      </c>
+      <c r="BE13">
+        <v>1.62</v>
+      </c>
+      <c r="BF13">
+        <v>1.56</v>
+      </c>
+      <c r="BG13">
+        <v>1.62</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.22</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -382,7 +382,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 01:46:57</t>
+    <t>2026-10-05 03:56:16</t>
   </si>
 </sst>
 </file>
@@ -985,7 +985,7 @@
         <v>3.1</v>
       </c>
       <c r="I2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J2">
         <v>3.6</v>
@@ -1027,7 +1027,7 @@
         <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1078,7 +1078,7 @@
         <v>95</v>
       </c>
       <c r="AN2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO2">
         <v>46</v>
@@ -1105,7 +1105,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1117,7 +1117,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>28</v>
@@ -1129,7 +1129,7 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF2">
         <v>17.5</v>
@@ -1138,64 +1138,64 @@
         <v>24</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB2" t="s">
         <v>122</v>
@@ -1218,10 +1218,10 @@
         <v>111</v>
       </c>
       <c r="F3">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G3">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H3">
         <v>1.77</v>
@@ -1230,10 +1230,10 @@
         <v>1.81</v>
       </c>
       <c r="J3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K3">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L3">
         <v>1.23</v>
@@ -1245,22 +1245,22 @@
         <v>6.8</v>
       </c>
       <c r="O3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
         <v>1.42</v>
       </c>
       <c r="R3">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S3">
         <v>2.08</v>
       </c>
       <c r="T3">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="U3">
         <v>2.7</v>
@@ -1269,115 +1269,115 @@
         <v>2.22</v>
       </c>
       <c r="W3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AP3">
-        <v>2.88</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>1.06</v>
+        <v>13.5</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS3">
         <v>15.5</v>
       </c>
       <c r="AT3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD3">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1463,13 +1463,13 @@
         <v>1.52</v>
       </c>
       <c r="G4">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H4">
         <v>7</v>
       </c>
       <c r="I4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
         <v>4.4</v>
@@ -1484,34 +1484,34 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T4">
         <v>1.89</v>
       </c>
       <c r="U4">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V4">
         <v>1.14</v>
       </c>
       <c r="W4">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1520,7 +1520,7 @@
         <v>27</v>
       </c>
       <c r="Z4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA4">
         <v>240</v>
@@ -1538,7 +1538,7 @@
         <v>120</v>
       </c>
       <c r="AF4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1550,55 +1550,55 @@
         <v>120</v>
       </c>
       <c r="AJ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL4">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM4">
         <v>140</v>
       </c>
       <c r="AN4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO4">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP4">
         <v>15</v>
       </c>
       <c r="AQ4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS4">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AW4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
         <v>34</v>
@@ -1610,76 +1610,76 @@
         <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BE4">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG4">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="s">
         <v>122</v>
@@ -1702,7 +1702,7 @@
         <v>113</v>
       </c>
       <c r="F5">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G5">
         <v>2.04</v>
@@ -1720,7 +1720,7 @@
         <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M5">
         <v>1.07</v>
@@ -1750,19 +1750,19 @@
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
         <v>1.96</v>
       </c>
       <c r="X5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y5">
         <v>16.5</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA5">
         <v>110</v>
@@ -1792,7 +1792,7 @@
         <v>75</v>
       </c>
       <c r="AJ5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK5">
         <v>26</v>
@@ -1819,22 +1819,22 @@
         <v>6</v>
       </c>
       <c r="AS5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY5">
         <v>9.199999999999999</v>
@@ -1846,7 +1846,7 @@
         <v>6.2</v>
       </c>
       <c r="BB5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC5">
         <v>5.4</v>
@@ -1855,7 +1855,7 @@
         <v>6</v>
       </c>
       <c r="BE5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF5">
         <v>12</v>
@@ -1864,64 +1864,64 @@
         <v>6.4</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
         <v>122</v>
@@ -1944,7 +1944,7 @@
         <v>114</v>
       </c>
       <c r="F6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G6">
         <v>4.7</v>
@@ -1971,7 +1971,7 @@
         <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P6">
         <v>1.69</v>
@@ -1980,7 +1980,7 @@
         <v>2.38</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
         <v>4.7</v>
@@ -1989,7 +1989,7 @@
         <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
         <v>1.97</v>
@@ -1998,7 +1998,7 @@
         <v>1.27</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y6">
         <v>7.2</v>
@@ -2013,40 +2013,40 @@
         <v>13.5</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF6">
         <v>36</v>
       </c>
       <c r="AG6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK6">
         <v>95</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM6">
-        <v>740</v>
+        <v>700</v>
       </c>
       <c r="AN6">
-        <v>710</v>
+        <v>670</v>
       </c>
       <c r="AO6">
         <v>20</v>
@@ -2058,22 +2058,22 @@
         <v>6.6</v>
       </c>
       <c r="AR6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX6">
         <v>23</v>
@@ -2082,28 +2082,28 @@
         <v>16.5</v>
       </c>
       <c r="AZ6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB6">
         <v>65</v>
       </c>
       <c r="BC6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BD6">
         <v>55</v>
       </c>
       <c r="BE6">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="BF6">
         <v>36</v>
       </c>
       <c r="BG6">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2186,22 +2186,22 @@
         <v>115</v>
       </c>
       <c r="F7">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G7">
         <v>3.15</v>
       </c>
       <c r="H7">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I7">
         <v>2.96</v>
       </c>
       <c r="J7">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
         <v>1.6</v>
@@ -2210,28 +2210,28 @@
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P7">
         <v>1.52</v>
       </c>
       <c r="Q7">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R7">
         <v>1.19</v>
       </c>
       <c r="S7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V7">
         <v>1.51</v>
@@ -2249,7 +2249,7 @@
         <v>22</v>
       </c>
       <c r="AA7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2267,7 +2267,7 @@
         <v>23</v>
       </c>
       <c r="AG7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH7">
         <v>28</v>
@@ -2282,19 +2282,19 @@
         <v>60</v>
       </c>
       <c r="AL7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM7">
         <v>230</v>
       </c>
       <c r="AN7">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AO7">
         <v>70</v>
       </c>
       <c r="AP7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7">
         <v>7.2</v>
@@ -2303,7 +2303,7 @@
         <v>13</v>
       </c>
       <c r="AS7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2315,7 +2315,7 @@
         <v>12</v>
       </c>
       <c r="AW7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX7">
         <v>13.5</v>
@@ -2333,79 +2333,79 @@
         <v>4.3</v>
       </c>
       <c r="BC7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BD7">
         <v>4.3</v>
       </c>
       <c r="BE7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF7">
         <v>4.2</v>
       </c>
       <c r="BG7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI7">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="BJ7">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>1.51</v>
+        <v>5.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.67</v>
+        <v>11.5</v>
       </c>
       <c r="BN7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO7">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP7">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.65</v>
+        <v>10</v>
       </c>
       <c r="BT7">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BU7">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV7">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.65</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.65</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>122</v>
@@ -2428,31 +2428,31 @@
         <v>116</v>
       </c>
       <c r="F8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G8">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
         <v>1.5</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
         <v>1.44</v>
@@ -2464,22 +2464,22 @@
         <v>2.34</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T8">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U8">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="V8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X8">
         <v>11</v>
@@ -2488,7 +2488,7 @@
         <v>13</v>
       </c>
       <c r="Z8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA8">
         <v>110</v>
@@ -2512,7 +2512,7 @@
         <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8">
         <v>85</v>
@@ -2521,10 +2521,10 @@
         <v>29</v>
       </c>
       <c r="AK8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM8">
         <v>160</v>
@@ -2533,10 +2533,10 @@
         <v>24</v>
       </c>
       <c r="AO8">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
@@ -2545,19 +2545,19 @@
         <v>22</v>
       </c>
       <c r="AS8">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT8">
         <v>6.6</v>
       </c>
       <c r="AU8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV8">
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
@@ -2569,85 +2569,85 @@
         <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB8">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BC8">
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BE8">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF8">
         <v>17.5</v>
       </c>
       <c r="BG8">
+        <v>9</v>
+      </c>
+      <c r="BH8">
+        <v>3.05</v>
+      </c>
+      <c r="BI8">
+        <v>2.68</v>
+      </c>
+      <c r="BJ8">
+        <v>11</v>
+      </c>
+      <c r="BK8">
+        <v>5.5</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>10.5</v>
+      </c>
+      <c r="BN8">
+        <v>5</v>
+      </c>
+      <c r="BO8">
+        <v>3.85</v>
+      </c>
+      <c r="BP8">
+        <v>18</v>
+      </c>
+      <c r="BQ8">
+        <v>6.8</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
         <v>8.6</v>
       </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.04</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.04</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.04</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>1.04</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>1.04</v>
-      </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB8" t="s">
         <v>122</v>
@@ -2670,13 +2670,13 @@
         <v>117</v>
       </c>
       <c r="F9">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
         <v>3</v>
@@ -2718,10 +2718,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W9">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3154,7 +3154,7 @@
         <v>119</v>
       </c>
       <c r="F11">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="G11">
         <v>2.18</v>
@@ -3196,7 +3196,7 @@
         <v>3.55</v>
       </c>
       <c r="T11">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U11">
         <v>1.87</v>
@@ -3256,7 +3256,7 @@
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO11">
         <v>1000</v>
@@ -3265,25 +3265,25 @@
         <v>8</v>
       </c>
       <c r="AQ11">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR11">
         <v>19</v>
       </c>
       <c r="AS11">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AT11">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU11">
         <v>5.4</v>
       </c>
       <c r="AV11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AX11">
         <v>8.4</v>
@@ -3301,19 +3301,19 @@
         <v>16.5</v>
       </c>
       <c r="BC11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD11">
         <v>2.78</v>
       </c>
       <c r="BE11">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BF11">
         <v>2.6</v>
       </c>
       <c r="BG11">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3396,22 +3396,22 @@
         <v>120</v>
       </c>
       <c r="F12">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="G12">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H12">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K12">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="L12">
         <v>1.38</v>
@@ -3420,16 +3420,16 @@
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P12">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="R12">
         <v>1.35</v>
@@ -3444,10 +3444,10 @@
         <v>1.96</v>
       </c>
       <c r="V12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3456,7 +3456,7 @@
         <v>1000</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3489,10 +3489,10 @@
         <v>1000</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM12">
         <v>1000</v>
@@ -3504,16 +3504,16 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AR12">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AS12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AT12">
         <v>6.6</v>
@@ -3522,10 +3522,10 @@
         <v>6.2</v>
       </c>
       <c r="AV12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AW12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AX12">
         <v>7.8</v>
@@ -3534,28 +3534,28 @@
         <v>7.2</v>
       </c>
       <c r="AZ12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="BA12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="BB12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="BC12">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="BD12">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="BE12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="BF12">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="BG12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3644,7 +3644,7 @@
         <v>1.89</v>
       </c>
       <c r="H13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I13">
         <v>7</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -382,7 +382,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 03:56:16</t>
+    <t>2026-10-05 06:05:49</t>
   </si>
 </sst>
 </file>
@@ -976,10 +976,10 @@
         <v>110</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H2">
         <v>3.1</v>
@@ -1027,7 +1027,7 @@
         <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1081,7 +1081,7 @@
         <v>21</v>
       </c>
       <c r="AO2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AP2">
         <v>12.5</v>
@@ -1141,40 +1141,40 @@
         <v>3.8</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN2">
         <v>6.2</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR2">
         <v>36</v>
       </c>
       <c r="BS2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
         <v>5</v>
@@ -1183,19 +1183,19 @@
         <v>29</v>
       </c>
       <c r="BW2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX2">
         <v>42</v>
       </c>
       <c r="BY2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ2">
         <v>32</v>
       </c>
       <c r="CA2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB2" t="s">
         <v>122</v>
@@ -1218,22 +1218,22 @@
         <v>111</v>
       </c>
       <c r="F3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I3">
         <v>1.81</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K3">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>1.23</v>
@@ -1278,13 +1278,13 @@
         <v>17</v>
       </c>
       <c r="Z3">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AA3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC3">
         <v>13</v>
@@ -1299,28 +1299,28 @@
         <v>44</v>
       </c>
       <c r="AG3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK3">
         <v>50</v>
       </c>
       <c r="AL3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM3">
         <v>60</v>
       </c>
       <c r="AN3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO3">
         <v>6.6</v>
@@ -1350,7 +1350,7 @@
         <v>12</v>
       </c>
       <c r="AX3">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AY3">
         <v>14.5</v>
@@ -1362,22 +1362,22 @@
         <v>17.5</v>
       </c>
       <c r="BB3">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BC3">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BD3">
         <v>32</v>
       </c>
       <c r="BE3">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
         <v>20</v>
       </c>
       <c r="BG3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1460,7 +1460,7 @@
         <v>112</v>
       </c>
       <c r="F4">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G4">
         <v>1.56</v>
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>4.4</v>
@@ -1490,22 +1490,22 @@
         <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R4">
         <v>1.46</v>
       </c>
       <c r="S4">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V4">
         <v>1.14</v>
@@ -1520,16 +1520,16 @@
         <v>27</v>
       </c>
       <c r="Z4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD4">
         <v>29</v>
@@ -1556,7 +1556,7 @@
         <v>16.5</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AM4">
         <v>140</v>
@@ -1565,19 +1565,19 @@
         <v>7.6</v>
       </c>
       <c r="AO4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP4">
         <v>15</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AR4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT4">
         <v>7.6</v>
@@ -1586,10 +1586,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW4">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
@@ -1601,7 +1601,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="BB4">
         <v>12</v>
@@ -1613,19 +1613,19 @@
         <v>28</v>
       </c>
       <c r="BE4">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF4">
         <v>6.2</v>
       </c>
       <c r="BG4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH4">
         <v>4</v>
       </c>
       <c r="BI4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
         <v>12</v>
@@ -1643,7 +1643,7 @@
         <v>4.1</v>
       </c>
       <c r="BO4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP4">
         <v>9.199999999999999</v>
@@ -1702,16 +1702,16 @@
         <v>113</v>
       </c>
       <c r="F5">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1723,7 +1723,7 @@
         <v>1.41</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
         <v>3.9</v>
@@ -1744,7 +1744,7 @@
         <v>3.5</v>
       </c>
       <c r="T5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U5">
         <v>2.16</v>
@@ -1753,13 +1753,13 @@
         <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z5">
         <v>38</v>
@@ -1786,7 +1786,7 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI5">
         <v>75</v>
@@ -1795,19 +1795,19 @@
         <v>29</v>
       </c>
       <c r="AK5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM5">
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AO5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP5">
         <v>13</v>
@@ -1816,52 +1816,52 @@
         <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA5">
+        <v>6.6</v>
+      </c>
+      <c r="BB5">
+        <v>5.9</v>
+      </c>
+      <c r="BC5">
+        <v>19</v>
+      </c>
+      <c r="BD5">
         <v>6.2</v>
       </c>
-      <c r="BB5">
-        <v>5.7</v>
-      </c>
-      <c r="BC5">
-        <v>5.4</v>
-      </c>
-      <c r="BD5">
-        <v>6</v>
-      </c>
       <c r="BE5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH5">
         <v>4</v>
@@ -1879,49 +1879,49 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BP5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BT5">
         <v>7.8</v>
       </c>
       <c r="BU5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV5">
         <v>40</v>
       </c>
       <c r="BW5">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX5">
         <v>50</v>
       </c>
       <c r="BY5">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BZ5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="CB5" t="s">
         <v>122</v>
@@ -1944,7 +1944,7 @@
         <v>114</v>
       </c>
       <c r="F6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G6">
         <v>4.7</v>
@@ -1977,10 +1977,10 @@
         <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
         <v>4.7</v>
@@ -2034,19 +2034,19 @@
         <v>65</v>
       </c>
       <c r="AJ6">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
         <v>95</v>
       </c>
       <c r="AL6">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>670</v>
+        <v>610</v>
       </c>
       <c r="AO6">
         <v>20</v>
@@ -2058,7 +2058,7 @@
         <v>6.6</v>
       </c>
       <c r="AR6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS6">
         <v>20</v>
@@ -2067,7 +2067,7 @@
         <v>11</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6">
         <v>9.800000000000001</v>
@@ -2085,13 +2085,13 @@
         <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB6">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BC6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD6">
         <v>55</v>
@@ -2186,19 +2186,19 @@
         <v>115</v>
       </c>
       <c r="F7">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="G7">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="H7">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="I7">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="J7">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K7">
         <v>3.1</v>
@@ -2210,19 +2210,19 @@
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O7">
         <v>1.58</v>
       </c>
       <c r="P7">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
         <v>5.9</v>
@@ -2231,58 +2231,58 @@
         <v>2.1</v>
       </c>
       <c r="U7">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Y7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z7">
         <v>22</v>
       </c>
       <c r="AA7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AB7">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
+        <v>18</v>
+      </c>
+      <c r="AE7">
+        <v>65</v>
+      </c>
+      <c r="AF7">
         <v>17</v>
       </c>
-      <c r="AE7">
-        <v>55</v>
-      </c>
-      <c r="AF7">
-        <v>23</v>
-      </c>
       <c r="AG7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH7">
         <v>28</v>
       </c>
       <c r="AI7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK7">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AL7">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AM7">
         <v>230</v>
@@ -2291,109 +2291,109 @@
         <v>60</v>
       </c>
       <c r="AO7">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP7">
         <v>7.2</v>
       </c>
       <c r="AQ7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR7">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AS7">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT7">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU7">
         <v>6</v>
       </c>
       <c r="AV7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW7">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AX7">
         <v>13.5</v>
       </c>
       <c r="AY7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC7">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD7">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG7">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH7">
         <v>2.72</v>
       </c>
       <c r="BI7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ7">
         <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN7">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT7">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BU7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7">
         <v>1000</v>
@@ -2405,7 +2405,7 @@
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="s">
         <v>122</v>
@@ -2428,7 +2428,7 @@
         <v>116</v>
       </c>
       <c r="F8">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G8">
         <v>2.2</v>
@@ -2437,7 +2437,7 @@
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2452,7 +2452,7 @@
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
         <v>1.44</v>
@@ -2470,13 +2470,13 @@
         <v>4.5</v>
       </c>
       <c r="T8">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U8">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W8">
         <v>1.83</v>
@@ -2488,7 +2488,7 @@
         <v>13</v>
       </c>
       <c r="Z8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA8">
         <v>110</v>
@@ -2503,7 +2503,7 @@
         <v>18</v>
       </c>
       <c r="AE8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF8">
         <v>13</v>
@@ -2515,7 +2515,7 @@
         <v>24</v>
       </c>
       <c r="AI8">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ8">
         <v>29</v>
@@ -2524,7 +2524,7 @@
         <v>29</v>
       </c>
       <c r="AL8">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AM8">
         <v>160</v>
@@ -2542,10 +2542,10 @@
         <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="AS8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT8">
         <v>6.6</v>
@@ -2557,7 +2557,7 @@
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
@@ -2569,25 +2569,25 @@
         <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BD8">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BE8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8">
         <v>17.5</v>
       </c>
       <c r="BG8">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH8">
         <v>3.05</v>
@@ -2599,7 +2599,7 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2608,13 +2608,13 @@
         <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8">
         <v>6.8</v>
@@ -2623,10 +2623,10 @@
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU8">
         <v>5.6</v>
@@ -2635,7 +2635,7 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8">
         <v>1000</v>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB8" t="s">
         <v>122</v>
@@ -2670,166 +2670,166 @@
         <v>117</v>
       </c>
       <c r="F9">
-        <v>1.69</v>
+        <v>3.65</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S9">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3154,10 +3154,10 @@
         <v>119</v>
       </c>
       <c r="F11">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G11">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H11">
         <v>4.3</v>
@@ -3166,10 +3166,10 @@
         <v>5.4</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3178,34 +3178,34 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O11">
         <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q11">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R11">
         <v>1.24</v>
       </c>
       <c r="S11">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T11">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U11">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V11">
         <v>1.23</v>
       </c>
       <c r="W11">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3256,124 +3256,124 @@
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AP11">
-        <v>8</v>
+        <v>3.05</v>
       </c>
       <c r="AQ11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR11">
-        <v>19</v>
+        <v>2.88</v>
       </c>
       <c r="AS11">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AT11">
+        <v>5.9</v>
+      </c>
+      <c r="AU11">
         <v>5.8</v>
-      </c>
-      <c r="AU11">
-        <v>5.4</v>
       </c>
       <c r="AV11">
         <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AX11">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11">
-        <v>7.8</v>
+        <v>2.5</v>
       </c>
       <c r="AZ11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA11">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BB11">
         <v>16.5</v>
       </c>
       <c r="BC11">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD11">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="BE11">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BF11">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="BG11">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.84</v>
+        <v>1.19</v>
       </c>
       <c r="BJ11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.64</v>
+        <v>1.1</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.84</v>
+        <v>1.19</v>
       </c>
       <c r="BN11">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="BR11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="BT11">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>5</v>
+        <v>1.19</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="BZ11">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="CB11" t="s">
         <v>122</v>
@@ -3396,7 +3396,7 @@
         <v>120</v>
       </c>
       <c r="F12">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G12">
         <v>1.95</v>
@@ -3408,7 +3408,7 @@
         <v>4.8</v>
       </c>
       <c r="J12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
         <v>4</v>
@@ -3420,142 +3420,142 @@
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O12">
         <v>1.31</v>
       </c>
       <c r="P12">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="R12">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U12">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="V12">
         <v>1.26</v>
       </c>
       <c r="W12">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB12">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC12">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF12">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG12">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL12">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN12">
+        <v>13</v>
+      </c>
+      <c r="AO12">
+        <v>75</v>
+      </c>
+      <c r="AP12">
         <v>14</v>
       </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>1.73</v>
-      </c>
       <c r="AQ12">
-        <v>1.73</v>
+        <v>15</v>
       </c>
       <c r="AR12">
-        <v>1.66</v>
+        <v>7.4</v>
       </c>
       <c r="AS12">
-        <v>1.73</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU12">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>1.73</v>
+        <v>16</v>
       </c>
       <c r="AW12">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="AX12">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AY12">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>1.73</v>
+        <v>16</v>
       </c>
       <c r="BA12">
-        <v>1.73</v>
+        <v>8</v>
       </c>
       <c r="BB12">
-        <v>1.73</v>
+        <v>18.5</v>
       </c>
       <c r="BC12">
-        <v>1.61</v>
+        <v>17</v>
       </c>
       <c r="BD12">
-        <v>1.66</v>
+        <v>7.4</v>
       </c>
       <c r="BE12">
-        <v>1.73</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12">
-        <v>1.54</v>
+        <v>11</v>
       </c>
       <c r="BG12">
-        <v>1.73</v>
+        <v>8</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3638,7 +3638,7 @@
         <v>121</v>
       </c>
       <c r="F13">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="G13">
         <v>1.89</v>
@@ -3647,13 +3647,13 @@
         <v>5.2</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L13">
         <v>1.5</v>
@@ -3662,7 +3662,7 @@
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="O13">
         <v>1.46</v>
@@ -3671,7 +3671,7 @@
         <v>1.58</v>
       </c>
       <c r="Q13">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R13">
         <v>1.21</v>
@@ -3680,16 +3680,16 @@
         <v>4.3</v>
       </c>
       <c r="T13">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U13">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V13">
         <v>1.17</v>
       </c>
       <c r="W13">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X13">
         <v>970</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="165">
   <si>
     <t>League</t>
   </si>
@@ -271,9 +271,18 @@
     <t>Colombian Primera B</t>
   </si>
   <si>
+    <t>Chinese League 2</t>
+  </si>
+  <si>
+    <t>Chinese League 1</t>
+  </si>
+  <si>
     <t>Slovenian 2 SNL</t>
   </si>
   <si>
+    <t>Argentinian Primera C</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -295,12 +304,33 @@
     <t>02:00:00</t>
   </si>
   <si>
+    <t>07:00:00</t>
+  </si>
+  <si>
+    <t>07:30:00</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
     <t>20:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
     <t>22:15:00</t>
   </si>
   <si>
@@ -331,12 +361,60 @@
     <t>Honduras</t>
   </si>
   <si>
+    <t>Changchun Xidu</t>
+  </si>
+  <si>
+    <t>Beijing Tech FC</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
+    <t>Shanghai Second</t>
+  </si>
+  <si>
+    <t>Hubei Istar</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
+    <t>Wuxi Wugou</t>
+  </si>
+  <si>
+    <t>Jiangxi Dingnan United</t>
+  </si>
+  <si>
+    <t>Shijiazhuang Gongfu FC</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun F.C</t>
+  </si>
+  <si>
+    <t>Shenzhen 2028</t>
+  </si>
+  <si>
+    <t>Guizhou Zhucheng Athletic</t>
+  </si>
+  <si>
+    <t>Guangdong Mingtu</t>
+  </si>
+  <si>
+    <t>Hangzhou Linping Wuyue</t>
+  </si>
+  <si>
     <t>NK Bilje</t>
   </si>
   <si>
+    <t>CA Claypole</t>
+  </si>
+  <si>
     <t>Club Sportivo Ameliano</t>
   </si>
   <si>
+    <t>St Vincent &amp; Grenadines</t>
+  </si>
+  <si>
     <t>Olimpia</t>
   </si>
   <si>
@@ -367,12 +445,60 @@
     <t>Jamaica</t>
   </si>
   <si>
+    <t>Guangzhou Alpha</t>
+  </si>
+  <si>
+    <t>Chengdu Rongcheng II</t>
+  </si>
+  <si>
+    <t>Wuhan Three Towns II</t>
+  </si>
+  <si>
+    <t>Wenzhou Professional</t>
+  </si>
+  <si>
+    <t>Lanzhou Longyuan Athletic</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Dalian Kun City FC</t>
+  </si>
+  <si>
+    <t>Ningbo Professional</t>
+  </si>
+  <si>
+    <t>Shandong Taishan B</t>
+  </si>
+  <si>
+    <t>Shanghai Port B</t>
+  </si>
+  <si>
+    <t>Dalian Yingbo II</t>
+  </si>
+  <si>
+    <t>Xian Chongde Ronghai</t>
+  </si>
+  <si>
     <t>NK Jadran Dekani</t>
   </si>
   <si>
+    <t>Deportivo Espanol</t>
+  </si>
+  <si>
     <t>Rubio Nu</t>
   </si>
   <si>
+    <t>Sint Maarten</t>
+  </si>
+  <si>
     <t>Nacional (Par)</t>
   </si>
   <si>
@@ -382,7 +508,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 06:05:49</t>
+    <t>2026-10-05 08:16:12</t>
   </si>
 </sst>
 </file>
@@ -714,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -964,37 +1090,37 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
         <v>2.44</v>
       </c>
       <c r="H2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J2">
         <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1009,22 +1135,22 @@
         <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S2">
         <v>3.5</v>
       </c>
       <c r="T2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
         <v>1.69</v>
@@ -1033,7 +1159,7 @@
         <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
         <v>23</v>
@@ -1042,7 +1168,7 @@
         <v>60</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
@@ -1051,16 +1177,16 @@
         <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="AG2">
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>18.5</v>
+        <v>65</v>
       </c>
       <c r="AI2">
         <v>55</v>
@@ -1069,10 +1195,10 @@
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="AM2">
         <v>95</v>
@@ -1084,28 +1210,28 @@
         <v>36</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
         <v>11</v>
       </c>
       <c r="AR2">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AT2">
         <v>9.6</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AV2">
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1117,10 +1243,10 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BB2">
-        <v>28</v>
+        <v>4.8</v>
       </c>
       <c r="BC2">
         <v>23</v>
@@ -1129,34 +1255,34 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG2">
         <v>24</v>
       </c>
       <c r="BH2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO2">
         <v>4.2</v>
@@ -1165,40 +1291,40 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR2">
         <v>36</v>
       </c>
       <c r="BS2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY2">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BZ2">
         <v>32</v>
       </c>
       <c r="CA2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB2" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1206,16 +1332,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -1239,19 +1365,19 @@
         <v>1.23</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R3">
         <v>1.84</v>
@@ -1260,7 +1386,7 @@
         <v>2.08</v>
       </c>
       <c r="T3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U3">
         <v>2.7</v>
@@ -1272,112 +1398,112 @@
         <v>1.3</v>
       </c>
       <c r="X3">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
         <v>13</v>
       </c>
-      <c r="AD3">
-        <v>12</v>
-      </c>
       <c r="AE3">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
+        <v>950</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>4.8</v>
+      </c>
+      <c r="AQ3">
+        <v>3.5</v>
+      </c>
+      <c r="AR3">
+        <v>3.25</v>
+      </c>
+      <c r="AS3">
         <v>16.5</v>
       </c>
-      <c r="AI3">
-        <v>24</v>
-      </c>
-      <c r="AJ3">
-        <v>95</v>
-      </c>
-      <c r="AK3">
-        <v>50</v>
-      </c>
-      <c r="AL3">
-        <v>40</v>
-      </c>
-      <c r="AM3">
-        <v>60</v>
-      </c>
-      <c r="AN3">
-        <v>30</v>
-      </c>
-      <c r="AO3">
-        <v>6.6</v>
-      </c>
-      <c r="AP3">
-        <v>6.4</v>
-      </c>
-      <c r="AQ3">
-        <v>13.5</v>
-      </c>
-      <c r="AR3">
-        <v>12</v>
-      </c>
-      <c r="AS3">
-        <v>15.5</v>
-      </c>
       <c r="AT3">
-        <v>21</v>
+        <v>1.1</v>
       </c>
       <c r="AU3">
-        <v>9.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="AV3">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3">
-        <v>12</v>
+        <v>1.1</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>1.1</v>
       </c>
       <c r="AY3">
-        <v>14.5</v>
+        <v>1.1</v>
       </c>
       <c r="AZ3">
-        <v>12</v>
+        <v>1.09</v>
       </c>
       <c r="BA3">
-        <v>17.5</v>
+        <v>1.1</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>1.1</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>1.1</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>1.1</v>
       </c>
       <c r="BE3">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="BF3">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="BG3">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1440,7 +1566,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1448,34 +1574,34 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="F4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G4">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H4">
         <v>7</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L4">
         <v>1.34</v>
@@ -1484,19 +1610,19 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
         <v>2.96</v>
@@ -1508,22 +1634,22 @@
         <v>1.96</v>
       </c>
       <c r="V4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W4">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y4">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="Z4">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="AA4">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB4">
         <v>9.199999999999999</v>
@@ -1535,7 +1661,7 @@
         <v>29</v>
       </c>
       <c r="AE4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF4">
         <v>10</v>
@@ -1547,19 +1673,19 @@
         <v>25</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL4">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN4">
         <v>7.6</v>
@@ -1568,121 +1694,121 @@
         <v>160</v>
       </c>
       <c r="AP4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AR4">
-        <v>22</v>
+        <v>4.9</v>
       </c>
       <c r="AS4">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV4">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AW4">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AX4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4">
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BB4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD4">
-        <v>28</v>
+        <v>4.7</v>
       </c>
       <c r="BE4">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BF4">
         <v>6.2</v>
       </c>
       <c r="BG4">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="BH4">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1690,16 +1816,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1717,7 +1843,7 @@
         <v>3.6</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L5">
         <v>1.41</v>
@@ -1726,28 +1852,28 @@
         <v>1.06</v>
       </c>
       <c r="N5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P5">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q5">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R5">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S5">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T5">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
         <v>1.3</v>
@@ -1756,112 +1882,112 @@
         <v>1.94</v>
       </c>
       <c r="X5">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AJ5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK5">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AL5">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>13</v>
+        <v>1.86</v>
       </c>
       <c r="AQ5">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR5">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="AS5">
-        <v>6.8</v>
+        <v>1.86</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>1.87</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>15</v>
+        <v>1.77</v>
       </c>
       <c r="AW5">
-        <v>6.6</v>
+        <v>1.86</v>
       </c>
       <c r="AX5">
-        <v>11.5</v>
+        <v>1.98</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>1.69</v>
       </c>
       <c r="BA5">
-        <v>6.6</v>
+        <v>1.79</v>
       </c>
       <c r="BB5">
-        <v>5.9</v>
+        <v>1.74</v>
       </c>
       <c r="BC5">
-        <v>19</v>
+        <v>1.81</v>
       </c>
       <c r="BD5">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>1.86</v>
       </c>
       <c r="BF5">
-        <v>12</v>
+        <v>1.86</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>1.83</v>
       </c>
       <c r="BH5">
         <v>4</v>
@@ -1870,37 +1996,37 @@
         <v>2.76</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>7.2</v>
+        <v>3.45</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BO5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ5">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BT5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5">
         <v>5.5</v>
@@ -1909,22 +2035,22 @@
         <v>40</v>
       </c>
       <c r="BW5">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BX5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA5">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1932,25 +2058,25 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F6">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G6">
         <v>4.7</v>
       </c>
       <c r="H6">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I6">
         <v>2.04</v>
@@ -1959,7 +2085,7 @@
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
         <v>1.51</v>
@@ -1971,13 +2097,13 @@
         <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
         <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
         <v>1.25</v>
@@ -1989,7 +2115,7 @@
         <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="V6">
         <v>1.97</v>
@@ -2001,7 +2127,7 @@
         <v>11</v>
       </c>
       <c r="Y6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z6">
         <v>11.5</v>
@@ -2037,22 +2163,22 @@
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
         <v>1000</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="AN6">
-        <v>610</v>
+        <v>550</v>
       </c>
       <c r="AO6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP6">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
         <v>6.6</v>
@@ -2064,7 +2190,7 @@
         <v>20</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
         <v>7</v>
@@ -2085,19 +2211,19 @@
         <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB6">
         <v>38</v>
       </c>
       <c r="BC6">
+        <v>48</v>
+      </c>
+      <c r="BD6">
+        <v>60</v>
+      </c>
+      <c r="BE6">
         <v>44</v>
-      </c>
-      <c r="BD6">
-        <v>55</v>
-      </c>
-      <c r="BE6">
-        <v>85</v>
       </c>
       <c r="BF6">
         <v>36</v>
@@ -2109,64 +2235,64 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.39</v>
+        <v>2.58</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.35</v>
+        <v>2.46</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.35</v>
+        <v>2.46</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.35</v>
+        <v>2.46</v>
       </c>
       <c r="BT6">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.35</v>
+        <v>2.46</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.35</v>
+        <v>2.46</v>
       </c>
       <c r="CB6" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2174,241 +2300,241 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="F7">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="G7">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="H7">
+        <v>2.92</v>
+      </c>
+      <c r="I7">
         <v>3.25</v>
       </c>
-      <c r="I7">
+      <c r="J7">
+        <v>3.75</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>1.37</v>
+      </c>
+      <c r="M7">
+        <v>1.05</v>
+      </c>
+      <c r="N7">
+        <v>4.6</v>
+      </c>
+      <c r="O7">
+        <v>1.25</v>
+      </c>
+      <c r="P7">
+        <v>2.3</v>
+      </c>
+      <c r="Q7">
+        <v>1.71</v>
+      </c>
+      <c r="R7">
+        <v>1.46</v>
+      </c>
+      <c r="S7">
+        <v>2.94</v>
+      </c>
+      <c r="T7">
+        <v>1.6</v>
+      </c>
+      <c r="U7">
+        <v>2.4</v>
+      </c>
+      <c r="V7">
+        <v>1.45</v>
+      </c>
+      <c r="W7">
+        <v>1.67</v>
+      </c>
+      <c r="X7">
+        <v>22</v>
+      </c>
+      <c r="Y7">
+        <v>17.5</v>
+      </c>
+      <c r="Z7">
+        <v>26</v>
+      </c>
+      <c r="AA7">
+        <v>60</v>
+      </c>
+      <c r="AB7">
+        <v>13.5</v>
+      </c>
+      <c r="AC7">
+        <v>10.5</v>
+      </c>
+      <c r="AD7">
+        <v>15.5</v>
+      </c>
+      <c r="AE7">
+        <v>40</v>
+      </c>
+      <c r="AF7">
+        <v>20</v>
+      </c>
+      <c r="AG7">
+        <v>13</v>
+      </c>
+      <c r="AH7">
+        <v>20</v>
+      </c>
+      <c r="AI7">
+        <v>46</v>
+      </c>
+      <c r="AJ7">
+        <v>34</v>
+      </c>
+      <c r="AK7">
+        <v>28</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>80</v>
+      </c>
+      <c r="AN7">
+        <v>17</v>
+      </c>
+      <c r="AO7">
+        <v>29</v>
+      </c>
+      <c r="AP7">
+        <v>13</v>
+      </c>
+      <c r="AQ7">
+        <v>12</v>
+      </c>
+      <c r="AR7">
+        <v>18</v>
+      </c>
+      <c r="AS7">
+        <v>4.3</v>
+      </c>
+      <c r="AT7">
+        <v>10</v>
+      </c>
+      <c r="AU7">
+        <v>7.2</v>
+      </c>
+      <c r="AV7">
+        <v>10.5</v>
+      </c>
+      <c r="AW7">
+        <v>4.1</v>
+      </c>
+      <c r="AX7">
+        <v>13</v>
+      </c>
+      <c r="AY7">
         <v>3.4</v>
       </c>
-      <c r="J7">
-        <v>2.98</v>
-      </c>
-      <c r="K7">
-        <v>3.1</v>
-      </c>
-      <c r="L7">
+      <c r="AZ7">
+        <v>12</v>
+      </c>
+      <c r="BA7">
+        <v>4.2</v>
+      </c>
+      <c r="BB7">
+        <v>23</v>
+      </c>
+      <c r="BC7">
+        <v>16</v>
+      </c>
+      <c r="BD7">
+        <v>21</v>
+      </c>
+      <c r="BE7">
+        <v>4.4</v>
+      </c>
+      <c r="BF7">
+        <v>11.5</v>
+      </c>
+      <c r="BG7">
+        <v>17.5</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>3.2</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
         <v>1.6</v>
       </c>
-      <c r="M7">
-        <v>1.13</v>
-      </c>
-      <c r="N7">
-        <v>2.58</v>
-      </c>
-      <c r="O7">
-        <v>1.58</v>
-      </c>
-      <c r="P7">
-        <v>1.53</v>
-      </c>
-      <c r="Q7">
-        <v>2.78</v>
-      </c>
-      <c r="R7">
-        <v>1.18</v>
-      </c>
-      <c r="S7">
-        <v>5.9</v>
-      </c>
-      <c r="T7">
-        <v>2.1</v>
-      </c>
-      <c r="U7">
-        <v>1.79</v>
-      </c>
-      <c r="V7">
-        <v>1.41</v>
-      </c>
-      <c r="W7">
-        <v>1.57</v>
-      </c>
-      <c r="X7">
-        <v>8.4</v>
-      </c>
-      <c r="Y7">
-        <v>11</v>
-      </c>
-      <c r="Z7">
-        <v>22</v>
-      </c>
-      <c r="AA7">
-        <v>80</v>
-      </c>
-      <c r="AB7">
-        <v>8</v>
-      </c>
-      <c r="AC7">
-        <v>7.4</v>
-      </c>
-      <c r="AD7">
-        <v>18</v>
-      </c>
-      <c r="AE7">
-        <v>65</v>
-      </c>
-      <c r="AF7">
-        <v>17</v>
-      </c>
-      <c r="AG7">
-        <v>16</v>
-      </c>
-      <c r="AH7">
-        <v>28</v>
-      </c>
-      <c r="AI7">
-        <v>85</v>
-      </c>
-      <c r="AJ7">
-        <v>55</v>
-      </c>
-      <c r="AK7">
-        <v>48</v>
-      </c>
-      <c r="AL7">
-        <v>75</v>
-      </c>
-      <c r="AM7">
-        <v>230</v>
-      </c>
-      <c r="AN7">
-        <v>60</v>
-      </c>
-      <c r="AO7">
-        <v>85</v>
-      </c>
-      <c r="AP7">
-        <v>7.2</v>
-      </c>
-      <c r="AQ7">
-        <v>7.8</v>
-      </c>
-      <c r="AR7">
-        <v>17.5</v>
-      </c>
-      <c r="AS7">
-        <v>6.2</v>
-      </c>
-      <c r="AT7">
-        <v>6.8</v>
-      </c>
-      <c r="AU7">
-        <v>6</v>
-      </c>
-      <c r="AV7">
-        <v>13</v>
-      </c>
-      <c r="AW7">
-        <v>6</v>
-      </c>
-      <c r="AX7">
-        <v>13.5</v>
-      </c>
-      <c r="AY7">
-        <v>11</v>
-      </c>
-      <c r="AZ7">
-        <v>19.5</v>
-      </c>
-      <c r="BA7">
-        <v>6.2</v>
-      </c>
-      <c r="BB7">
-        <v>6.2</v>
-      </c>
-      <c r="BC7">
-        <v>6.2</v>
-      </c>
-      <c r="BD7">
-        <v>6.2</v>
-      </c>
-      <c r="BE7">
-        <v>6.6</v>
-      </c>
-      <c r="BF7">
-        <v>6.2</v>
-      </c>
-      <c r="BG7">
-        <v>6.2</v>
-      </c>
-      <c r="BH7">
-        <v>2.72</v>
-      </c>
-      <c r="BI7">
-        <v>2.2</v>
-      </c>
-      <c r="BJ7">
-        <v>11.5</v>
-      </c>
-      <c r="BK7">
-        <v>5.8</v>
-      </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>11</v>
+        <v>1.6</v>
       </c>
       <c r="BN7">
         <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9.6</v>
+        <v>1.6</v>
       </c>
       <c r="BT7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU7">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BV7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8.800000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>1.6</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA7">
-        <v>9.800000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="CB7" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2416,25 +2542,25 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="F8">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G8">
         <v>2.2</v>
       </c>
       <c r="H8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I8">
         <v>4.2</v>
@@ -2443,37 +2569,37 @@
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>1.5</v>
       </c>
       <c r="M8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
         <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U8">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="V8">
         <v>1.31</v>
@@ -2482,130 +2608,130 @@
         <v>1.83</v>
       </c>
       <c r="X8">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="Y8">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="Z8">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AA8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
+        <v>32</v>
+      </c>
+      <c r="AC8">
+        <v>9</v>
+      </c>
+      <c r="AD8">
+        <v>23</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>14.5</v>
+      </c>
+      <c r="AG8">
+        <v>14.5</v>
+      </c>
+      <c r="AH8">
+        <v>950</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>250</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC8">
-        <v>7.8</v>
-      </c>
-      <c r="AD8">
-        <v>18</v>
-      </c>
-      <c r="AE8">
-        <v>65</v>
-      </c>
-      <c r="AF8">
-        <v>13</v>
-      </c>
-      <c r="AG8">
-        <v>11.5</v>
-      </c>
-      <c r="AH8">
-        <v>24</v>
-      </c>
-      <c r="AI8">
-        <v>80</v>
-      </c>
-      <c r="AJ8">
-        <v>29</v>
-      </c>
-      <c r="AK8">
-        <v>29</v>
-      </c>
-      <c r="AL8">
-        <v>50</v>
-      </c>
-      <c r="AM8">
-        <v>160</v>
-      </c>
-      <c r="AN8">
-        <v>24</v>
-      </c>
-      <c r="AO8">
-        <v>85</v>
-      </c>
-      <c r="AP8">
-        <v>9.4</v>
-      </c>
       <c r="AQ8">
-        <v>10.5</v>
+        <v>2.08</v>
       </c>
       <c r="AR8">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AS8">
-        <v>9.6</v>
+        <v>2.34</v>
       </c>
       <c r="AT8">
         <v>6.6</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW8">
-        <v>9.4</v>
+        <v>2.34</v>
       </c>
       <c r="AX8">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="AY8">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>5.3</v>
       </c>
       <c r="BA8">
-        <v>9.199999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="BB8">
-        <v>7.8</v>
+        <v>2.32</v>
       </c>
       <c r="BC8">
-        <v>7.8</v>
+        <v>2.34</v>
       </c>
       <c r="BD8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE8">
-        <v>9.800000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="BF8">
-        <v>17.5</v>
+        <v>2.34</v>
       </c>
       <c r="BG8">
-        <v>9.6</v>
+        <v>2.34</v>
       </c>
       <c r="BH8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI8">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN8">
         <v>4.9</v>
@@ -2617,13 +2743,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
         <v>7.6</v>
@@ -2635,22 +2761,22 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2658,276 +2784,276 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="F9">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="G9">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="I9">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.07</v>
+      </c>
+      <c r="O9">
+        <v>1.01</v>
+      </c>
+      <c r="P9">
         <v>1.06</v>
       </c>
-      <c r="N9">
-        <v>3.9</v>
-      </c>
-      <c r="O9">
-        <v>1.25</v>
-      </c>
-      <c r="P9">
-        <v>2</v>
-      </c>
       <c r="Q9">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.06</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2936,34 +3062,34 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>2.96</v>
       </c>
       <c r="O10">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P10">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="Q10">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="R10">
         <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3020,52 +3146,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3077,790 +3203,4662 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="F11">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="G11">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="I11">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>2.98</v>
+        <v>1.75</v>
       </c>
       <c r="K11">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
+        <v>1.91</v>
+      </c>
+      <c r="O11">
+        <v>1.01</v>
+      </c>
+      <c r="P11">
+        <v>1.3</v>
+      </c>
+      <c r="Q11">
+        <v>1.71</v>
+      </c>
+      <c r="R11">
+        <v>1.06</v>
+      </c>
+      <c r="S11">
+        <v>1.71</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
+        <v>1.17</v>
+      </c>
+      <c r="W11">
+        <v>1.39</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11">
+        <v>1.03</v>
+      </c>
+      <c r="AR11">
+        <v>1.03</v>
+      </c>
+      <c r="AS11">
+        <v>1.03</v>
+      </c>
+      <c r="AT11">
+        <v>1.03</v>
+      </c>
+      <c r="AU11">
+        <v>1.03</v>
+      </c>
+      <c r="AV11">
+        <v>1.03</v>
+      </c>
+      <c r="AW11">
+        <v>1.03</v>
+      </c>
+      <c r="AX11">
+        <v>1.03</v>
+      </c>
+      <c r="AY11">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11">
+        <v>1.03</v>
+      </c>
+      <c r="BA11">
+        <v>1.03</v>
+      </c>
+      <c r="BB11">
+        <v>1.03</v>
+      </c>
+      <c r="BC11">
+        <v>1.03</v>
+      </c>
+      <c r="BD11">
+        <v>1.03</v>
+      </c>
+      <c r="BE11">
+        <v>1.03</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
         <v>3</v>
       </c>
-      <c r="O11">
-        <v>1.4</v>
-      </c>
-      <c r="P11">
-        <v>1.68</v>
-      </c>
-      <c r="Q11">
-        <v>2.04</v>
-      </c>
-      <c r="R11">
-        <v>1.24</v>
-      </c>
-      <c r="S11">
-        <v>3.65</v>
-      </c>
-      <c r="T11">
-        <v>1.84</v>
-      </c>
-      <c r="U11">
-        <v>1.9</v>
-      </c>
-      <c r="V11">
-        <v>1.23</v>
-      </c>
-      <c r="W11">
-        <v>1.87</v>
-      </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
-      <c r="Y11">
-        <v>17</v>
-      </c>
-      <c r="Z11">
-        <v>44</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD11">
-        <v>23</v>
-      </c>
-      <c r="AE11">
-        <v>90</v>
-      </c>
-      <c r="AF11">
-        <v>15.5</v>
-      </c>
-      <c r="AG11">
-        <v>13.5</v>
-      </c>
-      <c r="AH11">
-        <v>950</v>
-      </c>
-      <c r="AI11">
-        <v>100</v>
-      </c>
-      <c r="AJ11">
-        <v>36</v>
-      </c>
-      <c r="AK11">
-        <v>34</v>
-      </c>
-      <c r="AL11">
-        <v>65</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>23</v>
-      </c>
-      <c r="AO11">
-        <v>990</v>
-      </c>
-      <c r="AP11">
-        <v>3.05</v>
-      </c>
-      <c r="AQ11">
-        <v>10.5</v>
-      </c>
-      <c r="AR11">
-        <v>2.88</v>
-      </c>
-      <c r="AS11">
-        <v>3.05</v>
-      </c>
-      <c r="AT11">
-        <v>5.9</v>
-      </c>
-      <c r="AU11">
-        <v>5.8</v>
-      </c>
-      <c r="AV11">
-        <v>13.5</v>
-      </c>
-      <c r="AW11">
-        <v>3</v>
-      </c>
-      <c r="AX11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY11">
-        <v>2.5</v>
-      </c>
-      <c r="AZ11">
-        <v>14</v>
-      </c>
-      <c r="BA11">
-        <v>3</v>
-      </c>
-      <c r="BB11">
-        <v>16.5</v>
-      </c>
-      <c r="BC11">
-        <v>16.5</v>
-      </c>
-      <c r="BD11">
-        <v>2.94</v>
-      </c>
-      <c r="BE11">
-        <v>3.05</v>
-      </c>
-      <c r="BF11">
-        <v>2.72</v>
-      </c>
-      <c r="BG11">
-        <v>3</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
       <c r="BI11">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="F12">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="G12">
-        <v>1.95</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="I12">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>1.07</v>
+      </c>
+      <c r="O12">
+        <v>1.52</v>
+      </c>
+      <c r="P12">
         <v>1.06</v>
       </c>
-      <c r="N12">
-        <v>3.95</v>
-      </c>
-      <c r="O12">
-        <v>1.31</v>
-      </c>
-      <c r="P12">
-        <v>2</v>
-      </c>
       <c r="Q12">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
-        <v>1.39</v>
+        <v>1.06</v>
       </c>
       <c r="S12">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="T12">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13">
+        <v>1.12</v>
+      </c>
+      <c r="G13">
+        <v>3.65</v>
+      </c>
+      <c r="H13">
+        <v>2.26</v>
+      </c>
+      <c r="I13">
+        <v>2.98</v>
+      </c>
+      <c r="J13">
+        <v>2.58</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>2.62</v>
+      </c>
+      <c r="O13">
+        <v>1.5</v>
+      </c>
+      <c r="P13">
+        <v>1.48</v>
+      </c>
+      <c r="Q13">
+        <v>1.51</v>
+      </c>
+      <c r="R13">
+        <v>1.15</v>
+      </c>
+      <c r="S13">
+        <v>1.01</v>
+      </c>
+      <c r="T13">
+        <v>1.01</v>
+      </c>
+      <c r="U13">
+        <v>1.01</v>
+      </c>
+      <c r="V13">
+        <v>1.52</v>
+      </c>
+      <c r="W13">
+        <v>1.38</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.03</v>
+      </c>
+      <c r="AS13">
+        <v>1.03</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.03</v>
+      </c>
+      <c r="AW13">
+        <v>1.03</v>
+      </c>
+      <c r="AX13">
+        <v>1.03</v>
+      </c>
+      <c r="AY13">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13">
+        <v>1.03</v>
+      </c>
+      <c r="BA13">
+        <v>1.03</v>
+      </c>
+      <c r="BB13">
+        <v>1.03</v>
+      </c>
+      <c r="BC13">
+        <v>1.03</v>
+      </c>
+      <c r="BD13">
+        <v>1.03</v>
+      </c>
+      <c r="BE13">
+        <v>1.03</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.01</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.01</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14">
+        <v>1.94</v>
+      </c>
+      <c r="G14">
+        <v>2.3</v>
+      </c>
+      <c r="H14">
+        <v>3.45</v>
+      </c>
+      <c r="I14">
+        <v>4.8</v>
+      </c>
+      <c r="J14">
+        <v>3.3</v>
+      </c>
+      <c r="K14">
+        <v>4.4</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.04</v>
+      </c>
+      <c r="N14">
+        <v>3.25</v>
+      </c>
+      <c r="O14">
+        <v>1.33</v>
+      </c>
+      <c r="P14">
+        <v>1.81</v>
+      </c>
+      <c r="Q14">
+        <v>1.94</v>
+      </c>
+      <c r="R14">
+        <v>1.29</v>
+      </c>
+      <c r="S14">
+        <v>3.25</v>
+      </c>
+      <c r="T14">
+        <v>1.76</v>
+      </c>
+      <c r="U14">
+        <v>1.95</v>
+      </c>
+      <c r="V14">
+        <v>1.27</v>
+      </c>
+      <c r="W14">
+        <v>1.78</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>15</v>
+      </c>
+      <c r="AC14">
+        <v>12</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.17</v>
+      </c>
+      <c r="AQ14">
+        <v>1.17</v>
+      </c>
+      <c r="AR14">
+        <v>1.17</v>
+      </c>
+      <c r="AS14">
+        <v>1.17</v>
+      </c>
+      <c r="AT14">
+        <v>1.09</v>
+      </c>
+      <c r="AU14">
+        <v>1.07</v>
+      </c>
+      <c r="AV14">
+        <v>1.17</v>
+      </c>
+      <c r="AW14">
+        <v>1.17</v>
+      </c>
+      <c r="AX14">
+        <v>1.17</v>
+      </c>
+      <c r="AY14">
+        <v>1.17</v>
+      </c>
+      <c r="AZ14">
+        <v>1.17</v>
+      </c>
+      <c r="BA14">
+        <v>1.17</v>
+      </c>
+      <c r="BB14">
+        <v>1.17</v>
+      </c>
+      <c r="BC14">
+        <v>1.17</v>
+      </c>
+      <c r="BD14">
+        <v>1.17</v>
+      </c>
+      <c r="BE14">
+        <v>1.17</v>
+      </c>
+      <c r="BF14">
+        <v>1.17</v>
+      </c>
+      <c r="BG14">
+        <v>1.17</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15">
+        <v>2.02</v>
+      </c>
+      <c r="G15">
+        <v>2.32</v>
+      </c>
+      <c r="H15">
+        <v>3.3</v>
+      </c>
+      <c r="I15">
+        <v>4.5</v>
+      </c>
+      <c r="J15">
+        <v>3.3</v>
+      </c>
+      <c r="K15">
+        <v>4.2</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.04</v>
+      </c>
+      <c r="N15">
+        <v>3.2</v>
+      </c>
+      <c r="O15">
+        <v>1.33</v>
+      </c>
+      <c r="P15">
+        <v>1.77</v>
+      </c>
+      <c r="Q15">
+        <v>1.97</v>
+      </c>
+      <c r="R15">
+        <v>1.28</v>
+      </c>
+      <c r="S15">
+        <v>3.3</v>
+      </c>
+      <c r="T15">
+        <v>1.74</v>
+      </c>
+      <c r="U15">
+        <v>1.97</v>
+      </c>
+      <c r="V15">
+        <v>1.29</v>
+      </c>
+      <c r="W15">
+        <v>1.75</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>15.5</v>
+      </c>
+      <c r="AC15">
+        <v>11.5</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>1.03</v>
+      </c>
+      <c r="BC15">
+        <v>1.03</v>
+      </c>
+      <c r="BD15">
+        <v>1.03</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16">
+        <v>1.12</v>
+      </c>
+      <c r="G16">
+        <v>2.22</v>
+      </c>
+      <c r="H16">
+        <v>3.55</v>
+      </c>
+      <c r="I16">
+        <v>110</v>
+      </c>
+      <c r="J16">
+        <v>3.6</v>
+      </c>
+      <c r="K16">
+        <v>950</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>2.96</v>
+      </c>
+      <c r="O16">
+        <v>1.26</v>
+      </c>
+      <c r="P16">
+        <v>1.96</v>
+      </c>
+      <c r="Q16">
+        <v>1.21</v>
+      </c>
+      <c r="R16">
+        <v>1.37</v>
+      </c>
+      <c r="S16">
+        <v>1.97</v>
+      </c>
+      <c r="T16">
+        <v>1.01</v>
+      </c>
+      <c r="U16">
+        <v>1.01</v>
+      </c>
+      <c r="V16">
+        <v>1.07</v>
+      </c>
+      <c r="W16">
+        <v>1.83</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16">
+        <v>1.03</v>
+      </c>
+      <c r="AR16">
+        <v>1.03</v>
+      </c>
+      <c r="AS16">
+        <v>1.03</v>
+      </c>
+      <c r="AT16">
+        <v>1.03</v>
+      </c>
+      <c r="AU16">
+        <v>1.03</v>
+      </c>
+      <c r="AV16">
+        <v>1.03</v>
+      </c>
+      <c r="AW16">
+        <v>1.03</v>
+      </c>
+      <c r="AX16">
+        <v>1.03</v>
+      </c>
+      <c r="AY16">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16">
+        <v>1.03</v>
+      </c>
+      <c r="BA16">
+        <v>1.03</v>
+      </c>
+      <c r="BB16">
+        <v>1.03</v>
+      </c>
+      <c r="BC16">
+        <v>1.03</v>
+      </c>
+      <c r="BD16">
+        <v>1.03</v>
+      </c>
+      <c r="BE16">
+        <v>1.03</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.01</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.01</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17">
+        <v>1.77</v>
+      </c>
+      <c r="G17">
+        <v>3.55</v>
+      </c>
+      <c r="H17">
+        <v>2.84</v>
+      </c>
+      <c r="I17">
+        <v>110</v>
+      </c>
+      <c r="J17">
+        <v>2.72</v>
+      </c>
+      <c r="K17">
+        <v>950</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>1.41</v>
+      </c>
+      <c r="O17">
+        <v>1.01</v>
+      </c>
+      <c r="P17">
+        <v>1.41</v>
+      </c>
+      <c r="Q17">
+        <v>1.01</v>
+      </c>
+      <c r="R17">
+        <v>1.07</v>
+      </c>
+      <c r="S17">
+        <v>2.32</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>1.14</v>
+      </c>
+      <c r="W17">
+        <v>1.39</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17">
+        <v>1.03</v>
+      </c>
+      <c r="AR17">
+        <v>1.03</v>
+      </c>
+      <c r="AS17">
+        <v>1.03</v>
+      </c>
+      <c r="AT17">
+        <v>1.03</v>
+      </c>
+      <c r="AU17">
+        <v>1.03</v>
+      </c>
+      <c r="AV17">
+        <v>1.03</v>
+      </c>
+      <c r="AW17">
+        <v>1.03</v>
+      </c>
+      <c r="AX17">
+        <v>1.03</v>
+      </c>
+      <c r="AY17">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17">
+        <v>1.03</v>
+      </c>
+      <c r="BA17">
+        <v>1.03</v>
+      </c>
+      <c r="BB17">
+        <v>1.03</v>
+      </c>
+      <c r="BC17">
+        <v>1.03</v>
+      </c>
+      <c r="BD17">
+        <v>1.03</v>
+      </c>
+      <c r="BE17">
+        <v>1.03</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18">
+        <v>1.39</v>
+      </c>
+      <c r="G18">
+        <v>1.56</v>
+      </c>
+      <c r="H18">
+        <v>2.78</v>
+      </c>
+      <c r="I18">
+        <v>110</v>
+      </c>
+      <c r="J18">
+        <v>1.12</v>
+      </c>
+      <c r="K18">
+        <v>950</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18">
+        <v>1.01</v>
+      </c>
+      <c r="P18">
+        <v>1.42</v>
+      </c>
+      <c r="Q18">
+        <v>1.98</v>
+      </c>
+      <c r="R18">
+        <v>1.28</v>
+      </c>
+      <c r="S18">
+        <v>3.15</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
+        <v>1.01</v>
+      </c>
+      <c r="W18">
+        <v>2.78</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18">
+        <v>1.03</v>
+      </c>
+      <c r="AR18">
+        <v>1.03</v>
+      </c>
+      <c r="AS18">
+        <v>1.03</v>
+      </c>
+      <c r="AT18">
+        <v>1.03</v>
+      </c>
+      <c r="AU18">
+        <v>1.03</v>
+      </c>
+      <c r="AV18">
+        <v>1.03</v>
+      </c>
+      <c r="AW18">
+        <v>1.03</v>
+      </c>
+      <c r="AX18">
+        <v>1.03</v>
+      </c>
+      <c r="AY18">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18">
+        <v>1.03</v>
+      </c>
+      <c r="BA18">
+        <v>1.03</v>
+      </c>
+      <c r="BB18">
+        <v>1.03</v>
+      </c>
+      <c r="BC18">
+        <v>1.03</v>
+      </c>
+      <c r="BD18">
+        <v>1.03</v>
+      </c>
+      <c r="BE18">
+        <v>1.03</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.01</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.01</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.01</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19">
+        <v>1.1</v>
+      </c>
+      <c r="G19">
+        <v>1000</v>
+      </c>
+      <c r="H19">
+        <v>1.1</v>
+      </c>
+      <c r="I19">
+        <v>1000</v>
+      </c>
+      <c r="J19">
+        <v>1.1</v>
+      </c>
+      <c r="K19">
+        <v>950</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>1.07</v>
+      </c>
+      <c r="O19">
+        <v>1.01</v>
+      </c>
+      <c r="P19">
+        <v>1.07</v>
+      </c>
+      <c r="Q19">
+        <v>1.01</v>
+      </c>
+      <c r="R19">
+        <v>1.07</v>
+      </c>
+      <c r="S19">
+        <v>1.01</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
+        <v>1.02</v>
+      </c>
+      <c r="W19">
+        <v>1.01</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19">
+        <v>1.01</v>
+      </c>
+      <c r="AR19">
+        <v>1.01</v>
+      </c>
+      <c r="AS19">
+        <v>1.01</v>
+      </c>
+      <c r="AT19">
+        <v>1.01</v>
+      </c>
+      <c r="AU19">
+        <v>1.01</v>
+      </c>
+      <c r="AV19">
+        <v>1.01</v>
+      </c>
+      <c r="AW19">
+        <v>1.01</v>
+      </c>
+      <c r="AX19">
+        <v>1.01</v>
+      </c>
+      <c r="AY19">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19">
+        <v>1.01</v>
+      </c>
+      <c r="BA19">
+        <v>1.01</v>
+      </c>
+      <c r="BB19">
+        <v>1.01</v>
+      </c>
+      <c r="BC19">
+        <v>1.01</v>
+      </c>
+      <c r="BD19">
+        <v>1.01</v>
+      </c>
+      <c r="BE19">
+        <v>1.01</v>
+      </c>
+      <c r="BF19">
+        <v>1.01</v>
+      </c>
+      <c r="BG19">
+        <v>1.01</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20">
+        <v>1.1</v>
+      </c>
+      <c r="G20">
+        <v>1000</v>
+      </c>
+      <c r="H20">
+        <v>1.1</v>
+      </c>
+      <c r="I20">
+        <v>1000</v>
+      </c>
+      <c r="J20">
+        <v>1.1</v>
+      </c>
+      <c r="K20">
+        <v>950</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>1.07</v>
+      </c>
+      <c r="O20">
+        <v>1.01</v>
+      </c>
+      <c r="P20">
+        <v>1.07</v>
+      </c>
+      <c r="Q20">
+        <v>1.01</v>
+      </c>
+      <c r="R20">
+        <v>1.07</v>
+      </c>
+      <c r="S20">
+        <v>1.01</v>
+      </c>
+      <c r="T20">
+        <v>1.01</v>
+      </c>
+      <c r="U20">
+        <v>1.01</v>
+      </c>
+      <c r="V20">
+        <v>1.01</v>
+      </c>
+      <c r="W20">
+        <v>1.01</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20">
+        <v>1.03</v>
+      </c>
+      <c r="AR20">
+        <v>1.03</v>
+      </c>
+      <c r="AS20">
+        <v>1.03</v>
+      </c>
+      <c r="AT20">
+        <v>1.03</v>
+      </c>
+      <c r="AU20">
+        <v>1.03</v>
+      </c>
+      <c r="AV20">
+        <v>1.03</v>
+      </c>
+      <c r="AW20">
+        <v>1.03</v>
+      </c>
+      <c r="AX20">
+        <v>1.03</v>
+      </c>
+      <c r="AY20">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20">
+        <v>1.03</v>
+      </c>
+      <c r="BA20">
+        <v>1.03</v>
+      </c>
+      <c r="BB20">
+        <v>1.03</v>
+      </c>
+      <c r="BC20">
+        <v>1.03</v>
+      </c>
+      <c r="BD20">
+        <v>1.03</v>
+      </c>
+      <c r="BE20">
+        <v>1.03</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21">
+        <v>1.1</v>
+      </c>
+      <c r="G21">
+        <v>1000</v>
+      </c>
+      <c r="H21">
+        <v>1.1</v>
+      </c>
+      <c r="I21">
+        <v>1000</v>
+      </c>
+      <c r="J21">
+        <v>1.1</v>
+      </c>
+      <c r="K21">
+        <v>950</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>1.06</v>
+      </c>
+      <c r="O21">
+        <v>1.01</v>
+      </c>
+      <c r="P21">
+        <v>1.07</v>
+      </c>
+      <c r="Q21">
+        <v>1.01</v>
+      </c>
+      <c r="R21">
+        <v>1.07</v>
+      </c>
+      <c r="S21">
+        <v>1.01</v>
+      </c>
+      <c r="T21">
+        <v>1.01</v>
+      </c>
+      <c r="U21">
+        <v>1.01</v>
+      </c>
+      <c r="V21">
+        <v>1.01</v>
+      </c>
+      <c r="W21">
+        <v>1.02</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21">
+        <v>1.03</v>
+      </c>
+      <c r="AR21">
+        <v>1.03</v>
+      </c>
+      <c r="AS21">
+        <v>1.03</v>
+      </c>
+      <c r="AT21">
+        <v>1.03</v>
+      </c>
+      <c r="AU21">
+        <v>1.03</v>
+      </c>
+      <c r="AV21">
+        <v>1.03</v>
+      </c>
+      <c r="AW21">
+        <v>1.03</v>
+      </c>
+      <c r="AX21">
+        <v>1.03</v>
+      </c>
+      <c r="AY21">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21">
+        <v>1.03</v>
+      </c>
+      <c r="BA21">
+        <v>1.03</v>
+      </c>
+      <c r="BB21">
+        <v>1.03</v>
+      </c>
+      <c r="BC21">
+        <v>1.03</v>
+      </c>
+      <c r="BD21">
+        <v>1.03</v>
+      </c>
+      <c r="BE21">
+        <v>1.03</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.01</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.01</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.01</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.01</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.01</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.01</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.01</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22">
+        <v>1.1</v>
+      </c>
+      <c r="G22">
+        <v>1000</v>
+      </c>
+      <c r="H22">
+        <v>1.1</v>
+      </c>
+      <c r="I22">
+        <v>1000</v>
+      </c>
+      <c r="J22">
+        <v>1.1</v>
+      </c>
+      <c r="K22">
+        <v>950</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>1.06</v>
+      </c>
+      <c r="O22">
+        <v>1.01</v>
+      </c>
+      <c r="P22">
+        <v>1.07</v>
+      </c>
+      <c r="Q22">
+        <v>1.01</v>
+      </c>
+      <c r="R22">
+        <v>1.07</v>
+      </c>
+      <c r="S22">
+        <v>1.01</v>
+      </c>
+      <c r="T22">
+        <v>1.01</v>
+      </c>
+      <c r="U22">
+        <v>1.01</v>
+      </c>
+      <c r="V22">
+        <v>1.01</v>
+      </c>
+      <c r="W22">
+        <v>1.02</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22">
+        <v>1.03</v>
+      </c>
+      <c r="AR22">
+        <v>1.03</v>
+      </c>
+      <c r="AS22">
+        <v>1.03</v>
+      </c>
+      <c r="AT22">
+        <v>1.03</v>
+      </c>
+      <c r="AU22">
+        <v>1.03</v>
+      </c>
+      <c r="AV22">
+        <v>1.03</v>
+      </c>
+      <c r="AW22">
+        <v>1.03</v>
+      </c>
+      <c r="AX22">
+        <v>1.03</v>
+      </c>
+      <c r="AY22">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22">
+        <v>1.03</v>
+      </c>
+      <c r="BA22">
+        <v>1.03</v>
+      </c>
+      <c r="BB22">
+        <v>1.03</v>
+      </c>
+      <c r="BC22">
+        <v>1.03</v>
+      </c>
+      <c r="BD22">
+        <v>1.03</v>
+      </c>
+      <c r="BE22">
+        <v>1.03</v>
+      </c>
+      <c r="BF22">
+        <v>1.01</v>
+      </c>
+      <c r="BG22">
+        <v>1.01</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.01</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.01</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.01</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.01</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.01</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.01</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23">
+        <v>3.45</v>
+      </c>
+      <c r="G23">
+        <v>4.8</v>
+      </c>
+      <c r="H23">
+        <v>1.83</v>
+      </c>
+      <c r="I23">
+        <v>2.16</v>
+      </c>
+      <c r="J23">
+        <v>3.5</v>
+      </c>
+      <c r="K23">
+        <v>4.5</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.05</v>
+      </c>
+      <c r="N23">
+        <v>3.6</v>
+      </c>
+      <c r="O23">
+        <v>1.24</v>
+      </c>
+      <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23">
+        <v>1.72</v>
+      </c>
+      <c r="R23">
+        <v>1.39</v>
+      </c>
+      <c r="S23">
+        <v>2.84</v>
+      </c>
+      <c r="T23">
+        <v>1.11</v>
+      </c>
+      <c r="U23">
+        <v>1.11</v>
+      </c>
+      <c r="V23">
+        <v>1.86</v>
+      </c>
+      <c r="W23">
+        <v>1.26</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>1000</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>1000</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23">
+        <v>1.01</v>
+      </c>
+      <c r="AR23">
+        <v>1.01</v>
+      </c>
+      <c r="AS23">
+        <v>1.01</v>
+      </c>
+      <c r="AT23">
+        <v>1.01</v>
+      </c>
+      <c r="AU23">
+        <v>1.01</v>
+      </c>
+      <c r="AV23">
+        <v>1.01</v>
+      </c>
+      <c r="AW23">
+        <v>1.01</v>
+      </c>
+      <c r="AX23">
+        <v>1.01</v>
+      </c>
+      <c r="AY23">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23">
+        <v>1.01</v>
+      </c>
+      <c r="BA23">
+        <v>1.01</v>
+      </c>
+      <c r="BB23">
+        <v>1.01</v>
+      </c>
+      <c r="BC23">
+        <v>1.01</v>
+      </c>
+      <c r="BD23">
+        <v>1.01</v>
+      </c>
+      <c r="BE23">
+        <v>1.01</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>1.01</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.04</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.04</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.04</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.04</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.04</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.04</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.04</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.04</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
         <v>88</v>
       </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13">
-        <v>1.73</v>
-      </c>
-      <c r="G13">
-        <v>1.89</v>
-      </c>
-      <c r="H13">
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24">
+        <v>1.01</v>
+      </c>
+      <c r="G24">
+        <v>1000</v>
+      </c>
+      <c r="H24">
+        <v>1.01</v>
+      </c>
+      <c r="I24">
+        <v>1000</v>
+      </c>
+      <c r="J24">
+        <v>1.01</v>
+      </c>
+      <c r="K24">
+        <v>1000</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>1.08</v>
+      </c>
+      <c r="O24">
+        <v>1.01</v>
+      </c>
+      <c r="P24">
+        <v>1.08</v>
+      </c>
+      <c r="Q24">
+        <v>1.01</v>
+      </c>
+      <c r="R24">
+        <v>1.08</v>
+      </c>
+      <c r="S24">
+        <v>1.01</v>
+      </c>
+      <c r="T24">
+        <v>1.01</v>
+      </c>
+      <c r="U24">
+        <v>1.01</v>
+      </c>
+      <c r="V24">
+        <v>1.01</v>
+      </c>
+      <c r="W24">
+        <v>1.01</v>
+      </c>
+      <c r="X24">
+        <v>1000</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>1000</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>1000</v>
+      </c>
+      <c r="AC24">
+        <v>1000</v>
+      </c>
+      <c r="AD24">
+        <v>1000</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>1000</v>
+      </c>
+      <c r="AG24">
+        <v>1000</v>
+      </c>
+      <c r="AH24">
+        <v>1000</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>1000</v>
+      </c>
+      <c r="AK24">
+        <v>1000</v>
+      </c>
+      <c r="AL24">
+        <v>1000</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>1000</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24">
+        <v>1.01</v>
+      </c>
+      <c r="AR24">
+        <v>1.01</v>
+      </c>
+      <c r="AS24">
+        <v>1.01</v>
+      </c>
+      <c r="AT24">
+        <v>1.01</v>
+      </c>
+      <c r="AU24">
+        <v>1.01</v>
+      </c>
+      <c r="AV24">
+        <v>1.01</v>
+      </c>
+      <c r="AW24">
+        <v>1.01</v>
+      </c>
+      <c r="AX24">
+        <v>1.01</v>
+      </c>
+      <c r="AY24">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24">
+        <v>1.01</v>
+      </c>
+      <c r="BA24">
+        <v>1.01</v>
+      </c>
+      <c r="BB24">
+        <v>1.01</v>
+      </c>
+      <c r="BC24">
+        <v>1.01</v>
+      </c>
+      <c r="BD24">
+        <v>1.01</v>
+      </c>
+      <c r="BE24">
+        <v>1.01</v>
+      </c>
+      <c r="BF24">
+        <v>1.01</v>
+      </c>
+      <c r="BG24">
+        <v>1.01</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.01</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.01</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.01</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.01</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.01</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>1.1</v>
+      </c>
+      <c r="O25">
+        <v>1.37</v>
+      </c>
+      <c r="P25">
+        <v>1.09</v>
+      </c>
+      <c r="Q25">
+        <v>1.37</v>
+      </c>
+      <c r="R25">
+        <v>1.08</v>
+      </c>
+      <c r="S25">
+        <v>1.38</v>
+      </c>
+      <c r="T25">
+        <v>1.11</v>
+      </c>
+      <c r="U25">
+        <v>1.11</v>
+      </c>
+      <c r="V25">
+        <v>1.01</v>
+      </c>
+      <c r="W25">
+        <v>1.01</v>
+      </c>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>1000</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25">
+        <v>1.01</v>
+      </c>
+      <c r="AR25">
+        <v>1.01</v>
+      </c>
+      <c r="AS25">
+        <v>1.01</v>
+      </c>
+      <c r="AT25">
+        <v>1.01</v>
+      </c>
+      <c r="AU25">
+        <v>1.01</v>
+      </c>
+      <c r="AV25">
+        <v>1.01</v>
+      </c>
+      <c r="AW25">
+        <v>1.01</v>
+      </c>
+      <c r="AX25">
+        <v>1.01</v>
+      </c>
+      <c r="AY25">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25">
+        <v>1.01</v>
+      </c>
+      <c r="BA25">
+        <v>1.01</v>
+      </c>
+      <c r="BB25">
+        <v>1.01</v>
+      </c>
+      <c r="BC25">
+        <v>1.01</v>
+      </c>
+      <c r="BD25">
+        <v>1.01</v>
+      </c>
+      <c r="BE25">
+        <v>1.01</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.04</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.04</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.04</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.04</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.04</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.04</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.04</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.04</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.04</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.04</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26">
+        <v>1.1</v>
+      </c>
+      <c r="G26">
+        <v>1000</v>
+      </c>
+      <c r="H26">
+        <v>1.1</v>
+      </c>
+      <c r="I26">
+        <v>1000</v>
+      </c>
+      <c r="J26">
+        <v>1.1</v>
+      </c>
+      <c r="K26">
+        <v>110</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>1.12</v>
+      </c>
+      <c r="O26">
+        <v>1.19</v>
+      </c>
+      <c r="P26">
+        <v>1.12</v>
+      </c>
+      <c r="Q26">
+        <v>1.19</v>
+      </c>
+      <c r="R26">
+        <v>1.08</v>
+      </c>
+      <c r="S26">
+        <v>1.19</v>
+      </c>
+      <c r="T26">
+        <v>1.01</v>
+      </c>
+      <c r="U26">
+        <v>1.01</v>
+      </c>
+      <c r="V26">
+        <v>1.02</v>
+      </c>
+      <c r="W26">
+        <v>1.02</v>
+      </c>
+      <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>1000</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>1000</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26">
+        <v>1.01</v>
+      </c>
+      <c r="AR26">
+        <v>1.01</v>
+      </c>
+      <c r="AS26">
+        <v>1.01</v>
+      </c>
+      <c r="AT26">
+        <v>1.01</v>
+      </c>
+      <c r="AU26">
+        <v>1.01</v>
+      </c>
+      <c r="AV26">
+        <v>1.01</v>
+      </c>
+      <c r="AW26">
+        <v>1.01</v>
+      </c>
+      <c r="AX26">
+        <v>1.01</v>
+      </c>
+      <c r="AY26">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26">
+        <v>1.01</v>
+      </c>
+      <c r="BA26">
+        <v>1.01</v>
+      </c>
+      <c r="BB26">
+        <v>1.01</v>
+      </c>
+      <c r="BC26">
+        <v>1.01</v>
+      </c>
+      <c r="BD26">
+        <v>1.01</v>
+      </c>
+      <c r="BE26">
+        <v>1.01</v>
+      </c>
+      <c r="BF26">
+        <v>1.01</v>
+      </c>
+      <c r="BG26">
+        <v>1.01</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>1.01</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>1.01</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>1.01</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>1.01</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>1.01</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>1.01</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27">
+        <v>1.93</v>
+      </c>
+      <c r="G27">
+        <v>2.16</v>
+      </c>
+      <c r="H27">
+        <v>4.6</v>
+      </c>
+      <c r="I27">
         <v>5.2</v>
       </c>
-      <c r="I13">
+      <c r="J27">
+        <v>3.15</v>
+      </c>
+      <c r="K27">
+        <v>3.6</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.1</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>1.39</v>
+      </c>
+      <c r="P27">
+        <v>1.69</v>
+      </c>
+      <c r="Q27">
+        <v>2.08</v>
+      </c>
+      <c r="R27">
+        <v>1.25</v>
+      </c>
+      <c r="S27">
+        <v>3.6</v>
+      </c>
+      <c r="T27">
+        <v>1.82</v>
+      </c>
+      <c r="U27">
+        <v>1.9</v>
+      </c>
+      <c r="V27">
+        <v>1.24</v>
+      </c>
+      <c r="W27">
+        <v>1.86</v>
+      </c>
+      <c r="X27">
+        <v>970</v>
+      </c>
+      <c r="Y27">
+        <v>970</v>
+      </c>
+      <c r="Z27">
+        <v>44</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>970</v>
+      </c>
+      <c r="AC27">
+        <v>970</v>
+      </c>
+      <c r="AD27">
+        <v>950</v>
+      </c>
+      <c r="AE27">
+        <v>90</v>
+      </c>
+      <c r="AF27">
+        <v>970</v>
+      </c>
+      <c r="AG27">
+        <v>970</v>
+      </c>
+      <c r="AH27">
+        <v>950</v>
+      </c>
+      <c r="AI27">
+        <v>95</v>
+      </c>
+      <c r="AJ27">
+        <v>36</v>
+      </c>
+      <c r="AK27">
+        <v>34</v>
+      </c>
+      <c r="AL27">
+        <v>65</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>23</v>
+      </c>
+      <c r="AO27">
+        <v>930</v>
+      </c>
+      <c r="AP27">
+        <v>2.4</v>
+      </c>
+      <c r="AQ27">
+        <v>1.98</v>
+      </c>
+      <c r="AR27">
+        <v>1.63</v>
+      </c>
+      <c r="AS27">
+        <v>1.69</v>
+      </c>
+      <c r="AT27">
+        <v>2.36</v>
+      </c>
+      <c r="AU27">
+        <v>2.3</v>
+      </c>
+      <c r="AV27">
+        <v>1.83</v>
+      </c>
+      <c r="AW27">
+        <v>1.67</v>
+      </c>
+      <c r="AX27">
+        <v>2.58</v>
+      </c>
+      <c r="AY27">
+        <v>2.02</v>
+      </c>
+      <c r="AZ27">
+        <v>1.98</v>
+      </c>
+      <c r="BA27">
+        <v>1.67</v>
+      </c>
+      <c r="BB27">
+        <v>1.62</v>
+      </c>
+      <c r="BC27">
+        <v>1.62</v>
+      </c>
+      <c r="BD27">
+        <v>1.65</v>
+      </c>
+      <c r="BE27">
+        <v>1.69</v>
+      </c>
+      <c r="BF27">
+        <v>2.5</v>
+      </c>
+      <c r="BG27">
+        <v>1.69</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.19</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.1</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.19</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.19</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.13</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.69</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.19</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.75</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.75</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>1.68</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28">
+        <v>1.85</v>
+      </c>
+      <c r="G28">
+        <v>1.95</v>
+      </c>
+      <c r="H28">
+        <v>4.4</v>
+      </c>
+      <c r="I28">
+        <v>4.8</v>
+      </c>
+      <c r="J28">
+        <v>3.55</v>
+      </c>
+      <c r="K28">
+        <v>4.4</v>
+      </c>
+      <c r="L28">
+        <v>1.39</v>
+      </c>
+      <c r="M28">
+        <v>1.06</v>
+      </c>
+      <c r="N28">
+        <v>3.6</v>
+      </c>
+      <c r="O28">
+        <v>1.29</v>
+      </c>
+      <c r="P28">
+        <v>2</v>
+      </c>
+      <c r="Q28">
+        <v>1.87</v>
+      </c>
+      <c r="R28">
+        <v>1.38</v>
+      </c>
+      <c r="S28">
+        <v>3.1</v>
+      </c>
+      <c r="T28">
+        <v>1.79</v>
+      </c>
+      <c r="U28">
+        <v>2.14</v>
+      </c>
+      <c r="V28">
+        <v>1.26</v>
+      </c>
+      <c r="W28">
+        <v>2.04</v>
+      </c>
+      <c r="X28">
+        <v>970</v>
+      </c>
+      <c r="Y28">
+        <v>970</v>
+      </c>
+      <c r="Z28">
+        <v>40</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>65</v>
+      </c>
+      <c r="AC28">
+        <v>55</v>
+      </c>
+      <c r="AD28">
+        <v>970</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>12.5</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+      <c r="AH28">
+        <v>970</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>1000</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>42</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>13.5</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>14</v>
+      </c>
+      <c r="AQ28">
+        <v>15</v>
+      </c>
+      <c r="AR28">
+        <v>1.81</v>
+      </c>
+      <c r="AS28">
+        <v>18.5</v>
+      </c>
+      <c r="AT28">
+        <v>8.4</v>
+      </c>
+      <c r="AU28">
+        <v>7.8</v>
+      </c>
+      <c r="AV28">
+        <v>15.5</v>
+      </c>
+      <c r="AW28">
+        <v>1.9</v>
+      </c>
+      <c r="AX28">
+        <v>10.5</v>
+      </c>
+      <c r="AY28">
+        <v>9</v>
+      </c>
+      <c r="AZ28">
+        <v>16</v>
+      </c>
+      <c r="BA28">
+        <v>1.9</v>
+      </c>
+      <c r="BB28">
+        <v>18.5</v>
+      </c>
+      <c r="BC28">
+        <v>17</v>
+      </c>
+      <c r="BD28">
+        <v>1.82</v>
+      </c>
+      <c r="BE28">
+        <v>1.9</v>
+      </c>
+      <c r="BF28">
+        <v>11</v>
+      </c>
+      <c r="BG28">
+        <v>1.9</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.23</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.23</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.23</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.37</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.23</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.23</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.23</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.23</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.23</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.23</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29">
+        <v>1.7</v>
+      </c>
+      <c r="G29">
+        <v>1.9</v>
+      </c>
+      <c r="H29">
+        <v>5.2</v>
+      </c>
+      <c r="I29">
         <v>7.2</v>
       </c>
-      <c r="J13">
+      <c r="J29">
         <v>3.2</v>
       </c>
-      <c r="K13">
+      <c r="K29">
         <v>4.4</v>
       </c>
-      <c r="L13">
+      <c r="L29">
         <v>1.5</v>
       </c>
-      <c r="M13">
-        <v>1.07</v>
-      </c>
-      <c r="N13">
-        <v>2.8</v>
-      </c>
-      <c r="O13">
-        <v>1.46</v>
-      </c>
-      <c r="P13">
+      <c r="M29">
+        <v>1.08</v>
+      </c>
+      <c r="N29">
+        <v>2.98</v>
+      </c>
+      <c r="O29">
+        <v>1.45</v>
+      </c>
+      <c r="P29">
         <v>1.58</v>
       </c>
-      <c r="Q13">
+      <c r="Q29">
         <v>2.32</v>
       </c>
-      <c r="R13">
-        <v>1.21</v>
-      </c>
-      <c r="S13">
-        <v>4.3</v>
-      </c>
-      <c r="T13">
+      <c r="R29">
+        <v>1.2</v>
+      </c>
+      <c r="S29">
+        <v>3.9</v>
+      </c>
+      <c r="T29">
         <v>2.1</v>
       </c>
-      <c r="U13">
+      <c r="U29">
         <v>1.65</v>
       </c>
-      <c r="V13">
-        <v>1.17</v>
-      </c>
-      <c r="W13">
+      <c r="V29">
+        <v>1.18</v>
+      </c>
+      <c r="W29">
         <v>2.1</v>
       </c>
-      <c r="X13">
+      <c r="X29">
         <v>970</v>
       </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
-      <c r="Z13">
-        <v>1000</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
+      <c r="Y29">
+        <v>1000</v>
+      </c>
+      <c r="Z29">
+        <v>1000</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
         <v>970</v>
       </c>
-      <c r="AC13">
+      <c r="AC29">
         <v>970</v>
       </c>
-      <c r="AD13">
-        <v>1000</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
+      <c r="AD29">
+        <v>1000</v>
+      </c>
+      <c r="AE29">
+        <v>1000</v>
+      </c>
+      <c r="AF29">
         <v>970</v>
       </c>
-      <c r="AG13">
+      <c r="AG29">
         <v>950</v>
       </c>
-      <c r="AH13">
-        <v>1000</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>40</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.48</v>
-      </c>
-      <c r="AQ13">
-        <v>1.62</v>
-      </c>
-      <c r="AR13">
-        <v>1.62</v>
-      </c>
-      <c r="AS13">
-        <v>1.62</v>
-      </c>
-      <c r="AT13">
+      <c r="AH29">
+        <v>1000</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>1000</v>
+      </c>
+      <c r="AK29">
+        <v>1000</v>
+      </c>
+      <c r="AL29">
+        <v>1000</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>1000</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
+        <v>1.43</v>
+      </c>
+      <c r="AQ29">
+        <v>1.55</v>
+      </c>
+      <c r="AR29">
+        <v>1.55</v>
+      </c>
+      <c r="AS29">
+        <v>1.55</v>
+      </c>
+      <c r="AT29">
         <v>5.4</v>
       </c>
-      <c r="AU13">
-        <v>5.9</v>
-      </c>
-      <c r="AV13">
-        <v>1.62</v>
-      </c>
-      <c r="AW13">
-        <v>1.62</v>
-      </c>
-      <c r="AX13">
-        <v>1.46</v>
-      </c>
-      <c r="AY13">
-        <v>1.51</v>
-      </c>
-      <c r="AZ13">
-        <v>1.62</v>
-      </c>
-      <c r="BA13">
-        <v>1.62</v>
-      </c>
-      <c r="BB13">
-        <v>1.62</v>
-      </c>
-      <c r="BC13">
-        <v>1.62</v>
-      </c>
-      <c r="BD13">
-        <v>1.62</v>
-      </c>
-      <c r="BE13">
-        <v>1.62</v>
-      </c>
-      <c r="BF13">
-        <v>1.56</v>
-      </c>
-      <c r="BG13">
-        <v>1.62</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.22</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
+      <c r="AU29">
+        <v>1.38</v>
+      </c>
+      <c r="AV29">
+        <v>1.55</v>
+      </c>
+      <c r="AW29">
+        <v>1.55</v>
+      </c>
+      <c r="AX29">
+        <v>1.4</v>
+      </c>
+      <c r="AY29">
+        <v>1.45</v>
+      </c>
+      <c r="AZ29">
+        <v>1.55</v>
+      </c>
+      <c r="BA29">
+        <v>1.55</v>
+      </c>
+      <c r="BB29">
+        <v>1.55</v>
+      </c>
+      <c r="BC29">
+        <v>1.55</v>
+      </c>
+      <c r="BD29">
+        <v>1.55</v>
+      </c>
+      <c r="BE29">
+        <v>1.55</v>
+      </c>
+      <c r="BF29">
+        <v>1.55</v>
+      </c>
+      <c r="BG29">
+        <v>1.55</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
         <v>1.04</v>
       </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
         <v>1.04</v>
       </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
         <v>1.04</v>
       </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
         <v>1.04</v>
       </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
         <v>1.04</v>
       </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
         <v>1.04</v>
       </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
         <v>1.04</v>
       </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
         <v>1.04</v>
       </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
         <v>1.04</v>
       </c>
-      <c r="CB13" t="s">
-        <v>122</v>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.04</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -508,7 +508,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 08:16:12</t>
+    <t>2026-10-05 10:27:43</t>
   </si>
 </sst>
 </file>
@@ -1102,22 +1102,22 @@
         <v>136</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="I2">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.41</v>
@@ -1132,13 +1132,13 @@
         <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q2">
         <v>1.96</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S2">
         <v>3.5</v>
@@ -1147,181 +1147,181 @@
         <v>1.8</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V2">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
         <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB2">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
+        <v>15.5</v>
+      </c>
+      <c r="AE2">
+        <v>46</v>
+      </c>
+      <c r="AF2">
         <v>14.5</v>
       </c>
-      <c r="AE2">
-        <v>120</v>
-      </c>
-      <c r="AF2">
-        <v>48</v>
-      </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>65</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AK2">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AL2">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO2">
+        <v>44</v>
+      </c>
+      <c r="AP2">
+        <v>13</v>
+      </c>
+      <c r="AQ2">
+        <v>12</v>
+      </c>
+      <c r="AR2">
+        <v>22</v>
+      </c>
+      <c r="AS2">
+        <v>55</v>
+      </c>
+      <c r="AT2">
+        <v>8.6</v>
+      </c>
+      <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
+        <v>13</v>
+      </c>
+      <c r="AW2">
         <v>36</v>
       </c>
-      <c r="AP2">
-        <v>10</v>
-      </c>
-      <c r="AQ2">
-        <v>11</v>
-      </c>
-      <c r="AR2">
-        <v>4.3</v>
-      </c>
-      <c r="AS2">
-        <v>4.9</v>
-      </c>
-      <c r="AT2">
-        <v>9.6</v>
-      </c>
-      <c r="AU2">
-        <v>6</v>
-      </c>
-      <c r="AV2">
+      <c r="AX2">
         <v>12</v>
-      </c>
-      <c r="AW2">
-        <v>10.5</v>
-      </c>
-      <c r="AX2">
-        <v>13.5</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BE2">
-        <v>6.8</v>
+        <v>70</v>
       </c>
       <c r="BF2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BG2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI2">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BN2">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2">
         <v>4.5</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS2">
+        <v>5</v>
+      </c>
+      <c r="BT2">
+        <v>7.8</v>
+      </c>
+      <c r="BU2">
+        <v>5.3</v>
+      </c>
+      <c r="BV2">
+        <v>34</v>
+      </c>
+      <c r="BW2">
+        <v>5</v>
+      </c>
+      <c r="BX2">
+        <v>46</v>
+      </c>
+      <c r="BY2">
+        <v>5.2</v>
+      </c>
+      <c r="BZ2">
+        <v>30</v>
+      </c>
+      <c r="CA2">
         <v>4.9</v>
-      </c>
-      <c r="BT2">
-        <v>7.4</v>
-      </c>
-      <c r="BU2">
-        <v>5.1</v>
-      </c>
-      <c r="BV2">
-        <v>32</v>
-      </c>
-      <c r="BW2">
-        <v>4.8</v>
-      </c>
-      <c r="BX2">
-        <v>44</v>
-      </c>
-      <c r="BY2">
-        <v>5.1</v>
-      </c>
-      <c r="BZ2">
-        <v>32</v>
-      </c>
-      <c r="CA2">
-        <v>4.8</v>
       </c>
       <c r="CB2" t="s">
         <v>164</v>
@@ -1344,166 +1344,166 @@
         <v>137</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="I3">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="J3">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
         <v>1.23</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O3">
         <v>1.13</v>
       </c>
       <c r="P3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q3">
         <v>1.43</v>
       </c>
       <c r="R3">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="S3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U3">
         <v>2.7</v>
       </c>
       <c r="V3">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="W3">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X3">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD3">
+        <v>12</v>
+      </c>
+      <c r="AE3">
+        <v>16.5</v>
+      </c>
+      <c r="AF3">
+        <v>46</v>
+      </c>
+      <c r="AG3">
+        <v>21</v>
+      </c>
+      <c r="AH3">
+        <v>18</v>
+      </c>
+      <c r="AI3">
+        <v>25</v>
+      </c>
+      <c r="AJ3">
+        <v>110</v>
+      </c>
+      <c r="AK3">
+        <v>55</v>
+      </c>
+      <c r="AL3">
+        <v>48</v>
+      </c>
+      <c r="AM3">
+        <v>65</v>
+      </c>
+      <c r="AN3">
+        <v>34</v>
+      </c>
+      <c r="AO3">
+        <v>5.9</v>
+      </c>
+      <c r="AP3">
+        <v>23</v>
+      </c>
+      <c r="AQ3">
+        <v>13.5</v>
+      </c>
+      <c r="AR3">
+        <v>12.5</v>
+      </c>
+      <c r="AS3">
+        <v>16</v>
+      </c>
+      <c r="AT3">
+        <v>24</v>
+      </c>
+      <c r="AU3">
+        <v>11</v>
+      </c>
+      <c r="AV3">
+        <v>9.6</v>
+      </c>
+      <c r="AW3">
         <v>13</v>
       </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>1000</v>
-      </c>
-      <c r="AG3">
-        <v>1000</v>
-      </c>
-      <c r="AH3">
-        <v>950</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>4.8</v>
-      </c>
-      <c r="AQ3">
-        <v>3.5</v>
-      </c>
-      <c r="AR3">
-        <v>3.25</v>
-      </c>
-      <c r="AS3">
+      <c r="AX3">
+        <v>36</v>
+      </c>
+      <c r="AY3">
         <v>16.5</v>
       </c>
-      <c r="AT3">
-        <v>1.1</v>
-      </c>
-      <c r="AU3">
-        <v>1.1</v>
-      </c>
-      <c r="AV3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW3">
-        <v>1.1</v>
-      </c>
-      <c r="AX3">
-        <v>1.1</v>
-      </c>
-      <c r="AY3">
-        <v>1.1</v>
-      </c>
       <c r="AZ3">
-        <v>1.09</v>
+        <v>16</v>
       </c>
       <c r="BA3">
-        <v>1.1</v>
+        <v>19.5</v>
       </c>
       <c r="BB3">
-        <v>1.1</v>
+        <v>60</v>
       </c>
       <c r="BC3">
-        <v>1.1</v>
+        <v>34</v>
       </c>
       <c r="BD3">
-        <v>1.1</v>
+        <v>29</v>
       </c>
       <c r="BE3">
-        <v>1.1</v>
+        <v>46</v>
       </c>
       <c r="BF3">
-        <v>1.1</v>
+        <v>22</v>
       </c>
       <c r="BG3">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1592,16 +1592,16 @@
         <v>1.54</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
         <v>4.5</v>
       </c>
       <c r="K4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>1.34</v>
@@ -1610,76 +1610,76 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
         <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
         <v>1.47</v>
       </c>
       <c r="S4">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
         <v>2.84</v>
       </c>
       <c r="X4">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y4">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="Z4">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AA4">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4">
         <v>11</v>
       </c>
       <c r="AD4">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AE4">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL4">
         <v>40</v>
@@ -1688,124 +1688,124 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR4">
-        <v>4.9</v>
+        <v>50</v>
       </c>
       <c r="AS4">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AT4">
+        <v>7.8</v>
+      </c>
+      <c r="AU4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV4">
+        <v>22</v>
+      </c>
+      <c r="AW4">
+        <v>65</v>
+      </c>
+      <c r="AX4">
         <v>8</v>
       </c>
-      <c r="AU4">
-        <v>9</v>
-      </c>
-      <c r="AV4">
-        <v>21</v>
-      </c>
-      <c r="AW4">
+      <c r="AY4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4">
         <v>20</v>
       </c>
-      <c r="AX4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ4">
-        <v>19.5</v>
-      </c>
       <c r="BA4">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="BB4">
         <v>11.5</v>
       </c>
       <c r="BC4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>4.7</v>
+        <v>27</v>
       </c>
       <c r="BE4">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="BF4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG4">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="s">
         <v>164</v>
@@ -1828,19 +1828,19 @@
         <v>139</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I5">
         <v>4.3</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
         <v>3.8</v>
@@ -1849,205 +1849,205 @@
         <v>1.41</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P5">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q5">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="R5">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S5">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T5">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
         <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB5">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
+        <v>10.5</v>
+      </c>
+      <c r="AH5">
+        <v>19</v>
+      </c>
+      <c r="AI5">
+        <v>70</v>
+      </c>
+      <c r="AJ5">
+        <v>26</v>
+      </c>
+      <c r="AK5">
+        <v>23</v>
+      </c>
+      <c r="AL5">
+        <v>36</v>
+      </c>
+      <c r="AM5">
+        <v>120</v>
+      </c>
+      <c r="AN5">
+        <v>17.5</v>
+      </c>
+      <c r="AO5">
+        <v>70</v>
+      </c>
+      <c r="AP5">
+        <v>13</v>
+      </c>
+      <c r="AQ5">
+        <v>13.5</v>
+      </c>
+      <c r="AR5">
+        <v>24</v>
+      </c>
+      <c r="AS5">
+        <v>55</v>
+      </c>
+      <c r="AT5">
+        <v>8.4</v>
+      </c>
+      <c r="AU5">
+        <v>7.4</v>
+      </c>
+      <c r="AV5">
+        <v>15</v>
+      </c>
+      <c r="AW5">
+        <v>42</v>
+      </c>
+      <c r="AX5">
         <v>11.5</v>
       </c>
-      <c r="AH5">
-        <v>970</v>
-      </c>
-      <c r="AI5">
-        <v>50</v>
-      </c>
-      <c r="AJ5">
-        <v>28</v>
-      </c>
-      <c r="AK5">
-        <v>970</v>
-      </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>1.86</v>
-      </c>
-      <c r="AQ5">
-        <v>12</v>
-      </c>
-      <c r="AR5">
-        <v>1.86</v>
-      </c>
-      <c r="AS5">
-        <v>1.86</v>
-      </c>
-      <c r="AT5">
-        <v>1.87</v>
-      </c>
-      <c r="AU5">
+      <c r="AY5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ5">
+        <v>16</v>
+      </c>
+      <c r="BA5">
+        <v>40</v>
+      </c>
+      <c r="BB5">
+        <v>21</v>
+      </c>
+      <c r="BC5">
+        <v>18</v>
+      </c>
+      <c r="BD5">
+        <v>29</v>
+      </c>
+      <c r="BE5">
+        <v>75</v>
+      </c>
+      <c r="BF5">
+        <v>13.5</v>
+      </c>
+      <c r="BG5">
+        <v>34</v>
+      </c>
+      <c r="BH5">
+        <v>3.95</v>
+      </c>
+      <c r="BI5">
+        <v>2.72</v>
+      </c>
+      <c r="BJ5">
+        <v>10.5</v>
+      </c>
+      <c r="BK5">
+        <v>7.4</v>
+      </c>
+      <c r="BL5">
+        <v>150</v>
+      </c>
+      <c r="BM5">
+        <v>7.2</v>
+      </c>
+      <c r="BN5">
+        <v>5</v>
+      </c>
+      <c r="BO5">
+        <v>4.1</v>
+      </c>
+      <c r="BP5">
+        <v>15.5</v>
+      </c>
+      <c r="BQ5">
+        <v>10.5</v>
+      </c>
+      <c r="BR5">
+        <v>30</v>
+      </c>
+      <c r="BS5">
+        <v>6</v>
+      </c>
+      <c r="BT5">
+        <v>7.8</v>
+      </c>
+      <c r="BU5">
+        <v>5.6</v>
+      </c>
+      <c r="BV5">
+        <v>36</v>
+      </c>
+      <c r="BW5">
+        <v>6.2</v>
+      </c>
+      <c r="BX5">
+        <v>46</v>
+      </c>
+      <c r="BY5">
         <v>6.4</v>
       </c>
-      <c r="AV5">
-        <v>1.77</v>
-      </c>
-      <c r="AW5">
-        <v>1.86</v>
-      </c>
-      <c r="AX5">
-        <v>1.98</v>
-      </c>
-      <c r="AY5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5">
-        <v>1.69</v>
-      </c>
-      <c r="BA5">
-        <v>1.79</v>
-      </c>
-      <c r="BB5">
-        <v>1.74</v>
-      </c>
-      <c r="BC5">
-        <v>1.81</v>
-      </c>
-      <c r="BD5">
-        <v>1.86</v>
-      </c>
-      <c r="BE5">
-        <v>1.86</v>
-      </c>
-      <c r="BF5">
-        <v>1.86</v>
-      </c>
-      <c r="BG5">
-        <v>1.83</v>
-      </c>
-      <c r="BH5">
-        <v>4</v>
-      </c>
-      <c r="BI5">
-        <v>2.76</v>
-      </c>
-      <c r="BJ5">
-        <v>11.5</v>
-      </c>
-      <c r="BK5">
-        <v>3.45</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>4.8</v>
-      </c>
-      <c r="BN5">
-        <v>5.6</v>
-      </c>
-      <c r="BO5">
-        <v>3.7</v>
-      </c>
-      <c r="BP5">
-        <v>17.5</v>
-      </c>
-      <c r="BQ5">
-        <v>3.9</v>
-      </c>
-      <c r="BR5">
-        <v>32</v>
-      </c>
-      <c r="BS5">
-        <v>4.3</v>
-      </c>
-      <c r="BT5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU5">
-        <v>5.5</v>
-      </c>
-      <c r="BV5">
-        <v>40</v>
-      </c>
-      <c r="BW5">
-        <v>4.4</v>
-      </c>
-      <c r="BX5">
-        <v>55</v>
-      </c>
-      <c r="BY5">
-        <v>4.5</v>
-      </c>
       <c r="BZ5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="CA5">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="CB5" t="s">
         <v>164</v>
@@ -2070,13 +2070,13 @@
         <v>140</v>
       </c>
       <c r="F6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G6">
         <v>4.7</v>
       </c>
       <c r="H6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>2.04</v>
@@ -2085,7 +2085,7 @@
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
         <v>1.51</v>
@@ -2094,7 +2094,7 @@
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
         <v>1.45</v>
@@ -2115,16 +2115,16 @@
         <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="W6">
         <v>1.27</v>
       </c>
       <c r="X6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y6">
         <v>7.4</v>
@@ -2169,16 +2169,16 @@
         <v>1000</v>
       </c>
       <c r="AM6">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>550</v>
+        <v>470</v>
       </c>
       <c r="AO6">
         <v>21</v>
       </c>
       <c r="AP6">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6">
         <v>6.6</v>
@@ -2202,7 +2202,7 @@
         <v>21</v>
       </c>
       <c r="AX6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY6">
         <v>16.5</v>
@@ -2214,13 +2214,13 @@
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BC6">
         <v>48</v>
       </c>
       <c r="BD6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE6">
         <v>44</v>
@@ -2235,7 +2235,7 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
@@ -2312,184 +2312,184 @@
         <v>141</v>
       </c>
       <c r="F7">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G7">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H7">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="I7">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
+        <v>3.5</v>
+      </c>
+      <c r="L7">
+        <v>1.45</v>
+      </c>
+      <c r="M7">
+        <v>1.09</v>
+      </c>
+      <c r="N7">
+        <v>3.35</v>
+      </c>
+      <c r="O7">
+        <v>1.4</v>
+      </c>
+      <c r="P7">
+        <v>1.78</v>
+      </c>
+      <c r="Q7">
+        <v>2.26</v>
+      </c>
+      <c r="R7">
+        <v>1.3</v>
+      </c>
+      <c r="S7">
         <v>4</v>
       </c>
-      <c r="L7">
-        <v>1.37</v>
-      </c>
-      <c r="M7">
-        <v>1.05</v>
-      </c>
-      <c r="N7">
-        <v>4.6</v>
-      </c>
-      <c r="O7">
-        <v>1.25</v>
-      </c>
-      <c r="P7">
-        <v>2.3</v>
-      </c>
-      <c r="Q7">
-        <v>1.71</v>
-      </c>
-      <c r="R7">
-        <v>1.46</v>
-      </c>
-      <c r="S7">
-        <v>2.94</v>
-      </c>
       <c r="T7">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="U7">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X7">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="Z7">
         <v>26</v>
       </c>
       <c r="AA7">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AB7">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7">
         <v>15.5</v>
       </c>
       <c r="AE7">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AF7">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AG7">
         <v>13</v>
       </c>
       <c r="AH7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
+        <v>40</v>
+      </c>
+      <c r="AK7">
+        <v>32</v>
+      </c>
+      <c r="AL7">
+        <v>60</v>
+      </c>
+      <c r="AM7">
+        <v>150</v>
+      </c>
+      <c r="AN7">
+        <v>28</v>
+      </c>
+      <c r="AO7">
+        <v>65</v>
+      </c>
+      <c r="AP7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ7">
+        <v>9.4</v>
+      </c>
+      <c r="AR7">
+        <v>18.5</v>
+      </c>
+      <c r="AS7">
+        <v>50</v>
+      </c>
+      <c r="AT7">
+        <v>7.6</v>
+      </c>
+      <c r="AU7">
+        <v>6</v>
+      </c>
+      <c r="AV7">
+        <v>11.5</v>
+      </c>
+      <c r="AW7">
+        <v>36</v>
+      </c>
+      <c r="AX7">
+        <v>12</v>
+      </c>
+      <c r="AY7">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7">
+        <v>16</v>
+      </c>
+      <c r="BA7">
+        <v>42</v>
+      </c>
+      <c r="BB7">
+        <v>25</v>
+      </c>
+      <c r="BC7">
+        <v>23</v>
+      </c>
+      <c r="BD7">
         <v>34</v>
       </c>
-      <c r="AK7">
-        <v>28</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>80</v>
-      </c>
-      <c r="AN7">
-        <v>17</v>
-      </c>
-      <c r="AO7">
-        <v>29</v>
-      </c>
-      <c r="AP7">
-        <v>13</v>
-      </c>
-      <c r="AQ7">
-        <v>12</v>
-      </c>
-      <c r="AR7">
-        <v>18</v>
-      </c>
-      <c r="AS7">
-        <v>4.3</v>
-      </c>
-      <c r="AT7">
-        <v>10</v>
-      </c>
-      <c r="AU7">
-        <v>7.2</v>
-      </c>
-      <c r="AV7">
-        <v>10.5</v>
-      </c>
-      <c r="AW7">
-        <v>4.1</v>
-      </c>
-      <c r="AX7">
-        <v>13</v>
-      </c>
-      <c r="AY7">
-        <v>3.4</v>
-      </c>
-      <c r="AZ7">
-        <v>12</v>
-      </c>
-      <c r="BA7">
-        <v>4.2</v>
-      </c>
-      <c r="BB7">
-        <v>23</v>
-      </c>
-      <c r="BC7">
-        <v>16</v>
-      </c>
-      <c r="BD7">
+      <c r="BE7">
+        <v>90</v>
+      </c>
+      <c r="BF7">
         <v>21</v>
       </c>
-      <c r="BE7">
-        <v>4.4</v>
-      </c>
-      <c r="BF7">
-        <v>11.5</v>
-      </c>
       <c r="BG7">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="BN7">
         <v>5.6</v>
@@ -2498,40 +2498,40 @@
         <v>4.2</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ7">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS7">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY7">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ7">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.49</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="s">
         <v>164</v>
@@ -2560,7 +2560,7 @@
         <v>2.2</v>
       </c>
       <c r="H8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I8">
         <v>4.2</v>
@@ -2569,37 +2569,37 @@
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
         <v>1.5</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
         <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R8">
         <v>1.25</v>
       </c>
       <c r="S8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T8">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U8">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="V8">
         <v>1.31</v>
@@ -2608,124 +2608,124 @@
         <v>1.83</v>
       </c>
       <c r="X8">
+        <v>11</v>
+      </c>
+      <c r="Y8">
+        <v>13</v>
+      </c>
+      <c r="Z8">
+        <v>32</v>
+      </c>
+      <c r="AA8">
+        <v>110</v>
+      </c>
+      <c r="AB8">
+        <v>8</v>
+      </c>
+      <c r="AC8">
+        <v>7.8</v>
+      </c>
+      <c r="AD8">
+        <v>18</v>
+      </c>
+      <c r="AE8">
+        <v>75</v>
+      </c>
+      <c r="AF8">
+        <v>13</v>
+      </c>
+      <c r="AG8">
+        <v>11.5</v>
+      </c>
+      <c r="AH8">
+        <v>22</v>
+      </c>
+      <c r="AI8">
+        <v>80</v>
+      </c>
+      <c r="AJ8">
+        <v>29</v>
+      </c>
+      <c r="AK8">
+        <v>28</v>
+      </c>
+      <c r="AL8">
+        <v>110</v>
+      </c>
+      <c r="AM8">
+        <v>170</v>
+      </c>
+      <c r="AN8">
+        <v>23</v>
+      </c>
+      <c r="AO8">
+        <v>95</v>
+      </c>
+      <c r="AP8">
+        <v>9</v>
+      </c>
+      <c r="AQ8">
+        <v>10.5</v>
+      </c>
+      <c r="AR8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS8">
+        <v>10</v>
+      </c>
+      <c r="AT8">
+        <v>6.8</v>
+      </c>
+      <c r="AU8">
+        <v>6.6</v>
+      </c>
+      <c r="AV8">
         <v>14.5</v>
       </c>
-      <c r="Y8">
-        <v>55</v>
-      </c>
-      <c r="Z8">
-        <v>90</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>32</v>
-      </c>
-      <c r="AC8">
-        <v>9</v>
-      </c>
-      <c r="AD8">
+      <c r="AW8">
+        <v>25</v>
+      </c>
+      <c r="AX8">
+        <v>10.5</v>
+      </c>
+      <c r="AY8">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8">
+        <v>17.5</v>
+      </c>
+      <c r="BA8">
+        <v>30</v>
+      </c>
+      <c r="BB8">
         <v>23</v>
       </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>14.5</v>
-      </c>
-      <c r="AG8">
-        <v>14.5</v>
-      </c>
-      <c r="AH8">
-        <v>950</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>250</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ8">
-        <v>2.08</v>
-      </c>
-      <c r="AR8">
-        <v>4.8</v>
-      </c>
-      <c r="AS8">
-        <v>2.34</v>
-      </c>
-      <c r="AT8">
-        <v>6.6</v>
-      </c>
-      <c r="AU8">
-        <v>6.4</v>
-      </c>
-      <c r="AV8">
-        <v>13</v>
-      </c>
-      <c r="AW8">
-        <v>2.34</v>
-      </c>
-      <c r="AX8">
-        <v>3.15</v>
-      </c>
-      <c r="AY8">
+      <c r="BC8">
+        <v>22</v>
+      </c>
+      <c r="BD8">
+        <v>19.5</v>
+      </c>
+      <c r="BE8">
+        <v>9.6</v>
+      </c>
+      <c r="BF8">
+        <v>18.5</v>
+      </c>
+      <c r="BG8">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ8">
-        <v>5.3</v>
-      </c>
-      <c r="BA8">
-        <v>2.34</v>
-      </c>
-      <c r="BB8">
-        <v>2.32</v>
-      </c>
-      <c r="BC8">
-        <v>2.34</v>
-      </c>
-      <c r="BD8">
-        <v>10</v>
-      </c>
-      <c r="BE8">
-        <v>2.34</v>
-      </c>
-      <c r="BF8">
-        <v>2.34</v>
-      </c>
-      <c r="BG8">
-        <v>2.34</v>
-      </c>
       <c r="BH8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI8">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2740,10 +2740,10 @@
         <v>3.8</v>
       </c>
       <c r="BP8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
         <v>1000</v>
@@ -2761,13 +2761,13 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
@@ -2796,46 +2796,46 @@
         <v>143</v>
       </c>
       <c r="F9">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H9">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
-        <v>1.07</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P9">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="R9">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2844,10 +2844,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2961,7 +2961,7 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3038,58 +3038,58 @@
         <v>144</v>
       </c>
       <c r="F10">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="H10">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O10">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="S10">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="T10">
         <v>1.01</v>
       </c>
       <c r="U10">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3200,64 +3200,64 @@
         <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB10" t="s">
         <v>164</v>
@@ -3280,58 +3280,58 @@
         <v>145</v>
       </c>
       <c r="F11">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="G11">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="H11">
+        <v>3.1</v>
+      </c>
+      <c r="I11">
+        <v>4.2</v>
+      </c>
+      <c r="J11">
+        <v>2.48</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>1.5</v>
+      </c>
+      <c r="M11">
+        <v>1.08</v>
+      </c>
+      <c r="N11">
+        <v>2.48</v>
+      </c>
+      <c r="O11">
+        <v>1.29</v>
+      </c>
+      <c r="P11">
+        <v>1.52</v>
+      </c>
+      <c r="Q11">
+        <v>2.6</v>
+      </c>
+      <c r="R11">
+        <v>1.08</v>
+      </c>
+      <c r="S11">
         <v>2.92</v>
       </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
-      <c r="J11">
-        <v>1.75</v>
-      </c>
-      <c r="K11">
-        <v>950</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>1.91</v>
-      </c>
-      <c r="O11">
-        <v>1.01</v>
-      </c>
-      <c r="P11">
-        <v>1.3</v>
-      </c>
-      <c r="Q11">
-        <v>1.71</v>
-      </c>
-      <c r="R11">
-        <v>1.06</v>
-      </c>
-      <c r="S11">
-        <v>1.71</v>
-      </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V11">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
         <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
         <v>1.01</v>
@@ -3522,46 +3522,46 @@
         <v>146</v>
       </c>
       <c r="F12">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="H12">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J12">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>1.07</v>
+        <v>2.56</v>
       </c>
       <c r="O12">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="P12">
-        <v>1.06</v>
+        <v>1.54</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R12">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="S12">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3570,10 +3570,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3630,52 +3630,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3687,7 +3687,7 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3764,46 +3764,46 @@
         <v>147</v>
       </c>
       <c r="F13">
+        <v>2.96</v>
+      </c>
+      <c r="G13">
+        <v>4.1</v>
+      </c>
+      <c r="H13">
+        <v>2.38</v>
+      </c>
+      <c r="I13">
+        <v>3.55</v>
+      </c>
+      <c r="J13">
         <v>1.12</v>
       </c>
-      <c r="G13">
-        <v>3.65</v>
-      </c>
-      <c r="H13">
-        <v>2.26</v>
-      </c>
-      <c r="I13">
-        <v>2.98</v>
-      </c>
-      <c r="J13">
-        <v>2.58</v>
-      </c>
       <c r="K13">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P13">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q13">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="S13">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3812,10 +3812,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4006,22 +4006,22 @@
         <v>148</v>
       </c>
       <c r="F14">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G14">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H14">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I14">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4030,34 +4030,34 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O14">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P14">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q14">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R14">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
         <v>3.25</v>
       </c>
       <c r="T14">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U14">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V14">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4066,16 +4066,16 @@
         <v>1000</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA14">
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AD14">
         <v>1000</v>
@@ -4090,7 +4090,7 @@
         <v>1000</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI14">
         <v>1000</v>
@@ -4114,61 +4114,61 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AR14">
-        <v>1.17</v>
+        <v>13.5</v>
       </c>
       <c r="AS14">
-        <v>1.17</v>
+        <v>23</v>
       </c>
       <c r="AT14">
-        <v>1.09</v>
+        <v>7</v>
       </c>
       <c r="AU14">
-        <v>1.07</v>
+        <v>6</v>
       </c>
       <c r="AV14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AW14">
-        <v>1.17</v>
+        <v>21</v>
       </c>
       <c r="AX14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AY14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AZ14">
-        <v>1.17</v>
+        <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BB14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BC14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BD14">
-        <v>1.17</v>
+        <v>1.84</v>
       </c>
       <c r="BE14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BF14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BG14">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI14">
         <v>1.01</v>
@@ -4177,55 +4177,55 @@
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB14" t="s">
         <v>164</v>
@@ -4248,40 +4248,40 @@
         <v>149</v>
       </c>
       <c r="F15">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G15">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H15">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="I15">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q15">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R15">
         <v>1.28</v>
@@ -4290,16 +4290,16 @@
         <v>3.3</v>
       </c>
       <c r="T15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U15">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4308,16 +4308,16 @@
         <v>1000</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA15">
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD15">
         <v>1000</v>
@@ -4356,58 +4356,58 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4490,58 +4490,58 @@
         <v>150</v>
       </c>
       <c r="F16">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="G16">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="H16">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="I16">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P16">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="Q16">
-        <v>1.21</v>
+        <v>1.68</v>
       </c>
       <c r="R16">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S16">
-        <v>1.97</v>
+        <v>2.66</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V16">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4556,10 +4556,10 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD16">
         <v>1000</v>
@@ -4568,10 +4568,10 @@
         <v>1000</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH16">
         <v>1000</v>
@@ -4592,64 +4592,64 @@
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4732,166 +4732,166 @@
         <v>151</v>
       </c>
       <c r="F17">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="G17">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="H17">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>3.95</v>
       </c>
       <c r="J17">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N17">
-        <v>1.41</v>
+        <v>2.96</v>
       </c>
       <c r="O17">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P17">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R17">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="S17">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V17">
+        <v>1.34</v>
+      </c>
+      <c r="W17">
+        <v>1.59</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>34</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>970</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>40</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.17</v>
+      </c>
+      <c r="AQ17">
+        <v>8.6</v>
+      </c>
+      <c r="AR17">
+        <v>1.13</v>
+      </c>
+      <c r="AS17">
+        <v>1.17</v>
+      </c>
+      <c r="AT17">
+        <v>7.2</v>
+      </c>
+      <c r="AU17">
+        <v>5.4</v>
+      </c>
+      <c r="AV17">
+        <v>9.4</v>
+      </c>
+      <c r="AW17">
+        <v>1.17</v>
+      </c>
+      <c r="AX17">
+        <v>9.4</v>
+      </c>
+      <c r="AY17">
+        <v>7.8</v>
+      </c>
+      <c r="AZ17">
         <v>1.14</v>
       </c>
-      <c r="W17">
-        <v>1.39</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>1000</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17">
-        <v>1.03</v>
-      </c>
-      <c r="AR17">
-        <v>1.03</v>
-      </c>
-      <c r="AS17">
-        <v>1.03</v>
-      </c>
-      <c r="AT17">
-        <v>1.03</v>
-      </c>
-      <c r="AU17">
-        <v>1.03</v>
-      </c>
-      <c r="AV17">
-        <v>1.03</v>
-      </c>
-      <c r="AW17">
-        <v>1.03</v>
-      </c>
-      <c r="AX17">
-        <v>1.03</v>
-      </c>
-      <c r="AY17">
-        <v>1.03</v>
-      </c>
-      <c r="AZ17">
-        <v>1.03</v>
-      </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4974,166 +4974,166 @@
         <v>152</v>
       </c>
       <c r="F18">
+        <v>1.44</v>
+      </c>
+      <c r="G18">
+        <v>1.55</v>
+      </c>
+      <c r="H18">
+        <v>8</v>
+      </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
+      <c r="J18">
+        <v>4.2</v>
+      </c>
+      <c r="K18">
+        <v>5.7</v>
+      </c>
+      <c r="L18">
         <v>1.39</v>
       </c>
-      <c r="G18">
-        <v>1.56</v>
-      </c>
-      <c r="H18">
-        <v>2.78</v>
-      </c>
-      <c r="I18">
-        <v>110</v>
-      </c>
-      <c r="J18">
-        <v>1.12</v>
-      </c>
-      <c r="K18">
-        <v>950</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O18">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P18">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="Q18">
+        <v>1.96</v>
+      </c>
+      <c r="R18">
+        <v>1.33</v>
+      </c>
+      <c r="S18">
+        <v>3.55</v>
+      </c>
+      <c r="T18">
+        <v>2.12</v>
+      </c>
+      <c r="U18">
+        <v>1.63</v>
+      </c>
+      <c r="V18">
+        <v>1.08</v>
+      </c>
+      <c r="W18">
+        <v>2.8</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>970</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>970</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.24</v>
+      </c>
+      <c r="AQ18">
         <v>1.98</v>
       </c>
-      <c r="R18">
-        <v>1.28</v>
-      </c>
-      <c r="S18">
-        <v>3.15</v>
-      </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.01</v>
-      </c>
-      <c r="V18">
-        <v>1.01</v>
-      </c>
-      <c r="W18">
-        <v>2.78</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
-      <c r="AC18">
-        <v>1000</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>1000</v>
-      </c>
-      <c r="AG18">
-        <v>1000</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>1000</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18">
-        <v>1.03</v>
-      </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5216,19 +5216,19 @@
         <v>153</v>
       </c>
       <c r="F19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J19">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="K19">
         <v>950</v>
@@ -5237,37 +5237,37 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="O19">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P19">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R19">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="S19">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U19">
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5324,52 +5324,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5458,46 +5458,46 @@
         <v>154</v>
       </c>
       <c r="F20">
-        <v>1.1</v>
+        <v>1.88</v>
       </c>
       <c r="G20">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H20">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="I20">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K20">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>1.07</v>
+        <v>2.72</v>
       </c>
       <c r="O20">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P20">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R20">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S20">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5506,10 +5506,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5700,46 +5700,46 @@
         <v>155</v>
       </c>
       <c r="F21">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="H21">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="I21">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J21">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N21">
-        <v>1.06</v>
+        <v>2.32</v>
       </c>
       <c r="O21">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P21">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="R21">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="S21">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5748,10 +5748,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5862,64 +5862,64 @@
         <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="CB21" t="s">
         <v>164</v>
@@ -5942,46 +5942,46 @@
         <v>156</v>
       </c>
       <c r="F22">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="G22">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="H22">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="I22">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J22">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N22">
-        <v>1.06</v>
+        <v>2.36</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P22">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="S22">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -5990,10 +5990,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6184,31 +6184,31 @@
         <v>157</v>
       </c>
       <c r="F23">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="G23">
         <v>4.8</v>
       </c>
       <c r="H23">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="I23">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="J23">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O23">
         <v>1.24</v>
@@ -6220,130 +6220,130 @@
         <v>1.72</v>
       </c>
       <c r="R23">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S23">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V23">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="W23">
         <v>1.26</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6426,22 +6426,22 @@
         <v>158</v>
       </c>
       <c r="F24">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
         <v>1000</v>
       </c>
       <c r="H24">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I24">
         <v>1000</v>
       </c>
       <c r="J24">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K24">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6534,52 +6534,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -6910,22 +6910,22 @@
         <v>160</v>
       </c>
       <c r="F26">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="G26">
-        <v>1000</v>
+        <v>1.54</v>
       </c>
       <c r="H26">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="I26">
         <v>1000</v>
       </c>
       <c r="J26">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="K26">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -6934,22 +6934,22 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.12</v>
+        <v>2.52</v>
       </c>
       <c r="O26">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P26">
-        <v>1.12</v>
+        <v>2.52</v>
       </c>
       <c r="Q26">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="R26">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="S26">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -6961,7 +6961,7 @@
         <v>1.02</v>
       </c>
       <c r="W26">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7018,52 +7018,52 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF26">
         <v>1.01</v>
@@ -7152,19 +7152,19 @@
         <v>161</v>
       </c>
       <c r="F27">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G27">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I27">
         <v>5.2</v>
       </c>
       <c r="J27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K27">
         <v>3.6</v>
@@ -7173,25 +7173,25 @@
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N27">
         <v>3</v>
       </c>
       <c r="O27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P27">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q27">
         <v>2.08</v>
       </c>
       <c r="R27">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S27">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T27">
         <v>1.82</v>
@@ -7203,7 +7203,7 @@
         <v>1.24</v>
       </c>
       <c r="W27">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="X27">
         <v>970</v>
@@ -7260,16 +7260,16 @@
         <v>930</v>
       </c>
       <c r="AP27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AQ27">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AR27">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AS27">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AT27">
         <v>2.36</v>
@@ -7278,40 +7278,40 @@
         <v>2.3</v>
       </c>
       <c r="AV27">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AW27">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AX27">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="AY27">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AZ27">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="BA27">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BB27">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BC27">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="BD27">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="BE27">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="BF27">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BG27">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7394,10 +7394,10 @@
         <v>162</v>
       </c>
       <c r="F28">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G28">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H28">
         <v>4.4</v>
@@ -7406,10 +7406,10 @@
         <v>4.8</v>
       </c>
       <c r="J28">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K28">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L28">
         <v>1.39</v>
@@ -7418,88 +7418,88 @@
         <v>1.06</v>
       </c>
       <c r="N28">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O28">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P28">
         <v>2</v>
       </c>
       <c r="Q28">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R28">
         <v>1.38</v>
       </c>
       <c r="S28">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U28">
         <v>2.14</v>
       </c>
       <c r="V28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X28">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y28">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z28">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB28">
-        <v>65</v>
+        <v>9.4</v>
       </c>
       <c r="AC28">
-        <v>55</v>
+        <v>8.6</v>
       </c>
       <c r="AD28">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG28">
         <v>10</v>
       </c>
       <c r="AH28">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL28">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN28">
         <v>13.5</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP28">
         <v>14</v>
@@ -7508,10 +7508,10 @@
         <v>15</v>
       </c>
       <c r="AR28">
-        <v>1.81</v>
+        <v>15</v>
       </c>
       <c r="AS28">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="AT28">
         <v>8.4</v>
@@ -7523,7 +7523,7 @@
         <v>15.5</v>
       </c>
       <c r="AW28">
-        <v>1.9</v>
+        <v>21</v>
       </c>
       <c r="AX28">
         <v>10.5</v>
@@ -7535,7 +7535,7 @@
         <v>16</v>
       </c>
       <c r="BA28">
-        <v>1.9</v>
+        <v>24</v>
       </c>
       <c r="BB28">
         <v>18.5</v>
@@ -7544,16 +7544,16 @@
         <v>17</v>
       </c>
       <c r="BD28">
-        <v>1.82</v>
+        <v>15</v>
       </c>
       <c r="BE28">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="BF28">
         <v>11</v>
       </c>
       <c r="BG28">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7565,13 +7565,13 @@
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="BN28">
         <v>1000</v>
@@ -7583,37 +7583,37 @@
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="s">
         <v>164</v>
@@ -7636,7 +7636,7 @@
         <v>163</v>
       </c>
       <c r="F29">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="G29">
         <v>1.9</v>
@@ -7645,43 +7645,43 @@
         <v>5.2</v>
       </c>
       <c r="I29">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J29">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
         <v>1.5</v>
       </c>
       <c r="M29">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N29">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O29">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P29">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q29">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S29">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="T29">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U29">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V29">
         <v>1.18</v>
@@ -7690,13 +7690,13 @@
         <v>2.1</v>
       </c>
       <c r="X29">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA29">
         <v>1000</v>
@@ -7708,7 +7708,7 @@
         <v>970</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE29">
         <v>1000</v>
@@ -7717,16 +7717,16 @@
         <v>970</v>
       </c>
       <c r="AG29">
+        <v>13.5</v>
+      </c>
+      <c r="AH29">
         <v>950</v>
       </c>
-      <c r="AH29">
-        <v>1000</v>
-      </c>
       <c r="AI29">
         <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK29">
         <v>1000</v>
@@ -7738,70 +7738,70 @@
         <v>1000</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO29">
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>1.43</v>
+        <v>2.22</v>
       </c>
       <c r="AQ29">
-        <v>1.55</v>
+        <v>2.46</v>
       </c>
       <c r="AR29">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="AS29">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="AT29">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU29">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="AV29">
-        <v>1.55</v>
+        <v>5.2</v>
       </c>
       <c r="AW29">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="AX29">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="AY29">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="AZ29">
-        <v>1.55</v>
+        <v>5.8</v>
       </c>
       <c r="BA29">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="BB29">
-        <v>1.55</v>
+        <v>2.72</v>
       </c>
       <c r="BC29">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BD29">
-        <v>1.55</v>
+        <v>16.5</v>
       </c>
       <c r="BE29">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="BF29">
-        <v>1.55</v>
+        <v>2.56</v>
       </c>
       <c r="BG29">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
@@ -7819,7 +7819,7 @@
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BP29">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="172">
   <si>
     <t>League</t>
   </si>
@@ -280,6 +280,9 @@
     <t>Slovenian 2 SNL</t>
   </si>
   <si>
+    <t>Peruvian Segunda Division</t>
+  </si>
+  <si>
     <t>Argentinian Primera C</t>
   </si>
   <si>
@@ -322,12 +325,18 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
     <t>20:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>21:00:00</t>
   </si>
   <si>
@@ -364,54 +373,60 @@
     <t>Changchun Xidu</t>
   </si>
   <si>
+    <t>Shanghai Second</t>
+  </si>
+  <si>
     <t>Beijing Tech FC</t>
   </si>
   <si>
     <t>Qingdao Red Lions</t>
   </si>
   <si>
-    <t>Shanghai Second</t>
-  </si>
-  <si>
     <t>Hubei Istar</t>
   </si>
   <si>
+    <t>Wuxi Wugou</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Wuxi Wugou</t>
+    <t>Guangdong Mingtu</t>
+  </si>
+  <si>
+    <t>Hangzhou Linping Wuyue</t>
+  </si>
+  <si>
+    <t>Guizhou Zhucheng Athletic</t>
   </si>
   <si>
     <t>Jiangxi Dingnan United</t>
   </si>
   <si>
+    <t>Nantong Zhiyun F.C</t>
+  </si>
+  <si>
     <t>Shijiazhuang Gongfu FC</t>
   </si>
   <si>
-    <t>Nantong Zhiyun F.C</t>
-  </si>
-  <si>
     <t>Shenzhen 2028</t>
   </si>
   <si>
-    <t>Guizhou Zhucheng Athletic</t>
-  </si>
-  <si>
-    <t>Guangdong Mingtu</t>
-  </si>
-  <si>
-    <t>Hangzhou Linping Wuyue</t>
-  </si>
-  <si>
     <t>NK Bilje</t>
   </si>
   <si>
+    <t>Pirata FC</t>
+  </si>
+  <si>
     <t>CA Claypole</t>
   </si>
   <si>
     <t>Club Sportivo Ameliano</t>
   </si>
   <si>
+    <t>Uni San Martin</t>
+  </si>
+  <si>
     <t>St Vincent &amp; Grenadines</t>
   </si>
   <si>
@@ -448,54 +463,60 @@
     <t>Guangzhou Alpha</t>
   </si>
   <si>
+    <t>Wenzhou Professional</t>
+  </si>
+  <si>
     <t>Chengdu Rongcheng II</t>
   </si>
   <si>
     <t>Wuhan Three Towns II</t>
   </si>
   <si>
-    <t>Wenzhou Professional</t>
-  </si>
-  <si>
     <t>Lanzhou Longyuan Athletic</t>
   </si>
   <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
-    <t>Suzhou Dongwu</t>
+    <t>Dalian Yingbo II</t>
+  </si>
+  <si>
+    <t>Xian Chongde Ronghai</t>
+  </si>
+  <si>
+    <t>Shanghai Port B</t>
   </si>
   <si>
     <t>Meizhou Hakka</t>
   </si>
   <si>
+    <t>Ningbo Professional</t>
+  </si>
+  <si>
     <t>Dalian Kun City FC</t>
   </si>
   <si>
-    <t>Ningbo Professional</t>
-  </si>
-  <si>
     <t>Shandong Taishan B</t>
   </si>
   <si>
-    <t>Shanghai Port B</t>
-  </si>
-  <si>
-    <t>Dalian Yingbo II</t>
-  </si>
-  <si>
-    <t>Xian Chongde Ronghai</t>
-  </si>
-  <si>
     <t>NK Jadran Dekani</t>
   </si>
   <si>
+    <t>Ayacucho Futbol Club</t>
+  </si>
+  <si>
     <t>Deportivo Espanol</t>
   </si>
   <si>
     <t>Rubio Nu</t>
   </si>
   <si>
+    <t>Alianza Universidad</t>
+  </si>
+  <si>
     <t>Sint Maarten</t>
   </si>
   <si>
@@ -508,7 +529,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 10:27:43</t>
+    <t>2026-10-05 12:39:35</t>
   </si>
 </sst>
 </file>
@@ -840,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB29"/>
+  <dimension ref="A1:CB31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1090,22 +1111,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H2">
         <v>3.45</v>
@@ -1138,7 +1159,7 @@
         <v>1.96</v>
       </c>
       <c r="R2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S2">
         <v>3.5</v>
@@ -1153,7 +1174,7 @@
         <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1168,7 +1189,7 @@
         <v>75</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
@@ -1180,7 +1201,7 @@
         <v>46</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1204,7 +1225,7 @@
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO2">
         <v>44</v>
@@ -1222,7 +1243,7 @@
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
@@ -1252,7 +1273,7 @@
         <v>20</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE2">
         <v>70</v>
@@ -1261,7 +1282,7 @@
         <v>15</v>
       </c>
       <c r="BG2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH2">
         <v>3.8</v>
@@ -1303,7 +1324,7 @@
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
         <v>34</v>
@@ -1324,7 +1345,7 @@
         <v>4.9</v>
       </c>
       <c r="CB2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1332,28 +1353,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F3">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G3">
         <v>4.9</v>
       </c>
       <c r="H3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="I3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J3">
         <v>5.1</v>
@@ -1374,10 +1395,10 @@
         <v>1.13</v>
       </c>
       <c r="P3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R3">
         <v>1.88</v>
@@ -1386,28 +1407,28 @@
         <v>2.06</v>
       </c>
       <c r="T3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U3">
         <v>2.7</v>
       </c>
       <c r="V3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="W3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X3">
         <v>42</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z3">
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AB3">
         <v>30</v>
@@ -1422,16 +1443,16 @@
         <v>16.5</v>
       </c>
       <c r="AF3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AG3">
         <v>21</v>
       </c>
       <c r="AH3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ3">
         <v>110</v>
@@ -1440,34 +1461,34 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM3">
         <v>65</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AP3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR3">
         <v>12.5</v>
       </c>
       <c r="AS3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT3">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AU3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV3">
         <v>9.6</v>
@@ -1476,10 +1497,10 @@
         <v>13</v>
       </c>
       <c r="AX3">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="AY3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ3">
         <v>16</v>
@@ -1488,22 +1509,22 @@
         <v>19.5</v>
       </c>
       <c r="BB3">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="BC3">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BD3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE3">
-        <v>46</v>
+        <v>7.6</v>
       </c>
       <c r="BF3">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BG3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1566,7 +1587,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1574,22 +1595,22 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F4">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G4">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -1598,163 +1619,163 @@
         <v>8.4</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L4">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q4">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S4">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="U4">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="V4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W4">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="X4">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y4">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="Z4">
         <v>85</v>
       </c>
       <c r="AA4">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="AB4">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE4">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF4">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
+        <v>12</v>
+      </c>
+      <c r="AK4">
+        <v>18</v>
+      </c>
+      <c r="AL4">
+        <v>44</v>
+      </c>
+      <c r="AM4">
+        <v>200</v>
+      </c>
+      <c r="AN4">
+        <v>8</v>
+      </c>
+      <c r="AO4">
+        <v>230</v>
+      </c>
+      <c r="AP4">
         <v>14.5</v>
       </c>
-      <c r="AK4">
-        <v>16.5</v>
-      </c>
-      <c r="AL4">
-        <v>40</v>
-      </c>
-      <c r="AM4">
-        <v>150</v>
-      </c>
-      <c r="AN4">
-        <v>7.4</v>
-      </c>
-      <c r="AO4">
-        <v>170</v>
-      </c>
-      <c r="AP4">
-        <v>15.5</v>
-      </c>
       <c r="AQ4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR4">
         <v>50</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AW4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AY4">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA4">
         <v>55</v>
       </c>
       <c r="BB4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD4">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="BF4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="BH4">
         <v>3.95</v>
       </c>
       <c r="BI4">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BK4">
         <v>5.7</v>
@@ -1763,13 +1784,13 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN4">
         <v>4</v>
       </c>
       <c r="BO4">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BP4">
         <v>9</v>
@@ -1781,34 +1802,34 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU4">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1816,16 +1837,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F5">
         <v>2.02</v>
@@ -1840,40 +1861,40 @@
         <v>4.3</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K5">
+        <v>3.65</v>
+      </c>
+      <c r="L5">
+        <v>1.43</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>3.65</v>
+      </c>
+      <c r="O5">
+        <v>1.36</v>
+      </c>
+      <c r="P5">
+        <v>1.87</v>
+      </c>
+      <c r="Q5">
+        <v>2.08</v>
+      </c>
+      <c r="R5">
+        <v>1.33</v>
+      </c>
+      <c r="S5">
         <v>3.8</v>
       </c>
-      <c r="L5">
-        <v>1.41</v>
-      </c>
-      <c r="M5">
-        <v>1.07</v>
-      </c>
-      <c r="N5">
-        <v>3.9</v>
-      </c>
-      <c r="O5">
-        <v>1.33</v>
-      </c>
-      <c r="P5">
-        <v>1.97</v>
-      </c>
-      <c r="Q5">
-        <v>1.98</v>
-      </c>
-      <c r="R5">
-        <v>1.37</v>
-      </c>
-      <c r="S5">
-        <v>3.5</v>
-      </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U5">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
         <v>1.3</v>
@@ -1882,28 +1903,28 @@
         <v>1.92</v>
       </c>
       <c r="X5">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF5">
         <v>12.5</v>
@@ -1912,103 +1933,103 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
         <v>26</v>
       </c>
       <c r="AK5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AO5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR5">
         <v>24</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
         <v>15</v>
       </c>
       <c r="AW5">
+        <v>36</v>
+      </c>
+      <c r="AX5">
+        <v>11</v>
+      </c>
+      <c r="AY5">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5">
+        <v>17</v>
+      </c>
+      <c r="BA5">
         <v>42</v>
-      </c>
-      <c r="AX5">
-        <v>11.5</v>
-      </c>
-      <c r="AY5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ5">
-        <v>16</v>
-      </c>
-      <c r="BA5">
-        <v>40</v>
       </c>
       <c r="BB5">
         <v>21</v>
       </c>
       <c r="BC5">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH5">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL5">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="BM5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
         <v>4.1</v>
@@ -2017,40 +2038,40 @@
         <v>15.5</v>
       </c>
       <c r="BQ5">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BT5">
         <v>7.8</v>
       </c>
       <c r="BU5">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW5">
+        <v>6.6</v>
+      </c>
+      <c r="BX5">
+        <v>50</v>
+      </c>
+      <c r="BY5">
+        <v>6.8</v>
+      </c>
+      <c r="BZ5">
+        <v>30</v>
+      </c>
+      <c r="CA5">
         <v>6.2</v>
       </c>
-      <c r="BX5">
-        <v>46</v>
-      </c>
-      <c r="BY5">
-        <v>6.4</v>
-      </c>
-      <c r="BZ5">
-        <v>26</v>
-      </c>
-      <c r="CA5">
-        <v>5.9</v>
-      </c>
       <c r="CB5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2058,16 +2079,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F6">
         <v>4.5</v>
@@ -2076,7 +2097,7 @@
         <v>4.7</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I6">
         <v>2.04</v>
@@ -2100,7 +2121,7 @@
         <v>1.45</v>
       </c>
       <c r="P6">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q6">
         <v>2.38</v>
@@ -2112,10 +2133,10 @@
         <v>4.7</v>
       </c>
       <c r="T6">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
         <v>1.96</v>
@@ -2124,7 +2145,7 @@
         <v>1.27</v>
       </c>
       <c r="X6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y6">
         <v>7.4</v>
@@ -2136,7 +2157,7 @@
         <v>25</v>
       </c>
       <c r="AB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
         <v>7.8</v>
@@ -2148,7 +2169,7 @@
         <v>26</v>
       </c>
       <c r="AF6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG6">
         <v>20</v>
@@ -2157,22 +2178,22 @@
         <v>23</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN6">
-        <v>470</v>
+        <v>110</v>
       </c>
       <c r="AO6">
         <v>21</v>
@@ -2181,7 +2202,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR6">
         <v>10</v>
@@ -2202,7 +2223,7 @@
         <v>21</v>
       </c>
       <c r="AX6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY6">
         <v>16.5</v>
@@ -2211,22 +2232,22 @@
         <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB6">
         <v>65</v>
       </c>
       <c r="BC6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BD6">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE6">
+        <v>65</v>
+      </c>
+      <c r="BF6">
         <v>44</v>
-      </c>
-      <c r="BF6">
-        <v>36</v>
       </c>
       <c r="BG6">
         <v>17</v>
@@ -2241,13 +2262,13 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BN6">
         <v>1000</v>
@@ -2259,40 +2280,40 @@
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="CB6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2300,43 +2321,43 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G7">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M7">
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
         <v>1.4</v>
@@ -2345,43 +2366,43 @@
         <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T7">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
         <v>15.5</v>
@@ -2390,55 +2411,55 @@
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI7">
         <v>80</v>
       </c>
       <c r="AJ7">
+        <v>38</v>
+      </c>
+      <c r="AK7">
         <v>40</v>
       </c>
-      <c r="AK7">
-        <v>32</v>
-      </c>
       <c r="AL7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM7">
         <v>150</v>
       </c>
       <c r="AN7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO7">
         <v>65</v>
       </c>
       <c r="AP7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS7">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT7">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW7">
         <v>36</v>
@@ -2447,10 +2468,10 @@
         <v>12</v>
       </c>
       <c r="AY7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
         <v>42</v>
@@ -2459,10 +2480,10 @@
         <v>25</v>
       </c>
       <c r="BC7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE7">
         <v>90</v>
@@ -2474,67 +2495,67 @@
         <v>32</v>
       </c>
       <c r="BH7">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BI7">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
+        <v>10.5</v>
+      </c>
+      <c r="BN7">
+        <v>5.3</v>
+      </c>
+      <c r="BO7">
+        <v>4.5</v>
+      </c>
+      <c r="BP7">
+        <v>19</v>
+      </c>
+      <c r="BQ7">
         <v>7</v>
       </c>
-      <c r="BN7">
-        <v>5.6</v>
-      </c>
-      <c r="BO7">
-        <v>4.2</v>
-      </c>
-      <c r="BP7">
-        <v>20</v>
-      </c>
-      <c r="BQ7">
-        <v>6</v>
-      </c>
       <c r="BR7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BT7">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV7">
         <v>32</v>
       </c>
       <c r="BW7">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2542,28 +2563,28 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G8">
         <v>2.2</v>
       </c>
       <c r="H8">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2578,7 +2599,7 @@
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
         <v>1.44</v>
@@ -2596,13 +2617,13 @@
         <v>4.5</v>
       </c>
       <c r="T8">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U8">
         <v>1.88</v>
       </c>
       <c r="V8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
         <v>1.83</v>
@@ -2611,10 +2632,10 @@
         <v>11</v>
       </c>
       <c r="Y8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA8">
         <v>110</v>
@@ -2626,10 +2647,10 @@
         <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE8">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF8">
         <v>13</v>
@@ -2641,40 +2662,40 @@
         <v>22</v>
       </c>
       <c r="AI8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK8">
         <v>28</v>
       </c>
       <c r="AL8">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AM8">
         <v>170</v>
       </c>
       <c r="AN8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO8">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AS8">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AT8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU8">
         <v>6.6</v>
@@ -2683,19 +2704,19 @@
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
       </c>
       <c r="AY8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA8">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BB8">
         <v>23</v>
@@ -2704,19 +2725,19 @@
         <v>22</v>
       </c>
       <c r="BD8">
+        <v>34</v>
+      </c>
+      <c r="BE8">
+        <v>100</v>
+      </c>
+      <c r="BF8">
         <v>19.5</v>
       </c>
-      <c r="BE8">
-        <v>9.6</v>
-      </c>
-      <c r="BF8">
-        <v>18.5</v>
-      </c>
       <c r="BG8">
-        <v>9.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BH8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI8">
         <v>2.68</v>
@@ -2725,13 +2746,13 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN8">
         <v>4.9</v>
@@ -2743,13 +2764,13 @@
         <v>18</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT8">
         <v>7.6</v>
@@ -2761,22 +2782,22 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="CB8" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2784,64 +2805,64 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F9">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H9">
         <v>2.74</v>
       </c>
       <c r="I9">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="J9">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="K9">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="L9">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O9">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="P9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q9">
         <v>2.66</v>
       </c>
       <c r="R9">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S9">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V9">
         <v>1.42</v>
@@ -2850,58 +2871,58 @@
         <v>1.42</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP9">
         <v>1.03</v>
@@ -3018,7 +3039,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3026,59 +3047,59 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F10">
-        <v>4.1</v>
+        <v>1.95</v>
       </c>
       <c r="G10">
-        <v>6.4</v>
+        <v>2.36</v>
       </c>
       <c r="H10">
-        <v>1.8</v>
+        <v>3.85</v>
       </c>
       <c r="I10">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="J10">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
+        <v>1.12</v>
+      </c>
+      <c r="N10">
+        <v>2.32</v>
+      </c>
+      <c r="O10">
+        <v>1.13</v>
+      </c>
+      <c r="P10">
         <v>1.04</v>
       </c>
-      <c r="N10">
+      <c r="Q10">
+        <v>2.42</v>
+      </c>
+      <c r="R10">
+        <v>1.07</v>
+      </c>
+      <c r="S10">
         <v>3.05</v>
       </c>
-      <c r="O10">
-        <v>1.37</v>
-      </c>
-      <c r="P10">
-        <v>1.7</v>
-      </c>
-      <c r="Q10">
-        <v>2.08</v>
-      </c>
-      <c r="R10">
-        <v>1.17</v>
-      </c>
-      <c r="S10">
-        <v>2.68</v>
-      </c>
       <c r="T10">
         <v>1.01</v>
       </c>
@@ -3086,10 +3107,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.96</v>
+        <v>1.22</v>
       </c>
       <c r="W10">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3200,67 +3221,67 @@
         <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3268,241 +3289,241 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F11">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="H11">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="I11">
-        <v>4.2</v>
+        <v>2.04</v>
       </c>
       <c r="J11">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.08</v>
       </c>
       <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11">
+        <v>1.37</v>
+      </c>
+      <c r="P11">
+        <v>1.69</v>
+      </c>
+      <c r="Q11">
+        <v>2.08</v>
+      </c>
+      <c r="R11">
+        <v>1.26</v>
+      </c>
+      <c r="S11">
+        <v>3.3</v>
+      </c>
+      <c r="T11">
+        <v>1.91</v>
+      </c>
+      <c r="U11">
+        <v>1.83</v>
+      </c>
+      <c r="V11">
+        <v>1.96</v>
+      </c>
+      <c r="W11">
+        <v>1.2</v>
+      </c>
+      <c r="X11">
+        <v>14.5</v>
+      </c>
+      <c r="Y11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z11">
+        <v>13.5</v>
+      </c>
+      <c r="AA11">
+        <v>27</v>
+      </c>
+      <c r="AB11">
+        <v>18.5</v>
+      </c>
+      <c r="AC11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD11">
+        <v>12.5</v>
+      </c>
+      <c r="AE11">
+        <v>27</v>
+      </c>
+      <c r="AF11">
+        <v>46</v>
+      </c>
+      <c r="AG11">
+        <v>25</v>
+      </c>
+      <c r="AH11">
+        <v>27</v>
+      </c>
+      <c r="AI11">
+        <v>55</v>
+      </c>
+      <c r="AJ11">
+        <v>160</v>
+      </c>
+      <c r="AK11">
+        <v>95</v>
+      </c>
+      <c r="AL11">
+        <v>110</v>
+      </c>
+      <c r="AM11">
+        <v>180</v>
+      </c>
+      <c r="AN11">
+        <v>130</v>
+      </c>
+      <c r="AO11">
+        <v>20</v>
+      </c>
+      <c r="AP11">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11">
+        <v>1.03</v>
+      </c>
+      <c r="AR11">
+        <v>1.03</v>
+      </c>
+      <c r="AS11">
+        <v>1.03</v>
+      </c>
+      <c r="AT11">
+        <v>1.03</v>
+      </c>
+      <c r="AU11">
+        <v>1.03</v>
+      </c>
+      <c r="AV11">
+        <v>1.03</v>
+      </c>
+      <c r="AW11">
+        <v>1.03</v>
+      </c>
+      <c r="AX11">
+        <v>1.03</v>
+      </c>
+      <c r="AY11">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11">
+        <v>1.03</v>
+      </c>
+      <c r="BA11">
+        <v>1.03</v>
+      </c>
+      <c r="BB11">
+        <v>1.03</v>
+      </c>
+      <c r="BC11">
+        <v>1.03</v>
+      </c>
+      <c r="BD11">
+        <v>1.03</v>
+      </c>
+      <c r="BE11">
+        <v>1.03</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>12</v>
+      </c>
+      <c r="BH11">
+        <v>3.55</v>
+      </c>
+      <c r="BI11">
         <v>2.48</v>
       </c>
-      <c r="O11">
-        <v>1.29</v>
-      </c>
-      <c r="P11">
-        <v>1.52</v>
-      </c>
-      <c r="Q11">
-        <v>2.6</v>
-      </c>
-      <c r="R11">
-        <v>1.08</v>
-      </c>
-      <c r="S11">
-        <v>2.92</v>
-      </c>
-      <c r="T11">
-        <v>2.14</v>
-      </c>
-      <c r="U11">
-        <v>1.61</v>
-      </c>
-      <c r="V11">
-        <v>1.33</v>
-      </c>
-      <c r="W11">
-        <v>1.52</v>
-      </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
-      <c r="Y11">
-        <v>1000</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>1000</v>
-      </c>
-      <c r="AC11">
-        <v>1000</v>
-      </c>
-      <c r="AD11">
-        <v>1000</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>1000</v>
-      </c>
-      <c r="AG11">
-        <v>1000</v>
-      </c>
-      <c r="AH11">
-        <v>1000</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>1000</v>
-      </c>
-      <c r="AK11">
-        <v>1000</v>
-      </c>
-      <c r="AL11">
-        <v>1000</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>1000</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
-        <v>1.03</v>
-      </c>
-      <c r="AQ11">
-        <v>1.03</v>
-      </c>
-      <c r="AR11">
-        <v>1.03</v>
-      </c>
-      <c r="AS11">
-        <v>1.03</v>
-      </c>
-      <c r="AT11">
-        <v>1.03</v>
-      </c>
-      <c r="AU11">
-        <v>1.03</v>
-      </c>
-      <c r="AV11">
-        <v>1.03</v>
-      </c>
-      <c r="AW11">
-        <v>1.03</v>
-      </c>
-      <c r="AX11">
-        <v>1.03</v>
-      </c>
-      <c r="AY11">
-        <v>1.03</v>
-      </c>
-      <c r="AZ11">
-        <v>1.03</v>
-      </c>
-      <c r="BA11">
-        <v>1.03</v>
-      </c>
-      <c r="BB11">
-        <v>1.03</v>
-      </c>
-      <c r="BC11">
-        <v>1.03</v>
-      </c>
-      <c r="BD11">
-        <v>1.03</v>
-      </c>
-      <c r="BE11">
-        <v>1.03</v>
-      </c>
-      <c r="BF11">
-        <v>1.01</v>
-      </c>
-      <c r="BG11">
-        <v>1.01</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.01</v>
-      </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3510,124 +3531,124 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F12">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="G12">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="H12">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="I12">
+        <v>4.4</v>
+      </c>
+      <c r="J12">
+        <v>2.74</v>
+      </c>
+      <c r="K12">
+        <v>3.65</v>
+      </c>
+      <c r="L12">
+        <v>1.5</v>
+      </c>
+      <c r="M12">
+        <v>1.13</v>
+      </c>
+      <c r="N12">
+        <v>2.26</v>
+      </c>
+      <c r="O12">
+        <v>1.49</v>
+      </c>
+      <c r="P12">
+        <v>1.43</v>
+      </c>
+      <c r="Q12">
+        <v>2.6</v>
+      </c>
+      <c r="R12">
+        <v>1.14</v>
+      </c>
+      <c r="S12">
+        <v>2.94</v>
+      </c>
+      <c r="T12">
+        <v>1.97</v>
+      </c>
+      <c r="U12">
+        <v>1.6</v>
+      </c>
+      <c r="V12">
+        <v>1.31</v>
+      </c>
+      <c r="W12">
+        <v>1.54</v>
+      </c>
+      <c r="X12">
+        <v>9.4</v>
+      </c>
+      <c r="Y12">
+        <v>10.5</v>
+      </c>
+      <c r="Z12">
+        <v>26</v>
+      </c>
+      <c r="AA12">
+        <v>100</v>
+      </c>
+      <c r="AB12">
+        <v>7.8</v>
+      </c>
+      <c r="AC12">
+        <v>7.6</v>
+      </c>
+      <c r="AD12">
+        <v>18</v>
+      </c>
+      <c r="AE12">
+        <v>80</v>
+      </c>
+      <c r="AF12">
+        <v>16</v>
+      </c>
+      <c r="AG12">
+        <v>14</v>
+      </c>
+      <c r="AH12">
+        <v>30</v>
+      </c>
+      <c r="AI12">
         <v>110</v>
       </c>
-      <c r="J12">
-        <v>1.12</v>
-      </c>
-      <c r="K12">
-        <v>3.45</v>
-      </c>
-      <c r="L12">
-        <v>1.55</v>
-      </c>
-      <c r="M12">
-        <v>1.08</v>
-      </c>
-      <c r="N12">
-        <v>2.56</v>
-      </c>
-      <c r="O12">
-        <v>1.09</v>
-      </c>
-      <c r="P12">
-        <v>1.54</v>
-      </c>
-      <c r="Q12">
-        <v>2.46</v>
-      </c>
-      <c r="R12">
-        <v>1.15</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-      <c r="T12">
-        <v>1.01</v>
-      </c>
-      <c r="U12">
-        <v>1.01</v>
-      </c>
-      <c r="V12">
-        <v>1.21</v>
-      </c>
-      <c r="W12">
-        <v>1.74</v>
-      </c>
-      <c r="X12">
-        <v>1000</v>
-      </c>
-      <c r="Y12">
-        <v>1000</v>
-      </c>
-      <c r="Z12">
-        <v>1000</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>1000</v>
-      </c>
-      <c r="AC12">
-        <v>1000</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP12">
         <v>1.03</v>
@@ -3678,16 +3699,16 @@
         <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3744,7 +3765,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3752,22 +3773,22 @@
         <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F13">
         <v>2.96</v>
       </c>
       <c r="G13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="H13">
         <v>2.38</v>
@@ -3776,10 +3797,10 @@
         <v>3.55</v>
       </c>
       <c r="J13">
-        <v>1.12</v>
+        <v>2.06</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3788,19 +3809,19 @@
         <v>1.08</v>
       </c>
       <c r="N13">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P13">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="R13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S13">
         <v>2.82</v>
@@ -3809,7 +3830,7 @@
         <v>1.01</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V13">
         <v>1.43</v>
@@ -3986,7 +4007,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3994,181 +4015,181 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F14">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="G14">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I14">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P14">
         <v>1.83</v>
       </c>
       <c r="Q14">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S14">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T14">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="U14">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z14">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB14">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>11</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>11.5</v>
       </c>
       <c r="AR14">
+        <v>5.8</v>
+      </c>
+      <c r="AS14">
+        <v>6.8</v>
+      </c>
+      <c r="AT14">
+        <v>8</v>
+      </c>
+      <c r="AU14">
+        <v>6.8</v>
+      </c>
+      <c r="AV14">
         <v>13.5</v>
       </c>
-      <c r="AS14">
-        <v>23</v>
-      </c>
-      <c r="AT14">
+      <c r="AW14">
+        <v>6.6</v>
+      </c>
+      <c r="AX14">
+        <v>11.5</v>
+      </c>
+      <c r="AY14">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14">
+        <v>16</v>
+      </c>
+      <c r="BA14">
+        <v>6.6</v>
+      </c>
+      <c r="BB14">
+        <v>6</v>
+      </c>
+      <c r="BC14">
+        <v>21</v>
+      </c>
+      <c r="BD14">
+        <v>6.4</v>
+      </c>
+      <c r="BE14">
         <v>7</v>
       </c>
-      <c r="AU14">
-        <v>6</v>
-      </c>
-      <c r="AV14">
-        <v>1.33</v>
-      </c>
-      <c r="AW14">
-        <v>21</v>
-      </c>
-      <c r="AX14">
-        <v>1.33</v>
-      </c>
-      <c r="AY14">
-        <v>1.33</v>
-      </c>
-      <c r="AZ14">
-        <v>12.5</v>
-      </c>
-      <c r="BA14">
-        <v>1.33</v>
-      </c>
-      <c r="BB14">
-        <v>1.33</v>
-      </c>
-      <c r="BC14">
-        <v>1.33</v>
-      </c>
-      <c r="BD14">
-        <v>1.84</v>
-      </c>
-      <c r="BE14">
-        <v>1.33</v>
-      </c>
       <c r="BF14">
-        <v>1.33</v>
+        <v>16</v>
       </c>
       <c r="BG14">
-        <v>1.33</v>
+        <v>6.6</v>
       </c>
       <c r="BH14">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
         <v>1.01</v>
@@ -4177,58 +4198,58 @@
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4236,178 +4257,178 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F15">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G15">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H15">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I15">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O15">
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T15">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="U15">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z15">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB15">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC15">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP15">
-        <v>1.23</v>
+        <v>12</v>
       </c>
       <c r="AQ15">
+        <v>12</v>
+      </c>
+      <c r="AR15">
+        <v>4.3</v>
+      </c>
+      <c r="AS15">
+        <v>4.7</v>
+      </c>
+      <c r="AT15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU15">
+        <v>7</v>
+      </c>
+      <c r="AV15">
+        <v>14</v>
+      </c>
+      <c r="AW15">
+        <v>4.6</v>
+      </c>
+      <c r="AX15">
+        <v>11</v>
+      </c>
+      <c r="AY15">
         <v>9.4</v>
       </c>
-      <c r="AR15">
-        <v>1.19</v>
-      </c>
-      <c r="AS15">
-        <v>1.23</v>
-      </c>
-      <c r="AT15">
-        <v>1.13</v>
-      </c>
-      <c r="AU15">
-        <v>6.4</v>
-      </c>
-      <c r="AV15">
-        <v>12</v>
-      </c>
-      <c r="AW15">
-        <v>1.23</v>
-      </c>
-      <c r="AX15">
-        <v>1.23</v>
-      </c>
-      <c r="AY15">
-        <v>1.23</v>
-      </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA15">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="BB15">
-        <v>16.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC15">
+        <v>19.5</v>
+      </c>
+      <c r="BD15">
+        <v>4.5</v>
+      </c>
+      <c r="BE15">
+        <v>4.7</v>
+      </c>
+      <c r="BF15">
         <v>14.5</v>
       </c>
-      <c r="BD15">
-        <v>1.23</v>
-      </c>
-      <c r="BE15">
-        <v>1.23</v>
-      </c>
-      <c r="BF15">
-        <v>1.23</v>
-      </c>
       <c r="BG15">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4470,320 +4491,320 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F16">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="G16">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="H16">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J16">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="O16">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="P16">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="Q16">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>1.46</v>
+        <v>1.07</v>
       </c>
       <c r="S16">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T16">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="U16">
-        <v>2.24</v>
+        <v>1.67</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W16">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16">
         <v>21</v>
       </c>
-      <c r="AC16">
-        <v>970</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF16">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AG16">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN16">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP16">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="CB16" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F17">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="G17">
-        <v>2.72</v>
+        <v>5.2</v>
       </c>
       <c r="H17">
+        <v>2.06</v>
+      </c>
+      <c r="I17">
+        <v>2.46</v>
+      </c>
+      <c r="J17">
+        <v>2.78</v>
+      </c>
+      <c r="K17">
+        <v>3.35</v>
+      </c>
+      <c r="L17">
+        <v>1.47</v>
+      </c>
+      <c r="M17">
+        <v>1.08</v>
+      </c>
+      <c r="N17">
+        <v>2.36</v>
+      </c>
+      <c r="O17">
+        <v>1.31</v>
+      </c>
+      <c r="P17">
+        <v>1.45</v>
+      </c>
+      <c r="Q17">
+        <v>2.5</v>
+      </c>
+      <c r="R17">
+        <v>1.07</v>
+      </c>
+      <c r="S17">
         <v>3</v>
       </c>
-      <c r="I17">
-        <v>3.95</v>
-      </c>
-      <c r="J17">
-        <v>2.92</v>
-      </c>
-      <c r="K17">
-        <v>3.95</v>
-      </c>
-      <c r="L17">
-        <v>1.45</v>
-      </c>
-      <c r="M17">
-        <v>1.1</v>
-      </c>
-      <c r="N17">
-        <v>2.96</v>
-      </c>
-      <c r="O17">
-        <v>1.4</v>
-      </c>
-      <c r="P17">
-        <v>1.65</v>
-      </c>
-      <c r="Q17">
-        <v>2.14</v>
-      </c>
-      <c r="R17">
-        <v>1.27</v>
-      </c>
-      <c r="S17">
-        <v>3.7</v>
-      </c>
       <c r="T17">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="W17">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4792,7 +4813,7 @@
         <v>1000</v>
       </c>
       <c r="Z17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
         <v>1000</v>
@@ -4801,7 +4822,7 @@
         <v>1000</v>
       </c>
       <c r="AC17">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
         <v>1000</v>
@@ -4816,7 +4837,7 @@
         <v>1000</v>
       </c>
       <c r="AH17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
         <v>1000</v>
@@ -4840,58 +4861,58 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4954,78 +4975,78 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F18">
+        <v>1.89</v>
+      </c>
+      <c r="G18">
+        <v>2.14</v>
+      </c>
+      <c r="H18">
+        <v>3.95</v>
+      </c>
+      <c r="I18">
+        <v>6.8</v>
+      </c>
+      <c r="J18">
+        <v>2.66</v>
+      </c>
+      <c r="K18">
+        <v>3.55</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
+        <v>2.2</v>
+      </c>
+      <c r="O18">
+        <v>1.23</v>
+      </c>
+      <c r="P18">
         <v>1.44</v>
       </c>
-      <c r="G18">
-        <v>1.55</v>
-      </c>
-      <c r="H18">
-        <v>8</v>
-      </c>
-      <c r="I18">
-        <v>17</v>
-      </c>
-      <c r="J18">
-        <v>4.2</v>
-      </c>
-      <c r="K18">
-        <v>5.7</v>
-      </c>
-      <c r="L18">
-        <v>1.39</v>
-      </c>
-      <c r="M18">
-        <v>1.05</v>
-      </c>
-      <c r="N18">
-        <v>3.35</v>
-      </c>
-      <c r="O18">
-        <v>1.34</v>
-      </c>
-      <c r="P18">
-        <v>1.83</v>
-      </c>
       <c r="Q18">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="R18">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="S18">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="T18">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U18">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V18">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="W18">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5040,7 +5061,7 @@
         <v>1000</v>
       </c>
       <c r="AB18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
         <v>1000</v>
@@ -5052,7 +5073,7 @@
         <v>1000</v>
       </c>
       <c r="AF18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
         <v>1000</v>
@@ -5082,58 +5103,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5196,428 +5217,428 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>2.12</v>
+      </c>
+      <c r="H19">
+        <v>3.7</v>
+      </c>
+      <c r="I19">
+        <v>4.2</v>
+      </c>
+      <c r="J19">
+        <v>3.8</v>
+      </c>
+      <c r="K19">
+        <v>4.2</v>
+      </c>
+      <c r="L19">
+        <v>1.28</v>
+      </c>
+      <c r="M19">
+        <v>1.05</v>
+      </c>
+      <c r="N19">
+        <v>4.5</v>
+      </c>
+      <c r="O19">
+        <v>1.24</v>
+      </c>
+      <c r="P19">
+        <v>2.16</v>
+      </c>
+      <c r="Q19">
+        <v>1.71</v>
+      </c>
+      <c r="R19">
+        <v>1.49</v>
+      </c>
+      <c r="S19">
+        <v>2.66</v>
+      </c>
+      <c r="T19">
+        <v>1.66</v>
+      </c>
+      <c r="U19">
+        <v>2.32</v>
+      </c>
+      <c r="V19">
+        <v>1.32</v>
+      </c>
+      <c r="W19">
+        <v>1.9</v>
+      </c>
+      <c r="X19">
+        <v>21</v>
+      </c>
+      <c r="Y19">
+        <v>21</v>
+      </c>
+      <c r="Z19">
+        <v>32</v>
+      </c>
+      <c r="AA19">
         <v>85</v>
       </c>
-      <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" t="s">
-        <v>153</v>
-      </c>
-      <c r="F19">
-        <v>1.12</v>
-      </c>
-      <c r="G19">
-        <v>2.72</v>
-      </c>
-      <c r="H19">
-        <v>1.12</v>
-      </c>
-      <c r="I19">
-        <v>110</v>
-      </c>
-      <c r="J19">
-        <v>3.3</v>
-      </c>
-      <c r="K19">
-        <v>950</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.04</v>
-      </c>
-      <c r="N19">
-        <v>1.02</v>
-      </c>
-      <c r="O19">
-        <v>1.31</v>
-      </c>
-      <c r="P19">
-        <v>1.29</v>
-      </c>
-      <c r="Q19">
-        <v>1.44</v>
-      </c>
-      <c r="R19">
-        <v>1.12</v>
-      </c>
-      <c r="S19">
-        <v>3.2</v>
-      </c>
-      <c r="T19">
-        <v>1.72</v>
-      </c>
-      <c r="U19">
-        <v>1.01</v>
-      </c>
-      <c r="V19">
-        <v>1.35</v>
-      </c>
-      <c r="W19">
-        <v>1.61</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB19" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F20">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="G20">
-        <v>2.42</v>
+        <v>1.5</v>
       </c>
       <c r="H20">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="I20">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="J20">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="K20">
+        <v>5.2</v>
+      </c>
+      <c r="L20">
+        <v>1.39</v>
+      </c>
+      <c r="M20">
+        <v>1.07</v>
+      </c>
+      <c r="N20">
         <v>3.55</v>
       </c>
-      <c r="L20">
-        <v>1.43</v>
-      </c>
-      <c r="M20">
-        <v>1.06</v>
-      </c>
-      <c r="N20">
-        <v>2.72</v>
-      </c>
       <c r="O20">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="P20">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="Q20">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="R20">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="S20">
-        <v>2.54</v>
+        <v>3.55</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V20">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="W20">
-        <v>1.7</v>
+        <v>2.98</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5680,249 +5701,249 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F21">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G21">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H21">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I21">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="J21">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K21">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M21">
         <v>1.09</v>
       </c>
       <c r="N21">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="O21">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="P21">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="Q21">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="R21">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="S21">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH21">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5930,70 +5951,70 @@
         <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F22">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="G22">
-        <v>5.2</v>
+        <v>110</v>
       </c>
       <c r="H22">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I22">
-        <v>2.46</v>
+        <v>990</v>
       </c>
       <c r="J22">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="K22">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="L22">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
-        <v>2.36</v>
+        <v>1.1</v>
       </c>
       <c r="O22">
         <v>1.31</v>
       </c>
       <c r="P22">
-        <v>1.45</v>
+        <v>1.07</v>
       </c>
       <c r="Q22">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="R22">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="S22">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.23</v>
+        <v>1.59</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6164,7 +6185,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6172,16 +6193,16 @@
         <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F23">
         <v>3.7</v>
@@ -6190,16 +6211,16 @@
         <v>4.8</v>
       </c>
       <c r="H23">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I23">
         <v>2.12</v>
       </c>
       <c r="J23">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6235,7 +6256,7 @@
         <v>1.89</v>
       </c>
       <c r="W23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X23">
         <v>19</v>
@@ -6247,7 +6268,7 @@
         <v>15.5</v>
       </c>
       <c r="AA23">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB23">
         <v>18.5</v>
@@ -6259,7 +6280,7 @@
         <v>12.5</v>
       </c>
       <c r="AE23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF23">
         <v>36</v>
@@ -6271,7 +6292,7 @@
         <v>20</v>
       </c>
       <c r="AI23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ23">
         <v>95</v>
@@ -6283,7 +6304,7 @@
         <v>60</v>
       </c>
       <c r="AM23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN23">
         <v>55</v>
@@ -6304,7 +6325,7 @@
         <v>20</v>
       </c>
       <c r="AT23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU23">
         <v>6.8</v>
@@ -6316,7 +6337,7 @@
         <v>17</v>
       </c>
       <c r="AX23">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY23">
         <v>13.5</v>
@@ -6325,22 +6346,22 @@
         <v>13</v>
       </c>
       <c r="BA23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB23">
+        <v>5</v>
+      </c>
+      <c r="BC23">
         <v>4.8</v>
       </c>
-      <c r="BC23">
-        <v>4.6</v>
-      </c>
       <c r="BD23">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE23">
+        <v>5</v>
+      </c>
+      <c r="BF23">
         <v>4.8</v>
-      </c>
-      <c r="BF23">
-        <v>4.6</v>
       </c>
       <c r="BG23">
         <v>10</v>
@@ -6406,7 +6427,7 @@
         <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6414,34 +6435,34 @@
         <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F24">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="G24">
         <v>1000</v>
       </c>
       <c r="H24">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="I24">
         <v>1000</v>
       </c>
       <c r="J24">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6465,7 +6486,7 @@
         <v>1.08</v>
       </c>
       <c r="S24">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6534,52 +6555,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -6648,7 +6669,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6656,70 +6677,70 @@
         <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M25">
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="O25">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="P25">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q25">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="R25">
         <v>1.08</v>
       </c>
       <c r="S25">
-        <v>1.38</v>
+        <v>1.03</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U25">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6776,52 +6797,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -6830,102 +6851,102 @@
         <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI25">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>26</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>18</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F26">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -6934,34 +6955,34 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>2.52</v>
+        <v>1.1</v>
       </c>
       <c r="O26">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="P26">
-        <v>2.52</v>
+        <v>1.09</v>
       </c>
       <c r="Q26">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="R26">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="S26">
-        <v>2.14</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W26">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7018,52 +7039,52 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
         <v>1.01</v>
@@ -7075,548 +7096,548 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F27">
-        <v>1.96</v>
+        <v>1.1</v>
       </c>
       <c r="G27">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="H27">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="I27">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J27">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>1.08</v>
       </c>
       <c r="O27">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P27">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="Q27">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="R27">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="S27">
-        <v>3.55</v>
+        <v>1.31</v>
       </c>
       <c r="T27">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W27">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
         <v>1000</v>
       </c>
       <c r="AB27">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>930</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>1.72</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>2.36</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>1.84</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>2.34</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>1.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F28">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="G28">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="H28">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="I28">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="J28">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L28">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>2.52</v>
+      </c>
+      <c r="O28">
+        <v>1.14</v>
+      </c>
+      <c r="P28">
+        <v>2.52</v>
+      </c>
+      <c r="Q28">
+        <v>1.43</v>
+      </c>
+      <c r="R28">
+        <v>1.58</v>
+      </c>
+      <c r="S28">
+        <v>2.14</v>
+      </c>
+      <c r="T28">
+        <v>1.11</v>
+      </c>
+      <c r="U28">
+        <v>1.11</v>
+      </c>
+      <c r="V28">
         <v>1.06</v>
       </c>
-      <c r="N28">
-        <v>3.95</v>
-      </c>
-      <c r="O28">
-        <v>1.31</v>
-      </c>
-      <c r="P28">
-        <v>2</v>
-      </c>
-      <c r="Q28">
-        <v>1.89</v>
-      </c>
-      <c r="R28">
-        <v>1.38</v>
-      </c>
-      <c r="S28">
-        <v>3.3</v>
-      </c>
-      <c r="T28">
-        <v>1.8</v>
-      </c>
-      <c r="U28">
-        <v>2.14</v>
-      </c>
-      <c r="V28">
-        <v>1.27</v>
-      </c>
       <c r="W28">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="X28">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR28">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS28">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT28">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU28">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV28">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW28">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX28">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY28">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA28">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BB28">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC28">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD28">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BE28">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BF28">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7624,241 +7645,725 @@
         <v>90</v>
       </c>
       <c r="B29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" t="s">
+        <v>168</v>
+      </c>
+      <c r="F29">
+        <v>1.95</v>
+      </c>
+      <c r="G29">
+        <v>2.1</v>
+      </c>
+      <c r="H29">
+        <v>4.4</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>3.15</v>
+      </c>
+      <c r="K29">
+        <v>3.6</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.1</v>
+      </c>
+      <c r="N29">
+        <v>3.1</v>
+      </c>
+      <c r="O29">
+        <v>1.4</v>
+      </c>
+      <c r="P29">
+        <v>1.7</v>
+      </c>
+      <c r="Q29">
+        <v>2.18</v>
+      </c>
+      <c r="R29">
+        <v>1.27</v>
+      </c>
+      <c r="S29">
+        <v>4.1</v>
+      </c>
+      <c r="T29">
+        <v>1.92</v>
+      </c>
+      <c r="U29">
+        <v>1.9</v>
+      </c>
+      <c r="V29">
+        <v>1.25</v>
+      </c>
+      <c r="W29">
+        <v>1.9</v>
+      </c>
+      <c r="X29">
+        <v>12</v>
+      </c>
+      <c r="Y29">
+        <v>15</v>
+      </c>
+      <c r="Z29">
+        <v>36</v>
+      </c>
+      <c r="AA29">
+        <v>990</v>
+      </c>
+      <c r="AB29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC29">
+        <v>8</v>
+      </c>
+      <c r="AD29">
+        <v>20</v>
+      </c>
+      <c r="AE29">
+        <v>90</v>
+      </c>
+      <c r="AF29">
+        <v>12.5</v>
+      </c>
+      <c r="AG29">
+        <v>11</v>
+      </c>
+      <c r="AH29">
+        <v>22</v>
+      </c>
+      <c r="AI29">
+        <v>90</v>
+      </c>
+      <c r="AJ29">
+        <v>27</v>
+      </c>
+      <c r="AK29">
+        <v>26</v>
+      </c>
+      <c r="AL29">
+        <v>65</v>
+      </c>
+      <c r="AM29">
+        <v>990</v>
+      </c>
+      <c r="AN29">
+        <v>23</v>
+      </c>
+      <c r="AO29">
+        <v>920</v>
+      </c>
+      <c r="AP29">
+        <v>9.6</v>
+      </c>
+      <c r="AQ29">
+        <v>12</v>
+      </c>
+      <c r="AR29">
+        <v>7.4</v>
+      </c>
+      <c r="AS29">
+        <v>8</v>
+      </c>
+      <c r="AT29">
+        <v>6.6</v>
+      </c>
+      <c r="AU29">
+        <v>6.6</v>
+      </c>
+      <c r="AV29">
+        <v>16</v>
+      </c>
+      <c r="AW29">
+        <v>7.6</v>
+      </c>
+      <c r="AX29">
+        <v>10</v>
+      </c>
+      <c r="AY29">
+        <v>9</v>
+      </c>
+      <c r="AZ29">
+        <v>17</v>
+      </c>
+      <c r="BA29">
+        <v>7.6</v>
+      </c>
+      <c r="BB29">
+        <v>19</v>
+      </c>
+      <c r="BC29">
+        <v>18.5</v>
+      </c>
+      <c r="BD29">
+        <v>7.6</v>
+      </c>
+      <c r="BE29">
+        <v>8</v>
+      </c>
+      <c r="BF29">
+        <v>16.5</v>
+      </c>
+      <c r="BG29">
+        <v>7.8</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>1.19</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>1.1</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.19</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.19</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.13</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.69</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.19</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.75</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.75</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.68</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
         <v>91</v>
       </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29">
-        <v>1.81</v>
-      </c>
-      <c r="G29">
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" t="s">
+        <v>169</v>
+      </c>
+      <c r="F30">
+        <v>1.88</v>
+      </c>
+      <c r="G30">
+        <v>1.96</v>
+      </c>
+      <c r="H30">
+        <v>4.4</v>
+      </c>
+      <c r="I30">
+        <v>4.7</v>
+      </c>
+      <c r="J30">
+        <v>3.75</v>
+      </c>
+      <c r="K30">
+        <v>4.1</v>
+      </c>
+      <c r="L30">
+        <v>1.42</v>
+      </c>
+      <c r="M30">
+        <v>1.06</v>
+      </c>
+      <c r="N30">
+        <v>3.95</v>
+      </c>
+      <c r="O30">
+        <v>1.31</v>
+      </c>
+      <c r="P30">
+        <v>2</v>
+      </c>
+      <c r="Q30">
         <v>1.9</v>
       </c>
-      <c r="H29">
+      <c r="R30">
+        <v>1.39</v>
+      </c>
+      <c r="S30">
+        <v>3.3</v>
+      </c>
+      <c r="T30">
+        <v>1.8</v>
+      </c>
+      <c r="U30">
+        <v>2.14</v>
+      </c>
+      <c r="V30">
+        <v>1.27</v>
+      </c>
+      <c r="W30">
+        <v>2.04</v>
+      </c>
+      <c r="X30">
+        <v>16</v>
+      </c>
+      <c r="Y30">
+        <v>17</v>
+      </c>
+      <c r="Z30">
+        <v>36</v>
+      </c>
+      <c r="AA30">
+        <v>120</v>
+      </c>
+      <c r="AB30">
+        <v>9.4</v>
+      </c>
+      <c r="AC30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD30">
+        <v>18</v>
+      </c>
+      <c r="AE30">
+        <v>60</v>
+      </c>
+      <c r="AF30">
+        <v>12</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
+      </c>
+      <c r="AH30">
+        <v>18.5</v>
+      </c>
+      <c r="AI30">
+        <v>75</v>
+      </c>
+      <c r="AJ30">
+        <v>26</v>
+      </c>
+      <c r="AK30">
+        <v>24</v>
+      </c>
+      <c r="AL30">
+        <v>34</v>
+      </c>
+      <c r="AM30">
+        <v>120</v>
+      </c>
+      <c r="AN30">
+        <v>13</v>
+      </c>
+      <c r="AO30">
+        <v>75</v>
+      </c>
+      <c r="AP30">
+        <v>14</v>
+      </c>
+      <c r="AQ30">
+        <v>15</v>
+      </c>
+      <c r="AR30">
+        <v>8.6</v>
+      </c>
+      <c r="AS30">
+        <v>10</v>
+      </c>
+      <c r="AT30">
+        <v>8.4</v>
+      </c>
+      <c r="AU30">
+        <v>7.8</v>
+      </c>
+      <c r="AV30">
+        <v>15.5</v>
+      </c>
+      <c r="AW30">
+        <v>20</v>
+      </c>
+      <c r="AX30">
+        <v>10.5</v>
+      </c>
+      <c r="AY30">
+        <v>9</v>
+      </c>
+      <c r="AZ30">
+        <v>16</v>
+      </c>
+      <c r="BA30">
+        <v>22</v>
+      </c>
+      <c r="BB30">
+        <v>18.5</v>
+      </c>
+      <c r="BC30">
+        <v>17</v>
+      </c>
+      <c r="BD30">
+        <v>8.4</v>
+      </c>
+      <c r="BE30">
+        <v>32</v>
+      </c>
+      <c r="BF30">
+        <v>11</v>
+      </c>
+      <c r="BG30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH30">
+        <v>3.4</v>
+      </c>
+      <c r="BI30">
+        <v>3.15</v>
+      </c>
+      <c r="BJ30">
+        <v>10</v>
+      </c>
+      <c r="BK30">
+        <v>6.4</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>15.5</v>
+      </c>
+      <c r="BN30">
+        <v>4.6</v>
+      </c>
+      <c r="BO30">
+        <v>4.2</v>
+      </c>
+      <c r="BP30">
+        <v>13.5</v>
+      </c>
+      <c r="BQ30">
+        <v>10</v>
+      </c>
+      <c r="BR30">
+        <v>28</v>
+      </c>
+      <c r="BS30">
+        <v>10.5</v>
+      </c>
+      <c r="BT30">
+        <v>7.8</v>
+      </c>
+      <c r="BU30">
+        <v>7</v>
+      </c>
+      <c r="BV30">
+        <v>38</v>
+      </c>
+      <c r="BW30">
+        <v>12</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>13</v>
+      </c>
+      <c r="BZ30">
+        <v>25</v>
+      </c>
+      <c r="CA30">
+        <v>10</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31">
+        <v>1.78</v>
+      </c>
+      <c r="G31">
+        <v>1.88</v>
+      </c>
+      <c r="H31">
         <v>5.2</v>
       </c>
-      <c r="I29">
+      <c r="I31">
         <v>6.6</v>
       </c>
-      <c r="J29">
-        <v>3.35</v>
-      </c>
-      <c r="K29">
-        <v>3.7</v>
-      </c>
-      <c r="L29">
+      <c r="J31">
+        <v>3.4</v>
+      </c>
+      <c r="K31">
+        <v>4.1</v>
+      </c>
+      <c r="L31">
         <v>1.5</v>
       </c>
-      <c r="M29">
-        <v>1.11</v>
-      </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-      <c r="O29">
+      <c r="M31">
+        <v>1.07</v>
+      </c>
+      <c r="N31">
+        <v>2.76</v>
+      </c>
+      <c r="O31">
         <v>1.46</v>
       </c>
-      <c r="P29">
-        <v>1.59</v>
-      </c>
-      <c r="Q29">
-        <v>2.4</v>
-      </c>
-      <c r="R29">
-        <v>1.22</v>
-      </c>
-      <c r="S29">
+      <c r="P31">
+        <v>1.58</v>
+      </c>
+      <c r="Q31">
+        <v>2.34</v>
+      </c>
+      <c r="R31">
+        <v>1.21</v>
+      </c>
+      <c r="S31">
         <v>4.4</v>
       </c>
-      <c r="T29">
-        <v>2.2</v>
-      </c>
-      <c r="U29">
-        <v>1.67</v>
-      </c>
-      <c r="V29">
-        <v>1.18</v>
-      </c>
-      <c r="W29">
-        <v>2.1</v>
-      </c>
-      <c r="X29">
+      <c r="T31">
+        <v>2.12</v>
+      </c>
+      <c r="U31">
+        <v>1.64</v>
+      </c>
+      <c r="V31">
+        <v>1.19</v>
+      </c>
+      <c r="W31">
+        <v>2.12</v>
+      </c>
+      <c r="X31">
+        <v>970</v>
+      </c>
+      <c r="Y31">
+        <v>950</v>
+      </c>
+      <c r="Z31">
+        <v>150</v>
+      </c>
+      <c r="AA31">
+        <v>1000</v>
+      </c>
+      <c r="AB31">
+        <v>9.6</v>
+      </c>
+      <c r="AC31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD31">
+        <v>950</v>
+      </c>
+      <c r="AE31">
+        <v>1000</v>
+      </c>
+      <c r="AF31">
         <v>11</v>
       </c>
-      <c r="Y29">
-        <v>20</v>
-      </c>
-      <c r="Z29">
-        <v>130</v>
-      </c>
-      <c r="AA29">
-        <v>1000</v>
-      </c>
-      <c r="AB29">
-        <v>970</v>
-      </c>
-      <c r="AC29">
-        <v>970</v>
-      </c>
-      <c r="AD29">
+      <c r="AG31">
+        <v>17</v>
+      </c>
+      <c r="AH31">
         <v>950</v>
       </c>
-      <c r="AE29">
-        <v>1000</v>
-      </c>
-      <c r="AF29">
-        <v>970</v>
-      </c>
-      <c r="AG29">
-        <v>13.5</v>
-      </c>
-      <c r="AH29">
-        <v>950</v>
-      </c>
-      <c r="AI29">
-        <v>1000</v>
-      </c>
-      <c r="AJ29">
-        <v>90</v>
-      </c>
-      <c r="AK29">
-        <v>1000</v>
-      </c>
-      <c r="AL29">
-        <v>1000</v>
-      </c>
-      <c r="AM29">
-        <v>1000</v>
-      </c>
-      <c r="AN29">
-        <v>29</v>
-      </c>
-      <c r="AO29">
-        <v>1000</v>
-      </c>
-      <c r="AP29">
-        <v>2.22</v>
-      </c>
-      <c r="AQ29">
-        <v>2.46</v>
-      </c>
-      <c r="AR29">
-        <v>6.8</v>
-      </c>
-      <c r="AS29">
-        <v>2.8</v>
-      </c>
-      <c r="AT29">
-        <v>6.2</v>
-      </c>
-      <c r="AU29">
-        <v>2.14</v>
-      </c>
-      <c r="AV29">
-        <v>5.2</v>
-      </c>
-      <c r="AW29">
-        <v>2.8</v>
-      </c>
-      <c r="AX29">
-        <v>2.16</v>
-      </c>
-      <c r="AY29">
-        <v>2.3</v>
-      </c>
-      <c r="AZ29">
-        <v>5.8</v>
-      </c>
-      <c r="BA29">
-        <v>2.8</v>
-      </c>
-      <c r="BB29">
-        <v>2.72</v>
-      </c>
-      <c r="BC29">
-        <v>7.8</v>
-      </c>
-      <c r="BD29">
-        <v>16.5</v>
-      </c>
-      <c r="BE29">
-        <v>2.8</v>
-      </c>
-      <c r="BF29">
-        <v>2.56</v>
-      </c>
-      <c r="BG29">
-        <v>2.8</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>1.27</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
-      </c>
-      <c r="BK29">
+      <c r="AI31">
+        <v>1000</v>
+      </c>
+      <c r="AJ31">
+        <v>140</v>
+      </c>
+      <c r="AK31">
+        <v>1000</v>
+      </c>
+      <c r="AL31">
+        <v>1000</v>
+      </c>
+      <c r="AM31">
+        <v>1000</v>
+      </c>
+      <c r="AN31">
+        <v>42</v>
+      </c>
+      <c r="AO31">
+        <v>1000</v>
+      </c>
+      <c r="AP31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ31">
+        <v>1.91</v>
+      </c>
+      <c r="AR31">
+        <v>4.9</v>
+      </c>
+      <c r="AS31">
+        <v>1.96</v>
+      </c>
+      <c r="AT31">
+        <v>5.9</v>
+      </c>
+      <c r="AU31">
+        <v>1.63</v>
+      </c>
+      <c r="AV31">
+        <v>3.9</v>
+      </c>
+      <c r="AW31">
+        <v>1.96</v>
+      </c>
+      <c r="AX31">
+        <v>7.2</v>
+      </c>
+      <c r="AY31">
+        <v>1.75</v>
+      </c>
+      <c r="AZ31">
+        <v>4.4</v>
+      </c>
+      <c r="BA31">
+        <v>1.96</v>
+      </c>
+      <c r="BB31">
+        <v>12</v>
+      </c>
+      <c r="BC31">
+        <v>1.96</v>
+      </c>
+      <c r="BD31">
+        <v>9.6</v>
+      </c>
+      <c r="BE31">
+        <v>1.96</v>
+      </c>
+      <c r="BF31">
+        <v>1.87</v>
+      </c>
+      <c r="BG31">
+        <v>1.96</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.26</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
         <v>1.04</v>
       </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
         <v>1.04</v>
       </c>
-      <c r="BN29">
-        <v>1000</v>
-      </c>
-      <c r="BO29">
-        <v>1.5</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.48</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
         <v>1.04</v>
       </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
         <v>1.04</v>
       </c>
-      <c r="BT29">
-        <v>1000</v>
-      </c>
-      <c r="BU29">
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
         <v>1.04</v>
       </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
         <v>1.04</v>
       </c>
-      <c r="BX29">
-        <v>1000</v>
-      </c>
-      <c r="BY29">
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
         <v>1.04</v>
       </c>
-      <c r="BZ29">
-        <v>1000</v>
-      </c>
-      <c r="CA29">
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
         <v>1.04</v>
       </c>
-      <c r="CB29" t="s">
-        <v>164</v>
+      <c r="CB31" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="175">
   <si>
     <t>League</t>
   </si>
@@ -331,6 +331,9 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
     <t>20:00:00</t>
   </si>
   <si>
@@ -400,15 +403,15 @@
     <t>Guizhou Zhucheng Athletic</t>
   </si>
   <si>
+    <t>Shijiazhuang Gongfu FC</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun F.C</t>
+  </si>
+  <si>
     <t>Jiangxi Dingnan United</t>
   </si>
   <si>
-    <t>Nantong Zhiyun F.C</t>
-  </si>
-  <si>
-    <t>Shijiazhuang Gongfu FC</t>
-  </si>
-  <si>
     <t>Shenzhen 2028</t>
   </si>
   <si>
@@ -421,6 +424,9 @@
     <t>CA Claypole</t>
   </si>
   <si>
+    <t>Union Minas</t>
+  </si>
+  <si>
     <t>Club Sportivo Ameliano</t>
   </si>
   <si>
@@ -490,15 +496,15 @@
     <t>Shanghai Port B</t>
   </si>
   <si>
+    <t>Dalian Kun City FC</t>
+  </si>
+  <si>
+    <t>Ningbo Professional</t>
+  </si>
+  <si>
     <t>Meizhou Hakka</t>
   </si>
   <si>
-    <t>Ningbo Professional</t>
-  </si>
-  <si>
-    <t>Dalian Kun City FC</t>
-  </si>
-  <si>
     <t>Shandong Taishan B</t>
   </si>
   <si>
@@ -511,6 +517,9 @@
     <t>Deportivo Espanol</t>
   </si>
   <si>
+    <t>Union Comercio</t>
+  </si>
+  <si>
     <t>Rubio Nu</t>
   </si>
   <si>
@@ -529,7 +538,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 12:39:35</t>
+    <t>2026-10-05 14:56:23</t>
   </si>
 </sst>
 </file>
@@ -861,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB31"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1117,25 +1126,25 @@
         <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F2">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="G2">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H2">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I2">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
         <v>3.9</v>
@@ -1156,55 +1165,55 @@
         <v>1.98</v>
       </c>
       <c r="Q2">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R2">
         <v>1.37</v>
       </c>
       <c r="S2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U2">
         <v>2.12</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y2">
         <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA2">
         <v>75</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE2">
         <v>46</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
         <v>18.5</v>
@@ -1213,22 +1222,22 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2">
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AP2">
         <v>13</v>
@@ -1246,7 +1255,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
         <v>13</v>
@@ -1255,19 +1264,19 @@
         <v>36</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BC2">
         <v>20</v>
@@ -1276,40 +1285,40 @@
         <v>32</v>
       </c>
       <c r="BE2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BH2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI2">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ2">
         <v>4.5</v>
@@ -1318,34 +1327,34 @@
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
         <v>34</v>
       </c>
       <c r="BW2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BX2">
         <v>46</v>
       </c>
       <c r="BY2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1359,10 +1368,10 @@
         <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F3">
         <v>4.5</v>
@@ -1374,13 +1383,13 @@
         <v>1.65</v>
       </c>
       <c r="I3">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="J3">
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L3">
         <v>1.23</v>
@@ -1395,7 +1404,7 @@
         <v>1.13</v>
       </c>
       <c r="P3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q3">
         <v>1.42</v>
@@ -1407,19 +1416,19 @@
         <v>2.06</v>
       </c>
       <c r="T3">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="U3">
         <v>2.7</v>
       </c>
       <c r="V3">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="W3">
         <v>1.25</v>
       </c>
       <c r="X3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y3">
         <v>17</v>
@@ -1428,10 +1437,10 @@
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC3">
         <v>13.5</v>
@@ -1440,7 +1449,7 @@
         <v>12</v>
       </c>
       <c r="AE3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF3">
         <v>55</v>
@@ -1461,19 +1470,19 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM3">
         <v>65</v>
       </c>
       <c r="AN3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AP3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ3">
         <v>14</v>
@@ -1485,7 +1494,7 @@
         <v>15.5</v>
       </c>
       <c r="AT3">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AU3">
         <v>10.5</v>
@@ -1497,34 +1506,34 @@
         <v>13</v>
       </c>
       <c r="AX3">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AY3">
         <v>17</v>
       </c>
       <c r="AZ3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA3">
         <v>19.5</v>
       </c>
       <c r="BB3">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BC3">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BD3">
         <v>28</v>
       </c>
       <c r="BE3">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="BF3">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BG3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1587,7 +1596,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1601,235 +1610,235 @@
         <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F4">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G4">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
+        <v>4.7</v>
+      </c>
+      <c r="K4">
         <v>5.1</v>
       </c>
-      <c r="K4">
-        <v>5.3</v>
-      </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="Q4">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="R4">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="X4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y4">
         <v>27</v>
       </c>
       <c r="Z4">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA4">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
         <v>12</v>
       </c>
       <c r="AD4">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AE4">
+        <v>120</v>
+      </c>
+      <c r="AF4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+      <c r="AH4">
+        <v>26</v>
+      </c>
+      <c r="AI4">
+        <v>110</v>
+      </c>
+      <c r="AJ4">
+        <v>13.5</v>
+      </c>
+      <c r="AK4">
+        <v>16</v>
+      </c>
+      <c r="AL4">
+        <v>40</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4">
+        <v>7.6</v>
+      </c>
+      <c r="AO4">
         <v>160</v>
       </c>
-      <c r="AF4">
+      <c r="AP4">
+        <v>16.5</v>
+      </c>
+      <c r="AQ4">
+        <v>23</v>
+      </c>
+      <c r="AR4">
+        <v>10.5</v>
+      </c>
+      <c r="AS4">
+        <v>11</v>
+      </c>
+      <c r="AT4">
         <v>8</v>
       </c>
-      <c r="AG4">
+      <c r="AU4">
+        <v>10</v>
+      </c>
+      <c r="AV4">
+        <v>24</v>
+      </c>
+      <c r="AW4">
+        <v>11</v>
+      </c>
+      <c r="AX4">
+        <v>7.8</v>
+      </c>
+      <c r="AY4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4">
+        <v>21</v>
+      </c>
+      <c r="BA4">
+        <v>11.5</v>
+      </c>
+      <c r="BB4">
+        <v>11.5</v>
+      </c>
+      <c r="BC4">
+        <v>13</v>
+      </c>
+      <c r="BD4">
+        <v>30</v>
+      </c>
+      <c r="BE4">
+        <v>11</v>
+      </c>
+      <c r="BF4">
+        <v>6.4</v>
+      </c>
+      <c r="BG4">
         <v>10.5</v>
       </c>
-      <c r="AH4">
-        <v>30</v>
-      </c>
-      <c r="AI4">
-        <v>130</v>
-      </c>
-      <c r="AJ4">
-        <v>12</v>
-      </c>
-      <c r="AK4">
-        <v>18</v>
-      </c>
-      <c r="AL4">
-        <v>44</v>
-      </c>
-      <c r="AM4">
-        <v>200</v>
-      </c>
-      <c r="AN4">
+      <c r="BH4">
+        <v>4.2</v>
+      </c>
+      <c r="BI4">
+        <v>3.55</v>
+      </c>
+      <c r="BJ4">
+        <v>13</v>
+      </c>
+      <c r="BK4">
+        <v>5.3</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>8.4</v>
+      </c>
+      <c r="BN4">
+        <v>4.2</v>
+      </c>
+      <c r="BO4">
+        <v>3.5</v>
+      </c>
+      <c r="BP4">
+        <v>9.4</v>
+      </c>
+      <c r="BQ4">
+        <v>4.6</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>6.6</v>
+      </c>
+      <c r="BT4">
+        <v>11</v>
+      </c>
+      <c r="BU4">
+        <v>4.9</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
         <v>8</v>
       </c>
-      <c r="AO4">
-        <v>230</v>
-      </c>
-      <c r="AP4">
-        <v>14.5</v>
-      </c>
-      <c r="AQ4">
-        <v>21</v>
-      </c>
-      <c r="AR4">
-        <v>50</v>
-      </c>
-      <c r="AS4">
-        <v>13</v>
-      </c>
-      <c r="AT4">
-        <v>7.2</v>
-      </c>
-      <c r="AU4">
-        <v>10.5</v>
-      </c>
-      <c r="AV4">
-        <v>26</v>
-      </c>
-      <c r="AW4">
-        <v>70</v>
-      </c>
-      <c r="AX4">
-        <v>7.2</v>
-      </c>
-      <c r="AY4">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4">
-        <v>23</v>
-      </c>
-      <c r="BA4">
-        <v>55</v>
-      </c>
-      <c r="BB4">
-        <v>10.5</v>
-      </c>
-      <c r="BC4">
-        <v>14.5</v>
-      </c>
-      <c r="BD4">
-        <v>36</v>
-      </c>
-      <c r="BE4">
-        <v>13</v>
-      </c>
-      <c r="BF4">
-        <v>6.8</v>
-      </c>
-      <c r="BG4">
-        <v>13</v>
-      </c>
-      <c r="BH4">
-        <v>3.95</v>
-      </c>
-      <c r="BI4">
-        <v>3.4</v>
-      </c>
-      <c r="BJ4">
-        <v>13.5</v>
-      </c>
-      <c r="BK4">
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>7.8</v>
+      </c>
+      <c r="BZ4">
+        <v>15.5</v>
+      </c>
+      <c r="CA4">
         <v>5.7</v>
       </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>9.4</v>
-      </c>
-      <c r="BN4">
-        <v>4</v>
-      </c>
-      <c r="BO4">
-        <v>3.45</v>
-      </c>
-      <c r="BP4">
-        <v>9</v>
-      </c>
-      <c r="BQ4">
-        <v>4.9</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>7.2</v>
-      </c>
-      <c r="BT4">
-        <v>12</v>
-      </c>
-      <c r="BU4">
-        <v>5.6</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>8.6</v>
-      </c>
-      <c r="BZ4">
-        <v>16.5</v>
-      </c>
-      <c r="CA4">
-        <v>6</v>
-      </c>
       <c r="CB4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1843,13 +1852,13 @@
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G5">
         <v>2.08</v>
@@ -1864,7 +1873,7 @@
         <v>3.5</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L5">
         <v>1.43</v>
@@ -1879,7 +1888,7 @@
         <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q5">
         <v>2.08</v>
@@ -1891,7 +1900,7 @@
         <v>3.8</v>
       </c>
       <c r="T5">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
         <v>2.06</v>
@@ -1906,13 +1915,13 @@
         <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB5">
         <v>8.6</v>
@@ -1921,10 +1930,10 @@
         <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF5">
         <v>12.5</v>
@@ -1936,7 +1945,7 @@
         <v>20</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
         <v>26</v>
@@ -1951,22 +1960,22 @@
         <v>140</v>
       </c>
       <c r="AN5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO5">
         <v>80</v>
       </c>
       <c r="AP5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
         <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT5">
         <v>7.8</v>
@@ -1981,7 +1990,7 @@
         <v>36</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
         <v>9.4</v>
@@ -1990,7 +1999,7 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB5">
         <v>21</v>
@@ -2026,7 +2035,7 @@
         <v>170</v>
       </c>
       <c r="BM5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN5">
         <v>4.9</v>
@@ -2038,7 +2047,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
         <v>32</v>
@@ -2047,7 +2056,7 @@
         <v>6.4</v>
       </c>
       <c r="BT5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU5">
         <v>4.8</v>
@@ -2062,16 +2071,16 @@
         <v>50</v>
       </c>
       <c r="BY5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ5">
         <v>30</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2085,10 +2094,10 @@
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F6">
         <v>4.5</v>
@@ -2106,7 +2115,7 @@
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
         <v>1.51</v>
@@ -2157,7 +2166,7 @@
         <v>25</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC6">
         <v>7.8</v>
@@ -2172,7 +2181,7 @@
         <v>34</v>
       </c>
       <c r="AG6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH6">
         <v>23</v>
@@ -2181,19 +2190,19 @@
         <v>50</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK6">
         <v>75</v>
       </c>
       <c r="AL6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM6">
         <v>170</v>
       </c>
       <c r="AN6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO6">
         <v>21</v>
@@ -2235,16 +2244,16 @@
         <v>40</v>
       </c>
       <c r="BB6">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BC6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BD6">
         <v>36</v>
       </c>
       <c r="BE6">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BF6">
         <v>44</v>
@@ -2253,7 +2262,7 @@
         <v>17</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI6">
         <v>2.56</v>
@@ -2262,58 +2271,58 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>2.42</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU6">
-        <v>1.65</v>
+        <v>3.65</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="CB6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2327,22 +2336,22 @@
         <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F7">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G7">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="H7">
+        <v>3.25</v>
+      </c>
+      <c r="I7">
         <v>3.4</v>
-      </c>
-      <c r="I7">
-        <v>3.6</v>
       </c>
       <c r="J7">
         <v>3.25</v>
@@ -2372,7 +2381,7 @@
         <v>1.29</v>
       </c>
       <c r="S7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7">
         <v>1.89</v>
@@ -2381,25 +2390,25 @@
         <v>2</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="X7">
         <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA7">
         <v>80</v>
       </c>
       <c r="AB7">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7">
         <v>7.6</v>
@@ -2411,7 +2420,7 @@
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG7">
         <v>12</v>
@@ -2426,7 +2435,7 @@
         <v>38</v>
       </c>
       <c r="AK7">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL7">
         <v>65</v>
@@ -2435,22 +2444,22 @@
         <v>150</v>
       </c>
       <c r="AN7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ7">
         <v>9.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT7">
         <v>8.800000000000001</v>
@@ -2474,10 +2483,10 @@
         <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC7">
         <v>24</v>
@@ -2489,10 +2498,10 @@
         <v>90</v>
       </c>
       <c r="BF7">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BG7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BH7">
         <v>3.1</v>
@@ -2504,7 +2513,7 @@
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2513,31 +2522,31 @@
         <v>10.5</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU7">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
         <v>8.199999999999999</v>
@@ -2546,16 +2555,16 @@
         <v>1000</v>
       </c>
       <c r="BY7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
         <v>9</v>
       </c>
-      <c r="BZ7">
-        <v>1000</v>
-      </c>
-      <c r="CA7">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2569,10 +2578,10 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F8">
         <v>2.14</v>
@@ -2581,16 +2590,16 @@
         <v>2.2</v>
       </c>
       <c r="H8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L8">
         <v>1.5</v>
@@ -2599,28 +2608,28 @@
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
         <v>1.44</v>
       </c>
       <c r="P8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q8">
         <v>2.34</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T8">
         <v>2</v>
       </c>
       <c r="U8">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -2650,7 +2659,7 @@
         <v>17.5</v>
       </c>
       <c r="AE8">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF8">
         <v>13</v>
@@ -2662,7 +2671,7 @@
         <v>22</v>
       </c>
       <c r="AI8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ8">
         <v>32</v>
@@ -2677,7 +2686,7 @@
         <v>170</v>
       </c>
       <c r="AN8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO8">
         <v>90</v>
@@ -2689,10 +2698,10 @@
         <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT8">
         <v>7</v>
@@ -2713,10 +2722,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB8">
         <v>23</v>
@@ -2797,7 +2806,7 @@
         <v>9</v>
       </c>
       <c r="CB8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2811,10 +2820,10 @@
         <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F9">
         <v>2.76</v>
@@ -2826,7 +2835,7 @@
         <v>2.74</v>
       </c>
       <c r="I9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J9">
         <v>2.72</v>
@@ -2838,7 +2847,7 @@
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N9">
         <v>2.48</v>
@@ -2850,7 +2859,7 @@
         <v>1.45</v>
       </c>
       <c r="Q9">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R9">
         <v>1.16</v>
@@ -2862,7 +2871,7 @@
         <v>2.1</v>
       </c>
       <c r="U9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V9">
         <v>1.42</v>
@@ -2925,37 +2934,37 @@
         <v>80</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
         <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
         <v>1.03</v>
@@ -2964,7 +2973,7 @@
         <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
         <v>1.03</v>
@@ -2982,7 +2991,7 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3039,7 +3048,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3053,43 +3062,43 @@
         <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F10">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H10">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="I10">
         <v>5.6</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>2.52</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
-        <v>1.13</v>
+        <v>1.51</v>
       </c>
       <c r="P10">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="Q10">
         <v>2.42</v>
@@ -3101,16 +3110,16 @@
         <v>3.05</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W10">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3281,7 +3290,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3295,28 +3304,28 @@
         <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F11">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="G11">
         <v>6.4</v>
       </c>
       <c r="H11">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I11">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3328,13 +3337,13 @@
         <v>3</v>
       </c>
       <c r="O11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P11">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
         <v>1.26</v>
@@ -3343,28 +3352,28 @@
         <v>3.3</v>
       </c>
       <c r="T11">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="U11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="W11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X11">
         <v>14.5</v>
       </c>
       <c r="Y11">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z11">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AA11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AB11">
         <v>18.5</v>
@@ -3376,10 +3385,10 @@
         <v>12.5</v>
       </c>
       <c r="AE11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF11">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AG11">
         <v>25</v>
@@ -3391,10 +3400,10 @@
         <v>55</v>
       </c>
       <c r="AJ11">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AK11">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
         <v>110</v>
@@ -3403,46 +3412,46 @@
         <v>180</v>
       </c>
       <c r="AN11">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
         <v>1.03</v>
@@ -3460,7 +3469,7 @@
         <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>3.55</v>
@@ -3523,7 +3532,7 @@
         <v>1.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3537,10 +3546,10 @@
         <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F12">
         <v>2.28</v>
@@ -3567,7 +3576,7 @@
         <v>1.13</v>
       </c>
       <c r="N12">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="O12">
         <v>1.49</v>
@@ -3585,16 +3594,16 @@
         <v>2.94</v>
       </c>
       <c r="T12">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X12">
         <v>9.4</v>
@@ -3651,58 +3660,58 @@
         <v>120</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF12">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BG12">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3765,7 +3774,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3779,43 +3788,43 @@
         <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F13">
         <v>2.96</v>
       </c>
       <c r="G13">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H13">
         <v>2.38</v>
       </c>
       <c r="I13">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J13">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="K13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N13">
         <v>2.2</v>
       </c>
       <c r="O13">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P13">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Q13">
         <v>2.24</v>
@@ -3827,7 +3836,7 @@
         <v>2.82</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
         <v>1.79</v>
@@ -3836,7 +3845,7 @@
         <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3950,7 +3959,7 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
@@ -4007,7 +4016,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4021,16 +4030,16 @@
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F14">
         <v>2.14</v>
       </c>
       <c r="G14">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H14">
         <v>3.6</v>
@@ -4057,16 +4066,16 @@
         <v>1.36</v>
       </c>
       <c r="P14">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R14">
         <v>1.33</v>
       </c>
       <c r="S14">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T14">
         <v>1.83</v>
@@ -4078,7 +4087,7 @@
         <v>1.34</v>
       </c>
       <c r="W14">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X14">
         <v>13.5</v>
@@ -4141,7 +4150,7 @@
         <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS14">
         <v>6.8</v>
@@ -4156,10 +4165,10 @@
         <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY14">
         <v>9.6</v>
@@ -4171,13 +4180,13 @@
         <v>6.6</v>
       </c>
       <c r="BB14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC14">
         <v>21</v>
       </c>
       <c r="BD14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE14">
         <v>7</v>
@@ -4186,7 +4195,7 @@
         <v>16</v>
       </c>
       <c r="BG14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4249,7 +4258,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4263,19 +4272,19 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F15">
         <v>2.08</v>
       </c>
       <c r="G15">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I15">
         <v>4.1</v>
@@ -4284,7 +4293,7 @@
         <v>3.45</v>
       </c>
       <c r="K15">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
         <v>1.39</v>
@@ -4296,7 +4305,7 @@
         <v>3.55</v>
       </c>
       <c r="O15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P15">
         <v>1.87</v>
@@ -4305,10 +4314,10 @@
         <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T15">
         <v>1.82</v>
@@ -4320,7 +4329,7 @@
         <v>1.32</v>
       </c>
       <c r="W15">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X15">
         <v>16.5</v>
@@ -4338,7 +4347,7 @@
         <v>11.5</v>
       </c>
       <c r="AC15">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD15">
         <v>19.5</v>
@@ -4359,10 +4368,10 @@
         <v>70</v>
       </c>
       <c r="AJ15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL15">
         <v>48</v>
@@ -4371,7 +4380,7 @@
         <v>130</v>
       </c>
       <c r="AN15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO15">
         <v>65</v>
@@ -4383,10 +4392,10 @@
         <v>12</v>
       </c>
       <c r="AR15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT15">
         <v>8.199999999999999</v>
@@ -4410,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="BA15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB15">
         <v>4.3</v>
@@ -4428,7 +4437,7 @@
         <v>14.5</v>
       </c>
       <c r="BG15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4491,7 +4500,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4505,10 +4514,10 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F16">
         <v>2.22</v>
@@ -4517,16 +4526,16 @@
         <v>2.66</v>
       </c>
       <c r="H16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I16">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J16">
-        <v>2.76</v>
+        <v>2.36</v>
       </c>
       <c r="K16">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4541,7 +4550,7 @@
         <v>1.33</v>
       </c>
       <c r="P16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q16">
         <v>2.62</v>
@@ -4553,10 +4562,10 @@
         <v>2.62</v>
       </c>
       <c r="T16">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
         <v>1.28</v>
@@ -4619,58 +4628,58 @@
         <v>130</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH16">
         <v>3</v>
@@ -4733,7 +4742,7 @@
         <v>1.51</v>
       </c>
       <c r="CB16" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4747,10 +4756,10 @@
         <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F17">
         <v>3.75</v>
@@ -4774,31 +4783,31 @@
         <v>1.47</v>
       </c>
       <c r="M17">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.36</v>
+        <v>1.1</v>
       </c>
       <c r="O17">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="P17">
         <v>1.45</v>
       </c>
       <c r="Q17">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R17">
         <v>1.07</v>
       </c>
       <c r="S17">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
         <v>1.68</v>
@@ -4975,7 +4984,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4989,10 +4998,10 @@
         <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F18">
         <v>1.89</v>
@@ -5016,7 +5025,7 @@
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18">
         <v>2.2</v>
@@ -5025,7 +5034,7 @@
         <v>1.23</v>
       </c>
       <c r="P18">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q18">
         <v>2.16</v>
@@ -5217,7 +5226,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5231,235 +5240,235 @@
         <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="H19">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="I19">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="J19">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K19">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L19">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
-        <v>4.5</v>
+        <v>2.98</v>
       </c>
       <c r="O19">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="P19">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="Q19">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="S19">
-        <v>2.66</v>
+        <v>4.1</v>
       </c>
       <c r="T19">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="U19">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="V19">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W19">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="X19">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y19">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="Z19">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AA19">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB19">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC19">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD19">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE19">
         <v>55</v>
       </c>
       <c r="AF19">
+        <v>16</v>
+      </c>
+      <c r="AG19">
+        <v>12.5</v>
+      </c>
+      <c r="AH19">
+        <v>21</v>
+      </c>
+      <c r="AI19">
+        <v>70</v>
+      </c>
+      <c r="AJ19">
+        <v>42</v>
+      </c>
+      <c r="AK19">
+        <v>36</v>
+      </c>
+      <c r="AL19">
+        <v>60</v>
+      </c>
+      <c r="AM19">
+        <v>150</v>
+      </c>
+      <c r="AN19">
+        <v>34</v>
+      </c>
+      <c r="AO19">
+        <v>60</v>
+      </c>
+      <c r="AP19">
+        <v>9.4</v>
+      </c>
+      <c r="AQ19">
+        <v>9.6</v>
+      </c>
+      <c r="AR19">
         <v>17.5</v>
       </c>
-      <c r="AG19">
-        <v>11.5</v>
-      </c>
-      <c r="AH19">
-        <v>20</v>
-      </c>
-      <c r="AI19">
-        <v>55</v>
-      </c>
-      <c r="AJ19">
-        <v>29</v>
-      </c>
-      <c r="AK19">
-        <v>24</v>
-      </c>
-      <c r="AL19">
-        <v>38</v>
-      </c>
-      <c r="AM19">
-        <v>90</v>
-      </c>
-      <c r="AN19">
-        <v>12</v>
-      </c>
-      <c r="AO19">
-        <v>44</v>
-      </c>
-      <c r="AP19">
-        <v>16.5</v>
-      </c>
-      <c r="AQ19">
-        <v>15</v>
-      </c>
-      <c r="AR19">
-        <v>4.7</v>
-      </c>
       <c r="AS19">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT19">
+        <v>7.6</v>
+      </c>
+      <c r="AU19">
+        <v>6.4</v>
+      </c>
+      <c r="AV19">
+        <v>12.5</v>
+      </c>
+      <c r="AW19">
+        <v>6.6</v>
+      </c>
+      <c r="AX19">
+        <v>12.5</v>
+      </c>
+      <c r="AY19">
         <v>10</v>
       </c>
-      <c r="AU19">
-        <v>7.8</v>
-      </c>
-      <c r="AV19">
-        <v>13.5</v>
-      </c>
-      <c r="AW19">
-        <v>5</v>
-      </c>
-      <c r="AX19">
-        <v>12</v>
-      </c>
-      <c r="AY19">
-        <v>9.4</v>
-      </c>
       <c r="AZ19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA19">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BB19">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BC19">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD19">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE19">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF19">
-        <v>9.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BG19">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH19">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5473,10 +5482,10 @@
         <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F20">
         <v>1.44</v>
@@ -5488,7 +5497,7 @@
         <v>8.6</v>
       </c>
       <c r="I20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J20">
         <v>4.3</v>
@@ -5503,13 +5512,13 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O20">
         <v>1.34</v>
       </c>
       <c r="P20">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q20">
         <v>1.96</v>
@@ -5518,7 +5527,7 @@
         <v>1.34</v>
       </c>
       <c r="S20">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T20">
         <v>2.2</v>
@@ -5527,7 +5536,7 @@
         <v>1.72</v>
       </c>
       <c r="V20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W20">
         <v>2.98</v>
@@ -5584,19 +5593,19 @@
         <v>10.5</v>
       </c>
       <c r="AO20">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AP20">
         <v>12.5</v>
       </c>
       <c r="AQ20">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR20">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS20">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT20">
         <v>6</v>
@@ -5605,10 +5614,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW20">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX20">
         <v>6.8</v>
@@ -5620,7 +5629,7 @@
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB20">
         <v>11</v>
@@ -5629,16 +5638,16 @@
         <v>15</v>
       </c>
       <c r="BD20">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE20">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF20">
         <v>7.6</v>
       </c>
       <c r="BG20">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5701,7 +5710,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5715,235 +5724,235 @@
         <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>2.08</v>
+      </c>
+      <c r="H21">
+        <v>3.75</v>
+      </c>
+      <c r="I21">
+        <v>4.4</v>
+      </c>
+      <c r="J21">
+        <v>3.7</v>
+      </c>
+      <c r="K21">
+        <v>4.1</v>
+      </c>
+      <c r="L21">
+        <v>1.29</v>
+      </c>
+      <c r="M21">
+        <v>1.05</v>
+      </c>
+      <c r="N21">
+        <v>4.5</v>
+      </c>
+      <c r="O21">
+        <v>1.25</v>
+      </c>
+      <c r="P21">
+        <v>2.2</v>
+      </c>
+      <c r="Q21">
+        <v>1.71</v>
+      </c>
+      <c r="R21">
+        <v>1.48</v>
+      </c>
+      <c r="S21">
+        <v>2.78</v>
+      </c>
+      <c r="T21">
+        <v>1.66</v>
+      </c>
+      <c r="U21">
         <v>2.34</v>
       </c>
-      <c r="G21">
-        <v>2.62</v>
-      </c>
-      <c r="H21">
-        <v>3.2</v>
-      </c>
-      <c r="I21">
-        <v>3.65</v>
-      </c>
-      <c r="J21">
-        <v>3.05</v>
-      </c>
-      <c r="K21">
-        <v>3.45</v>
-      </c>
-      <c r="L21">
-        <v>1.47</v>
-      </c>
-      <c r="M21">
-        <v>1.09</v>
-      </c>
-      <c r="N21">
-        <v>3.15</v>
-      </c>
-      <c r="O21">
-        <v>1.42</v>
-      </c>
-      <c r="P21">
-        <v>1.69</v>
-      </c>
-      <c r="Q21">
-        <v>2.2</v>
-      </c>
-      <c r="R21">
-        <v>1.26</v>
-      </c>
-      <c r="S21">
-        <v>4.1</v>
-      </c>
-      <c r="T21">
-        <v>1.88</v>
-      </c>
-      <c r="U21">
-        <v>1.93</v>
-      </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="X21">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="Y21">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="Z21">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA21">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB21">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC21">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE21">
         <v>55</v>
       </c>
       <c r="AF21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG21">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
+        <v>19.5</v>
+      </c>
+      <c r="AI21">
+        <v>55</v>
+      </c>
+      <c r="AJ21">
+        <v>29</v>
+      </c>
+      <c r="AK21">
         <v>21</v>
       </c>
-      <c r="AI21">
-        <v>70</v>
-      </c>
-      <c r="AJ21">
-        <v>42</v>
-      </c>
-      <c r="AK21">
-        <v>36</v>
-      </c>
       <c r="AL21">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM21">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AN21">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="AO21">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AP21">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="AQ21">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AR21">
-        <v>17.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS21">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT21">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AU21">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV21">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW21">
         <v>6</v>
       </c>
       <c r="AX21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY21">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA21">
+        <v>6</v>
+      </c>
+      <c r="BB21">
+        <v>20</v>
+      </c>
+      <c r="BC21">
+        <v>16.5</v>
+      </c>
+      <c r="BD21">
+        <v>5.8</v>
+      </c>
+      <c r="BE21">
         <v>6.2</v>
       </c>
-      <c r="BB21">
-        <v>6.2</v>
-      </c>
-      <c r="BC21">
+      <c r="BF21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG21">
+        <v>5.9</v>
+      </c>
+      <c r="BH21">
+        <v>4.1</v>
+      </c>
+      <c r="BI21">
+        <v>3.1</v>
+      </c>
+      <c r="BJ21">
+        <v>9.4</v>
+      </c>
+      <c r="BK21">
+        <v>4.9</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN21">
+        <v>5.2</v>
+      </c>
+      <c r="BO21">
+        <v>3.85</v>
+      </c>
+      <c r="BP21">
+        <v>14.5</v>
+      </c>
+      <c r="BQ21">
         <v>6</v>
       </c>
-      <c r="BD21">
-        <v>6.2</v>
-      </c>
-      <c r="BE21">
+      <c r="BR21">
+        <v>26</v>
+      </c>
+      <c r="BS21">
+        <v>7.2</v>
+      </c>
+      <c r="BT21">
+        <v>7.6</v>
+      </c>
+      <c r="BU21">
+        <v>5.5</v>
+      </c>
+      <c r="BV21">
+        <v>30</v>
+      </c>
+      <c r="BW21">
+        <v>7.6</v>
+      </c>
+      <c r="BX21">
+        <v>38</v>
+      </c>
+      <c r="BY21">
+        <v>8</v>
+      </c>
+      <c r="BZ21">
+        <v>19.5</v>
+      </c>
+      <c r="CA21">
         <v>6.6</v>
       </c>
-      <c r="BF21">
-        <v>21</v>
-      </c>
-      <c r="BG21">
-        <v>6.2</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.01</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>1.01</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.01</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.01</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.01</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.01</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>1.01</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>1.01</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
-        <v>1.01</v>
-      </c>
-      <c r="BZ21">
-        <v>1000</v>
-      </c>
-      <c r="CA21">
-        <v>1.01</v>
-      </c>
       <c r="CB21" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5957,25 +5966,25 @@
         <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F22">
         <v>1.7</v>
       </c>
       <c r="G22">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H22">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="I22">
         <v>990</v>
       </c>
       <c r="J22">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K22">
         <v>6.6</v>
@@ -5984,10 +5993,10 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O22">
         <v>1.31</v>
@@ -5996,13 +6005,13 @@
         <v>1.07</v>
       </c>
       <c r="Q22">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="R22">
         <v>1.1</v>
       </c>
       <c r="S22">
-        <v>2.8</v>
+        <v>1.05</v>
       </c>
       <c r="T22">
         <v>1.72</v>
@@ -6014,7 +6023,7 @@
         <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6185,7 +6194,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6199,10 +6208,10 @@
         <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F23">
         <v>3.7</v>
@@ -6217,7 +6226,7 @@
         <v>2.12</v>
       </c>
       <c r="J23">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K23">
         <v>4.1</v>
@@ -6313,7 +6322,7 @@
         <v>15.5</v>
       </c>
       <c r="AP23">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23">
         <v>7.8</v>
@@ -6322,10 +6331,10 @@
         <v>10</v>
       </c>
       <c r="AS23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU23">
         <v>6.8</v>
@@ -6334,13 +6343,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW23">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AX23">
         <v>4.6</v>
       </c>
       <c r="AY23">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ23">
         <v>13</v>
@@ -6427,7 +6436,7 @@
         <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6441,28 +6450,28 @@
         <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F24">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
         <v>1000</v>
       </c>
       <c r="H24">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I24">
         <v>1000</v>
       </c>
       <c r="J24">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K24">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6471,13 +6480,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O24">
         <v>1.01</v>
       </c>
       <c r="P24">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q24">
         <v>1.01</v>
@@ -6486,13 +6495,13 @@
         <v>1.08</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V24">
         <v>1.01</v>
@@ -6555,52 +6564,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -6669,7 +6678,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6683,37 +6692,37 @@
         <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="G25">
-        <v>4.1</v>
+        <v>990</v>
       </c>
       <c r="H25">
-        <v>2.3</v>
+        <v>1.12</v>
       </c>
       <c r="I25">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J25">
-        <v>2.6</v>
+        <v>1.13</v>
       </c>
       <c r="K25">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L25">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O25">
         <v>1.02</v>
@@ -6722,25 +6731,25 @@
         <v>1.08</v>
       </c>
       <c r="Q25">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="R25">
         <v>1.08</v>
       </c>
       <c r="S25">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="T25">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.51</v>
+        <v>1.02</v>
       </c>
       <c r="W25">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6860,63 +6869,63 @@
         <v>13</v>
       </c>
       <c r="BK25">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BN25">
         <v>7</v>
       </c>
       <c r="BO25">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="BP25">
         <v>38</v>
       </c>
       <c r="BQ25">
-        <v>26</v>
+        <v>1.93</v>
       </c>
       <c r="BR25">
         <v>65</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BT25">
         <v>5.8</v>
       </c>
       <c r="BU25">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BV25">
         <v>27</v>
       </c>
       <c r="BW25">
-        <v>18</v>
+        <v>5.8</v>
       </c>
       <c r="BX25">
         <v>55</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BZ25">
         <v>65</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="CB25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
         <v>92</v>
@@ -6925,28 +6934,28 @@
         <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -6955,34 +6964,34 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="O26">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q26">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R26">
         <v>1.08</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="T26">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
         <v>1.01</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7096,69 +7105,69 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
@@ -7167,58 +7176,58 @@
         <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
         <v>1.1</v>
       </c>
-      <c r="G27">
-        <v>1000</v>
-      </c>
-      <c r="H27">
-        <v>1.1</v>
-      </c>
-      <c r="I27">
-        <v>1000</v>
-      </c>
-      <c r="J27">
-        <v>1.1</v>
-      </c>
-      <c r="K27">
-        <v>950</v>
-      </c>
-      <c r="L27">
-        <v>1.01</v>
-      </c>
-      <c r="M27">
-        <v>1.01</v>
-      </c>
-      <c r="N27">
-        <v>1.08</v>
-      </c>
       <c r="O27">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q27">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="R27">
         <v>1.08</v>
       </c>
       <c r="S27">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27">
         <v>1.01</v>
@@ -7281,52 +7290,52 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
         <v>1.01</v>
@@ -7338,69 +7347,69 @@
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
         <v>92</v>
@@ -7409,28 +7418,28 @@
         <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F28">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="G28">
-        <v>1.57</v>
+        <v>990</v>
       </c>
       <c r="H28">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="I28">
-        <v>17.5</v>
+        <v>990</v>
       </c>
       <c r="J28">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="K28">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7439,22 +7448,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>2.52</v>
+        <v>1.1</v>
       </c>
       <c r="O28">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P28">
-        <v>2.52</v>
+        <v>1.08</v>
       </c>
       <c r="Q28">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="R28">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="S28">
-        <v>2.14</v>
+        <v>2.74</v>
       </c>
       <c r="T28">
         <v>1.11</v>
@@ -7463,10 +7472,10 @@
         <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W28">
-        <v>2.72</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7637,12 +7646,12 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
         <v>92</v>
@@ -7651,240 +7660,240 @@
         <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E29" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F29">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="G29">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="H29">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <v>7.2</v>
+      </c>
+      <c r="J29">
         <v>4.4</v>
       </c>
-      <c r="I29">
+      <c r="K29">
+        <v>5.6</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.02</v>
+      </c>
+      <c r="N29">
+        <v>4.5</v>
+      </c>
+      <c r="O29">
+        <v>1.17</v>
+      </c>
+      <c r="P29">
+        <v>2.34</v>
+      </c>
+      <c r="Q29">
+        <v>1.52</v>
+      </c>
+      <c r="R29">
+        <v>1.55</v>
+      </c>
+      <c r="S29">
+        <v>2.24</v>
+      </c>
+      <c r="T29">
+        <v>1.61</v>
+      </c>
+      <c r="U29">
+        <v>2.16</v>
+      </c>
+      <c r="V29">
+        <v>1.17</v>
+      </c>
+      <c r="W29">
+        <v>2.36</v>
+      </c>
+      <c r="X29">
+        <v>1000</v>
+      </c>
+      <c r="Y29">
+        <v>1000</v>
+      </c>
+      <c r="Z29">
+        <v>1000</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>1000</v>
+      </c>
+      <c r="AC29">
+        <v>1000</v>
+      </c>
+      <c r="AD29">
+        <v>1000</v>
+      </c>
+      <c r="AE29">
+        <v>1000</v>
+      </c>
+      <c r="AF29">
+        <v>1000</v>
+      </c>
+      <c r="AG29">
+        <v>1000</v>
+      </c>
+      <c r="AH29">
+        <v>1000</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>1000</v>
+      </c>
+      <c r="AK29">
+        <v>1000</v>
+      </c>
+      <c r="AL29">
+        <v>1000</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>8.4</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
+        <v>1.03</v>
+      </c>
+      <c r="AQ29">
+        <v>1.85</v>
+      </c>
+      <c r="AR29">
+        <v>1.03</v>
+      </c>
+      <c r="AS29">
+        <v>1.03</v>
+      </c>
+      <c r="AT29">
+        <v>1.03</v>
+      </c>
+      <c r="AU29">
+        <v>1.03</v>
+      </c>
+      <c r="AV29">
+        <v>1.2</v>
+      </c>
+      <c r="AW29">
+        <v>1.03</v>
+      </c>
+      <c r="AX29">
+        <v>1.03</v>
+      </c>
+      <c r="AY29">
+        <v>1.03</v>
+      </c>
+      <c r="AZ29">
+        <v>1.03</v>
+      </c>
+      <c r="BA29">
+        <v>1.2</v>
+      </c>
+      <c r="BB29">
+        <v>1.03</v>
+      </c>
+      <c r="BC29">
+        <v>1.03</v>
+      </c>
+      <c r="BD29">
+        <v>1.03</v>
+      </c>
+      <c r="BE29">
+        <v>1.85</v>
+      </c>
+      <c r="BF29">
         <v>5</v>
       </c>
-      <c r="J29">
-        <v>3.15</v>
-      </c>
-      <c r="K29">
-        <v>3.6</v>
-      </c>
-      <c r="L29">
-        <v>1.01</v>
-      </c>
-      <c r="M29">
-        <v>1.1</v>
-      </c>
-      <c r="N29">
-        <v>3.1</v>
-      </c>
-      <c r="O29">
-        <v>1.4</v>
-      </c>
-      <c r="P29">
-        <v>1.7</v>
-      </c>
-      <c r="Q29">
-        <v>2.18</v>
-      </c>
-      <c r="R29">
-        <v>1.27</v>
-      </c>
-      <c r="S29">
-        <v>4.1</v>
-      </c>
-      <c r="T29">
-        <v>1.92</v>
-      </c>
-      <c r="U29">
-        <v>1.9</v>
-      </c>
-      <c r="V29">
-        <v>1.25</v>
-      </c>
-      <c r="W29">
-        <v>1.9</v>
-      </c>
-      <c r="X29">
-        <v>12</v>
-      </c>
-      <c r="Y29">
-        <v>15</v>
-      </c>
-      <c r="Z29">
-        <v>36</v>
-      </c>
-      <c r="AA29">
-        <v>990</v>
-      </c>
-      <c r="AB29">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC29">
-        <v>8</v>
-      </c>
-      <c r="AD29">
-        <v>20</v>
-      </c>
-      <c r="AE29">
-        <v>90</v>
-      </c>
-      <c r="AF29">
-        <v>12.5</v>
-      </c>
-      <c r="AG29">
-        <v>11</v>
-      </c>
-      <c r="AH29">
-        <v>22</v>
-      </c>
-      <c r="AI29">
-        <v>90</v>
-      </c>
-      <c r="AJ29">
-        <v>27</v>
-      </c>
-      <c r="AK29">
-        <v>26</v>
-      </c>
-      <c r="AL29">
-        <v>65</v>
-      </c>
-      <c r="AM29">
-        <v>990</v>
-      </c>
-      <c r="AN29">
-        <v>23</v>
-      </c>
-      <c r="AO29">
-        <v>920</v>
-      </c>
-      <c r="AP29">
-        <v>9.6</v>
-      </c>
-      <c r="AQ29">
-        <v>12</v>
-      </c>
-      <c r="AR29">
-        <v>7.4</v>
-      </c>
-      <c r="AS29">
-        <v>8</v>
-      </c>
-      <c r="AT29">
-        <v>6.6</v>
-      </c>
-      <c r="AU29">
-        <v>6.6</v>
-      </c>
-      <c r="AV29">
-        <v>16</v>
-      </c>
-      <c r="AW29">
-        <v>7.6</v>
-      </c>
-      <c r="AX29">
-        <v>10</v>
-      </c>
-      <c r="AY29">
-        <v>9</v>
-      </c>
-      <c r="AZ29">
-        <v>17</v>
-      </c>
-      <c r="BA29">
-        <v>7.6</v>
-      </c>
-      <c r="BB29">
-        <v>19</v>
-      </c>
-      <c r="BC29">
-        <v>18.5</v>
-      </c>
-      <c r="BD29">
-        <v>7.6</v>
-      </c>
-      <c r="BE29">
-        <v>8</v>
-      </c>
-      <c r="BF29">
-        <v>16.5</v>
-      </c>
       <c r="BG29">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
         <v>92</v>
@@ -7893,70 +7902,70 @@
         <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F30">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="H30">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I30">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J30">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
+        <v>3.65</v>
+      </c>
+      <c r="L30">
+        <v>1.01</v>
+      </c>
+      <c r="M30">
+        <v>1.1</v>
+      </c>
+      <c r="N30">
+        <v>3.05</v>
+      </c>
+      <c r="O30">
+        <v>1.41</v>
+      </c>
+      <c r="P30">
+        <v>1.71</v>
+      </c>
+      <c r="Q30">
+        <v>2.18</v>
+      </c>
+      <c r="R30">
+        <v>1.27</v>
+      </c>
+      <c r="S30">
         <v>4.1</v>
       </c>
-      <c r="L30">
-        <v>1.42</v>
-      </c>
-      <c r="M30">
-        <v>1.06</v>
-      </c>
-      <c r="N30">
-        <v>3.95</v>
-      </c>
-      <c r="O30">
-        <v>1.31</v>
-      </c>
-      <c r="P30">
-        <v>2</v>
-      </c>
-      <c r="Q30">
+      <c r="T30">
+        <v>1.92</v>
+      </c>
+      <c r="U30">
         <v>1.9</v>
-      </c>
-      <c r="R30">
-        <v>1.39</v>
-      </c>
-      <c r="S30">
-        <v>3.3</v>
-      </c>
-      <c r="T30">
-        <v>1.8</v>
-      </c>
-      <c r="U30">
-        <v>2.14</v>
       </c>
       <c r="V30">
         <v>1.27</v>
       </c>
       <c r="W30">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="X30">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y30">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z30">
         <v>36</v>
@@ -7965,163 +7974,163 @@
         <v>120</v>
       </c>
       <c r="AB30">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC30">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE30">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AF30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH30">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI30">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ30">
+        <v>28</v>
+      </c>
+      <c r="AK30">
         <v>26</v>
       </c>
-      <c r="AK30">
-        <v>24</v>
-      </c>
       <c r="AL30">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AM30">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AN30">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AO30">
-        <v>75</v>
+        <v>830</v>
       </c>
       <c r="AP30">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AQ30">
+        <v>11</v>
+      </c>
+      <c r="AR30">
+        <v>8</v>
+      </c>
+      <c r="AS30">
+        <v>8.6</v>
+      </c>
+      <c r="AT30">
+        <v>6.8</v>
+      </c>
+      <c r="AU30">
+        <v>6.6</v>
+      </c>
+      <c r="AV30">
         <v>15</v>
       </c>
-      <c r="AR30">
-        <v>8.6</v>
-      </c>
-      <c r="AS30">
-        <v>10</v>
-      </c>
-      <c r="AT30">
-        <v>8.4</v>
-      </c>
-      <c r="AU30">
-        <v>7.8</v>
-      </c>
-      <c r="AV30">
-        <v>15.5</v>
-      </c>
       <c r="AW30">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX30">
         <v>10.5</v>
       </c>
       <c r="AY30">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA30">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="BB30">
+        <v>19</v>
+      </c>
+      <c r="BC30">
         <v>18.5</v>
-      </c>
-      <c r="BC30">
-        <v>17</v>
       </c>
       <c r="BD30">
         <v>8.4</v>
       </c>
       <c r="BE30">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BG30">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH30">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>3.15</v>
+        <v>1.19</v>
       </c>
       <c r="BJ30">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>15.5</v>
+        <v>1.19</v>
       </c>
       <c r="BN30">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>4.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP30">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>10</v>
+        <v>1.13</v>
       </c>
       <c r="BR30">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>10.5</v>
+        <v>1.69</v>
       </c>
       <c r="BT30">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>7</v>
+        <v>1.19</v>
       </c>
       <c r="BV30">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>12</v>
+        <v>1.75</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>13</v>
+        <v>1.75</v>
       </c>
       <c r="BZ30">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>10</v>
+        <v>1.68</v>
       </c>
       <c r="CB30" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8135,235 +8144,477 @@
         <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F31">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="G31">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="H31">
+        <v>4.4</v>
+      </c>
+      <c r="I31">
+        <v>4.7</v>
+      </c>
+      <c r="J31">
+        <v>3.75</v>
+      </c>
+      <c r="K31">
+        <v>4</v>
+      </c>
+      <c r="L31">
+        <v>1.42</v>
+      </c>
+      <c r="M31">
+        <v>1.06</v>
+      </c>
+      <c r="N31">
+        <v>3.9</v>
+      </c>
+      <c r="O31">
+        <v>1.31</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="Q31">
+        <v>1.9</v>
+      </c>
+      <c r="R31">
+        <v>1.39</v>
+      </c>
+      <c r="S31">
+        <v>3.3</v>
+      </c>
+      <c r="T31">
+        <v>1.8</v>
+      </c>
+      <c r="U31">
+        <v>2.14</v>
+      </c>
+      <c r="V31">
+        <v>1.27</v>
+      </c>
+      <c r="W31">
+        <v>2.04</v>
+      </c>
+      <c r="X31">
+        <v>16</v>
+      </c>
+      <c r="Y31">
+        <v>17</v>
+      </c>
+      <c r="Z31">
+        <v>36</v>
+      </c>
+      <c r="AA31">
+        <v>120</v>
+      </c>
+      <c r="AB31">
+        <v>9.4</v>
+      </c>
+      <c r="AC31">
+        <v>8.6</v>
+      </c>
+      <c r="AD31">
+        <v>18</v>
+      </c>
+      <c r="AE31">
+        <v>60</v>
+      </c>
+      <c r="AF31">
+        <v>12</v>
+      </c>
+      <c r="AG31">
+        <v>10</v>
+      </c>
+      <c r="AH31">
+        <v>18.5</v>
+      </c>
+      <c r="AI31">
+        <v>75</v>
+      </c>
+      <c r="AJ31">
+        <v>25</v>
+      </c>
+      <c r="AK31">
+        <v>23</v>
+      </c>
+      <c r="AL31">
+        <v>34</v>
+      </c>
+      <c r="AM31">
+        <v>120</v>
+      </c>
+      <c r="AN31">
+        <v>13</v>
+      </c>
+      <c r="AO31">
+        <v>75</v>
+      </c>
+      <c r="AP31">
+        <v>14</v>
+      </c>
+      <c r="AQ31">
+        <v>15</v>
+      </c>
+      <c r="AR31">
+        <v>15</v>
+      </c>
+      <c r="AS31">
+        <v>10.5</v>
+      </c>
+      <c r="AT31">
+        <v>8.4</v>
+      </c>
+      <c r="AU31">
+        <v>7.8</v>
+      </c>
+      <c r="AV31">
+        <v>15.5</v>
+      </c>
+      <c r="AW31">
+        <v>21</v>
+      </c>
+      <c r="AX31">
+        <v>10.5</v>
+      </c>
+      <c r="AY31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ31">
+        <v>16</v>
+      </c>
+      <c r="BA31">
+        <v>23</v>
+      </c>
+      <c r="BB31">
+        <v>18.5</v>
+      </c>
+      <c r="BC31">
+        <v>17</v>
+      </c>
+      <c r="BD31">
+        <v>15</v>
+      </c>
+      <c r="BE31">
+        <v>34</v>
+      </c>
+      <c r="BF31">
+        <v>11</v>
+      </c>
+      <c r="BG31">
+        <v>10</v>
+      </c>
+      <c r="BH31">
+        <v>3.4</v>
+      </c>
+      <c r="BI31">
+        <v>3.15</v>
+      </c>
+      <c r="BJ31">
+        <v>10</v>
+      </c>
+      <c r="BK31">
+        <v>7.2</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>15</v>
+      </c>
+      <c r="BN31">
+        <v>4.6</v>
+      </c>
+      <c r="BO31">
+        <v>4.2</v>
+      </c>
+      <c r="BP31">
+        <v>14</v>
+      </c>
+      <c r="BQ31">
+        <v>7.6</v>
+      </c>
+      <c r="BR31">
+        <v>28</v>
+      </c>
+      <c r="BS31">
+        <v>10.5</v>
+      </c>
+      <c r="BT31">
+        <v>7.8</v>
+      </c>
+      <c r="BU31">
+        <v>7</v>
+      </c>
+      <c r="BV31">
+        <v>38</v>
+      </c>
+      <c r="BW31">
+        <v>11.5</v>
+      </c>
+      <c r="BX31">
+        <v>48</v>
+      </c>
+      <c r="BY31">
+        <v>12.5</v>
+      </c>
+      <c r="BZ31">
+        <v>25</v>
+      </c>
+      <c r="CA31">
+        <v>10</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32">
+        <v>1.82</v>
+      </c>
+      <c r="G32">
+        <v>1.9</v>
+      </c>
+      <c r="H32">
         <v>5.2</v>
       </c>
-      <c r="I31">
-        <v>6.6</v>
-      </c>
-      <c r="J31">
-        <v>3.4</v>
-      </c>
-      <c r="K31">
-        <v>4.1</v>
-      </c>
-      <c r="L31">
+      <c r="I32">
+        <v>5.7</v>
+      </c>
+      <c r="J32">
+        <v>3.35</v>
+      </c>
+      <c r="K32">
+        <v>4.2</v>
+      </c>
+      <c r="L32">
         <v>1.5</v>
       </c>
-      <c r="M31">
-        <v>1.07</v>
-      </c>
-      <c r="N31">
-        <v>2.76</v>
-      </c>
-      <c r="O31">
+      <c r="M32">
+        <v>1.11</v>
+      </c>
+      <c r="N32">
+        <v>2.98</v>
+      </c>
+      <c r="O32">
         <v>1.46</v>
       </c>
-      <c r="P31">
+      <c r="P32">
         <v>1.58</v>
       </c>
-      <c r="Q31">
-        <v>2.34</v>
-      </c>
-      <c r="R31">
+      <c r="Q32">
+        <v>2.3</v>
+      </c>
+      <c r="R32">
         <v>1.21</v>
       </c>
-      <c r="S31">
+      <c r="S32">
         <v>4.4</v>
       </c>
-      <c r="T31">
+      <c r="T32">
         <v>2.12</v>
       </c>
-      <c r="U31">
+      <c r="U32">
         <v>1.64</v>
       </c>
-      <c r="V31">
-        <v>1.19</v>
-      </c>
-      <c r="W31">
-        <v>2.12</v>
-      </c>
-      <c r="X31">
+      <c r="V32">
+        <v>1.21</v>
+      </c>
+      <c r="W32">
+        <v>2.1</v>
+      </c>
+      <c r="X32">
+        <v>12</v>
+      </c>
+      <c r="Y32">
         <v>970</v>
       </c>
-      <c r="Y31">
+      <c r="Z32">
+        <v>120</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>8.4</v>
+      </c>
+      <c r="AC32">
+        <v>11</v>
+      </c>
+      <c r="AD32">
         <v>950</v>
       </c>
-      <c r="Z31">
-        <v>150</v>
-      </c>
-      <c r="AA31">
-        <v>1000</v>
-      </c>
-      <c r="AB31">
-        <v>9.6</v>
-      </c>
-      <c r="AC31">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD31">
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>14</v>
+      </c>
+      <c r="AG32">
+        <v>17</v>
+      </c>
+      <c r="AH32">
         <v>950</v>
       </c>
-      <c r="AE31">
-        <v>1000</v>
-      </c>
-      <c r="AF31">
-        <v>11</v>
-      </c>
-      <c r="AG31">
-        <v>17</v>
-      </c>
-      <c r="AH31">
-        <v>950</v>
-      </c>
-      <c r="AI31">
-        <v>1000</v>
-      </c>
-      <c r="AJ31">
-        <v>140</v>
-      </c>
-      <c r="AK31">
-        <v>1000</v>
-      </c>
-      <c r="AL31">
-        <v>1000</v>
-      </c>
-      <c r="AM31">
-        <v>1000</v>
-      </c>
-      <c r="AN31">
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>85</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
         <v>42</v>
       </c>
-      <c r="AO31">
-        <v>1000</v>
-      </c>
-      <c r="AP31">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ31">
-        <v>1.91</v>
-      </c>
-      <c r="AR31">
-        <v>4.9</v>
-      </c>
-      <c r="AS31">
-        <v>1.96</v>
-      </c>
-      <c r="AT31">
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>6.8</v>
+      </c>
+      <c r="AQ32">
+        <v>2</v>
+      </c>
+      <c r="AR32">
+        <v>6.8</v>
+      </c>
+      <c r="AS32">
+        <v>2.08</v>
+      </c>
+      <c r="AT32">
         <v>5.9</v>
       </c>
-      <c r="AU31">
-        <v>1.63</v>
-      </c>
-      <c r="AV31">
-        <v>3.9</v>
-      </c>
-      <c r="AW31">
-        <v>1.96</v>
-      </c>
-      <c r="AX31">
-        <v>7.2</v>
-      </c>
-      <c r="AY31">
-        <v>1.75</v>
-      </c>
-      <c r="AZ31">
-        <v>4.4</v>
-      </c>
-      <c r="BA31">
-        <v>1.96</v>
-      </c>
-      <c r="BB31">
-        <v>12</v>
-      </c>
-      <c r="BC31">
-        <v>1.96</v>
-      </c>
-      <c r="BD31">
-        <v>9.6</v>
-      </c>
-      <c r="BE31">
-        <v>1.96</v>
-      </c>
-      <c r="BF31">
-        <v>1.87</v>
-      </c>
-      <c r="BG31">
-        <v>1.96</v>
-      </c>
-      <c r="BH31">
-        <v>1000</v>
-      </c>
-      <c r="BI31">
-        <v>1.26</v>
-      </c>
-      <c r="BJ31">
-        <v>1000</v>
-      </c>
-      <c r="BK31">
-        <v>1.04</v>
-      </c>
-      <c r="BL31">
-        <v>1000</v>
-      </c>
-      <c r="BM31">
-        <v>1.04</v>
-      </c>
-      <c r="BN31">
-        <v>1000</v>
-      </c>
-      <c r="BO31">
-        <v>1.48</v>
-      </c>
-      <c r="BP31">
-        <v>1000</v>
-      </c>
-      <c r="BQ31">
-        <v>1.04</v>
-      </c>
-      <c r="BR31">
-        <v>1000</v>
-      </c>
-      <c r="BS31">
-        <v>1.04</v>
-      </c>
-      <c r="BT31">
-        <v>1000</v>
-      </c>
-      <c r="BU31">
-        <v>1.04</v>
-      </c>
-      <c r="BV31">
-        <v>1000</v>
-      </c>
-      <c r="BW31">
-        <v>1.04</v>
-      </c>
-      <c r="BX31">
-        <v>1000</v>
-      </c>
-      <c r="BY31">
-        <v>1.04</v>
-      </c>
-      <c r="BZ31">
-        <v>1000</v>
-      </c>
-      <c r="CA31">
-        <v>1.04</v>
-      </c>
-      <c r="CB31" t="s">
-        <v>171</v>
+      <c r="AU32">
+        <v>6</v>
+      </c>
+      <c r="AV32">
+        <v>5</v>
+      </c>
+      <c r="AW32">
+        <v>2.08</v>
+      </c>
+      <c r="AX32">
+        <v>7.6</v>
+      </c>
+      <c r="AY32">
+        <v>1.86</v>
+      </c>
+      <c r="AZ32">
+        <v>5.8</v>
+      </c>
+      <c r="BA32">
+        <v>2.08</v>
+      </c>
+      <c r="BB32">
+        <v>13.5</v>
+      </c>
+      <c r="BC32">
+        <v>10</v>
+      </c>
+      <c r="BD32">
+        <v>2.08</v>
+      </c>
+      <c r="BE32">
+        <v>2.08</v>
+      </c>
+      <c r="BF32">
+        <v>1.99</v>
+      </c>
+      <c r="BG32">
+        <v>2.08</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.25</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.21</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.21</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.47</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.21</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.21</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.21</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.21</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.21</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.21</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -538,7 +538,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 14:56:23</t>
+    <t>2026-10-05 17:07:52</t>
   </si>
 </sst>
 </file>
@@ -1135,22 +1135,22 @@
         <v>2.06</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J2">
         <v>3.8</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1159,7 +1159,7 @@
         <v>3.85</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
         <v>1.98</v>
@@ -1174,55 +1174,55 @@
         <v>3.55</v>
       </c>
       <c r="T2">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="U2">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
         <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK2">
         <v>23</v>
@@ -1231,13 +1231,13 @@
         <v>38</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP2">
         <v>13</v>
@@ -1252,34 +1252,34 @@
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU2">
         <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD2">
         <v>32</v>
@@ -1288,13 +1288,13 @@
         <v>75</v>
       </c>
       <c r="BF2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
         <v>34</v>
       </c>
       <c r="BH2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI2">
         <v>3.1</v>
@@ -1303,22 +1303,22 @@
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BQ2">
         <v>4.5</v>
@@ -1330,10 +1330,10 @@
         <v>5.1</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV2">
         <v>34</v>
@@ -1348,10 +1348,10 @@
         <v>5.3</v>
       </c>
       <c r="BZ2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB2" t="s">
         <v>174</v>
@@ -1374,22 +1374,22 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I3">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="J3">
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L3">
         <v>1.23</v>
@@ -1404,100 +1404,100 @@
         <v>1.13</v>
       </c>
       <c r="P3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R3">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="S3">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="T3">
         <v>1.5</v>
       </c>
       <c r="U3">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="W3">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X3">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Y3">
         <v>17</v>
       </c>
       <c r="Z3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB3">
         <v>32</v>
       </c>
       <c r="AC3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF3">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AG3">
         <v>21</v>
       </c>
       <c r="AH3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ3">
         <v>110</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO3">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AP3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AQ3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AT3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV3">
         <v>9.6</v>
@@ -1521,76 +1521,76 @@
         <v>55</v>
       </c>
       <c r="BC3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF3">
         <v>23</v>
       </c>
       <c r="BG3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK3">
         <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM3">
         <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO3">
         <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ3">
         <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS3">
         <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW3">
         <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY3">
         <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA3">
         <v>1.04</v>
@@ -1616,226 +1616,226 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G4">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
         <v>6.8</v>
-      </c>
-      <c r="I4">
-        <v>7.8</v>
       </c>
       <c r="J4">
         <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P4">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="S4">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z4">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AA4">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD4">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AF4">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AG4">
         <v>10</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AJ4">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM4">
         <v>170</v>
       </c>
       <c r="AN4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AP4">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AQ4">
         <v>23</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BB4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="BF4">
         <v>6.4</v>
       </c>
       <c r="BG4">
+        <v>50</v>
+      </c>
+      <c r="BH4">
+        <v>4.5</v>
+      </c>
+      <c r="BI4">
+        <v>3.75</v>
+      </c>
+      <c r="BJ4">
+        <v>11.5</v>
+      </c>
+      <c r="BK4">
+        <v>5.2</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>7.8</v>
+      </c>
+      <c r="BN4">
+        <v>4.6</v>
+      </c>
+      <c r="BO4">
+        <v>3.85</v>
+      </c>
+      <c r="BP4">
         <v>10.5</v>
       </c>
-      <c r="BH4">
-        <v>4.2</v>
-      </c>
-      <c r="BI4">
-        <v>3.55</v>
-      </c>
-      <c r="BJ4">
-        <v>13</v>
-      </c>
-      <c r="BK4">
-        <v>5.3</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
+      <c r="BQ4">
         <v>8.4</v>
       </c>
-      <c r="BN4">
-        <v>4.2</v>
-      </c>
-      <c r="BO4">
-        <v>3.5</v>
-      </c>
-      <c r="BP4">
-        <v>9.4</v>
-      </c>
-      <c r="BQ4">
-        <v>4.6</v>
-      </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT4">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BZ4">
         <v>15.5</v>
       </c>
       <c r="CA4">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="CB4" t="s">
         <v>174</v>
@@ -1858,16 +1858,16 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J5">
         <v>3.5</v>
@@ -1885,16 +1885,16 @@
         <v>3.65</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q5">
         <v>2.08</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
         <v>3.8</v>
@@ -1906,7 +1906,7 @@
         <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
         <v>1.92</v>
@@ -1921,28 +1921,28 @@
         <v>32</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
         <v>75</v>
@@ -1951,10 +1951,10 @@
         <v>26</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM5">
         <v>140</v>
@@ -1963,7 +1963,7 @@
         <v>18</v>
       </c>
       <c r="AO5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP5">
         <v>12</v>
@@ -1978,16 +1978,16 @@
         <v>55</v>
       </c>
       <c r="AT5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>15</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
@@ -1999,10 +1999,10 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC5">
         <v>19.5</v>
@@ -2014,16 +2014,16 @@
         <v>80</v>
       </c>
       <c r="BF5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH5">
         <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
@@ -2032,28 +2032,28 @@
         <v>6.2</v>
       </c>
       <c r="BL5">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN5">
         <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP5">
         <v>15.5</v>
       </c>
       <c r="BQ5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT5">
         <v>7.6</v>
@@ -2062,13 +2062,13 @@
         <v>4.8</v>
       </c>
       <c r="BV5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY5">
         <v>7</v>
@@ -2103,19 +2103,19 @@
         <v>4.5</v>
       </c>
       <c r="G6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H6">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I6">
         <v>2.04</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L6">
         <v>1.51</v>
@@ -2145,13 +2145,13 @@
         <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V6">
         <v>1.96</v>
       </c>
       <c r="W6">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X6">
         <v>11</v>
@@ -2169,7 +2169,7 @@
         <v>13.5</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
         <v>11</v>
@@ -2184,7 +2184,7 @@
         <v>19</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI6">
         <v>50</v>
@@ -2196,13 +2196,13 @@
         <v>75</v>
       </c>
       <c r="AL6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM6">
         <v>170</v>
       </c>
       <c r="AN6">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO6">
         <v>21</v>
@@ -2226,7 +2226,7 @@
         <v>7</v>
       </c>
       <c r="AV6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW6">
         <v>21</v>
@@ -2247,79 +2247,79 @@
         <v>38</v>
       </c>
       <c r="BC6">
+        <v>40</v>
+      </c>
+      <c r="BD6">
         <v>48</v>
-      </c>
-      <c r="BD6">
-        <v>36</v>
       </c>
       <c r="BE6">
         <v>85</v>
       </c>
       <c r="BF6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BG6">
         <v>17</v>
       </c>
       <c r="BH6">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="BI6">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM6">
-        <v>2.76</v>
+        <v>13</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO6">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ6">
-        <v>2.76</v>
+        <v>10.5</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS6">
-        <v>2.76</v>
+        <v>11.5</v>
       </c>
       <c r="BT6">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BU6">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW6">
         <v>8</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY6">
-        <v>2.76</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA6">
-        <v>2.76</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
         <v>174</v>
@@ -2342,22 +2342,22 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G7">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J7">
         <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L7">
         <v>1.47</v>
@@ -2366,16 +2366,16 @@
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
         <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R7">
         <v>1.29</v>
@@ -2387,13 +2387,13 @@
         <v>1.89</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X7">
         <v>11.5</v>
@@ -2402,28 +2402,28 @@
         <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC7">
         <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE7">
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
         <v>20</v>
@@ -2435,7 +2435,7 @@
         <v>38</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL7">
         <v>65</v>
@@ -2447,31 +2447,31 @@
         <v>36</v>
       </c>
       <c r="AO7">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AP7">
         <v>9.6</v>
       </c>
       <c r="AQ7">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR7">
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT7">
         <v>8.800000000000001</v>
       </c>
       <c r="AU7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW7">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AX7">
         <v>12</v>
@@ -2480,40 +2480,40 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA7">
         <v>40</v>
       </c>
       <c r="BB7">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC7">
         <v>24</v>
       </c>
       <c r="BD7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF7">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BG7">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BH7">
         <v>3.1</v>
       </c>
       <c r="BI7">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2522,7 +2522,7 @@
         <v>10.5</v>
       </c>
       <c r="BN7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO7">
         <v>4.6</v>
@@ -2531,7 +2531,7 @@
         <v>20</v>
       </c>
       <c r="BQ7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2543,25 +2543,25 @@
         <v>6.6</v>
       </c>
       <c r="BU7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="s">
         <v>174</v>
@@ -2593,16 +2593,16 @@
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M8">
         <v>1.1</v>
@@ -2617,7 +2617,7 @@
         <v>1.7</v>
       </c>
       <c r="Q8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R8">
         <v>1.26</v>
@@ -2629,7 +2629,7 @@
         <v>2</v>
       </c>
       <c r="U8">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -2647,13 +2647,13 @@
         <v>29</v>
       </c>
       <c r="AA8">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AB8">
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD8">
         <v>17.5</v>
@@ -2662,7 +2662,7 @@
         <v>75</v>
       </c>
       <c r="AF8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
@@ -2671,7 +2671,7 @@
         <v>22</v>
       </c>
       <c r="AI8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ8">
         <v>32</v>
@@ -2689,10 +2689,10 @@
         <v>24</v>
       </c>
       <c r="AO8">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AP8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
@@ -2707,13 +2707,13 @@
         <v>7</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV8">
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
@@ -2725,7 +2725,7 @@
         <v>17</v>
       </c>
       <c r="BA8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB8">
         <v>23</v>
@@ -2755,55 +2755,55 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO8">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP8">
         <v>18</v>
       </c>
       <c r="BQ8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8">
         <v>7.6</v>
       </c>
       <c r="BU8">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB8" t="s">
         <v>174</v>
@@ -2826,64 +2826,64 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G9">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H9">
+        <v>2.8</v>
+      </c>
+      <c r="I9">
+        <v>3.3</v>
+      </c>
+      <c r="J9">
         <v>2.74</v>
       </c>
-      <c r="I9">
-        <v>3.4</v>
-      </c>
-      <c r="J9">
-        <v>2.72</v>
-      </c>
       <c r="K9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="O9">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P9">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S9">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="T9">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X9">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z9">
         <v>23</v>
@@ -2892,10 +2892,10 @@
         <v>70</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
         <v>17.5</v>
@@ -2904,16 +2904,16 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ9">
         <v>70</v>
@@ -2922,130 +2922,130 @@
         <v>60</v>
       </c>
       <c r="AL9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM9">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="CB9" t="s">
         <v>174</v>
@@ -3068,226 +3068,226 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="G10">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="H10">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I10">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J10">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="O10">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P10">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q10">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="R10">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="S10">
-        <v>3.05</v>
+        <v>1.05</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V10">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W10">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI10">
         <v>2.16</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB10" t="s">
         <v>174</v>
@@ -3316,10 +3316,10 @@
         <v>6.4</v>
       </c>
       <c r="H11">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="I11">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3328,16 +3328,16 @@
         <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M11">
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O11">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
         <v>1.7</v>
@@ -3349,7 +3349,7 @@
         <v>1.26</v>
       </c>
       <c r="S11">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T11">
         <v>1.97</v>
@@ -3358,52 +3358,52 @@
         <v>1.8</v>
       </c>
       <c r="V11">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W11">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X11">
         <v>14.5</v>
       </c>
       <c r="Y11">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA11">
+        <v>21</v>
+      </c>
+      <c r="AB11">
+        <v>17.5</v>
+      </c>
+      <c r="AC11">
+        <v>9</v>
+      </c>
+      <c r="AD11">
+        <v>11</v>
+      </c>
+      <c r="AE11">
         <v>23</v>
       </c>
-      <c r="AB11">
-        <v>18.5</v>
-      </c>
-      <c r="AC11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD11">
-        <v>12.5</v>
-      </c>
-      <c r="AE11">
-        <v>26</v>
-      </c>
       <c r="AF11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG11">
+        <v>24</v>
+      </c>
+      <c r="AH11">
         <v>25</v>
       </c>
-      <c r="AH11">
-        <v>27</v>
-      </c>
       <c r="AI11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ11">
         <v>200</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL11">
         <v>110</v>
@@ -3412,124 +3412,124 @@
         <v>180</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO11">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH11">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BI11">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK11">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO11">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU11">
-        <v>1.4</v>
+        <v>2.98</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW11">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB11" t="s">
         <v>174</v>
@@ -3555,31 +3555,31 @@
         <v>2.28</v>
       </c>
       <c r="G12">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="H12">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I12">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>2.74</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L12">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M12">
         <v>1.13</v>
       </c>
       <c r="N12">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O12">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="P12">
         <v>1.43</v>
@@ -3588,22 +3588,22 @@
         <v>2.6</v>
       </c>
       <c r="R12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S12">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>2.12</v>
       </c>
       <c r="U12">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X12">
         <v>9.4</v>
@@ -3630,13 +3630,13 @@
         <v>80</v>
       </c>
       <c r="AF12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG12">
         <v>14</v>
       </c>
       <c r="AH12">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI12">
         <v>110</v>
@@ -3660,118 +3660,118 @@
         <v>120</v>
       </c>
       <c r="AP12">
+        <v>4</v>
+      </c>
+      <c r="AQ12">
+        <v>4.2</v>
+      </c>
+      <c r="AR12">
+        <v>5.2</v>
+      </c>
+      <c r="AS12">
+        <v>6</v>
+      </c>
+      <c r="AT12">
         <v>3.7</v>
       </c>
-      <c r="AQ12">
-        <v>3.9</v>
-      </c>
-      <c r="AR12">
+      <c r="AU12">
+        <v>3.7</v>
+      </c>
+      <c r="AV12">
+        <v>4.8</v>
+      </c>
+      <c r="AW12">
+        <v>6</v>
+      </c>
+      <c r="AX12">
+        <v>4.6</v>
+      </c>
+      <c r="AY12">
+        <v>4.4</v>
+      </c>
+      <c r="AZ12">
+        <v>5.2</v>
+      </c>
+      <c r="BA12">
+        <v>6.2</v>
+      </c>
+      <c r="BB12">
+        <v>5.7</v>
+      </c>
+      <c r="BC12">
+        <v>5.6</v>
+      </c>
+      <c r="BD12">
+        <v>6</v>
+      </c>
+      <c r="BE12">
+        <v>6.4</v>
+      </c>
+      <c r="BF12">
+        <v>5.8</v>
+      </c>
+      <c r="BG12">
+        <v>6.2</v>
+      </c>
+      <c r="BH12">
+        <v>2.96</v>
+      </c>
+      <c r="BI12">
+        <v>2.14</v>
+      </c>
+      <c r="BJ12">
+        <v>14</v>
+      </c>
+      <c r="BK12">
+        <v>3.75</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
         <v>5</v>
       </c>
-      <c r="AS12">
-        <v>5.8</v>
-      </c>
-      <c r="AT12">
-        <v>3.45</v>
-      </c>
-      <c r="AU12">
-        <v>3.4</v>
-      </c>
-      <c r="AV12">
-        <v>4.6</v>
-      </c>
-      <c r="AW12">
-        <v>5.7</v>
-      </c>
-      <c r="AX12">
-        <v>4.4</v>
-      </c>
-      <c r="AY12">
+      <c r="BN12">
+        <v>6.2</v>
+      </c>
+      <c r="BO12">
+        <v>2.8</v>
+      </c>
+      <c r="BP12">
+        <v>28</v>
+      </c>
+      <c r="BQ12">
         <v>4.3</v>
       </c>
-      <c r="AZ12">
-        <v>5.1</v>
-      </c>
-      <c r="BA12">
-        <v>5.8</v>
-      </c>
-      <c r="BB12">
-        <v>5.5</v>
-      </c>
-      <c r="BC12">
-        <v>5.4</v>
-      </c>
-      <c r="BD12">
-        <v>5.8</v>
-      </c>
-      <c r="BE12">
-        <v>6</v>
-      </c>
-      <c r="BF12">
-        <v>5.5</v>
-      </c>
-      <c r="BG12">
-        <v>5.9</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.01</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.01</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.01</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.01</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.01</v>
-      </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB12" t="s">
         <v>174</v>
@@ -3797,13 +3797,13 @@
         <v>2.96</v>
       </c>
       <c r="G13">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H13">
         <v>2.38</v>
       </c>
       <c r="I13">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="J13">
         <v>1.12</v>
@@ -3839,13 +3839,13 @@
         <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3965,55 +3965,55 @@
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>174</v>
@@ -4036,7 +4036,7 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G14">
         <v>2.3</v>
@@ -4201,61 +4201,61 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>174</v>
@@ -4284,7 +4284,7 @@
         <v>2.2</v>
       </c>
       <c r="H15">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I15">
         <v>4.1</v>
@@ -4443,61 +4443,61 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>174</v>
@@ -4562,10 +4562,10 @@
         <v>2.62</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V16">
         <v>1.28</v>
@@ -4807,7 +4807,7 @@
         <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V17">
         <v>1.68</v>
@@ -4870,52 +4870,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4927,61 +4927,61 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
         <v>174</v>
@@ -5004,7 +5004,7 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="G18">
         <v>2.14</v>
@@ -5019,7 +5019,7 @@
         <v>2.66</v>
       </c>
       <c r="K18">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5046,10 +5046,10 @@
         <v>2.54</v>
       </c>
       <c r="T18">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V18">
         <v>1.17</v>
@@ -5112,52 +5112,52 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5169,61 +5169,61 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
         <v>174</v>
@@ -5249,16 +5249,16 @@
         <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H19">
         <v>3.2</v>
       </c>
       <c r="I19">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J19">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K19">
         <v>3.4</v>
@@ -5294,10 +5294,10 @@
         <v>1.93</v>
       </c>
       <c r="V19">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X19">
         <v>13</v>
@@ -5411,61 +5411,61 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>174</v>
@@ -5497,7 +5497,7 @@
         <v>8.6</v>
       </c>
       <c r="I20">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J20">
         <v>4.3</v>
@@ -5605,7 +5605,7 @@
         <v>4.5</v>
       </c>
       <c r="AS20">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT20">
         <v>6</v>
@@ -5653,61 +5653,61 @@
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>174</v>
@@ -5886,7 +5886,7 @@
         <v>6.2</v>
       </c>
       <c r="BF21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG21">
         <v>5.9</v>
@@ -5972,7 +5972,7 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>1.7</v>
+        <v>1.12</v>
       </c>
       <c r="G22">
         <v>990</v>
@@ -5984,7 +5984,7 @@
         <v>990</v>
       </c>
       <c r="J22">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="K22">
         <v>6.6</v>
@@ -5996,22 +5996,22 @@
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>3.45</v>
+        <v>1.71</v>
       </c>
       <c r="O22">
         <v>1.31</v>
       </c>
       <c r="P22">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="Q22">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="R22">
         <v>1.1</v>
       </c>
       <c r="S22">
-        <v>1.05</v>
+        <v>2.78</v>
       </c>
       <c r="T22">
         <v>1.72</v>
@@ -6080,52 +6080,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6137,61 +6137,61 @@
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>174</v>
@@ -6214,34 +6214,34 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="G23">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="H23">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="I23">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="J23">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M23">
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P23">
         <v>2</v>
@@ -6259,13 +6259,13 @@
         <v>1.63</v>
       </c>
       <c r="U23">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V23">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="W23">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X23">
         <v>19</v>
@@ -6280,10 +6280,10 @@
         <v>26</v>
       </c>
       <c r="AB23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23">
         <v>12.5</v>
@@ -6292,10 +6292,10 @@
         <v>23</v>
       </c>
       <c r="AF23">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG23">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH23">
         <v>20</v>
@@ -6304,7 +6304,7 @@
         <v>38</v>
       </c>
       <c r="AJ23">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK23">
         <v>55</v>
@@ -6316,7 +6316,7 @@
         <v>95</v>
       </c>
       <c r="AN23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO23">
         <v>15.5</v>
@@ -6325,7 +6325,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ23">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR23">
         <v>10</v>
@@ -6346,7 +6346,7 @@
         <v>15.5</v>
       </c>
       <c r="AX23">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY23">
         <v>12.5</v>
@@ -6355,22 +6355,22 @@
         <v>13</v>
       </c>
       <c r="BA23">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB23">
+        <v>5.2</v>
+      </c>
+      <c r="BC23">
         <v>5</v>
       </c>
-      <c r="BC23">
-        <v>4.8</v>
-      </c>
       <c r="BD23">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE23">
+        <v>5.2</v>
+      </c>
+      <c r="BF23">
         <v>5</v>
-      </c>
-      <c r="BF23">
-        <v>4.8</v>
       </c>
       <c r="BG23">
         <v>10</v>
@@ -6459,13 +6459,13 @@
         <v>1.1</v>
       </c>
       <c r="G24">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H24">
         <v>1.1</v>
       </c>
       <c r="I24">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J24">
         <v>1.1</v>
@@ -6486,16 +6486,16 @@
         <v>1.01</v>
       </c>
       <c r="P24">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="R24">
         <v>1.08</v>
       </c>
       <c r="S24">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="T24">
         <v>1.11</v>
@@ -6504,10 +6504,10 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6564,52 +6564,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -6621,61 +6621,61 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
         <v>174</v>
@@ -6722,7 +6722,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O25">
         <v>1.02</v>
@@ -6731,25 +6731,25 @@
         <v>1.08</v>
       </c>
       <c r="Q25">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="R25">
         <v>1.08</v>
       </c>
       <c r="S25">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U25">
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6940,58 +6940,58 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="G26">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H26">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="I26">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J26">
-        <v>2.04</v>
+        <v>1.13</v>
       </c>
       <c r="K26">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O26">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P26">
         <v>1.08</v>
       </c>
       <c r="Q26">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R26">
         <v>1.08</v>
       </c>
       <c r="S26">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V26">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W26">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7105,55 +7105,55 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7182,166 +7182,166 @@
         <v>168</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N27">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="O27">
+        <v>1.38</v>
+      </c>
+      <c r="P27">
+        <v>1.86</v>
+      </c>
+      <c r="Q27">
+        <v>2</v>
+      </c>
+      <c r="R27">
+        <v>1.34</v>
+      </c>
+      <c r="S27">
+        <v>3.65</v>
+      </c>
+      <c r="T27">
+        <v>1.85</v>
+      </c>
+      <c r="U27">
+        <v>1.92</v>
+      </c>
+      <c r="V27">
         <v>1.37</v>
       </c>
-      <c r="P27">
-        <v>1.09</v>
-      </c>
-      <c r="Q27">
-        <v>1.37</v>
-      </c>
-      <c r="R27">
-        <v>1.08</v>
-      </c>
-      <c r="S27">
+      <c r="W27">
+        <v>1.67</v>
+      </c>
+      <c r="X27">
+        <v>1000</v>
+      </c>
+      <c r="Y27">
+        <v>1000</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>1000</v>
+      </c>
+      <c r="AC27">
+        <v>1000</v>
+      </c>
+      <c r="AD27">
+        <v>1000</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>1000</v>
+      </c>
+      <c r="AG27">
+        <v>1000</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>1000</v>
+      </c>
+      <c r="AK27">
+        <v>1000</v>
+      </c>
+      <c r="AL27">
+        <v>1000</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>1000</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>1.32</v>
+      </c>
+      <c r="AQ27">
+        <v>1.31</v>
+      </c>
+      <c r="AR27">
         <v>1.38</v>
       </c>
-      <c r="T27">
-        <v>1.11</v>
-      </c>
-      <c r="U27">
-        <v>1.11</v>
-      </c>
-      <c r="V27">
-        <v>1.01</v>
-      </c>
-      <c r="W27">
-        <v>1.01</v>
-      </c>
-      <c r="X27">
-        <v>1000</v>
-      </c>
-      <c r="Y27">
-        <v>1000</v>
-      </c>
-      <c r="Z27">
-        <v>1000</v>
-      </c>
-      <c r="AA27">
-        <v>1000</v>
-      </c>
-      <c r="AB27">
-        <v>1000</v>
-      </c>
-      <c r="AC27">
-        <v>1000</v>
-      </c>
-      <c r="AD27">
-        <v>1000</v>
-      </c>
-      <c r="AE27">
-        <v>1000</v>
-      </c>
-      <c r="AF27">
-        <v>1000</v>
-      </c>
-      <c r="AG27">
-        <v>1000</v>
-      </c>
-      <c r="AH27">
-        <v>1000</v>
-      </c>
-      <c r="AI27">
-        <v>1000</v>
-      </c>
-      <c r="AJ27">
-        <v>1000</v>
-      </c>
-      <c r="AK27">
-        <v>1000</v>
-      </c>
-      <c r="AL27">
-        <v>1000</v>
-      </c>
-      <c r="AM27">
-        <v>1000</v>
-      </c>
-      <c r="AN27">
-        <v>1000</v>
-      </c>
-      <c r="AO27">
-        <v>1000</v>
-      </c>
-      <c r="AP27">
-        <v>1.01</v>
-      </c>
-      <c r="AQ27">
-        <v>1.01</v>
-      </c>
-      <c r="AR27">
-        <v>1.01</v>
-      </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7454,7 +7454,7 @@
         <v>1.01</v>
       </c>
       <c r="P28">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -7472,10 +7472,10 @@
         <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7532,52 +7532,52 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
         <v>1.01</v>
@@ -7589,61 +7589,61 @@
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="s">
         <v>174</v>
@@ -7681,7 +7681,7 @@
         <v>4.4</v>
       </c>
       <c r="K29">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7699,19 +7699,19 @@
         <v>2.34</v>
       </c>
       <c r="Q29">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R29">
         <v>1.55</v>
       </c>
       <c r="S29">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T29">
         <v>1.61</v>
       </c>
       <c r="U29">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V29">
         <v>1.17</v>
@@ -7732,10 +7732,10 @@
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD29">
         <v>1000</v>
@@ -7747,7 +7747,7 @@
         <v>1000</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH29">
         <v>1000</v>
@@ -7774,118 +7774,118 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AQ29">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AR29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AS29">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AT29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AU29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AV29">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AW29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AX29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AY29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AZ29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BA29">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BB29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BC29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BD29">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BE29">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="BF29">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
         <v>174</v>
@@ -7911,19 +7911,19 @@
         <v>2</v>
       </c>
       <c r="G30">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="H30">
         <v>4.1</v>
       </c>
       <c r="I30">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J30">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K30">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -7944,7 +7944,7 @@
         <v>2.18</v>
       </c>
       <c r="R30">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S30">
         <v>4.1</v>
@@ -7959,7 +7959,7 @@
         <v>1.27</v>
       </c>
       <c r="W30">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="X30">
         <v>12</v>
@@ -8007,13 +8007,13 @@
         <v>65</v>
       </c>
       <c r="AM30">
-        <v>900</v>
+        <v>790</v>
       </c>
       <c r="AN30">
         <v>22</v>
       </c>
       <c r="AO30">
-        <v>830</v>
+        <v>720</v>
       </c>
       <c r="AP30">
         <v>9.6</v>
@@ -8174,7 +8174,7 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O31">
         <v>1.31</v>
@@ -8222,7 +8222,7 @@
         <v>8.6</v>
       </c>
       <c r="AD31">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE31">
         <v>60</v>
@@ -8267,7 +8267,7 @@
         <v>15</v>
       </c>
       <c r="AS31">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT31">
         <v>8.4</v>
@@ -8401,22 +8401,22 @@
         <v>5.2</v>
       </c>
       <c r="I32">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J32">
         <v>3.35</v>
       </c>
       <c r="K32">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L32">
         <v>1.5</v>
       </c>
       <c r="M32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N32">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O32">
         <v>1.46</v>
@@ -8425,7 +8425,7 @@
         <v>1.58</v>
       </c>
       <c r="Q32">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R32">
         <v>1.21</v>
@@ -8434,10 +8434,10 @@
         <v>4.4</v>
       </c>
       <c r="T32">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U32">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V32">
         <v>1.21</v>
@@ -8446,22 +8446,22 @@
         <v>2.1</v>
       </c>
       <c r="X32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y32">
         <v>970</v>
       </c>
       <c r="Z32">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AA32">
         <v>1000</v>
       </c>
       <c r="AB32">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC32">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD32">
         <v>950</v>
@@ -8470,10 +8470,10 @@
         <v>1000</v>
       </c>
       <c r="AF32">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG32">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AH32">
         <v>950</v>
@@ -8482,10 +8482,10 @@
         <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL32">
         <v>1000</v>
@@ -8500,46 +8500,46 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AR32">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="AS32">
         <v>2.08</v>
       </c>
       <c r="AT32">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AU32">
-        <v>6</v>
+        <v>1.69</v>
       </c>
       <c r="AV32">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="AW32">
         <v>2.08</v>
       </c>
       <c r="AX32">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY32">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AZ32">
-        <v>5.8</v>
+        <v>2.68</v>
       </c>
       <c r="BA32">
         <v>2.08</v>
       </c>
       <c r="BB32">
-        <v>13.5</v>
+        <v>2.06</v>
       </c>
       <c r="BC32">
-        <v>10</v>
+        <v>2.74</v>
       </c>
       <c r="BD32">
         <v>2.08</v>
@@ -8548,7 +8548,7 @@
         <v>2.08</v>
       </c>
       <c r="BF32">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BG32">
         <v>2.08</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -538,7 +538,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 17:07:52</t>
+    <t>2026-10-05 19:18:38</t>
   </si>
 </sst>
 </file>
@@ -1132,46 +1132,46 @@
         <v>143</v>
       </c>
       <c r="F2">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="H2">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K2">
+        <v>4.2</v>
+      </c>
+      <c r="L2">
+        <v>1.41</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
         <v>3.95</v>
       </c>
-      <c r="L2">
-        <v>1.42</v>
-      </c>
-      <c r="M2">
-        <v>1.07</v>
-      </c>
-      <c r="N2">
-        <v>3.85</v>
-      </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R2">
         <v>1.37</v>
       </c>
       <c r="S2">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
         <v>1.82</v>
@@ -1180,52 +1180,52 @@
         <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>890</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL2">
         <v>38</v>
@@ -1234,124 +1234,124 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO2">
+        <v>60</v>
+      </c>
+      <c r="AP2">
+        <v>14</v>
+      </c>
+      <c r="AQ2">
+        <v>13</v>
+      </c>
+      <c r="AR2">
+        <v>27</v>
+      </c>
+      <c r="AS2">
+        <v>65</v>
+      </c>
+      <c r="AT2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>15</v>
+      </c>
+      <c r="AW2">
+        <v>44</v>
+      </c>
+      <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>17.5</v>
+      </c>
+      <c r="BA2">
         <v>50</v>
       </c>
-      <c r="AP2">
-        <v>13</v>
-      </c>
-      <c r="AQ2">
-        <v>12</v>
-      </c>
-      <c r="AR2">
-        <v>22</v>
-      </c>
-      <c r="AS2">
-        <v>55</v>
-      </c>
-      <c r="AT2">
-        <v>8.6</v>
-      </c>
-      <c r="AU2">
-        <v>7.6</v>
-      </c>
-      <c r="AV2">
-        <v>14</v>
-      </c>
-      <c r="AW2">
-        <v>40</v>
-      </c>
-      <c r="AX2">
-        <v>11.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2">
-        <v>16.5</v>
-      </c>
-      <c r="BA2">
-        <v>48</v>
-      </c>
       <c r="BB2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE2">
         <v>75</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
         <v>34</v>
       </c>
       <c r="BH2">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BN2">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BX2">
         <v>46</v>
       </c>
       <c r="BY2">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="s">
         <v>174</v>
@@ -1374,67 +1374,67 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I3">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="J3">
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M3">
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="O3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q3">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R3">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="S3">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="T3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="V3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="W3">
         <v>1.27</v>
       </c>
       <c r="X3">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA3">
         <v>20</v>
@@ -1443,22 +1443,22 @@
         <v>32</v>
       </c>
       <c r="AC3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD3">
         <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AF3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AG3">
         <v>21</v>
       </c>
       <c r="AH3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI3">
         <v>23</v>
@@ -1470,16 +1470,16 @@
         <v>48</v>
       </c>
       <c r="AL3">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO3">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AP3">
         <v>30</v>
@@ -1491,34 +1491,34 @@
         <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT3">
         <v>26</v>
       </c>
       <c r="AU3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW3">
         <v>13</v>
       </c>
       <c r="AX3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA3">
         <v>19.5</v>
       </c>
       <c r="BB3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC3">
         <v>38</v>
@@ -1527,73 +1527,73 @@
         <v>32</v>
       </c>
       <c r="BE3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BG3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BI3">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BJ3">
         <v>10</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BN3">
         <v>10.5</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BP3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
         <v>11.5</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="CB3" t="s">
         <v>174</v>
@@ -1616,16 +1616,16 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="G4">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="J4">
         <v>4.7</v>
@@ -1634,160 +1634,160 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="Q4">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="S4">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="X4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA4">
         <v>200</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AC4">
         <v>11.5</v>
       </c>
       <c r="AD4">
+        <v>22</v>
+      </c>
+      <c r="AE4">
+        <v>65</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>10.5</v>
+      </c>
+      <c r="AH4">
+        <v>18</v>
+      </c>
+      <c r="AI4">
+        <v>60</v>
+      </c>
+      <c r="AJ4">
+        <v>20</v>
+      </c>
+      <c r="AK4">
+        <v>15</v>
+      </c>
+      <c r="AL4">
+        <v>26</v>
+      </c>
+      <c r="AM4">
+        <v>80</v>
+      </c>
+      <c r="AN4">
+        <v>6.8</v>
+      </c>
+      <c r="AO4">
+        <v>60</v>
+      </c>
+      <c r="AP4">
+        <v>21</v>
+      </c>
+      <c r="AQ4">
         <v>24</v>
       </c>
-      <c r="AE4">
-        <v>90</v>
-      </c>
-      <c r="AF4">
-        <v>11</v>
-      </c>
-      <c r="AG4">
+      <c r="AR4">
+        <v>44</v>
+      </c>
+      <c r="AS4">
+        <v>85</v>
+      </c>
+      <c r="AT4">
+        <v>10.5</v>
+      </c>
+      <c r="AU4">
         <v>10</v>
       </c>
-      <c r="AH4">
-        <v>21</v>
-      </c>
-      <c r="AI4">
-        <v>75</v>
-      </c>
-      <c r="AJ4">
-        <v>15.5</v>
-      </c>
-      <c r="AK4">
-        <v>15.5</v>
-      </c>
-      <c r="AL4">
-        <v>32</v>
-      </c>
-      <c r="AM4">
-        <v>170</v>
-      </c>
-      <c r="AN4">
-        <v>8</v>
-      </c>
-      <c r="AO4">
-        <v>85</v>
-      </c>
-      <c r="AP4">
-        <v>19</v>
-      </c>
-      <c r="AQ4">
-        <v>23</v>
-      </c>
-      <c r="AR4">
+      <c r="AV4">
+        <v>18.5</v>
+      </c>
+      <c r="AW4">
         <v>42</v>
       </c>
-      <c r="AS4">
-        <v>110</v>
-      </c>
-      <c r="AT4">
-        <v>8.6</v>
-      </c>
-      <c r="AU4">
+      <c r="AX4">
+        <v>10.5</v>
+      </c>
+      <c r="AY4">
         <v>9.800000000000001</v>
       </c>
-      <c r="AV4">
-        <v>21</v>
-      </c>
-      <c r="AW4">
-        <v>55</v>
-      </c>
-      <c r="AX4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY4">
-        <v>9</v>
-      </c>
       <c r="AZ4">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BA4">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BB4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC4">
         <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BE4">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BF4">
         <v>6.4</v>
       </c>
       <c r="BG4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI4">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1796,46 +1796,46 @@
         <v>7.8</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP4">
         <v>10.5</v>
       </c>
       <c r="BQ4">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BR4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BW4">
         <v>7</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BY4">
         <v>7</v>
       </c>
       <c r="BZ4">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="CA4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB4" t="s">
         <v>174</v>
@@ -1858,22 +1858,22 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G5">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J5">
         <v>3.5</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
         <v>1.43</v>
@@ -1891,7 +1891,7 @@
         <v>1.88</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
         <v>1.34</v>
@@ -1900,16 +1900,16 @@
         <v>3.8</v>
       </c>
       <c r="T5">
+        <v>1.84</v>
+      </c>
+      <c r="U5">
+        <v>2.1</v>
+      </c>
+      <c r="V5">
+        <v>1.32</v>
+      </c>
+      <c r="W5">
         <v>1.86</v>
-      </c>
-      <c r="U5">
-        <v>2.06</v>
-      </c>
-      <c r="V5">
-        <v>1.31</v>
-      </c>
-      <c r="W5">
-        <v>1.92</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1918,19 +1918,19 @@
         <v>14</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
         <v>55</v>
@@ -1951,19 +1951,19 @@
         <v>26</v>
       </c>
       <c r="AK5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM5">
         <v>140</v>
       </c>
       <c r="AN5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP5">
         <v>12</v>
@@ -1972,7 +1972,7 @@
         <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS5">
         <v>55</v>
@@ -1984,7 +1984,7 @@
         <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
         <v>40</v>
@@ -1993,10 +1993,10 @@
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA5">
         <v>42</v>
@@ -2014,28 +2014,28 @@
         <v>80</v>
       </c>
       <c r="BF5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH5">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BL5">
         <v>160</v>
       </c>
       <c r="BM5">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
         <v>4.9</v>
@@ -2047,37 +2047,37 @@
         <v>15.5</v>
       </c>
       <c r="BQ5">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BT5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU5">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV5">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BW5">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
         <v>30</v>
       </c>
       <c r="CA5">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="s">
         <v>174</v>
@@ -2103,19 +2103,19 @@
         <v>4.5</v>
       </c>
       <c r="G6">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H6">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J6">
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
         <v>1.51</v>
@@ -2136,22 +2136,22 @@
         <v>2.38</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
         <v>4.7</v>
       </c>
       <c r="T6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
         <v>1.87</v>
       </c>
       <c r="V6">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X6">
         <v>11</v>
@@ -2160,7 +2160,7 @@
         <v>7.4</v>
       </c>
       <c r="Z6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA6">
         <v>25</v>
@@ -2169,7 +2169,7 @@
         <v>13.5</v>
       </c>
       <c r="AC6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
         <v>11</v>
@@ -2178,10 +2178,10 @@
         <v>26</v>
       </c>
       <c r="AF6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH6">
         <v>24</v>
@@ -2190,25 +2190,25 @@
         <v>50</v>
       </c>
       <c r="AJ6">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AK6">
         <v>75</v>
       </c>
       <c r="AL6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN6">
         <v>110</v>
       </c>
       <c r="AO6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6">
         <v>6.8</v>
@@ -2220,7 +2220,7 @@
         <v>20</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU6">
         <v>7</v>
@@ -2232,10 +2232,10 @@
         <v>21</v>
       </c>
       <c r="AX6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ6">
         <v>19.5</v>
@@ -2244,16 +2244,16 @@
         <v>40</v>
       </c>
       <c r="BB6">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BC6">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BD6">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BE6">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="BF6">
         <v>48</v>
@@ -2277,49 +2277,49 @@
         <v>210</v>
       </c>
       <c r="BM6">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BN6">
         <v>7.8</v>
       </c>
       <c r="BO6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BP6">
         <v>46</v>
       </c>
       <c r="BQ6">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR6">
         <v>65</v>
       </c>
       <c r="BS6">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BT6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU6">
         <v>4.1</v>
       </c>
       <c r="BV6">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BX6">
         <v>36</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>36</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CB6" t="s">
         <v>174</v>
@@ -2342,76 +2342,76 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G7">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
         <v>3.4</v>
       </c>
       <c r="L7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q7">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T7">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U7">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X7">
         <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB7">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
         <v>15</v>
@@ -2420,25 +2420,25 @@
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ7">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM7">
         <v>150</v>
@@ -2447,73 +2447,73 @@
         <v>36</v>
       </c>
       <c r="AO7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7">
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7">
+        <v>8</v>
+      </c>
+      <c r="AU7">
+        <v>6.4</v>
+      </c>
+      <c r="AV7">
+        <v>12.5</v>
+      </c>
+      <c r="AW7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX7">
+        <v>13.5</v>
+      </c>
+      <c r="AY7">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7">
+        <v>17</v>
+      </c>
+      <c r="BA7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB7">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU7">
-        <v>6.2</v>
-      </c>
-      <c r="AV7">
-        <v>12</v>
-      </c>
-      <c r="AW7">
-        <v>29</v>
-      </c>
-      <c r="AX7">
-        <v>12</v>
-      </c>
-      <c r="AY7">
+      <c r="BC7">
+        <v>25</v>
+      </c>
+      <c r="BD7">
+        <v>9.6</v>
+      </c>
+      <c r="BE7">
         <v>10</v>
       </c>
-      <c r="AZ7">
-        <v>16</v>
-      </c>
-      <c r="BA7">
-        <v>40</v>
-      </c>
-      <c r="BB7">
-        <v>25</v>
-      </c>
-      <c r="BC7">
-        <v>24</v>
-      </c>
-      <c r="BD7">
-        <v>34</v>
-      </c>
-      <c r="BE7">
-        <v>85</v>
-      </c>
       <c r="BF7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BG7">
-        <v>36</v>
+        <v>9.4</v>
       </c>
       <c r="BH7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI7">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2528,7 +2528,7 @@
         <v>4.6</v>
       </c>
       <c r="BP7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ7">
         <v>7.2</v>
@@ -2549,19 +2549,19 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>174</v>
@@ -2596,10 +2596,10 @@
         <v>4.1</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
         <v>1.51</v>
@@ -2620,7 +2620,7 @@
         <v>2.36</v>
       </c>
       <c r="R8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
         <v>4.6</v>
@@ -2629,7 +2629,7 @@
         <v>2</v>
       </c>
       <c r="U8">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -2644,7 +2644,7 @@
         <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA8">
         <v>150</v>
@@ -2713,7 +2713,7 @@
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
@@ -2722,16 +2722,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD8">
         <v>34</v>
@@ -2740,7 +2740,7 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG8">
         <v>46</v>
@@ -2749,19 +2749,19 @@
         <v>3</v>
       </c>
       <c r="BI8">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN8">
         <v>4.8</v>
@@ -2773,37 +2773,37 @@
         <v>18</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB8" t="s">
         <v>174</v>
@@ -2826,16 +2826,16 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="G9">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H9">
         <v>2.8</v>
       </c>
       <c r="I9">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J9">
         <v>2.74</v>
@@ -2844,7 +2844,7 @@
         <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M9">
         <v>1.13</v>
@@ -2856,7 +2856,7 @@
         <v>1.54</v>
       </c>
       <c r="P9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -2865,22 +2865,22 @@
         <v>1.17</v>
       </c>
       <c r="S9">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U9">
         <v>1.73</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X9">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -2907,7 +2907,7 @@
         <v>22</v>
       </c>
       <c r="AG9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH9">
         <v>28</v>
@@ -2934,58 +2934,58 @@
         <v>65</v>
       </c>
       <c r="AP9">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AQ9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AR9">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AS9">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AT9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AU9">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AV9">
         <v>4.3</v>
       </c>
       <c r="AW9">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX9">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AY9">
         <v>4.3</v>
       </c>
       <c r="AZ9">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BA9">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB9">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BC9">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD9">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE9">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF9">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BG9">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BH9">
         <v>2.76</v>
@@ -3071,13 +3071,13 @@
         <v>2.28</v>
       </c>
       <c r="G10">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
         <v>2.86</v>
@@ -3092,13 +3092,13 @@
         <v>1.13</v>
       </c>
       <c r="N10">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P10">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q10">
         <v>2.68</v>
@@ -3107,19 +3107,19 @@
         <v>1.17</v>
       </c>
       <c r="S10">
-        <v>1.05</v>
+        <v>6.6</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U10">
         <v>1.71</v>
       </c>
       <c r="V10">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X10">
         <v>9.800000000000001</v>
@@ -3137,7 +3137,7 @@
         <v>7.4</v>
       </c>
       <c r="AC10">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD10">
         <v>18.5</v>
@@ -3176,58 +3176,58 @@
         <v>130</v>
       </c>
       <c r="AP10">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AQ10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AR10">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS10">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT10">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="AU10">
         <v>3.1</v>
       </c>
       <c r="AV10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AW10">
+        <v>5.1</v>
+      </c>
+      <c r="AX10">
+        <v>4.1</v>
+      </c>
+      <c r="AY10">
+        <v>4</v>
+      </c>
+      <c r="AZ10">
         <v>4.6</v>
       </c>
-      <c r="AX10">
-        <v>3.8</v>
-      </c>
-      <c r="AY10">
-        <v>3.7</v>
-      </c>
-      <c r="AZ10">
-        <v>4.2</v>
-      </c>
       <c r="BA10">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB10">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC10">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD10">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE10">
+        <v>5.3</v>
+      </c>
+      <c r="BF10">
         <v>4.8</v>
       </c>
-      <c r="BF10">
-        <v>4.4</v>
-      </c>
       <c r="BG10">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH10">
         <v>3</v>
@@ -3313,223 +3313,223 @@
         <v>4.8</v>
       </c>
       <c r="G11">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H11">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I11">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M11">
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="P11">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q11">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="R11">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
         <v>3.5</v>
       </c>
       <c r="T11">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="U11">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V11">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="W11">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y11">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="Z11">
         <v>11</v>
       </c>
       <c r="AA11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB11">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD11">
         <v>11</v>
       </c>
       <c r="AE11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF11">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI11">
         <v>50</v>
       </c>
       <c r="AJ11">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AK11">
         <v>120</v>
       </c>
       <c r="AL11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM11">
+        <v>200</v>
+      </c>
+      <c r="AN11">
         <v>180</v>
       </c>
-      <c r="AN11">
-        <v>160</v>
-      </c>
       <c r="AO11">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP11">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AQ11">
+        <v>5.8</v>
+      </c>
+      <c r="AR11">
         <v>3.7</v>
       </c>
-      <c r="AR11">
-        <v>4.3</v>
-      </c>
       <c r="AS11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT11">
+        <v>4.2</v>
+      </c>
+      <c r="AU11">
+        <v>3.6</v>
+      </c>
+      <c r="AV11">
+        <v>3.65</v>
+      </c>
+      <c r="AW11">
+        <v>4.4</v>
+      </c>
+      <c r="AX11">
+        <v>4.9</v>
+      </c>
+      <c r="AY11">
+        <v>4.5</v>
+      </c>
+      <c r="AZ11">
+        <v>4.5</v>
+      </c>
+      <c r="BA11">
+        <v>4.9</v>
+      </c>
+      <c r="BB11">
+        <v>5.3</v>
+      </c>
+      <c r="BC11">
         <v>5.2</v>
       </c>
-      <c r="AT11">
-        <v>5</v>
-      </c>
-      <c r="AU11">
+      <c r="BD11">
+        <v>5.2</v>
+      </c>
+      <c r="BE11">
+        <v>5.3</v>
+      </c>
+      <c r="BF11">
+        <v>5.3</v>
+      </c>
+      <c r="BG11">
         <v>3.95</v>
       </c>
-      <c r="AV11">
-        <v>4.3</v>
-      </c>
-      <c r="AW11">
+      <c r="BH11">
+        <v>3.55</v>
+      </c>
+      <c r="BI11">
+        <v>2.68</v>
+      </c>
+      <c r="BJ11">
+        <v>13</v>
+      </c>
+      <c r="BK11">
+        <v>4.5</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>6.6</v>
+      </c>
+      <c r="BN11">
+        <v>11</v>
+      </c>
+      <c r="BO11">
+        <v>4.2</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>6.2</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>6.2</v>
+      </c>
+      <c r="BT11">
+        <v>4.4</v>
+      </c>
+      <c r="BU11">
+        <v>2.68</v>
+      </c>
+      <c r="BV11">
+        <v>12.5</v>
+      </c>
+      <c r="BW11">
+        <v>4.4</v>
+      </c>
+      <c r="BX11">
+        <v>34</v>
+      </c>
+      <c r="BY11">
+        <v>5.7</v>
+      </c>
+      <c r="BZ11">
+        <v>27</v>
+      </c>
+      <c r="CA11">
         <v>5.4</v>
-      </c>
-      <c r="AX11">
-        <v>6</v>
-      </c>
-      <c r="AY11">
-        <v>5.4</v>
-      </c>
-      <c r="AZ11">
-        <v>5.5</v>
-      </c>
-      <c r="BA11">
-        <v>6</v>
-      </c>
-      <c r="BB11">
-        <v>6.8</v>
-      </c>
-      <c r="BC11">
-        <v>6.6</v>
-      </c>
-      <c r="BD11">
-        <v>6.6</v>
-      </c>
-      <c r="BE11">
-        <v>6.6</v>
-      </c>
-      <c r="BF11">
-        <v>6.6</v>
-      </c>
-      <c r="BG11">
-        <v>4.8</v>
-      </c>
-      <c r="BH11">
-        <v>3.3</v>
-      </c>
-      <c r="BI11">
-        <v>2.74</v>
-      </c>
-      <c r="BJ11">
-        <v>12</v>
-      </c>
-      <c r="BK11">
-        <v>5.1</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>7.2</v>
-      </c>
-      <c r="BN11">
-        <v>9.4</v>
-      </c>
-      <c r="BO11">
-        <v>4.5</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>6.6</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>6.6</v>
-      </c>
-      <c r="BT11">
-        <v>4.5</v>
-      </c>
-      <c r="BU11">
-        <v>2.98</v>
-      </c>
-      <c r="BV11">
-        <v>13.5</v>
-      </c>
-      <c r="BW11">
-        <v>5.3</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>7</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
-        <v>6.8</v>
       </c>
       <c r="CB11" t="s">
         <v>174</v>
@@ -3552,13 +3552,13 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G12">
         <v>2.74</v>
       </c>
       <c r="H12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I12">
         <v>4</v>
@@ -3573,31 +3573,31 @@
         <v>1.58</v>
       </c>
       <c r="M12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N12">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O12">
         <v>1.56</v>
       </c>
       <c r="P12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q12">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R12">
         <v>1.15</v>
       </c>
       <c r="S12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U12">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V12">
         <v>1.33</v>
@@ -3663,7 +3663,7 @@
         <v>4</v>
       </c>
       <c r="AQ12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR12">
         <v>5.2</v>
@@ -3672,10 +3672,10 @@
         <v>6</v>
       </c>
       <c r="AT12">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU12">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AV12">
         <v>4.8</v>
@@ -3684,7 +3684,7 @@
         <v>6</v>
       </c>
       <c r="AX12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AY12">
         <v>4.4</v>
@@ -3794,226 +3794,226 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G13">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="H13">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="I13">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="J13">
+        <v>2.88</v>
+      </c>
+      <c r="K13">
+        <v>3.3</v>
+      </c>
+      <c r="L13">
+        <v>1.55</v>
+      </c>
+      <c r="M13">
         <v>1.12</v>
       </c>
-      <c r="K13">
+      <c r="N13">
+        <v>2.6</v>
+      </c>
+      <c r="O13">
+        <v>1.55</v>
+      </c>
+      <c r="P13">
+        <v>1.54</v>
+      </c>
+      <c r="Q13">
+        <v>2.5</v>
+      </c>
+      <c r="R13">
+        <v>1.19</v>
+      </c>
+      <c r="S13">
+        <v>4.4</v>
+      </c>
+      <c r="T13">
+        <v>2.02</v>
+      </c>
+      <c r="U13">
+        <v>1.8</v>
+      </c>
+      <c r="V13">
+        <v>1.53</v>
+      </c>
+      <c r="W13">
+        <v>1.41</v>
+      </c>
+      <c r="X13">
+        <v>11</v>
+      </c>
+      <c r="Y13">
+        <v>8.6</v>
+      </c>
+      <c r="Z13">
+        <v>17</v>
+      </c>
+      <c r="AA13">
+        <v>55</v>
+      </c>
+      <c r="AB13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC13">
+        <v>7.4</v>
+      </c>
+      <c r="AD13">
+        <v>13.5</v>
+      </c>
+      <c r="AE13">
+        <v>48</v>
+      </c>
+      <c r="AF13">
+        <v>22</v>
+      </c>
+      <c r="AG13">
+        <v>15.5</v>
+      </c>
+      <c r="AH13">
+        <v>23</v>
+      </c>
+      <c r="AI13">
+        <v>80</v>
+      </c>
+      <c r="AJ13">
+        <v>160</v>
+      </c>
+      <c r="AK13">
+        <v>60</v>
+      </c>
+      <c r="AL13">
+        <v>90</v>
+      </c>
+      <c r="AM13">
+        <v>500</v>
+      </c>
+      <c r="AN13">
+        <v>80</v>
+      </c>
+      <c r="AO13">
+        <v>55</v>
+      </c>
+      <c r="AP13">
+        <v>4.4</v>
+      </c>
+      <c r="AQ13">
+        <v>4</v>
+      </c>
+      <c r="AR13">
+        <v>5.2</v>
+      </c>
+      <c r="AS13">
+        <v>6.4</v>
+      </c>
+      <c r="AT13">
         <v>4.2</v>
       </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.09</v>
-      </c>
-      <c r="N13">
-        <v>2.2</v>
-      </c>
-      <c r="O13">
-        <v>1.49</v>
-      </c>
-      <c r="P13">
-        <v>1.4</v>
-      </c>
-      <c r="Q13">
+      <c r="AU13">
+        <v>3.7</v>
+      </c>
+      <c r="AV13">
+        <v>4.8</v>
+      </c>
+      <c r="AW13">
+        <v>6.4</v>
+      </c>
+      <c r="AX13">
+        <v>5.6</v>
+      </c>
+      <c r="AY13">
+        <v>5</v>
+      </c>
+      <c r="AZ13">
+        <v>5.7</v>
+      </c>
+      <c r="BA13">
+        <v>6.8</v>
+      </c>
+      <c r="BB13">
+        <v>6.8</v>
+      </c>
+      <c r="BC13">
+        <v>6.6</v>
+      </c>
+      <c r="BD13">
+        <v>6.8</v>
+      </c>
+      <c r="BE13">
+        <v>7.2</v>
+      </c>
+      <c r="BF13">
+        <v>6.8</v>
+      </c>
+      <c r="BG13">
+        <v>6.4</v>
+      </c>
+      <c r="BH13">
+        <v>2.82</v>
+      </c>
+      <c r="BI13">
+        <v>2.48</v>
+      </c>
+      <c r="BJ13">
+        <v>11.5</v>
+      </c>
+      <c r="BK13">
+        <v>5.7</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
         <v>2.24</v>
       </c>
-      <c r="R13">
-        <v>1.07</v>
-      </c>
-      <c r="S13">
-        <v>2.82</v>
-      </c>
-      <c r="T13">
-        <v>1.11</v>
-      </c>
-      <c r="U13">
-        <v>1.11</v>
-      </c>
-      <c r="V13">
-        <v>1.48</v>
-      </c>
-      <c r="W13">
-        <v>1.34</v>
-      </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
-      <c r="Z13">
-        <v>1000</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>1000</v>
-      </c>
-      <c r="AC13">
-        <v>1000</v>
-      </c>
-      <c r="AD13">
-        <v>1000</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
-        <v>1000</v>
-      </c>
-      <c r="AH13">
-        <v>1000</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>1000</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.01</v>
-      </c>
-      <c r="AQ13">
-        <v>1.01</v>
-      </c>
-      <c r="AR13">
-        <v>1.03</v>
-      </c>
-      <c r="AS13">
-        <v>1.03</v>
-      </c>
-      <c r="AT13">
-        <v>1.01</v>
-      </c>
-      <c r="AU13">
-        <v>1.01</v>
-      </c>
-      <c r="AV13">
-        <v>1.03</v>
-      </c>
-      <c r="AW13">
-        <v>1.03</v>
-      </c>
-      <c r="AX13">
-        <v>1.03</v>
-      </c>
-      <c r="AY13">
-        <v>1.03</v>
-      </c>
-      <c r="AZ13">
-        <v>1.03</v>
-      </c>
-      <c r="BA13">
-        <v>1.03</v>
-      </c>
-      <c r="BB13">
-        <v>1.03</v>
-      </c>
-      <c r="BC13">
-        <v>1.03</v>
-      </c>
-      <c r="BD13">
-        <v>1.03</v>
-      </c>
-      <c r="BE13">
-        <v>1.03</v>
-      </c>
-      <c r="BF13">
-        <v>1.01</v>
-      </c>
-      <c r="BG13">
-        <v>1.01</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>2.18</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.04</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.04</v>
-      </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="CB13" t="s">
         <v>174</v>
@@ -4072,7 +4072,7 @@
         <v>2.06</v>
       </c>
       <c r="R14">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S14">
         <v>3.7</v>
@@ -4111,7 +4111,7 @@
         <v>16</v>
       </c>
       <c r="AE14">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF14">
         <v>14</v>
@@ -4120,28 +4120,28 @@
         <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI14">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ14">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AK14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL14">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM14">
         <v>130</v>
       </c>
       <c r="AN14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO14">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP14">
         <v>11</v>
@@ -4150,10 +4150,10 @@
         <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AS14">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AT14">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14">
         <v>12</v>
@@ -4177,25 +4177,25 @@
         <v>16</v>
       </c>
       <c r="BA14">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC14">
         <v>21</v>
       </c>
       <c r="BD14">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE14">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BF14">
         <v>16</v>
       </c>
       <c r="BG14">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4281,7 +4281,7 @@
         <v>2.08</v>
       </c>
       <c r="G15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H15">
         <v>3.75</v>
@@ -4296,7 +4296,7 @@
         <v>3.7</v>
       </c>
       <c r="L15">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M15">
         <v>1.07</v>
@@ -4329,7 +4329,7 @@
         <v>1.32</v>
       </c>
       <c r="W15">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X15">
         <v>16.5</v>
@@ -4338,16 +4338,16 @@
         <v>17</v>
       </c>
       <c r="Z15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA15">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AB15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC15">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15">
         <v>19.5</v>
@@ -4356,16 +4356,16 @@
         <v>60</v>
       </c>
       <c r="AF15">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG15">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH15">
         <v>19</v>
       </c>
       <c r="AI15">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ15">
         <v>32</v>
@@ -4377,7 +4377,7 @@
         <v>48</v>
       </c>
       <c r="AM15">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN15">
         <v>21</v>
@@ -4392,10 +4392,10 @@
         <v>12</v>
       </c>
       <c r="AR15">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS15">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT15">
         <v>8.199999999999999</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="AW15">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX15">
         <v>11</v>
@@ -4419,25 +4419,25 @@
         <v>16</v>
       </c>
       <c r="BA15">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB15">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BC15">
         <v>19.5</v>
       </c>
       <c r="BD15">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE15">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG15">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4532,7 +4532,7 @@
         <v>4.8</v>
       </c>
       <c r="J16">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="K16">
         <v>3.9</v>
@@ -4544,10 +4544,10 @@
         <v>1.09</v>
       </c>
       <c r="N16">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O16">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="P16">
         <v>1.41</v>
@@ -4559,7 +4559,7 @@
         <v>1.07</v>
       </c>
       <c r="S16">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T16">
         <v>1.12</v>
@@ -4574,112 +4574,112 @@
         <v>1.6</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z16">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA16">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB16">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC16">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD16">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE16">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG16">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI16">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ16">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK16">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL16">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM16">
         <v>250</v>
       </c>
       <c r="AN16">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO16">
         <v>130</v>
       </c>
       <c r="AP16">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ16">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR16">
+        <v>6</v>
+      </c>
+      <c r="AS16">
+        <v>7</v>
+      </c>
+      <c r="AT16">
+        <v>4.2</v>
+      </c>
+      <c r="AU16">
         <v>4.4</v>
       </c>
-      <c r="AS16">
-        <v>5</v>
-      </c>
-      <c r="AT16">
-        <v>3.15</v>
-      </c>
-      <c r="AU16">
-        <v>3.15</v>
-      </c>
       <c r="AV16">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW16">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX16">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY16">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AZ16">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB16">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC16">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD16">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE16">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BF16">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG16">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BH16">
         <v>3</v>
@@ -4771,13 +4771,13 @@
         <v>2.06</v>
       </c>
       <c r="I17">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J17">
         <v>2.78</v>
       </c>
       <c r="K17">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L17">
         <v>1.47</v>
@@ -4786,10 +4786,10 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="O17">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="P17">
         <v>1.45</v>
@@ -4804,13 +4804,13 @@
         <v>2.94</v>
       </c>
       <c r="T17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U17">
         <v>1.12</v>
       </c>
       <c r="V17">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W17">
         <v>1.23</v>
@@ -4825,13 +4825,13 @@
         <v>1000</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17">
         <v>1000</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD17">
         <v>1000</v>
@@ -4852,7 +4852,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK17">
         <v>1000</v>
@@ -4870,58 +4870,58 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
         <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5004,22 +5004,22 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="G18">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H18">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J18">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="K18">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5055,37 +5055,37 @@
         <v>1.17</v>
       </c>
       <c r="W18">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y18">
         <v>1000</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE18">
         <v>1000</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH18">
         <v>1000</v>
@@ -5094,13 +5094,13 @@
         <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM18">
         <v>1000</v>
@@ -5112,58 +5112,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5246,22 +5246,22 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G19">
         <v>2.6</v>
       </c>
       <c r="H19">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I19">
         <v>3.65</v>
       </c>
       <c r="J19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K19">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L19">
         <v>1.47</v>
@@ -5270,10 +5270,10 @@
         <v>1.09</v>
       </c>
       <c r="N19">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O19">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P19">
         <v>1.69</v>
@@ -5282,7 +5282,7 @@
         <v>2.2</v>
       </c>
       <c r="R19">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S19">
         <v>4.1</v>
@@ -5291,7 +5291,7 @@
         <v>1.88</v>
       </c>
       <c r="U19">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V19">
         <v>1.37</v>
@@ -5300,7 +5300,7 @@
         <v>1.62</v>
       </c>
       <c r="X19">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y19">
         <v>11.5</v>
@@ -5309,7 +5309,7 @@
         <v>26</v>
       </c>
       <c r="AA19">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB19">
         <v>9.199999999999999</v>
@@ -5333,19 +5333,19 @@
         <v>21</v>
       </c>
       <c r="AI19">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ19">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AK19">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL19">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM19">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN19">
         <v>34</v>
@@ -5363,7 +5363,7 @@
         <v>17.5</v>
       </c>
       <c r="AS19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT19">
         <v>7.6</v>
@@ -5375,7 +5375,7 @@
         <v>12.5</v>
       </c>
       <c r="AW19">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX19">
         <v>12.5</v>
@@ -5387,25 +5387,25 @@
         <v>16</v>
       </c>
       <c r="BA19">
+        <v>7.4</v>
+      </c>
+      <c r="BB19">
+        <v>7.2</v>
+      </c>
+      <c r="BC19">
         <v>6.8</v>
       </c>
-      <c r="BB19">
-        <v>6.6</v>
-      </c>
-      <c r="BC19">
-        <v>6.4</v>
-      </c>
       <c r="BD19">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE19">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF19">
         <v>21</v>
       </c>
       <c r="BG19">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5488,7 +5488,7 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G20">
         <v>1.5</v>
@@ -5497,13 +5497,13 @@
         <v>8.6</v>
       </c>
       <c r="I20">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K20">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L20">
         <v>1.39</v>
@@ -5527,7 +5527,7 @@
         <v>1.34</v>
       </c>
       <c r="S20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T20">
         <v>2.2</v>
@@ -5536,7 +5536,7 @@
         <v>1.72</v>
       </c>
       <c r="V20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W20">
         <v>2.98</v>
@@ -5545,13 +5545,13 @@
         <v>17.5</v>
       </c>
       <c r="Y20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z20">
         <v>110</v>
       </c>
       <c r="AA20">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AB20">
         <v>8.4</v>
@@ -5563,7 +5563,7 @@
         <v>44</v>
       </c>
       <c r="AE20">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF20">
         <v>9.4</v>
@@ -5575,13 +5575,13 @@
         <v>36</v>
       </c>
       <c r="AI20">
-        <v>200</v>
+        <v>470</v>
       </c>
       <c r="AJ20">
         <v>15</v>
       </c>
       <c r="AK20">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL20">
         <v>60</v>
@@ -5590,7 +5590,7 @@
         <v>260</v>
       </c>
       <c r="AN20">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AO20">
         <v>380</v>
@@ -5599,28 +5599,28 @@
         <v>12.5</v>
       </c>
       <c r="AQ20">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="AR20">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AS20">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU20">
         <v>9.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AW20">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX20">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY20">
         <v>9</v>
@@ -5629,7 +5629,7 @@
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BB20">
         <v>11</v>
@@ -5638,16 +5638,16 @@
         <v>15</v>
       </c>
       <c r="BD20">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE20">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BF20">
         <v>7.6</v>
       </c>
       <c r="BG20">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5733,22 +5733,22 @@
         <v>2</v>
       </c>
       <c r="G21">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H21">
+        <v>3.9</v>
+      </c>
+      <c r="I21">
+        <v>4.2</v>
+      </c>
+      <c r="J21">
         <v>3.75</v>
-      </c>
-      <c r="I21">
-        <v>4.4</v>
-      </c>
-      <c r="J21">
-        <v>3.7</v>
       </c>
       <c r="K21">
         <v>4.1</v>
       </c>
       <c r="L21">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M21">
         <v>1.05</v>
@@ -5763,7 +5763,7 @@
         <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R21">
         <v>1.48</v>
@@ -5778,10 +5778,10 @@
         <v>2.34</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W21">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X21">
         <v>19.5</v>
@@ -5814,19 +5814,19 @@
         <v>11</v>
       </c>
       <c r="AH21">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI21">
         <v>55</v>
       </c>
       <c r="AJ21">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AK21">
         <v>21</v>
       </c>
       <c r="AL21">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM21">
         <v>90</v>
@@ -5844,10 +5844,10 @@
         <v>15</v>
       </c>
       <c r="AR21">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS21">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT21">
         <v>10</v>
@@ -5859,7 +5859,7 @@
         <v>14</v>
       </c>
       <c r="AW21">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX21">
         <v>12</v>
@@ -5871,7 +5871,7 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB21">
         <v>20</v>
@@ -5880,16 +5880,16 @@
         <v>16.5</v>
       </c>
       <c r="BD21">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE21">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BF21">
         <v>10</v>
       </c>
       <c r="BG21">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH21">
         <v>4.1</v>
@@ -5972,19 +5972,19 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="G22">
-        <v>990</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>1.12</v>
+        <v>2.18</v>
       </c>
       <c r="I22">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="J22">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="K22">
         <v>6.6</v>
@@ -5993,37 +5993,37 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="O22">
         <v>1.31</v>
       </c>
       <c r="P22">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="Q22">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R22">
         <v>1.1</v>
       </c>
       <c r="S22">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T22">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U22">
         <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6035,13 +6035,13 @@
         <v>1000</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22">
         <v>1000</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD22">
         <v>1000</v>
@@ -6056,13 +6056,13 @@
         <v>1000</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI22">
         <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22">
         <v>1000</v>
@@ -6071,67 +6071,67 @@
         <v>1000</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6217,52 +6217,52 @@
         <v>3.55</v>
       </c>
       <c r="G23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H23">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I23">
         <v>2.2</v>
       </c>
       <c r="J23">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>1.26</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
         <v>1.25</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q23">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R23">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S23">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T23">
         <v>1.63</v>
       </c>
       <c r="U23">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="V23">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W23">
         <v>1.3</v>
@@ -6283,10 +6283,10 @@
         <v>18</v>
       </c>
       <c r="AC23">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE23">
         <v>23</v>
@@ -6295,40 +6295,40 @@
         <v>34</v>
       </c>
       <c r="AG23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH23">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI23">
         <v>38</v>
       </c>
       <c r="AJ23">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL23">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM23">
-        <v>95</v>
+        <v>580</v>
       </c>
       <c r="AN23">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AO23">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP23">
         <v>12.5</v>
       </c>
       <c r="AQ23">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS23">
         <v>18</v>
@@ -6337,7 +6337,7 @@
         <v>12</v>
       </c>
       <c r="AU23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV23">
         <v>8.199999999999999</v>
@@ -6346,7 +6346,7 @@
         <v>15.5</v>
       </c>
       <c r="AX23">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY23">
         <v>12.5</v>
@@ -6355,22 +6355,22 @@
         <v>13</v>
       </c>
       <c r="BA23">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB23">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BC23">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BD23">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BE23">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF23">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BG23">
         <v>10</v>
@@ -6486,10 +6486,10 @@
         <v>1.01</v>
       </c>
       <c r="P24">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R24">
         <v>1.08</v>
@@ -6698,22 +6698,22 @@
         <v>166</v>
       </c>
       <c r="F25">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="G25">
         <v>990</v>
       </c>
       <c r="H25">
-        <v>1.12</v>
+        <v>1.93</v>
       </c>
       <c r="I25">
         <v>1000</v>
       </c>
       <c r="J25">
-        <v>1.13</v>
+        <v>2.32</v>
       </c>
       <c r="K25">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6722,79 +6722,79 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="O25">
         <v>1.02</v>
       </c>
       <c r="P25">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="Q25">
         <v>1.14</v>
       </c>
       <c r="R25">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S25">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T25">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM25">
         <v>1000</v>
@@ -6806,58 +6806,58 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR25">
         <v>1.03</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV25">
         <v>1.03</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH25">
         <v>2.8</v>
@@ -6893,7 +6893,7 @@
         <v>65</v>
       </c>
       <c r="BS25">
-        <v>1.97</v>
+        <v>6.6</v>
       </c>
       <c r="BT25">
         <v>5.8</v>
@@ -6917,7 +6917,7 @@
         <v>65</v>
       </c>
       <c r="CA25">
-        <v>1.97</v>
+        <v>6.6</v>
       </c>
       <c r="CB25" t="s">
         <v>174</v>
@@ -6940,46 +6940,46 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="G26">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H26">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="I26">
         <v>990</v>
       </c>
       <c r="J26">
-        <v>1.13</v>
+        <v>2.18</v>
       </c>
       <c r="K26">
-        <v>3.9</v>
+        <v>420</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N26">
         <v>1.1</v>
       </c>
       <c r="O26">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P26">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q26">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="R26">
         <v>1.08</v>
       </c>
       <c r="S26">
-        <v>1.47</v>
+        <v>1.05</v>
       </c>
       <c r="T26">
         <v>1.11</v>
@@ -6988,10 +6988,10 @@
         <v>1.11</v>
       </c>
       <c r="V26">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W26">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7185,19 +7185,19 @@
         <v>2.24</v>
       </c>
       <c r="G27">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H27">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I27">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J27">
         <v>3.45</v>
       </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L27">
         <v>1.35</v>
@@ -7206,25 +7206,25 @@
         <v>1.04</v>
       </c>
       <c r="N27">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P27">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R27">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S27">
         <v>3.65</v>
       </c>
       <c r="T27">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="U27">
         <v>1.92</v>
@@ -7233,115 +7233,115 @@
         <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AP27">
-        <v>1.32</v>
+        <v>6.2</v>
       </c>
       <c r="AQ27">
-        <v>1.31</v>
+        <v>8</v>
       </c>
       <c r="AR27">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="AS27">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="AT27">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="AU27">
-        <v>1.24</v>
+        <v>4.4</v>
       </c>
       <c r="AV27">
-        <v>1.38</v>
+        <v>8.4</v>
       </c>
       <c r="AW27">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AX27">
-        <v>1.38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27">
-        <v>1.31</v>
+        <v>6.4</v>
       </c>
       <c r="AZ27">
-        <v>1.38</v>
+        <v>1.84</v>
       </c>
       <c r="BA27">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="BB27">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="BC27">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="BD27">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="BE27">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="BF27">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="BG27">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7424,13 +7424,13 @@
         <v>169</v>
       </c>
       <c r="F28">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G28">
         <v>990</v>
       </c>
       <c r="H28">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I28">
         <v>990</v>
@@ -7457,13 +7457,13 @@
         <v>1.09</v>
       </c>
       <c r="Q28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R28">
         <v>1.08</v>
       </c>
       <c r="S28">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T28">
         <v>1.11</v>
@@ -7666,64 +7666,64 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G29">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H29">
         <v>5</v>
       </c>
       <c r="I29">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J29">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="L29">
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N29">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="O29">
         <v>1.17</v>
       </c>
       <c r="P29">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="Q29">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R29">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="S29">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T29">
         <v>1.61</v>
       </c>
       <c r="U29">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V29">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W29">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X29">
         <v>1000</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z29">
         <v>1000</v>
@@ -7735,97 +7735,97 @@
         <v>950</v>
       </c>
       <c r="AC29">
+        <v>40</v>
+      </c>
+      <c r="AD29">
         <v>950</v>
       </c>
-      <c r="AD29">
-        <v>1000</v>
-      </c>
       <c r="AE29">
         <v>1000</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG29">
+        <v>26</v>
+      </c>
+      <c r="AH29">
         <v>950</v>
       </c>
-      <c r="AH29">
-        <v>1000</v>
-      </c>
       <c r="AI29">
         <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM29">
         <v>1000</v>
       </c>
       <c r="AN29">
-        <v>8.4</v>
+        <v>500</v>
       </c>
       <c r="AO29">
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>1.14</v>
+        <v>13</v>
       </c>
       <c r="AQ29">
-        <v>1.88</v>
+        <v>4.1</v>
       </c>
       <c r="AR29">
-        <v>1.14</v>
+        <v>9.4</v>
       </c>
       <c r="AS29">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AT29">
-        <v>1.14</v>
+        <v>3.1</v>
       </c>
       <c r="AU29">
-        <v>1.14</v>
+        <v>3.1</v>
       </c>
       <c r="AV29">
-        <v>1.14</v>
+        <v>17</v>
       </c>
       <c r="AW29">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AX29">
-        <v>1.14</v>
+        <v>3</v>
       </c>
       <c r="AY29">
-        <v>1.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>1.14</v>
+        <v>15</v>
       </c>
       <c r="BA29">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BB29">
-        <v>1.14</v>
+        <v>12</v>
       </c>
       <c r="BC29">
-        <v>1.14</v>
+        <v>12</v>
       </c>
       <c r="BD29">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BE29">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="BF29">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG29">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7917,10 +7917,10 @@
         <v>4.1</v>
       </c>
       <c r="I30">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
         <v>3.55</v>
@@ -7929,16 +7929,16 @@
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N30">
         <v>3.05</v>
       </c>
       <c r="O30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P30">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q30">
         <v>2.18</v>
@@ -7953,13 +7953,13 @@
         <v>1.92</v>
       </c>
       <c r="U30">
+        <v>1.91</v>
+      </c>
+      <c r="V30">
+        <v>1.28</v>
+      </c>
+      <c r="W30">
         <v>1.9</v>
-      </c>
-      <c r="V30">
-        <v>1.27</v>
-      </c>
-      <c r="W30">
-        <v>1.89</v>
       </c>
       <c r="X30">
         <v>12</v>
@@ -7968,7 +7968,7 @@
         <v>14</v>
       </c>
       <c r="Z30">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA30">
         <v>120</v>
@@ -8007,13 +8007,13 @@
         <v>65</v>
       </c>
       <c r="AM30">
-        <v>790</v>
+        <v>680</v>
       </c>
       <c r="AN30">
         <v>22</v>
       </c>
       <c r="AO30">
-        <v>720</v>
+        <v>610</v>
       </c>
       <c r="AP30">
         <v>9.6</v>
@@ -8025,7 +8025,7 @@
         <v>8</v>
       </c>
       <c r="AS30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT30">
         <v>6.8</v>
@@ -8037,7 +8037,7 @@
         <v>15</v>
       </c>
       <c r="AW30">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX30">
         <v>10.5</v>
@@ -8049,7 +8049,7 @@
         <v>17</v>
       </c>
       <c r="BA30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB30">
         <v>19</v>
@@ -8058,16 +8058,16 @@
         <v>18.5</v>
       </c>
       <c r="BD30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF30">
         <v>16.5</v>
       </c>
       <c r="BG30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8153,7 +8153,7 @@
         <v>1.89</v>
       </c>
       <c r="G31">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H31">
         <v>4.4</v>
@@ -8162,13 +8162,13 @@
         <v>4.7</v>
       </c>
       <c r="J31">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L31">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M31">
         <v>1.06</v>
@@ -8189,10 +8189,10 @@
         <v>1.39</v>
       </c>
       <c r="S31">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T31">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U31">
         <v>2.14</v>
@@ -8219,7 +8219,7 @@
         <v>9.4</v>
       </c>
       <c r="AC31">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD31">
         <v>17.5</v>
@@ -8255,7 +8255,7 @@
         <v>13</v>
       </c>
       <c r="AO31">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP31">
         <v>14</v>
@@ -8264,16 +8264,16 @@
         <v>15</v>
       </c>
       <c r="AR31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT31">
         <v>8.4</v>
       </c>
       <c r="AU31">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV31">
         <v>15.5</v>
@@ -8285,13 +8285,13 @@
         <v>10.5</v>
       </c>
       <c r="AY31">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ31">
         <v>16</v>
       </c>
       <c r="BA31">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB31">
         <v>18.5</v>
@@ -8309,7 +8309,7 @@
         <v>11</v>
       </c>
       <c r="BG31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH31">
         <v>3.4</v>
@@ -8392,10 +8392,10 @@
         <v>173</v>
       </c>
       <c r="F32">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G32">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H32">
         <v>5.2</v>
@@ -8404,10 +8404,10 @@
         <v>5.8</v>
       </c>
       <c r="J32">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K32">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L32">
         <v>1.5</v>
@@ -8437,28 +8437,28 @@
         <v>2.18</v>
       </c>
       <c r="U32">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V32">
         <v>1.21</v>
       </c>
       <c r="W32">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X32">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="Y32">
         <v>970</v>
       </c>
       <c r="Z32">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="AA32">
         <v>1000</v>
       </c>
       <c r="AB32">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC32">
         <v>9.199999999999999</v>
@@ -8470,10 +8470,10 @@
         <v>1000</v>
       </c>
       <c r="AF32">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG32">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH32">
         <v>950</v>
@@ -8482,10 +8482,10 @@
         <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>270</v>
+        <v>120</v>
       </c>
       <c r="AK32">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="AL32">
         <v>1000</v>
@@ -8500,58 +8500,58 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ32">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AR32">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AS32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AT32">
         <v>5.3</v>
       </c>
       <c r="AU32">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AV32">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="AW32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AX32">
         <v>6.8</v>
       </c>
       <c r="AY32">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AZ32">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="BA32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BB32">
-        <v>2.06</v>
+        <v>3.45</v>
       </c>
       <c r="BC32">
-        <v>2.74</v>
+        <v>2</v>
       </c>
       <c r="BD32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BE32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BF32">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BG32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BH32">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -538,7 +538,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 19:18:38</t>
+    <t>2026-10-05 21:30:43</t>
   </si>
 </sst>
 </file>
@@ -1132,226 +1132,226 @@
         <v>143</v>
       </c>
       <c r="F2">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="I2">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>2.58</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
-        <v>3.95</v>
+        <v>2.24</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="Q2">
-        <v>1.95</v>
+        <v>3.55</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="Y2">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA2">
-        <v>890</v>
+        <v>120</v>
       </c>
       <c r="AB2">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AF2">
         <v>12</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
+        <v>36</v>
+      </c>
+      <c r="AI2">
+        <v>180</v>
+      </c>
+      <c r="AJ2">
+        <v>38</v>
+      </c>
+      <c r="AK2">
+        <v>42</v>
+      </c>
+      <c r="AL2">
+        <v>110</v>
+      </c>
+      <c r="AM2">
+        <v>470</v>
+      </c>
+      <c r="AN2">
+        <v>60</v>
+      </c>
+      <c r="AO2">
+        <v>180</v>
+      </c>
+      <c r="AP2">
+        <v>6.8</v>
+      </c>
+      <c r="AQ2">
+        <v>8</v>
+      </c>
+      <c r="AR2">
         <v>21</v>
       </c>
-      <c r="AI2">
-        <v>65</v>
-      </c>
-      <c r="AJ2">
-        <v>25</v>
-      </c>
-      <c r="AK2">
-        <v>21</v>
-      </c>
-      <c r="AL2">
-        <v>38</v>
-      </c>
-      <c r="AM2">
-        <v>110</v>
-      </c>
-      <c r="AN2">
-        <v>13.5</v>
-      </c>
-      <c r="AO2">
-        <v>60</v>
-      </c>
-      <c r="AP2">
-        <v>14</v>
-      </c>
-      <c r="AQ2">
-        <v>13</v>
-      </c>
-      <c r="AR2">
-        <v>27</v>
-      </c>
       <c r="AS2">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AU2">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW2">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="BA2">
+        <v>110</v>
+      </c>
+      <c r="BB2">
+        <v>30</v>
+      </c>
+      <c r="BC2">
+        <v>34</v>
+      </c>
+      <c r="BD2">
+        <v>85</v>
+      </c>
+      <c r="BE2">
+        <v>200</v>
+      </c>
+      <c r="BF2">
+        <v>42</v>
+      </c>
+      <c r="BG2">
+        <v>110</v>
+      </c>
+      <c r="BH2">
+        <v>1.74</v>
+      </c>
+      <c r="BI2">
+        <v>1.67</v>
+      </c>
+      <c r="BJ2">
+        <v>29</v>
+      </c>
+      <c r="BK2">
+        <v>21</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>16.5</v>
+      </c>
+      <c r="BN2">
+        <v>5.6</v>
+      </c>
+      <c r="BO2">
+        <v>4.9</v>
+      </c>
+      <c r="BP2">
         <v>50</v>
       </c>
-      <c r="BB2">
-        <v>20</v>
-      </c>
-      <c r="BC2">
-        <v>18</v>
-      </c>
-      <c r="BD2">
-        <v>30</v>
-      </c>
-      <c r="BE2">
-        <v>75</v>
-      </c>
-      <c r="BF2">
-        <v>11.5</v>
-      </c>
-      <c r="BG2">
+      <c r="BQ2">
         <v>34</v>
       </c>
-      <c r="BH2">
-        <v>3.55</v>
-      </c>
-      <c r="BI2">
-        <v>3.15</v>
-      </c>
-      <c r="BJ2">
-        <v>11.5</v>
-      </c>
-      <c r="BK2">
-        <v>7.8</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>7.4</v>
-      </c>
-      <c r="BN2">
-        <v>4.9</v>
-      </c>
-      <c r="BO2">
-        <v>4.2</v>
-      </c>
-      <c r="BP2">
-        <v>15.5</v>
-      </c>
-      <c r="BQ2">
-        <v>10.5</v>
-      </c>
       <c r="BR2">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="BS2">
-        <v>6.4</v>
+        <v>120</v>
       </c>
       <c r="BT2">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BU2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="BW2">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="BY2">
-        <v>6.8</v>
+        <v>120</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>960</v>
       </c>
       <c r="CA2">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="CB2" t="s">
         <v>174</v>
@@ -1374,226 +1374,226 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="G3">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="H3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I3">
         <v>1.7</v>
       </c>
       <c r="J3">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
+        <v>2.04</v>
+      </c>
+      <c r="Q3">
+        <v>1.9</v>
+      </c>
+      <c r="R3">
+        <v>1.39</v>
+      </c>
+      <c r="S3">
         <v>3.35</v>
       </c>
-      <c r="Q3">
-        <v>1.39</v>
-      </c>
-      <c r="R3">
-        <v>2.02</v>
-      </c>
-      <c r="S3">
-        <v>1.96</v>
-      </c>
       <c r="T3">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="U3">
-        <v>2.92</v>
+        <v>1.95</v>
       </c>
       <c r="V3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="W3">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X3">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="Y3">
+        <v>9.4</v>
+      </c>
+      <c r="Z3">
+        <v>9.6</v>
+      </c>
+      <c r="AA3">
+        <v>140</v>
+      </c>
+      <c r="AB3">
+        <v>22</v>
+      </c>
+      <c r="AC3">
+        <v>10.5</v>
+      </c>
+      <c r="AD3">
+        <v>10.5</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>75</v>
+      </c>
+      <c r="AG3">
+        <v>22</v>
+      </c>
+      <c r="AH3">
+        <v>990</v>
+      </c>
+      <c r="AI3">
+        <v>40</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>16</v>
+      </c>
+      <c r="AP3">
+        <v>15.5</v>
+      </c>
+      <c r="AQ3">
+        <v>7.6</v>
+      </c>
+      <c r="AR3">
+        <v>8.4</v>
+      </c>
+      <c r="AS3">
+        <v>13</v>
+      </c>
+      <c r="AT3">
+        <v>15</v>
+      </c>
+      <c r="AU3">
+        <v>9.4</v>
+      </c>
+      <c r="AV3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW3">
+        <v>15</v>
+      </c>
+      <c r="AX3">
+        <v>34</v>
+      </c>
+      <c r="AY3">
+        <v>3.35</v>
+      </c>
+      <c r="AZ3">
+        <v>4</v>
+      </c>
+      <c r="BA3">
+        <v>25</v>
+      </c>
+      <c r="BB3">
+        <v>4</v>
+      </c>
+      <c r="BC3">
+        <v>55</v>
+      </c>
+      <c r="BD3">
+        <v>60</v>
+      </c>
+      <c r="BE3">
+        <v>95</v>
+      </c>
+      <c r="BF3">
+        <v>4.3</v>
+      </c>
+      <c r="BG3">
+        <v>6.8</v>
+      </c>
+      <c r="BH3">
+        <v>2.3</v>
+      </c>
+      <c r="BI3">
+        <v>2.12</v>
+      </c>
+      <c r="BJ3">
         <v>18</v>
       </c>
-      <c r="Z3">
-        <v>16.5</v>
-      </c>
-      <c r="AA3">
-        <v>20</v>
-      </c>
-      <c r="AB3">
-        <v>32</v>
-      </c>
-      <c r="AC3">
-        <v>13.5</v>
-      </c>
-      <c r="AD3">
-        <v>11.5</v>
-      </c>
-      <c r="AE3">
-        <v>16</v>
-      </c>
-      <c r="AF3">
+      <c r="BK3">
+        <v>14</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>10</v>
+      </c>
+      <c r="BN3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO3">
+        <v>7.4</v>
+      </c>
+      <c r="BP3">
+        <v>80</v>
+      </c>
+      <c r="BQ3">
+        <v>60</v>
+      </c>
+      <c r="BR3">
+        <v>160</v>
+      </c>
+      <c r="BS3">
+        <v>95</v>
+      </c>
+      <c r="BT3">
+        <v>4.1</v>
+      </c>
+      <c r="BU3">
+        <v>3.85</v>
+      </c>
+      <c r="BV3">
+        <v>21</v>
+      </c>
+      <c r="BW3">
+        <v>14.5</v>
+      </c>
+      <c r="BX3">
+        <v>90</v>
+      </c>
+      <c r="BY3">
         <v>55</v>
       </c>
-      <c r="AG3">
-        <v>21</v>
-      </c>
-      <c r="AH3">
-        <v>17</v>
-      </c>
-      <c r="AI3">
-        <v>23</v>
-      </c>
-      <c r="AJ3">
-        <v>110</v>
-      </c>
-      <c r="AK3">
-        <v>48</v>
-      </c>
-      <c r="AL3">
-        <v>42</v>
-      </c>
-      <c r="AM3">
-        <v>55</v>
-      </c>
-      <c r="AN3">
-        <v>27</v>
-      </c>
-      <c r="AO3">
-        <v>5.3</v>
-      </c>
-      <c r="AP3">
-        <v>30</v>
-      </c>
-      <c r="AQ3">
-        <v>14.5</v>
-      </c>
-      <c r="AR3">
-        <v>13.5</v>
-      </c>
-      <c r="AS3">
-        <v>17</v>
-      </c>
-      <c r="AT3">
-        <v>26</v>
-      </c>
-      <c r="AU3">
-        <v>11.5</v>
-      </c>
-      <c r="AV3">
-        <v>10</v>
-      </c>
-      <c r="AW3">
-        <v>13</v>
-      </c>
-      <c r="AX3">
-        <v>42</v>
-      </c>
-      <c r="AY3">
-        <v>17.5</v>
-      </c>
-      <c r="AZ3">
-        <v>14.5</v>
-      </c>
-      <c r="BA3">
-        <v>19.5</v>
-      </c>
-      <c r="BB3">
-        <v>60</v>
-      </c>
-      <c r="BC3">
-        <v>38</v>
-      </c>
-      <c r="BD3">
-        <v>32</v>
-      </c>
-      <c r="BE3">
-        <v>42</v>
-      </c>
-      <c r="BF3">
-        <v>21</v>
-      </c>
-      <c r="BG3">
-        <v>4.9</v>
-      </c>
-      <c r="BH3">
-        <v>6.4</v>
-      </c>
-      <c r="BI3">
-        <v>4.8</v>
-      </c>
-      <c r="BJ3">
-        <v>10</v>
-      </c>
-      <c r="BK3">
-        <v>6.8</v>
-      </c>
-      <c r="BL3">
-        <v>70</v>
-      </c>
-      <c r="BM3">
-        <v>5.1</v>
-      </c>
-      <c r="BN3">
-        <v>10.5</v>
-      </c>
-      <c r="BO3">
-        <v>7.2</v>
-      </c>
-      <c r="BP3">
-        <v>36</v>
-      </c>
-      <c r="BQ3">
-        <v>5</v>
-      </c>
-      <c r="BR3">
-        <v>34</v>
-      </c>
-      <c r="BS3">
-        <v>5</v>
-      </c>
-      <c r="BT3">
-        <v>5.8</v>
-      </c>
-      <c r="BU3">
-        <v>4.5</v>
-      </c>
-      <c r="BV3">
-        <v>11.5</v>
-      </c>
-      <c r="BW3">
-        <v>8</v>
-      </c>
-      <c r="BX3">
-        <v>19.5</v>
-      </c>
-      <c r="BY3">
-        <v>4.5</v>
-      </c>
       <c r="BZ3">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="CA3">
-        <v>3.9</v>
+        <v>50</v>
       </c>
       <c r="CB3" t="s">
         <v>174</v>
@@ -1616,226 +1616,226 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="G4">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>10</v>
+      </c>
+      <c r="Q4">
+        <v>1.1</v>
+      </c>
+      <c r="R4">
+        <v>2.78</v>
+      </c>
+      <c r="S4">
+        <v>1.54</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>1.17</v>
+      </c>
+      <c r="W4">
+        <v>2.28</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>11</v>
+      </c>
+      <c r="AD4">
+        <v>16</v>
+      </c>
+      <c r="AE4">
+        <v>60</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>6.6</v>
+      </c>
+      <c r="AH4">
+        <v>8.4</v>
+      </c>
+      <c r="AI4">
+        <v>32</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>8.4</v>
+      </c>
+      <c r="AL4">
+        <v>10.5</v>
+      </c>
+      <c r="AM4">
+        <v>34</v>
+      </c>
+      <c r="AN4">
+        <v>5.9</v>
+      </c>
+      <c r="AO4">
+        <v>50</v>
+      </c>
+      <c r="AP4">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4">
+        <v>11.5</v>
+      </c>
+      <c r="AR4">
+        <v>11.5</v>
+      </c>
+      <c r="AS4">
+        <v>11.5</v>
+      </c>
+      <c r="AT4">
+        <v>11.5</v>
+      </c>
+      <c r="AU4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV4">
+        <v>13</v>
+      </c>
+      <c r="AW4">
+        <v>38</v>
+      </c>
+      <c r="AX4">
+        <v>11.5</v>
+      </c>
+      <c r="AY4">
         <v>5.5</v>
       </c>
-      <c r="O4">
-        <v>1.19</v>
-      </c>
-      <c r="P4">
-        <v>2.58</v>
-      </c>
-      <c r="Q4">
-        <v>1.6</v>
-      </c>
-      <c r="R4">
-        <v>1.65</v>
-      </c>
-      <c r="S4">
-        <v>2.42</v>
-      </c>
-      <c r="T4">
-        <v>1.7</v>
-      </c>
-      <c r="U4">
-        <v>2.32</v>
-      </c>
-      <c r="V4">
-        <v>1.21</v>
-      </c>
-      <c r="W4">
-        <v>2.46</v>
-      </c>
-      <c r="X4">
-        <v>27</v>
-      </c>
-      <c r="Y4">
-        <v>25</v>
-      </c>
-      <c r="Z4">
-        <v>65</v>
-      </c>
-      <c r="AA4">
-        <v>200</v>
-      </c>
-      <c r="AB4">
+      <c r="AZ4">
+        <v>7.6</v>
+      </c>
+      <c r="BA4">
+        <v>26</v>
+      </c>
+      <c r="BB4">
         <v>11.5</v>
       </c>
-      <c r="AC4">
-        <v>11.5</v>
-      </c>
-      <c r="AD4">
-        <v>22</v>
-      </c>
-      <c r="AE4">
-        <v>65</v>
-      </c>
-      <c r="AF4">
-        <v>12</v>
-      </c>
-      <c r="AG4">
-        <v>10.5</v>
-      </c>
-      <c r="AH4">
-        <v>18</v>
-      </c>
-      <c r="AI4">
-        <v>60</v>
-      </c>
-      <c r="AJ4">
-        <v>20</v>
-      </c>
-      <c r="AK4">
-        <v>15</v>
-      </c>
-      <c r="AL4">
+      <c r="BC4">
+        <v>7.4</v>
+      </c>
+      <c r="BD4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE4">
         <v>26</v>
       </c>
-      <c r="AM4">
-        <v>80</v>
-      </c>
-      <c r="AN4">
-        <v>6.8</v>
-      </c>
-      <c r="AO4">
-        <v>60</v>
-      </c>
-      <c r="AP4">
-        <v>21</v>
-      </c>
-      <c r="AQ4">
-        <v>24</v>
-      </c>
-      <c r="AR4">
-        <v>44</v>
-      </c>
-      <c r="AS4">
-        <v>85</v>
-      </c>
-      <c r="AT4">
-        <v>10.5</v>
-      </c>
-      <c r="AU4">
-        <v>10</v>
-      </c>
-      <c r="AV4">
-        <v>18.5</v>
-      </c>
-      <c r="AW4">
-        <v>42</v>
-      </c>
-      <c r="AX4">
-        <v>10.5</v>
-      </c>
-      <c r="AY4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4">
-        <v>16</v>
-      </c>
-      <c r="BA4">
-        <v>34</v>
-      </c>
-      <c r="BB4">
-        <v>15</v>
-      </c>
-      <c r="BC4">
-        <v>13.5</v>
-      </c>
-      <c r="BD4">
-        <v>21</v>
-      </c>
-      <c r="BE4">
-        <v>55</v>
-      </c>
       <c r="BF4">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG4">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BH4">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
+        <v>1.28</v>
+      </c>
+      <c r="BJ4">
+        <v>1.89</v>
+      </c>
+      <c r="BK4">
+        <v>1.79</v>
+      </c>
+      <c r="BL4">
+        <v>960</v>
+      </c>
+      <c r="BM4">
+        <v>19</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.28</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.28</v>
+      </c>
+      <c r="BR4">
+        <v>4.6</v>
+      </c>
+      <c r="BS4">
         <v>4</v>
       </c>
-      <c r="BJ4">
-        <v>11.5</v>
-      </c>
-      <c r="BK4">
-        <v>7.6</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>7.8</v>
-      </c>
-      <c r="BN4">
-        <v>4.8</v>
-      </c>
-      <c r="BO4">
-        <v>4</v>
-      </c>
-      <c r="BP4">
-        <v>10.5</v>
-      </c>
-      <c r="BQ4">
-        <v>7</v>
-      </c>
-      <c r="BR4">
-        <v>23</v>
-      </c>
-      <c r="BS4">
-        <v>6.4</v>
-      </c>
       <c r="BT4">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6.6</v>
+        <v>1.28</v>
       </c>
       <c r="BV4">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7</v>
+        <v>1.28</v>
       </c>
       <c r="BX4">
-        <v>42</v>
+        <v>870</v>
       </c>
       <c r="BY4">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="BZ4">
-        <v>14</v>
+        <v>960</v>
       </c>
       <c r="CA4">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="s">
         <v>174</v>
@@ -1858,226 +1858,226 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="G5">
-        <v>2.16</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>1.61</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="L5">
+        <v>2.2</v>
+      </c>
+      <c r="M5">
+        <v>1.15</v>
+      </c>
+      <c r="N5">
+        <v>2.34</v>
+      </c>
+      <c r="O5">
+        <v>1.73</v>
+      </c>
+      <c r="P5">
         <v>1.43</v>
       </c>
-      <c r="M5">
-        <v>1.08</v>
-      </c>
-      <c r="N5">
-        <v>3.65</v>
-      </c>
-      <c r="O5">
-        <v>1.35</v>
-      </c>
-      <c r="P5">
-        <v>1.88</v>
-      </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="R5">
+        <v>1.14</v>
+      </c>
+      <c r="S5">
+        <v>7.2</v>
+      </c>
+      <c r="T5">
+        <v>2.42</v>
+      </c>
+      <c r="U5">
+        <v>1.65</v>
+      </c>
+      <c r="V5">
         <v>1.34</v>
       </c>
-      <c r="S5">
-        <v>3.8</v>
-      </c>
-      <c r="T5">
-        <v>1.84</v>
-      </c>
-      <c r="U5">
-        <v>2.1</v>
-      </c>
-      <c r="V5">
-        <v>1.32</v>
-      </c>
       <c r="W5">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="Y5">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA5">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AC5">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AF5">
         <v>13</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ5">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AL5">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>410</v>
       </c>
       <c r="AN5">
-        <v>18.5</v>
+        <v>50</v>
       </c>
       <c r="AO5">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AP5">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AS5">
+        <v>65</v>
+      </c>
+      <c r="AT5">
+        <v>6.2</v>
+      </c>
+      <c r="AU5">
+        <v>6.6</v>
+      </c>
+      <c r="AV5">
+        <v>16</v>
+      </c>
+      <c r="AW5">
         <v>55</v>
-      </c>
-      <c r="AT5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU5">
-        <v>7.4</v>
-      </c>
-      <c r="AV5">
-        <v>14.5</v>
-      </c>
-      <c r="AW5">
-        <v>40</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BB5">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BC5">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="BD5">
+        <v>80</v>
+      </c>
+      <c r="BE5">
+        <v>180</v>
+      </c>
+      <c r="BF5">
+        <v>40</v>
+      </c>
+      <c r="BG5">
+        <v>100</v>
+      </c>
+      <c r="BH5">
+        <v>1.77</v>
+      </c>
+      <c r="BI5">
+        <v>1.69</v>
+      </c>
+      <c r="BJ5">
         <v>32</v>
       </c>
-      <c r="BE5">
-        <v>80</v>
-      </c>
-      <c r="BF5">
-        <v>16</v>
-      </c>
-      <c r="BG5">
-        <v>34</v>
-      </c>
-      <c r="BH5">
-        <v>3.25</v>
-      </c>
-      <c r="BI5">
-        <v>2.96</v>
-      </c>
-      <c r="BJ5">
-        <v>10.5</v>
-      </c>
       <c r="BK5">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BL5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
+        <v>14.5</v>
+      </c>
+      <c r="BN5">
+        <v>5.7</v>
+      </c>
+      <c r="BO5">
+        <v>5.2</v>
+      </c>
+      <c r="BP5">
+        <v>55</v>
+      </c>
+      <c r="BQ5">
+        <v>30</v>
+      </c>
+      <c r="BR5">
+        <v>260</v>
+      </c>
+      <c r="BS5">
         <v>13.5</v>
       </c>
-      <c r="BN5">
-        <v>4.9</v>
-      </c>
-      <c r="BO5">
-        <v>4.2</v>
-      </c>
-      <c r="BP5">
-        <v>15.5</v>
-      </c>
-      <c r="BQ5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR5">
-        <v>32</v>
-      </c>
-      <c r="BS5">
-        <v>10</v>
-      </c>
       <c r="BT5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU5">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BV5">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="BW5">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="BY5">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BZ5">
-        <v>30</v>
+        <v>370</v>
       </c>
       <c r="CA5">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="CB5" t="s">
         <v>174</v>
@@ -2100,226 +2100,226 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="G6">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="I6">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L6">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="M6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="O6">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="P6">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S6">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V6">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="W6">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="X6">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6">
+        <v>7.6</v>
+      </c>
+      <c r="Z6">
+        <v>13.5</v>
+      </c>
+      <c r="AA6">
+        <v>36</v>
+      </c>
+      <c r="AB6">
+        <v>10.5</v>
+      </c>
+      <c r="AC6">
         <v>7.4</v>
       </c>
-      <c r="Z6">
-        <v>11</v>
-      </c>
-      <c r="AA6">
+      <c r="AD6">
+        <v>12.5</v>
+      </c>
+      <c r="AE6">
+        <v>34</v>
+      </c>
+      <c r="AF6">
         <v>25</v>
       </c>
-      <c r="AB6">
-        <v>13.5</v>
-      </c>
-      <c r="AC6">
-        <v>7.8</v>
-      </c>
-      <c r="AD6">
-        <v>11</v>
-      </c>
-      <c r="AE6">
-        <v>26</v>
-      </c>
-      <c r="AF6">
-        <v>32</v>
-      </c>
       <c r="AG6">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AH6">
         <v>24</v>
       </c>
       <c r="AI6">
+        <v>65</v>
+      </c>
+      <c r="AJ6">
+        <v>90</v>
+      </c>
+      <c r="AK6">
+        <v>70</v>
+      </c>
+      <c r="AL6">
+        <v>110</v>
+      </c>
+      <c r="AM6">
+        <v>210</v>
+      </c>
+      <c r="AN6">
+        <v>95</v>
+      </c>
+      <c r="AO6">
+        <v>36</v>
+      </c>
+      <c r="AP6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ6">
+        <v>7</v>
+      </c>
+      <c r="AR6">
+        <v>12</v>
+      </c>
+      <c r="AS6">
+        <v>28</v>
+      </c>
+      <c r="AT6">
+        <v>9.4</v>
+      </c>
+      <c r="AU6">
+        <v>6.8</v>
+      </c>
+      <c r="AV6">
+        <v>10.5</v>
+      </c>
+      <c r="AW6">
+        <v>26</v>
+      </c>
+      <c r="AX6">
+        <v>21</v>
+      </c>
+      <c r="AY6">
+        <v>14</v>
+      </c>
+      <c r="AZ6">
+        <v>20</v>
+      </c>
+      <c r="BA6">
         <v>50</v>
       </c>
-      <c r="AJ6">
-        <v>120</v>
-      </c>
-      <c r="AK6">
+      <c r="BB6">
+        <v>65</v>
+      </c>
+      <c r="BC6">
+        <v>50</v>
+      </c>
+      <c r="BD6">
         <v>75</v>
       </c>
-      <c r="AL6">
-        <v>95</v>
-      </c>
-      <c r="AM6">
+      <c r="BE6">
+        <v>160</v>
+      </c>
+      <c r="BF6">
+        <v>70</v>
+      </c>
+      <c r="BG6">
+        <v>24</v>
+      </c>
+      <c r="BH6">
+        <v>2.46</v>
+      </c>
+      <c r="BI6">
+        <v>2.3</v>
+      </c>
+      <c r="BJ6">
+        <v>12.5</v>
+      </c>
+      <c r="BK6">
+        <v>11.5</v>
+      </c>
+      <c r="BL6">
+        <v>340</v>
+      </c>
+      <c r="BM6">
         <v>180</v>
       </c>
-      <c r="AN6">
-        <v>110</v>
-      </c>
-      <c r="AO6">
-        <v>20</v>
-      </c>
-      <c r="AP6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ6">
-        <v>6.8</v>
-      </c>
-      <c r="AR6">
+      <c r="BN6">
+        <v>7</v>
+      </c>
+      <c r="BO6">
+        <v>5.8</v>
+      </c>
+      <c r="BP6">
+        <v>48</v>
+      </c>
+      <c r="BQ6">
+        <v>32</v>
+      </c>
+      <c r="BR6">
+        <v>80</v>
+      </c>
+      <c r="BS6">
+        <v>60</v>
+      </c>
+      <c r="BT6">
+        <v>5.1</v>
+      </c>
+      <c r="BU6">
+        <v>4.4</v>
+      </c>
+      <c r="BV6">
+        <v>25</v>
+      </c>
+      <c r="BW6">
+        <v>15.5</v>
+      </c>
+      <c r="BX6">
+        <v>950</v>
+      </c>
+      <c r="BY6">
         <v>10</v>
       </c>
-      <c r="AS6">
-        <v>20</v>
-      </c>
-      <c r="AT6">
-        <v>12</v>
-      </c>
-      <c r="AU6">
-        <v>7</v>
-      </c>
-      <c r="AV6">
-        <v>9.6</v>
-      </c>
-      <c r="AW6">
-        <v>21</v>
-      </c>
-      <c r="AX6">
-        <v>27</v>
-      </c>
-      <c r="AY6">
-        <v>17</v>
-      </c>
-      <c r="AZ6">
-        <v>19.5</v>
-      </c>
-      <c r="BA6">
-        <v>40</v>
-      </c>
-      <c r="BB6">
-        <v>60</v>
-      </c>
-      <c r="BC6">
-        <v>48</v>
-      </c>
-      <c r="BD6">
-        <v>60</v>
-      </c>
-      <c r="BE6">
-        <v>44</v>
-      </c>
-      <c r="BF6">
-        <v>48</v>
-      </c>
-      <c r="BG6">
-        <v>17</v>
-      </c>
-      <c r="BH6">
-        <v>2.94</v>
-      </c>
-      <c r="BI6">
-        <v>2.76</v>
-      </c>
-      <c r="BJ6">
-        <v>11.5</v>
-      </c>
-      <c r="BK6">
-        <v>9.6</v>
-      </c>
-      <c r="BL6">
-        <v>210</v>
-      </c>
-      <c r="BM6">
-        <v>16.5</v>
-      </c>
-      <c r="BN6">
-        <v>7.8</v>
-      </c>
-      <c r="BO6">
-        <v>7</v>
-      </c>
-      <c r="BP6">
-        <v>46</v>
-      </c>
-      <c r="BQ6">
-        <v>12.5</v>
-      </c>
-      <c r="BR6">
-        <v>65</v>
-      </c>
-      <c r="BS6">
-        <v>14</v>
-      </c>
-      <c r="BT6">
-        <v>4.4</v>
-      </c>
-      <c r="BU6">
-        <v>4.1</v>
-      </c>
-      <c r="BV6">
-        <v>15.5</v>
-      </c>
-      <c r="BW6">
-        <v>11</v>
-      </c>
-      <c r="BX6">
-        <v>36</v>
-      </c>
-      <c r="BY6">
-        <v>12</v>
-      </c>
       <c r="BZ6">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="CA6">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="s">
         <v>174</v>
@@ -2342,226 +2342,226 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="G7">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="H7">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="I7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="K7">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O7">
         <v>1.45</v>
       </c>
       <c r="P7">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T7">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="V7">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA7">
         <v>65</v>
       </c>
       <c r="AB7">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF7">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH7">
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ7">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK7">
         <v>42</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN7">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AO7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AP7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR7">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AT7">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW7">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7">
         <v>17</v>
       </c>
       <c r="BA7">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BB7">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BC7">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BD7">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="BF7">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BG7">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BH7">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BI7">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>10.5</v>
+        <v>130</v>
       </c>
       <c r="BN7">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="BP7">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.800000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="BT7">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.4</v>
+        <v>2.04</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.199999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>1.78</v>
       </c>
       <c r="CB7" t="s">
         <v>174</v>
@@ -2584,13 +2584,13 @@
         <v>149</v>
       </c>
       <c r="F8">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G8">
         <v>2.2</v>
       </c>
       <c r="H8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I8">
         <v>4.1</v>
@@ -2599,22 +2599,22 @@
         <v>3.4</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M8">
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P8">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q8">
         <v>2.36</v>
@@ -2626,10 +2626,10 @@
         <v>4.6</v>
       </c>
       <c r="T8">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -2638,19 +2638,19 @@
         <v>1.83</v>
       </c>
       <c r="X8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA8">
-        <v>150</v>
+        <v>620</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -2659,7 +2659,7 @@
         <v>17.5</v>
       </c>
       <c r="AE8">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF8">
         <v>12.5</v>
@@ -2668,22 +2668,22 @@
         <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>95</v>
+        <v>380</v>
       </c>
       <c r="AJ8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN8">
         <v>24</v>
@@ -2695,76 +2695,76 @@
         <v>9.4</v>
       </c>
       <c r="AQ8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU8">
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW8">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
       </c>
       <c r="AY8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA8">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE8">
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG8">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BH8">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BI8">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="BN8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO8">
         <v>4.2</v>
@@ -2773,16 +2773,16 @@
         <v>18</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU8">
         <v>6.2</v>
@@ -2791,19 +2791,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB8" t="s">
         <v>174</v>
@@ -2826,19 +2826,19 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H9">
         <v>2.8</v>
       </c>
       <c r="I9">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J9">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="K9">
         <v>3.2</v>
@@ -2865,22 +2865,22 @@
         <v>1.17</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U9">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W9">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X9">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -2889,7 +2889,7 @@
         <v>23</v>
       </c>
       <c r="AA9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -2910,16 +2910,16 @@
         <v>17.5</v>
       </c>
       <c r="AH9">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI9">
         <v>90</v>
       </c>
       <c r="AJ9">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL9">
         <v>90</v>
@@ -2934,58 +2934,58 @@
         <v>65</v>
       </c>
       <c r="AP9">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AQ9">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AR9">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS9">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT9">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AU9">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AV9">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW9">
+        <v>5.6</v>
+      </c>
+      <c r="AX9">
+        <v>4.8</v>
+      </c>
+      <c r="AY9">
+        <v>4.5</v>
+      </c>
+      <c r="AZ9">
         <v>4.9</v>
       </c>
-      <c r="AX9">
-        <v>4.3</v>
-      </c>
-      <c r="AY9">
-        <v>4.3</v>
-      </c>
-      <c r="AZ9">
-        <v>4.5</v>
-      </c>
       <c r="BA9">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB9">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC9">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD9">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BE9">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF9">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BG9">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH9">
         <v>2.76</v>
@@ -3068,22 +3068,22 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G10">
         <v>2.5</v>
       </c>
       <c r="H10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J10">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L10">
         <v>1.53</v>
@@ -3095,10 +3095,10 @@
         <v>2.44</v>
       </c>
       <c r="O10">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P10">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q10">
         <v>2.68</v>
@@ -3107,13 +3107,13 @@
         <v>1.17</v>
       </c>
       <c r="S10">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="T10">
         <v>2.16</v>
       </c>
       <c r="U10">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V10">
         <v>1.31</v>
@@ -3131,7 +3131,7 @@
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB10">
         <v>7.4</v>
@@ -3155,7 +3155,7 @@
         <v>30</v>
       </c>
       <c r="AI10">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ10">
         <v>44</v>
@@ -3164,7 +3164,7 @@
         <v>44</v>
       </c>
       <c r="AL10">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM10">
         <v>260</v>
@@ -3173,7 +3173,7 @@
         <v>46</v>
       </c>
       <c r="AO10">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AP10">
         <v>3.55</v>
@@ -3325,7 +3325,7 @@
         <v>3.55</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
         <v>1.4</v>
@@ -3334,16 +3334,16 @@
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P11">
         <v>1.74</v>
       </c>
       <c r="Q11">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>1.27</v>
@@ -3364,7 +3364,7 @@
         <v>1.17</v>
       </c>
       <c r="X11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y11">
         <v>8.6</v>
@@ -3400,76 +3400,76 @@
         <v>50</v>
       </c>
       <c r="AJ11">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AK11">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AL11">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AM11">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AO11">
         <v>14.5</v>
       </c>
       <c r="AP11">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ11">
         <v>5.8</v>
       </c>
       <c r="AR11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AS11">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AT11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU11">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AV11">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AW11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX11">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB11">
+        <v>5.5</v>
+      </c>
+      <c r="BC11">
         <v>5.3</v>
       </c>
-      <c r="BC11">
-        <v>5.2</v>
-      </c>
       <c r="BD11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE11">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG11">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH11">
         <v>3.55</v>
@@ -3576,19 +3576,19 @@
         <v>1.12</v>
       </c>
       <c r="N12">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O12">
         <v>1.56</v>
       </c>
       <c r="P12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q12">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S12">
         <v>5.1</v>
@@ -3615,7 +3615,7 @@
         <v>26</v>
       </c>
       <c r="AA12">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB12">
         <v>7.8</v>
@@ -3639,7 +3639,7 @@
         <v>27</v>
       </c>
       <c r="AI12">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AJ12">
         <v>50</v>
@@ -3657,16 +3657,16 @@
         <v>55</v>
       </c>
       <c r="AO12">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AP12">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ12">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AR12">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS12">
         <v>6</v>
@@ -3678,40 +3678,40 @@
         <v>5.4</v>
       </c>
       <c r="AV12">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW12">
         <v>6</v>
       </c>
       <c r="AX12">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY12">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA12">
+        <v>6.6</v>
+      </c>
+      <c r="BB12">
+        <v>6.4</v>
+      </c>
+      <c r="BC12">
         <v>6.2</v>
-      </c>
-      <c r="BB12">
-        <v>5.7</v>
-      </c>
-      <c r="BC12">
-        <v>5.6</v>
       </c>
       <c r="BD12">
         <v>6</v>
       </c>
       <c r="BE12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF12">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG12">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH12">
         <v>2.96</v>
@@ -3794,19 +3794,19 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G13">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H13">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="I13">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J13">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K13">
         <v>3.3</v>
@@ -3818,10 +3818,10 @@
         <v>1.12</v>
       </c>
       <c r="N13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O13">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="P13">
         <v>1.54</v>
@@ -3833,7 +3833,7 @@
         <v>1.19</v>
       </c>
       <c r="S13">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>2.02</v>
@@ -3845,10 +3845,10 @@
         <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X13">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y13">
         <v>8.6</v>
@@ -3905,55 +3905,55 @@
         <v>4.4</v>
       </c>
       <c r="AQ13">
+        <v>4.3</v>
+      </c>
+      <c r="AR13">
+        <v>5.7</v>
+      </c>
+      <c r="AS13">
+        <v>7.4</v>
+      </c>
+      <c r="AT13">
+        <v>4.6</v>
+      </c>
+      <c r="AU13">
         <v>4</v>
       </c>
-      <c r="AR13">
-        <v>5.2</v>
-      </c>
-      <c r="AS13">
-        <v>6.4</v>
-      </c>
-      <c r="AT13">
-        <v>4.2</v>
-      </c>
-      <c r="AU13">
-        <v>3.7</v>
-      </c>
       <c r="AV13">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AW13">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX13">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY13">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ13">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA13">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB13">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD13">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE13">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF13">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG13">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH13">
         <v>2.82</v>
@@ -4054,13 +4054,13 @@
         <v>3.6</v>
       </c>
       <c r="L14">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M14">
         <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O14">
         <v>1.36</v>
@@ -4072,7 +4072,7 @@
         <v>2.06</v>
       </c>
       <c r="R14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S14">
         <v>3.7</v>
@@ -4099,7 +4099,7 @@
         <v>28</v>
       </c>
       <c r="AA14">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AB14">
         <v>9.6</v>
@@ -4123,7 +4123,7 @@
         <v>19.5</v>
       </c>
       <c r="AI14">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ14">
         <v>30</v>
@@ -4138,7 +4138,7 @@
         <v>130</v>
       </c>
       <c r="AN14">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO14">
         <v>55</v>
@@ -4150,10 +4150,10 @@
         <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AS14">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="AT14">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AX14">
         <v>12</v>
@@ -4177,85 +4177,85 @@
         <v>16</v>
       </c>
       <c r="BA14">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BB14">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BC14">
         <v>21</v>
       </c>
       <c r="BD14">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BE14">
-        <v>9.4</v>
+        <v>75</v>
       </c>
       <c r="BF14">
         <v>16</v>
       </c>
       <c r="BG14">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB14" t="s">
         <v>174</v>
@@ -4281,7 +4281,7 @@
         <v>2.08</v>
       </c>
       <c r="G15">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H15">
         <v>3.75</v>
@@ -4290,19 +4290,19 @@
         <v>4.1</v>
       </c>
       <c r="J15">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K15">
         <v>3.7</v>
       </c>
       <c r="L15">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M15">
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O15">
         <v>1.35</v>
@@ -4329,7 +4329,7 @@
         <v>1.32</v>
       </c>
       <c r="W15">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X15">
         <v>16.5</v>
@@ -4344,13 +4344,13 @@
         <v>500</v>
       </c>
       <c r="AB15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC15">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE15">
         <v>60</v>
@@ -4365,16 +4365,16 @@
         <v>19</v>
       </c>
       <c r="AI15">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AJ15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK15">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL15">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM15">
         <v>580</v>
@@ -4392,10 +4392,10 @@
         <v>12</v>
       </c>
       <c r="AR15">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AS15">
-        <v>5.3</v>
+        <v>55</v>
       </c>
       <c r="AT15">
         <v>8.199999999999999</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="AW15">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="AX15">
         <v>11</v>
@@ -4419,85 +4419,85 @@
         <v>16</v>
       </c>
       <c r="BA15">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="BB15">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BC15">
         <v>19.5</v>
       </c>
       <c r="BD15">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="BE15">
-        <v>5.4</v>
+        <v>75</v>
       </c>
       <c r="BF15">
         <v>15</v>
       </c>
       <c r="BG15">
+        <v>30</v>
+      </c>
+      <c r="BH15">
+        <v>3.85</v>
+      </c>
+      <c r="BI15">
+        <v>2.66</v>
+      </c>
+      <c r="BJ15">
+        <v>12</v>
+      </c>
+      <c r="BK15">
+        <v>3.45</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>4.6</v>
+      </c>
+      <c r="BN15">
+        <v>5.8</v>
+      </c>
+      <c r="BO15">
+        <v>4.2</v>
+      </c>
+      <c r="BP15">
+        <v>19</v>
+      </c>
+      <c r="BQ15">
+        <v>3.8</v>
+      </c>
+      <c r="BR15">
+        <v>38</v>
+      </c>
+      <c r="BS15">
+        <v>4.2</v>
+      </c>
+      <c r="BT15">
         <v>8.4</v>
       </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.04</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.04</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.04</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.04</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.04</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB15" t="s">
         <v>174</v>
@@ -4520,58 +4520,58 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G16">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I16">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J16">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M16">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N16">
         <v>2.36</v>
       </c>
       <c r="O16">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P16">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R16">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T16">
-        <v>1.12</v>
+        <v>2.12</v>
       </c>
       <c r="U16">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V16">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W16">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X16">
         <v>8.4</v>
@@ -4595,7 +4595,7 @@
         <v>19</v>
       </c>
       <c r="AE16">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AF16">
         <v>15</v>
@@ -4616,16 +4616,16 @@
         <v>40</v>
       </c>
       <c r="AL16">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AM16">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN16">
         <v>44</v>
       </c>
       <c r="AO16">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AP16">
         <v>4.2</v>
@@ -4655,7 +4655,7 @@
         <v>6.2</v>
       </c>
       <c r="AY16">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ16">
         <v>5.9</v>
@@ -4682,64 +4682,64 @@
         <v>7.2</v>
       </c>
       <c r="BH16">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="BI16">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK16">
-        <v>1.51</v>
+        <v>5.4</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.51</v>
+        <v>7</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO16">
-        <v>1.51</v>
+        <v>3.4</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ16">
-        <v>1.51</v>
+        <v>5.5</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS16">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU16">
-        <v>1.51</v>
+        <v>4.1</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW16">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY16">
-        <v>1.51</v>
+        <v>6.6</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA16">
-        <v>1.51</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="s">
         <v>174</v>
@@ -4762,226 +4762,226 @@
         <v>158</v>
       </c>
       <c r="F17">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="G17">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H17">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="I17">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="J17">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K17">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L17">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N17">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="O17">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="P17">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q17">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="S17">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="T17">
-        <v>1.12</v>
+        <v>2.12</v>
       </c>
       <c r="U17">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="V17">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="W17">
         <v>1.23</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA17">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC17">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ17">
         <v>900</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF17">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BG17">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI17">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB17" t="s">
         <v>174</v>
@@ -5004,7 +5004,7 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G18">
         <v>2.08</v>
@@ -5013,55 +5013,55 @@
         <v>4.2</v>
       </c>
       <c r="I18">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="J18">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="K18">
         <v>3.55</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M18">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N18">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="O18">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="P18">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q18">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="R18">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="S18">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="T18">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U18">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="V18">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="W18">
         <v>1.92</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z18">
         <v>120</v>
@@ -5070,58 +5070,58 @@
         <v>900</v>
       </c>
       <c r="AB18">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="AC18">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="AD18">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF18">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="AG18">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AJ18">
-        <v>900</v>
+        <v>28</v>
       </c>
       <c r="AK18">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="AL18">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP18">
         <v>4.9</v>
       </c>
       <c r="AQ18">
-        <v>1.32</v>
+        <v>4.5</v>
       </c>
       <c r="AR18">
-        <v>1.31</v>
+        <v>5.8</v>
       </c>
       <c r="AS18">
-        <v>1.32</v>
+        <v>6.6</v>
       </c>
       <c r="AT18">
         <v>4.2</v>
@@ -5130,100 +5130,100 @@
         <v>4.9</v>
       </c>
       <c r="AV18">
-        <v>1.31</v>
+        <v>5.2</v>
       </c>
       <c r="AW18">
-        <v>1.32</v>
+        <v>6.4</v>
       </c>
       <c r="AX18">
         <v>5.1</v>
       </c>
       <c r="AY18">
-        <v>1.28</v>
+        <v>7.6</v>
       </c>
       <c r="AZ18">
-        <v>1.32</v>
+        <v>5.4</v>
       </c>
       <c r="BA18">
-        <v>1.32</v>
+        <v>6.4</v>
       </c>
       <c r="BB18">
-        <v>1.31</v>
+        <v>5.5</v>
       </c>
       <c r="BC18">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD18">
-        <v>1.32</v>
+        <v>6.2</v>
       </c>
       <c r="BE18">
-        <v>1.32</v>
+        <v>6.6</v>
       </c>
       <c r="BF18">
-        <v>1.55</v>
+        <v>5.4</v>
       </c>
       <c r="BG18">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB18" t="s">
         <v>174</v>
@@ -5246,22 +5246,22 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="G19">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H19">
         <v>3.3</v>
       </c>
       <c r="I19">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J19">
         <v>3.15</v>
       </c>
       <c r="K19">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L19">
         <v>1.47</v>
@@ -5276,13 +5276,13 @@
         <v>1.41</v>
       </c>
       <c r="P19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q19">
         <v>2.2</v>
       </c>
       <c r="R19">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S19">
         <v>4.1</v>
@@ -5294,22 +5294,22 @@
         <v>1.94</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X19">
         <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z19">
         <v>26</v>
       </c>
       <c r="AA19">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AB19">
         <v>9.199999999999999</v>
@@ -5324,7 +5324,7 @@
         <v>55</v>
       </c>
       <c r="AF19">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG19">
         <v>12.5</v>
@@ -5336,10 +5336,10 @@
         <v>160</v>
       </c>
       <c r="AJ19">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AK19">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AL19">
         <v>130</v>
@@ -5348,22 +5348,22 @@
         <v>580</v>
       </c>
       <c r="AN19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO19">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AP19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR19">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS19">
-        <v>7.4</v>
+        <v>46</v>
       </c>
       <c r="AT19">
         <v>7.6</v>
@@ -5375,97 +5375,97 @@
         <v>12.5</v>
       </c>
       <c r="AW19">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AX19">
         <v>12.5</v>
       </c>
       <c r="AY19">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BB19">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BC19">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BD19">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BE19">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BF19">
         <v>21</v>
       </c>
       <c r="BG19">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB19" t="s">
         <v>174</v>
@@ -5494,34 +5494,34 @@
         <v>1.5</v>
       </c>
       <c r="H20">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20">
         <v>10.5</v>
       </c>
       <c r="J20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K20">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L20">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M20">
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O20">
         <v>1.34</v>
       </c>
       <c r="P20">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q20">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R20">
         <v>1.34</v>
@@ -5530,13 +5530,13 @@
         <v>3.55</v>
       </c>
       <c r="T20">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U20">
         <v>1.72</v>
       </c>
       <c r="V20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W20">
         <v>2.98</v>
@@ -5554,10 +5554,10 @@
         <v>480</v>
       </c>
       <c r="AB20">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC20">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD20">
         <v>44</v>
@@ -5566,7 +5566,7 @@
         <v>220</v>
       </c>
       <c r="AF20">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG20">
         <v>12.5</v>
@@ -5578,7 +5578,7 @@
         <v>470</v>
       </c>
       <c r="AJ20">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK20">
         <v>18</v>
@@ -5593,19 +5593,19 @@
         <v>9</v>
       </c>
       <c r="AO20">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="AP20">
         <v>12.5</v>
       </c>
       <c r="AQ20">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AR20">
-        <v>5.5</v>
+        <v>55</v>
       </c>
       <c r="AS20">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT20">
         <v>6.2</v>
@@ -5614,10 +5614,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AW20">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX20">
         <v>7</v>
@@ -5629,7 +5629,7 @@
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>5.6</v>
+        <v>29</v>
       </c>
       <c r="BB20">
         <v>11</v>
@@ -5638,76 +5638,76 @@
         <v>15</v>
       </c>
       <c r="BD20">
-        <v>5.7</v>
+        <v>26</v>
       </c>
       <c r="BE20">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BF20">
         <v>7.6</v>
       </c>
       <c r="BG20">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB20" t="s">
         <v>174</v>
@@ -5736,7 +5736,7 @@
         <v>2.06</v>
       </c>
       <c r="H21">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I21">
         <v>4.2</v>
@@ -5745,7 +5745,7 @@
         <v>3.75</v>
       </c>
       <c r="K21">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L21">
         <v>1.33</v>
@@ -5763,19 +5763,19 @@
         <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R21">
         <v>1.48</v>
       </c>
       <c r="S21">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T21">
         <v>1.66</v>
       </c>
       <c r="U21">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V21">
         <v>1.31</v>
@@ -5808,7 +5808,7 @@
         <v>55</v>
       </c>
       <c r="AF21">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG21">
         <v>11</v>
@@ -5844,10 +5844,10 @@
         <v>15</v>
       </c>
       <c r="AR21">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="AS21">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="AT21">
         <v>10</v>
@@ -5859,7 +5859,7 @@
         <v>14</v>
       </c>
       <c r="AW21">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AX21">
         <v>12</v>
@@ -5871,7 +5871,7 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BB21">
         <v>20</v>
@@ -5880,16 +5880,16 @@
         <v>16.5</v>
       </c>
       <c r="BD21">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BE21">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="BF21">
         <v>10</v>
       </c>
       <c r="BG21">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BH21">
         <v>4.1</v>
@@ -5972,160 +5972,160 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="G22">
+        <v>2.62</v>
+      </c>
+      <c r="H22">
         <v>3</v>
       </c>
-      <c r="H22">
-        <v>2.18</v>
-      </c>
       <c r="I22">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J22">
         <v>3.4</v>
       </c>
       <c r="K22">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M22">
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="O22">
         <v>1.31</v>
       </c>
       <c r="P22">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Q22">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R22">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="S22">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T22">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U22">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA22">
         <v>900</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC22">
+        <v>42</v>
+      </c>
+      <c r="AD22">
         <v>950</v>
       </c>
-      <c r="AD22">
-        <v>1000</v>
-      </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH22">
         <v>950</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ22">
         <v>900</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM22">
         <v>580</v>
       </c>
       <c r="AN22">
-        <v>36</v>
+        <v>600</v>
       </c>
       <c r="AO22">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AP22">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ22">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AR22">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AS22">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AT22">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AU22">
         <v>4.9</v>
       </c>
       <c r="AV22">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AW22">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AX22">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AY22">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AZ22">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="BA22">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BB22">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BC22">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BD22">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BE22">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BF22">
         <v>4.3</v>
@@ -6214,7 +6214,7 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G23">
         <v>4.3</v>
@@ -6256,7 +6256,7 @@
         <v>2.88</v>
       </c>
       <c r="T23">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U23">
         <v>2.22</v>
@@ -6301,7 +6301,7 @@
         <v>19</v>
       </c>
       <c r="AI23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ23">
         <v>900</v>
@@ -6346,7 +6346,7 @@
         <v>15.5</v>
       </c>
       <c r="AX23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY23">
         <v>12.5</v>
@@ -6361,16 +6361,16 @@
         <v>6</v>
       </c>
       <c r="BC23">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD23">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE23">
         <v>6</v>
       </c>
       <c r="BF23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG23">
         <v>10</v>
@@ -6504,10 +6504,10 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6701,13 +6701,13 @@
         <v>2.18</v>
       </c>
       <c r="G25">
-        <v>990</v>
+        <v>5.8</v>
       </c>
       <c r="H25">
         <v>1.93</v>
       </c>
       <c r="I25">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J25">
         <v>2.32</v>
@@ -6728,16 +6728,16 @@
         <v>1.02</v>
       </c>
       <c r="P25">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Q25">
-        <v>1.14</v>
+        <v>2.52</v>
       </c>
       <c r="R25">
         <v>1.14</v>
       </c>
       <c r="S25">
-        <v>1.15</v>
+        <v>2.52</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -6746,10 +6746,10 @@
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X25">
         <v>950</v>
@@ -6812,10 +6812,10 @@
         <v>4.4</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AT25">
         <v>5.1</v>
@@ -6824,40 +6824,40 @@
         <v>3.85</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BF25">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BG25">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BH25">
         <v>2.8</v>
@@ -6940,22 +6940,22 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G26">
         <v>1.88</v>
       </c>
       <c r="H26">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="I26">
         <v>990</v>
       </c>
       <c r="J26">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="K26">
-        <v>420</v>
+        <v>5.8</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -6973,7 +6973,7 @@
         <v>1.09</v>
       </c>
       <c r="Q26">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R26">
         <v>1.08</v>
@@ -6988,118 +6988,118 @@
         <v>1.11</v>
       </c>
       <c r="V26">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W26">
         <v>2.12</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7203,7 +7203,7 @@
         <v>1.35</v>
       </c>
       <c r="M27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N27">
         <v>3.15</v>
@@ -7212,16 +7212,16 @@
         <v>1.36</v>
       </c>
       <c r="P27">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q27">
         <v>2.06</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S27">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
         <v>1.79</v>
@@ -7236,58 +7236,58 @@
         <v>1.7</v>
       </c>
       <c r="X27">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Y27">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="Z27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AA27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AB27">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AC27">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD27">
         <v>950</v>
       </c>
       <c r="AE27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AF27">
-        <v>900</v>
+        <v>860</v>
       </c>
       <c r="AG27">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="AH27">
         <v>950</v>
       </c>
       <c r="AI27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AJ27">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="AK27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AL27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AM27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AN27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AO27">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AP27">
         <v>6.2</v>
@@ -7296,10 +7296,10 @@
         <v>8</v>
       </c>
       <c r="AR27">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AS27">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AT27">
         <v>5.1</v>
@@ -7311,7 +7311,7 @@
         <v>8.4</v>
       </c>
       <c r="AW27">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AX27">
         <v>9.199999999999999</v>
@@ -7320,28 +7320,28 @@
         <v>6.4</v>
       </c>
       <c r="AZ27">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="BA27">
+        <v>1.93</v>
+      </c>
+      <c r="BB27">
+        <v>1.91</v>
+      </c>
+      <c r="BC27">
+        <v>1.9</v>
+      </c>
+      <c r="BD27">
         <v>1.92</v>
       </c>
-      <c r="BB27">
-        <v>1.9</v>
-      </c>
-      <c r="BC27">
-        <v>1.89</v>
-      </c>
-      <c r="BD27">
-        <v>1.91</v>
-      </c>
       <c r="BE27">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BF27">
         <v>5</v>
       </c>
       <c r="BG27">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7436,7 +7436,7 @@
         <v>990</v>
       </c>
       <c r="J28">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K28">
         <v>950</v>
@@ -7472,10 +7472,10 @@
         <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7666,16 +7666,16 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G29">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J29">
         <v>4.2</v>
@@ -7687,7 +7687,7 @@
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N29">
         <v>5.1</v>
@@ -7711,37 +7711,37 @@
         <v>1.61</v>
       </c>
       <c r="U29">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="V29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W29">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y29">
         <v>950</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB29">
         <v>950</v>
       </c>
       <c r="AC29">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="AD29">
         <v>950</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF29">
         <v>500</v>
@@ -7750,13 +7750,13 @@
         <v>26</v>
       </c>
       <c r="AH29">
-        <v>950</v>
+        <v>230</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ29">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK29">
         <v>500</v>
@@ -7765,40 +7765,40 @@
         <v>500</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN29">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP29">
-        <v>13</v>
+        <v>3.9</v>
       </c>
       <c r="AQ29">
-        <v>4.1</v>
+        <v>19.5</v>
       </c>
       <c r="AR29">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS29">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="AT29">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AU29">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AV29">
         <v>17</v>
       </c>
       <c r="AW29">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="AX29">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AY29">
         <v>8.800000000000001</v>
@@ -7807,7 +7807,7 @@
         <v>15</v>
       </c>
       <c r="BA29">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="BB29">
         <v>12</v>
@@ -7816,16 +7816,16 @@
         <v>12</v>
       </c>
       <c r="BD29">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="BE29">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="BF29">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="BG29">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7914,16 +7914,16 @@
         <v>2.12</v>
       </c>
       <c r="H30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I30">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J30">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K30">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -7932,13 +7932,13 @@
         <v>1.09</v>
       </c>
       <c r="N30">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O30">
         <v>1.4</v>
       </c>
       <c r="P30">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q30">
         <v>2.18</v>
@@ -7950,16 +7950,16 @@
         <v>4.1</v>
       </c>
       <c r="T30">
+        <v>1.93</v>
+      </c>
+      <c r="U30">
         <v>1.92</v>
       </c>
-      <c r="U30">
-        <v>1.91</v>
-      </c>
       <c r="V30">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W30">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X30">
         <v>12</v>
@@ -7971,7 +7971,7 @@
         <v>32</v>
       </c>
       <c r="AA30">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB30">
         <v>8.199999999999999</v>
@@ -7983,10 +7983,10 @@
         <v>18.5</v>
       </c>
       <c r="AE30">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AF30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG30">
         <v>11</v>
@@ -7995,10 +7995,10 @@
         <v>22</v>
       </c>
       <c r="AI30">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AJ30">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK30">
         <v>26</v>
@@ -8007,25 +8007,25 @@
         <v>65</v>
       </c>
       <c r="AM30">
-        <v>680</v>
+        <v>640</v>
       </c>
       <c r="AN30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO30">
-        <v>610</v>
+        <v>570</v>
       </c>
       <c r="AP30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ30">
+        <v>11.5</v>
+      </c>
+      <c r="AR30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS30">
         <v>9.6</v>
-      </c>
-      <c r="AQ30">
-        <v>11</v>
-      </c>
-      <c r="AR30">
-        <v>8</v>
-      </c>
-      <c r="AS30">
-        <v>8.800000000000001</v>
       </c>
       <c r="AT30">
         <v>6.8</v>
@@ -8034,10 +8034,10 @@
         <v>6.6</v>
       </c>
       <c r="AV30">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW30">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX30">
         <v>10.5</v>
@@ -8046,10 +8046,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB30">
         <v>19</v>
@@ -8058,16 +8058,16 @@
         <v>18.5</v>
       </c>
       <c r="BD30">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE30">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF30">
         <v>16.5</v>
       </c>
       <c r="BG30">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8079,13 +8079,13 @@
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="BN30">
         <v>1000</v>
@@ -8150,184 +8150,184 @@
         <v>172</v>
       </c>
       <c r="F31">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G31">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I31">
         <v>4.7</v>
       </c>
       <c r="J31">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K31">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L31">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N31">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="O31">
+        <v>1.35</v>
+      </c>
+      <c r="P31">
+        <v>1.9</v>
+      </c>
+      <c r="Q31">
+        <v>2</v>
+      </c>
+      <c r="R31">
         <v>1.31</v>
       </c>
-      <c r="P31">
-        <v>2</v>
-      </c>
-      <c r="Q31">
-        <v>1.9</v>
-      </c>
-      <c r="R31">
-        <v>1.39</v>
-      </c>
       <c r="S31">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T31">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="U31">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="V31">
         <v>1.27</v>
       </c>
       <c r="W31">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X31">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Y31">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Z31">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AA31">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB31">
+        <v>29</v>
+      </c>
+      <c r="AC31">
+        <v>12.5</v>
+      </c>
+      <c r="AD31">
+        <v>23</v>
+      </c>
+      <c r="AE31">
+        <v>980</v>
+      </c>
+      <c r="AF31">
+        <v>24</v>
+      </c>
+      <c r="AG31">
+        <v>15</v>
+      </c>
+      <c r="AH31">
+        <v>60</v>
+      </c>
+      <c r="AI31">
+        <v>980</v>
+      </c>
+      <c r="AJ31">
+        <v>40</v>
+      </c>
+      <c r="AK31">
+        <v>130</v>
+      </c>
+      <c r="AL31">
+        <v>980</v>
+      </c>
+      <c r="AM31">
+        <v>580</v>
+      </c>
+      <c r="AN31">
+        <v>85</v>
+      </c>
+      <c r="AO31">
+        <v>500</v>
+      </c>
+      <c r="AP31">
+        <v>10</v>
+      </c>
+      <c r="AQ31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR31">
+        <v>6.8</v>
+      </c>
+      <c r="AS31">
+        <v>2.64</v>
+      </c>
+      <c r="AT31">
+        <v>6.4</v>
+      </c>
+      <c r="AU31">
+        <v>7.4</v>
+      </c>
+      <c r="AV31">
+        <v>10.5</v>
+      </c>
+      <c r="AW31">
+        <v>12.5</v>
+      </c>
+      <c r="AX31">
         <v>9.4</v>
-      </c>
-      <c r="AC31">
-        <v>8.4</v>
-      </c>
-      <c r="AD31">
-        <v>17.5</v>
-      </c>
-      <c r="AE31">
-        <v>60</v>
-      </c>
-      <c r="AF31">
-        <v>12</v>
-      </c>
-      <c r="AG31">
-        <v>10</v>
-      </c>
-      <c r="AH31">
-        <v>18.5</v>
-      </c>
-      <c r="AI31">
-        <v>75</v>
-      </c>
-      <c r="AJ31">
-        <v>25</v>
-      </c>
-      <c r="AK31">
-        <v>23</v>
-      </c>
-      <c r="AL31">
-        <v>34</v>
-      </c>
-      <c r="AM31">
-        <v>120</v>
-      </c>
-      <c r="AN31">
-        <v>13</v>
-      </c>
-      <c r="AO31">
-        <v>65</v>
-      </c>
-      <c r="AP31">
-        <v>14</v>
-      </c>
-      <c r="AQ31">
-        <v>15</v>
-      </c>
-      <c r="AR31">
-        <v>15.5</v>
-      </c>
-      <c r="AS31">
-        <v>11.5</v>
-      </c>
-      <c r="AT31">
-        <v>8.4</v>
-      </c>
-      <c r="AU31">
-        <v>7.6</v>
-      </c>
-      <c r="AV31">
-        <v>15.5</v>
-      </c>
-      <c r="AW31">
-        <v>21</v>
-      </c>
-      <c r="AX31">
-        <v>10.5</v>
       </c>
       <c r="AY31">
         <v>9</v>
       </c>
       <c r="AZ31">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BA31">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="BB31">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="BC31">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BD31">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BE31">
-        <v>34</v>
+        <v>2.64</v>
       </c>
       <c r="BF31">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG31">
-        <v>10.5</v>
+        <v>2.62</v>
       </c>
       <c r="BH31">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ31">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK31">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BN31">
         <v>4.6</v>
@@ -8336,16 +8336,16 @@
         <v>4.2</v>
       </c>
       <c r="BP31">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ31">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BR31">
         <v>28</v>
       </c>
       <c r="BS31">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT31">
         <v>7.8</v>
@@ -8357,19 +8357,19 @@
         <v>38</v>
       </c>
       <c r="BW31">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX31">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ31">
         <v>25</v>
       </c>
       <c r="CA31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB31" t="s">
         <v>174</v>
@@ -8392,166 +8392,166 @@
         <v>173</v>
       </c>
       <c r="F32">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="G32">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="H32">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I32">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J32">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K32">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L32">
         <v>1.5</v>
       </c>
       <c r="M32">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N32">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="O32">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P32">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q32">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="R32">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S32">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T32">
         <v>2.18</v>
       </c>
       <c r="U32">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="V32">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="X32">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="Y32">
+        <v>15</v>
+      </c>
+      <c r="Z32">
+        <v>42</v>
+      </c>
+      <c r="AA32">
+        <v>180</v>
+      </c>
+      <c r="AB32">
+        <v>6.8</v>
+      </c>
+      <c r="AC32">
+        <v>8</v>
+      </c>
+      <c r="AD32">
+        <v>23</v>
+      </c>
+      <c r="AE32">
+        <v>110</v>
+      </c>
+      <c r="AF32">
+        <v>10.5</v>
+      </c>
+      <c r="AG32">
+        <v>11.5</v>
+      </c>
+      <c r="AH32">
+        <v>28</v>
+      </c>
+      <c r="AI32">
+        <v>120</v>
+      </c>
+      <c r="AJ32">
+        <v>23</v>
+      </c>
+      <c r="AK32">
+        <v>26</v>
+      </c>
+      <c r="AL32">
+        <v>60</v>
+      </c>
+      <c r="AM32">
+        <v>210</v>
+      </c>
+      <c r="AN32">
         <v>970</v>
       </c>
-      <c r="Z32">
-        <v>150</v>
-      </c>
-      <c r="AA32">
-        <v>1000</v>
-      </c>
-      <c r="AB32">
-        <v>7.6</v>
-      </c>
-      <c r="AC32">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD32">
-        <v>950</v>
-      </c>
-      <c r="AE32">
-        <v>1000</v>
-      </c>
-      <c r="AF32">
-        <v>970</v>
-      </c>
-      <c r="AG32">
+      <c r="AO32">
+        <v>170</v>
+      </c>
+      <c r="AP32">
+        <v>9</v>
+      </c>
+      <c r="AQ32">
+        <v>12</v>
+      </c>
+      <c r="AR32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS32">
+        <v>10</v>
+      </c>
+      <c r="AT32">
+        <v>6.2</v>
+      </c>
+      <c r="AU32">
+        <v>7</v>
+      </c>
+      <c r="AV32">
+        <v>18</v>
+      </c>
+      <c r="AW32">
+        <v>9.6</v>
+      </c>
+      <c r="AX32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY32">
+        <v>9.6</v>
+      </c>
+      <c r="AZ32">
+        <v>7.8</v>
+      </c>
+      <c r="BA32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB32">
+        <v>18.5</v>
+      </c>
+      <c r="BC32">
+        <v>20</v>
+      </c>
+      <c r="BD32">
+        <v>9.4</v>
+      </c>
+      <c r="BE32">
+        <v>10</v>
+      </c>
+      <c r="BF32">
         <v>16.5</v>
       </c>
-      <c r="AH32">
-        <v>950</v>
-      </c>
-      <c r="AI32">
-        <v>1000</v>
-      </c>
-      <c r="AJ32">
-        <v>120</v>
-      </c>
-      <c r="AK32">
-        <v>140</v>
-      </c>
-      <c r="AL32">
-        <v>1000</v>
-      </c>
-      <c r="AM32">
-        <v>1000</v>
-      </c>
-      <c r="AN32">
-        <v>42</v>
-      </c>
-      <c r="AO32">
-        <v>1000</v>
-      </c>
-      <c r="AP32">
-        <v>8</v>
-      </c>
-      <c r="AQ32">
-        <v>1.98</v>
-      </c>
-      <c r="AR32">
-        <v>4.2</v>
-      </c>
-      <c r="AS32">
-        <v>2.02</v>
-      </c>
-      <c r="AT32">
-        <v>5.3</v>
-      </c>
-      <c r="AU32">
-        <v>1.65</v>
-      </c>
-      <c r="AV32">
-        <v>3.45</v>
-      </c>
-      <c r="AW32">
-        <v>2.02</v>
-      </c>
-      <c r="AX32">
-        <v>6.8</v>
-      </c>
-      <c r="AY32">
-        <v>1.8</v>
-      </c>
-      <c r="AZ32">
-        <v>3.85</v>
-      </c>
-      <c r="BA32">
-        <v>2.02</v>
-      </c>
-      <c r="BB32">
-        <v>3.45</v>
-      </c>
-      <c r="BC32">
-        <v>2</v>
-      </c>
-      <c r="BD32">
-        <v>2.02</v>
-      </c>
-      <c r="BE32">
-        <v>2.02</v>
-      </c>
-      <c r="BF32">
-        <v>1.93</v>
-      </c>
       <c r="BG32">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="BH32">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="153">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>CONCACAF Nations League A</t>
-  </si>
-  <si>
     <t>Chinese League 2</t>
   </si>
   <si>
@@ -286,9 +283,6 @@
     <t>2026-10-06</t>
   </si>
   <si>
-    <t>02:00:00</t>
-  </si>
-  <si>
     <t>07:00:00</t>
   </si>
   <si>
@@ -334,9 +328,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>Honduras</t>
-  </si>
-  <si>
     <t>Changchun Xidu</t>
   </si>
   <si>
@@ -409,9 +400,6 @@
     <t>Goias</t>
   </si>
   <si>
-    <t>Jamaica</t>
-  </si>
-  <si>
     <t>Guangzhou Alpha</t>
   </si>
   <si>
@@ -484,7 +472,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-05 23:41:44</t>
+    <t>2026-10-06 01:52:54</t>
   </si>
 </sst>
 </file>
@@ -816,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1066,835 +1054,835 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
         <v>89</v>
       </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F2">
-        <v>6.8</v>
+        <v>2.74</v>
       </c>
       <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2.9</v>
+      </c>
+      <c r="I2">
+        <v>3.2</v>
+      </c>
+      <c r="J2">
+        <v>2.92</v>
+      </c>
+      <c r="K2">
+        <v>3.15</v>
+      </c>
+      <c r="L2">
+        <v>1.54</v>
+      </c>
+      <c r="M2">
+        <v>1.12</v>
+      </c>
+      <c r="N2">
+        <v>2.72</v>
+      </c>
+      <c r="O2">
+        <v>1.51</v>
+      </c>
+      <c r="P2">
+        <v>1.55</v>
+      </c>
+      <c r="Q2">
+        <v>2.6</v>
+      </c>
+      <c r="R2">
+        <v>1.2</v>
+      </c>
+      <c r="S2">
+        <v>5.3</v>
+      </c>
+      <c r="T2">
+        <v>2.06</v>
+      </c>
+      <c r="U2">
+        <v>1.79</v>
+      </c>
+      <c r="V2">
+        <v>1.46</v>
+      </c>
+      <c r="W2">
+        <v>1.5</v>
+      </c>
+      <c r="X2">
+        <v>9.6</v>
+      </c>
+      <c r="Y2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z2">
+        <v>21</v>
+      </c>
+      <c r="AA2">
+        <v>60</v>
+      </c>
+      <c r="AB2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC2">
+        <v>7.8</v>
+      </c>
+      <c r="AD2">
+        <v>15</v>
+      </c>
+      <c r="AE2">
+        <v>48</v>
+      </c>
+      <c r="AF2">
+        <v>18.5</v>
+      </c>
+      <c r="AG2">
+        <v>14</v>
+      </c>
+      <c r="AH2">
+        <v>23</v>
+      </c>
+      <c r="AI2">
+        <v>75</v>
+      </c>
+      <c r="AJ2">
+        <v>50</v>
+      </c>
+      <c r="AK2">
+        <v>42</v>
+      </c>
+      <c r="AL2">
+        <v>120</v>
+      </c>
+      <c r="AM2">
+        <v>220</v>
+      </c>
+      <c r="AN2">
+        <v>48</v>
+      </c>
+      <c r="AO2">
+        <v>60</v>
+      </c>
+      <c r="AP2">
+        <v>7.6</v>
+      </c>
+      <c r="AQ2">
+        <v>7.6</v>
+      </c>
+      <c r="AR2">
+        <v>16</v>
+      </c>
+      <c r="AS2">
+        <v>7.2</v>
+      </c>
+      <c r="AT2">
+        <v>7.2</v>
+      </c>
+      <c r="AU2">
+        <v>6.2</v>
+      </c>
+      <c r="AV2">
+        <v>11.5</v>
+      </c>
+      <c r="AW2">
+        <v>7</v>
+      </c>
+      <c r="AX2">
+        <v>14</v>
+      </c>
+      <c r="AY2">
+        <v>11</v>
+      </c>
+      <c r="AZ2">
+        <v>17.5</v>
+      </c>
+      <c r="BA2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB2">
+        <v>7.8</v>
+      </c>
+      <c r="BC2">
+        <v>7.6</v>
+      </c>
+      <c r="BD2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE2">
+        <v>140</v>
+      </c>
+      <c r="BF2">
+        <v>7.8</v>
+      </c>
+      <c r="BG2">
+        <v>8</v>
+      </c>
+      <c r="BH2">
+        <v>2.88</v>
+      </c>
+      <c r="BI2">
+        <v>2.44</v>
+      </c>
+      <c r="BJ2">
+        <v>11.5</v>
+      </c>
+      <c r="BK2">
+        <v>5.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>170</v>
+      </c>
+      <c r="BN2">
+        <v>5.9</v>
+      </c>
+      <c r="BO2">
+        <v>3.75</v>
+      </c>
+      <c r="BP2">
+        <v>26</v>
+      </c>
+      <c r="BQ2">
         <v>7.4</v>
       </c>
-      <c r="H2">
-        <v>1.6</v>
-      </c>
-      <c r="I2">
-        <v>1.62</v>
-      </c>
-      <c r="J2">
-        <v>4.1</v>
-      </c>
-      <c r="K2">
-        <v>4.2</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="O2">
-        <v>1.24</v>
-      </c>
-      <c r="P2">
-        <v>1.91</v>
-      </c>
-      <c r="Q2">
-        <v>2.06</v>
-      </c>
-      <c r="R2">
-        <v>1.24</v>
-      </c>
-      <c r="S2">
-        <v>4.8</v>
-      </c>
-      <c r="T2">
-        <v>1.63</v>
-      </c>
-      <c r="U2">
-        <v>2.34</v>
-      </c>
-      <c r="V2">
-        <v>2.62</v>
-      </c>
-      <c r="W2">
-        <v>1.15</v>
-      </c>
-      <c r="X2">
-        <v>1000</v>
-      </c>
-      <c r="Y2">
-        <v>5.1</v>
-      </c>
-      <c r="Z2">
+      <c r="BR2">
+        <v>48</v>
+      </c>
+      <c r="BS2">
+        <v>8.4</v>
+      </c>
+      <c r="BT2">
+        <v>6.2</v>
+      </c>
+      <c r="BU2">
+        <v>4.5</v>
+      </c>
+      <c r="BV2">
+        <v>29</v>
+      </c>
+      <c r="BW2">
         <v>7.6</v>
       </c>
-      <c r="AA2">
-        <v>22</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>5.8</v>
-      </c>
-      <c r="AD2">
-        <v>8</v>
-      </c>
-      <c r="AE2">
-        <v>28</v>
-      </c>
-      <c r="AF2">
-        <v>1000</v>
-      </c>
-      <c r="AG2">
-        <v>12.5</v>
-      </c>
-      <c r="AH2">
-        <v>19.5</v>
-      </c>
-      <c r="AI2">
-        <v>60</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>55</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
-        <v>270</v>
-      </c>
-      <c r="AN2">
-        <v>140</v>
-      </c>
-      <c r="AO2">
-        <v>34</v>
-      </c>
-      <c r="AP2">
-        <v>13.5</v>
-      </c>
-      <c r="AQ2">
-        <v>4.7</v>
-      </c>
-      <c r="AR2">
-        <v>6.4</v>
-      </c>
-      <c r="AS2">
-        <v>17.5</v>
-      </c>
-      <c r="AT2">
-        <v>11.5</v>
-      </c>
-      <c r="AU2">
-        <v>5.3</v>
-      </c>
-      <c r="AV2">
-        <v>7</v>
-      </c>
-      <c r="AW2">
-        <v>21</v>
-      </c>
-      <c r="AX2">
-        <v>11.5</v>
-      </c>
-      <c r="AY2">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2">
-        <v>16.5</v>
-      </c>
-      <c r="BA2">
-        <v>42</v>
-      </c>
-      <c r="BB2">
-        <v>11.5</v>
-      </c>
-      <c r="BC2">
-        <v>40</v>
-      </c>
-      <c r="BD2">
-        <v>55</v>
-      </c>
-      <c r="BE2">
-        <v>130</v>
-      </c>
-      <c r="BF2">
-        <v>75</v>
-      </c>
-      <c r="BG2">
-        <v>27</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>14.5</v>
-      </c>
-      <c r="BJ2">
-        <v>10.5</v>
-      </c>
-      <c r="BK2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>14.5</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>14.5</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>14.5</v>
-      </c>
-      <c r="BR2">
-        <v>900</v>
-      </c>
-      <c r="BS2">
-        <v>90</v>
-      </c>
-      <c r="BT2">
-        <v>1.29</v>
-      </c>
-      <c r="BU2">
-        <v>1.26</v>
-      </c>
-      <c r="BV2">
-        <v>12.5</v>
-      </c>
-      <c r="BW2">
-        <v>9.6</v>
-      </c>
       <c r="BX2">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="BY2">
-        <v>70</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA2">
-        <v>17</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
+        <v>5.5</v>
+      </c>
+      <c r="H3">
+        <v>1.81</v>
+      </c>
+      <c r="I3">
+        <v>1.93</v>
+      </c>
+      <c r="J3">
+        <v>3.45</v>
+      </c>
+      <c r="K3">
+        <v>3.85</v>
+      </c>
+      <c r="L3">
+        <v>1.45</v>
+      </c>
+      <c r="M3">
+        <v>1.09</v>
+      </c>
+      <c r="N3">
         <v>3.2</v>
       </c>
-      <c r="H3">
-        <v>2.8</v>
-      </c>
-      <c r="I3">
-        <v>3.15</v>
-      </c>
-      <c r="J3">
-        <v>2.9</v>
-      </c>
-      <c r="K3">
-        <v>3.3</v>
-      </c>
-      <c r="L3">
-        <v>1.58</v>
-      </c>
-      <c r="M3">
-        <v>1.11</v>
-      </c>
-      <c r="N3">
-        <v>2.42</v>
-      </c>
       <c r="O3">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="T3">
+        <v>2.04</v>
+      </c>
+      <c r="U3">
+        <v>1.81</v>
+      </c>
+      <c r="V3">
         <v>2.06</v>
       </c>
-      <c r="U3">
-        <v>1.72</v>
-      </c>
-      <c r="V3">
-        <v>1.47</v>
-      </c>
       <c r="W3">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="X3">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
+        <v>11.5</v>
+      </c>
+      <c r="AA3">
+        <v>22</v>
+      </c>
+      <c r="AB3">
+        <v>16.5</v>
+      </c>
+      <c r="AC3">
+        <v>9.4</v>
+      </c>
+      <c r="AD3">
+        <v>12</v>
+      </c>
+      <c r="AE3">
+        <v>24</v>
+      </c>
+      <c r="AF3">
+        <v>46</v>
+      </c>
+      <c r="AG3">
         <v>23</v>
       </c>
-      <c r="AA3">
-        <v>60</v>
-      </c>
-      <c r="AB3">
-        <v>9</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>17.5</v>
-      </c>
-      <c r="AE3">
-        <v>60</v>
-      </c>
-      <c r="AF3">
-        <v>22</v>
-      </c>
-      <c r="AG3">
-        <v>17.5</v>
-      </c>
       <c r="AH3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AK3">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AM3">
-        <v>230</v>
+        <v>580</v>
       </c>
       <c r="AN3">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="AP3">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR3">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="AT3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AU3">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW3">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="AX3">
+        <v>5.7</v>
+      </c>
+      <c r="AY3">
+        <v>16.5</v>
+      </c>
+      <c r="AZ3">
+        <v>18.5</v>
+      </c>
+      <c r="BA3">
+        <v>6.4</v>
+      </c>
+      <c r="BB3">
+        <v>6.2</v>
+      </c>
+      <c r="BC3">
+        <v>6</v>
+      </c>
+      <c r="BD3">
+        <v>6</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>6.2</v>
+      </c>
+      <c r="BG3">
+        <v>12</v>
+      </c>
+      <c r="BH3">
+        <v>3.35</v>
+      </c>
+      <c r="BI3">
+        <v>2.68</v>
+      </c>
+      <c r="BJ3">
+        <v>12.5</v>
+      </c>
+      <c r="BK3">
+        <v>4.6</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>130</v>
+      </c>
+      <c r="BN3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO3">
+        <v>4.2</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>6.6</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>6.6</v>
+      </c>
+      <c r="BT3">
+        <v>4.6</v>
+      </c>
+      <c r="BU3">
+        <v>2.86</v>
+      </c>
+      <c r="BV3">
+        <v>14</v>
+      </c>
+      <c r="BW3">
         <v>4.8</v>
       </c>
-      <c r="AY3">
-        <v>4.5</v>
-      </c>
-      <c r="AZ3">
-        <v>4.9</v>
-      </c>
-      <c r="BA3">
-        <v>5.8</v>
-      </c>
-      <c r="BB3">
-        <v>5.6</v>
-      </c>
-      <c r="BC3">
-        <v>5.5</v>
-      </c>
-      <c r="BD3">
-        <v>5.8</v>
-      </c>
-      <c r="BE3">
-        <v>140</v>
-      </c>
-      <c r="BF3">
-        <v>5.7</v>
-      </c>
-      <c r="BG3">
-        <v>5.6</v>
-      </c>
-      <c r="BH3">
-        <v>2.76</v>
-      </c>
-      <c r="BI3">
-        <v>2.34</v>
-      </c>
-      <c r="BJ3">
-        <v>12</v>
-      </c>
-      <c r="BK3">
-        <v>5.2</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>170</v>
-      </c>
-      <c r="BN3">
-        <v>6.2</v>
-      </c>
-      <c r="BO3">
-        <v>3.7</v>
-      </c>
-      <c r="BP3">
-        <v>30</v>
-      </c>
-      <c r="BQ3">
-        <v>1.99</v>
-      </c>
-      <c r="BR3">
-        <v>55</v>
-      </c>
-      <c r="BS3">
-        <v>2.04</v>
-      </c>
-      <c r="BT3">
-        <v>6.2</v>
-      </c>
-      <c r="BU3">
-        <v>3.7</v>
-      </c>
-      <c r="BV3">
-        <v>30</v>
-      </c>
-      <c r="BW3">
-        <v>1.99</v>
-      </c>
       <c r="BX3">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BY3">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="BZ3">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="CA3">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F4">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2.72</v>
       </c>
       <c r="H4">
-        <v>1.74</v>
+        <v>3.4</v>
       </c>
       <c r="I4">
-        <v>1.99</v>
+        <v>3.95</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="K4">
+        <v>3.25</v>
+      </c>
+      <c r="L4">
+        <v>1.6</v>
+      </c>
+      <c r="M4">
+        <v>1.14</v>
+      </c>
+      <c r="N4">
+        <v>2.5</v>
+      </c>
+      <c r="O4">
+        <v>1.58</v>
+      </c>
+      <c r="P4">
+        <v>1.47</v>
+      </c>
+      <c r="Q4">
+        <v>2.78</v>
+      </c>
+      <c r="R4">
+        <v>1.17</v>
+      </c>
+      <c r="S4">
+        <v>5.7</v>
+      </c>
+      <c r="T4">
+        <v>2.12</v>
+      </c>
+      <c r="U4">
+        <v>1.72</v>
+      </c>
+      <c r="V4">
+        <v>1.33</v>
+      </c>
+      <c r="W4">
+        <v>1.58</v>
+      </c>
+      <c r="X4">
+        <v>9.6</v>
+      </c>
+      <c r="Y4">
+        <v>11.5</v>
+      </c>
+      <c r="Z4">
+        <v>26</v>
+      </c>
+      <c r="AA4">
+        <v>500</v>
+      </c>
+      <c r="AB4">
+        <v>8</v>
+      </c>
+      <c r="AC4">
+        <v>7.6</v>
+      </c>
+      <c r="AD4">
+        <v>17.5</v>
+      </c>
+      <c r="AE4">
+        <v>80</v>
+      </c>
+      <c r="AF4">
+        <v>15.5</v>
+      </c>
+      <c r="AG4">
+        <v>14</v>
+      </c>
+      <c r="AH4">
+        <v>26</v>
+      </c>
+      <c r="AI4">
+        <v>540</v>
+      </c>
+      <c r="AJ4">
+        <v>50</v>
+      </c>
+      <c r="AK4">
+        <v>48</v>
+      </c>
+      <c r="AL4">
+        <v>90</v>
+      </c>
+      <c r="AM4">
+        <v>500</v>
+      </c>
+      <c r="AN4">
+        <v>55</v>
+      </c>
+      <c r="AO4">
+        <v>600</v>
+      </c>
+      <c r="AP4">
+        <v>6.6</v>
+      </c>
+      <c r="AQ4">
+        <v>8</v>
+      </c>
+      <c r="AR4">
+        <v>17</v>
+      </c>
+      <c r="AS4">
+        <v>7.2</v>
+      </c>
+      <c r="AT4">
+        <v>6.2</v>
+      </c>
+      <c r="AU4">
+        <v>5.9</v>
+      </c>
+      <c r="AV4">
+        <v>13.5</v>
+      </c>
+      <c r="AW4">
+        <v>7</v>
+      </c>
+      <c r="AX4">
+        <v>12</v>
+      </c>
+      <c r="AY4">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4">
+        <v>20</v>
+      </c>
+      <c r="BA4">
+        <v>7.2</v>
+      </c>
+      <c r="BB4">
+        <v>6.8</v>
+      </c>
+      <c r="BC4">
+        <v>6.6</v>
+      </c>
+      <c r="BD4">
+        <v>7</v>
+      </c>
+      <c r="BE4">
+        <v>140</v>
+      </c>
+      <c r="BF4">
+        <v>6.6</v>
+      </c>
+      <c r="BG4">
+        <v>7.2</v>
+      </c>
+      <c r="BH4">
+        <v>3</v>
+      </c>
+      <c r="BI4">
+        <v>2.16</v>
+      </c>
+      <c r="BJ4">
+        <v>14</v>
+      </c>
+      <c r="BK4">
+        <v>3.7</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>5.3</v>
+      </c>
+      <c r="BN4">
+        <v>6.2</v>
+      </c>
+      <c r="BO4">
+        <v>3.95</v>
+      </c>
+      <c r="BP4">
+        <v>28</v>
+      </c>
+      <c r="BQ4">
         <v>4.2</v>
       </c>
-      <c r="L4">
-        <v>1.41</v>
-      </c>
-      <c r="M4">
-        <v>1.07</v>
-      </c>
-      <c r="N4">
-        <v>3.25</v>
-      </c>
-      <c r="O4">
-        <v>1.36</v>
-      </c>
-      <c r="P4">
-        <v>1.71</v>
-      </c>
-      <c r="Q4">
-        <v>2</v>
-      </c>
-      <c r="R4">
-        <v>1.27</v>
-      </c>
-      <c r="S4">
-        <v>3.55</v>
-      </c>
-      <c r="T4">
-        <v>1.93</v>
-      </c>
-      <c r="U4">
-        <v>1.81</v>
-      </c>
-      <c r="V4">
-        <v>2</v>
-      </c>
-      <c r="W4">
-        <v>1.2</v>
-      </c>
-      <c r="X4">
-        <v>14</v>
-      </c>
-      <c r="Y4">
-        <v>8.6</v>
-      </c>
-      <c r="Z4">
-        <v>11</v>
-      </c>
-      <c r="AA4">
-        <v>23</v>
-      </c>
-      <c r="AB4">
-        <v>17</v>
-      </c>
-      <c r="AC4">
-        <v>9.6</v>
-      </c>
-      <c r="AD4">
-        <v>12</v>
-      </c>
-      <c r="AE4">
-        <v>24</v>
-      </c>
-      <c r="AF4">
-        <v>120</v>
-      </c>
-      <c r="AG4">
-        <v>24</v>
-      </c>
-      <c r="AH4">
-        <v>27</v>
-      </c>
-      <c r="AI4">
-        <v>55</v>
-      </c>
-      <c r="AJ4">
-        <v>900</v>
-      </c>
-      <c r="AK4">
-        <v>700</v>
-      </c>
-      <c r="AL4">
-        <v>700</v>
-      </c>
-      <c r="AM4">
-        <v>580</v>
-      </c>
-      <c r="AN4">
-        <v>700</v>
-      </c>
-      <c r="AO4">
-        <v>17</v>
-      </c>
-      <c r="AP4">
-        <v>5.5</v>
-      </c>
-      <c r="AQ4">
-        <v>5.8</v>
-      </c>
-      <c r="AR4">
-        <v>3.85</v>
-      </c>
-      <c r="AS4">
+      <c r="BR4">
+        <v>60</v>
+      </c>
+      <c r="BS4">
         <v>4.6</v>
       </c>
-      <c r="AT4">
-        <v>4.4</v>
-      </c>
-      <c r="AU4">
-        <v>3.85</v>
-      </c>
-      <c r="AV4">
-        <v>3.85</v>
-      </c>
-      <c r="AW4">
+      <c r="BT4">
+        <v>7.8</v>
+      </c>
+      <c r="BU4">
+        <v>4.9</v>
+      </c>
+      <c r="BV4">
+        <v>44</v>
+      </c>
+      <c r="BW4">
+        <v>4.5</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>4.7</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
         <v>4.6</v>
       </c>
-      <c r="AX4">
-        <v>5.3</v>
-      </c>
-      <c r="AY4">
-        <v>4.6</v>
-      </c>
-      <c r="AZ4">
-        <v>4.9</v>
-      </c>
-      <c r="BA4">
-        <v>5.2</v>
-      </c>
-      <c r="BB4">
-        <v>5.5</v>
-      </c>
-      <c r="BC4">
-        <v>5.4</v>
-      </c>
-      <c r="BD4">
-        <v>5.4</v>
-      </c>
-      <c r="BE4">
-        <v>5.8</v>
-      </c>
-      <c r="BF4">
-        <v>5.5</v>
-      </c>
-      <c r="BG4">
-        <v>4.2</v>
-      </c>
-      <c r="BH4">
-        <v>3.45</v>
-      </c>
-      <c r="BI4">
-        <v>2.64</v>
-      </c>
-      <c r="BJ4">
-        <v>12.5</v>
-      </c>
-      <c r="BK4">
-        <v>4.2</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>6.2</v>
-      </c>
-      <c r="BN4">
-        <v>10</v>
-      </c>
-      <c r="BO4">
-        <v>3.9</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>5.9</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>5.9</v>
-      </c>
-      <c r="BT4">
-        <v>4.7</v>
-      </c>
-      <c r="BU4">
-        <v>2.76</v>
-      </c>
-      <c r="BV4">
-        <v>14.5</v>
-      </c>
-      <c r="BW4">
-        <v>4.4</v>
-      </c>
-      <c r="BX4">
-        <v>34</v>
-      </c>
-      <c r="BY4">
-        <v>5.4</v>
-      </c>
-      <c r="BZ4">
-        <v>32</v>
-      </c>
-      <c r="CA4">
-        <v>5.4</v>
-      </c>
       <c r="CB4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F5">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="G5">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="H5">
+        <v>3.1</v>
+      </c>
+      <c r="I5">
         <v>3.3</v>
       </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
       <c r="J5">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
         <v>1.58</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="O5">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P5">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q5">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R5">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U5">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="X5">
+        <v>8.6</v>
+      </c>
+      <c r="Y5">
         <v>9.4</v>
       </c>
-      <c r="Y5">
-        <v>10.5</v>
-      </c>
       <c r="Z5">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA5">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AB5">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AC5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AF5">
+        <v>18.5</v>
+      </c>
+      <c r="AG5">
         <v>15.5</v>
       </c>
-      <c r="AG5">
-        <v>14</v>
-      </c>
       <c r="AH5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI5">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="AJ5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AK5">
         <v>48</v>
@@ -1909,237 +1897,237 @@
         <v>55</v>
       </c>
       <c r="AO5">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP5">
+        <v>7</v>
+      </c>
+      <c r="AQ5">
+        <v>7.8</v>
+      </c>
+      <c r="AR5">
+        <v>16</v>
+      </c>
+      <c r="AS5">
+        <v>46</v>
+      </c>
+      <c r="AT5">
+        <v>7.2</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>12.5</v>
+      </c>
+      <c r="AW5">
+        <v>32</v>
+      </c>
+      <c r="AX5">
+        <v>14</v>
+      </c>
+      <c r="AY5">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5">
+        <v>17</v>
+      </c>
+      <c r="BA5">
+        <v>46</v>
+      </c>
+      <c r="BB5">
+        <v>27</v>
+      </c>
+      <c r="BC5">
+        <v>23</v>
+      </c>
+      <c r="BD5">
+        <v>36</v>
+      </c>
+      <c r="BE5">
+        <v>140</v>
+      </c>
+      <c r="BF5">
+        <v>26</v>
+      </c>
+      <c r="BG5">
+        <v>44</v>
+      </c>
+      <c r="BH5">
+        <v>3.1</v>
+      </c>
+      <c r="BI5">
+        <v>2.2</v>
+      </c>
+      <c r="BJ5">
+        <v>13</v>
+      </c>
+      <c r="BK5">
+        <v>3.8</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>170</v>
+      </c>
+      <c r="BN5">
+        <v>6.4</v>
+      </c>
+      <c r="BO5">
         <v>4.2</v>
       </c>
-      <c r="AQ5">
-        <v>5.8</v>
-      </c>
-      <c r="AR5">
-        <v>5.6</v>
-      </c>
-      <c r="AS5">
-        <v>6.6</v>
-      </c>
-      <c r="AT5">
-        <v>5.6</v>
-      </c>
-      <c r="AU5">
-        <v>5.4</v>
-      </c>
-      <c r="AV5">
-        <v>5.1</v>
-      </c>
-      <c r="AW5">
-        <v>6.4</v>
-      </c>
-      <c r="AX5">
-        <v>6.4</v>
-      </c>
-      <c r="AY5">
-        <v>7.6</v>
-      </c>
-      <c r="AZ5">
-        <v>5.9</v>
-      </c>
-      <c r="BA5">
-        <v>6.6</v>
-      </c>
-      <c r="BB5">
-        <v>6</v>
-      </c>
-      <c r="BC5">
-        <v>6</v>
-      </c>
-      <c r="BD5">
-        <v>6.6</v>
-      </c>
-      <c r="BE5">
-        <v>6.8</v>
-      </c>
-      <c r="BF5">
-        <v>6.6</v>
-      </c>
-      <c r="BG5">
-        <v>6.6</v>
-      </c>
-      <c r="BH5">
-        <v>2.96</v>
-      </c>
-      <c r="BI5">
-        <v>2.14</v>
-      </c>
-      <c r="BJ5">
-        <v>14</v>
-      </c>
-      <c r="BK5">
-        <v>3.75</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
+      <c r="BP5">
+        <v>29</v>
+      </c>
+      <c r="BQ5">
+        <v>4.5</v>
+      </c>
+      <c r="BR5">
+        <v>55</v>
+      </c>
+      <c r="BS5">
+        <v>4.9</v>
+      </c>
+      <c r="BT5">
+        <v>7</v>
+      </c>
+      <c r="BU5">
+        <v>4.6</v>
+      </c>
+      <c r="BV5">
+        <v>36</v>
+      </c>
+      <c r="BW5">
+        <v>4.7</v>
+      </c>
+      <c r="BX5">
+        <v>65</v>
+      </c>
+      <c r="BY5">
         <v>5</v>
       </c>
-      <c r="BN5">
-        <v>6.2</v>
-      </c>
-      <c r="BO5">
-        <v>2.8</v>
-      </c>
-      <c r="BP5">
-        <v>28</v>
-      </c>
-      <c r="BQ5">
-        <v>4.3</v>
-      </c>
-      <c r="BR5">
+      <c r="BZ5">
         <v>60</v>
       </c>
-      <c r="BS5">
-        <v>4.7</v>
-      </c>
-      <c r="BT5">
-        <v>7.8</v>
-      </c>
-      <c r="BU5">
-        <v>3.05</v>
-      </c>
-      <c r="BV5">
-        <v>44</v>
-      </c>
-      <c r="BW5">
-        <v>4.5</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>4.8</v>
-      </c>
-      <c r="BZ5">
-        <v>70</v>
-      </c>
       <c r="CA5">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="CB5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F6">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="G6">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="H6">
-        <v>3.65</v>
+        <v>2.54</v>
       </c>
       <c r="I6">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="J6">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N6">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
+        <v>1.52</v>
+      </c>
+      <c r="P6">
+        <v>1.57</v>
+      </c>
+      <c r="Q6">
+        <v>2.56</v>
+      </c>
+      <c r="R6">
+        <v>1.2</v>
+      </c>
+      <c r="S6">
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>1.83</v>
+      </c>
+      <c r="V6">
         <v>1.55</v>
       </c>
-      <c r="P6">
-        <v>1.46</v>
-      </c>
-      <c r="Q6">
-        <v>2.64</v>
-      </c>
-      <c r="R6">
-        <v>1.17</v>
-      </c>
-      <c r="S6">
-        <v>5.5</v>
-      </c>
-      <c r="T6">
-        <v>2.16</v>
-      </c>
-      <c r="U6">
-        <v>1.72</v>
-      </c>
-      <c r="V6">
-        <v>1.32</v>
-      </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="X6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y6">
+        <v>8.6</v>
+      </c>
+      <c r="Z6">
+        <v>17</v>
+      </c>
+      <c r="AA6">
+        <v>120</v>
+      </c>
+      <c r="AB6">
         <v>9.800000000000001</v>
-      </c>
-      <c r="Y6">
-        <v>12.5</v>
-      </c>
-      <c r="Z6">
-        <v>32</v>
-      </c>
-      <c r="AA6">
-        <v>900</v>
-      </c>
-      <c r="AB6">
-        <v>8.4</v>
       </c>
       <c r="AC6">
         <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AF6">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AG6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="AJ6">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="AK6">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AL6">
         <v>190</v>
@@ -2148,127 +2136,127 @@
         <v>500</v>
       </c>
       <c r="AN6">
+        <v>600</v>
+      </c>
+      <c r="AO6">
+        <v>55</v>
+      </c>
+      <c r="AP6">
+        <v>7.8</v>
+      </c>
+      <c r="AQ6">
+        <v>7.2</v>
+      </c>
+      <c r="AR6">
+        <v>11.5</v>
+      </c>
+      <c r="AS6">
+        <v>19</v>
+      </c>
+      <c r="AT6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU6">
+        <v>6.2</v>
+      </c>
+      <c r="AV6">
+        <v>11</v>
+      </c>
+      <c r="AW6">
+        <v>23</v>
+      </c>
+      <c r="AX6">
+        <v>18</v>
+      </c>
+      <c r="AY6">
+        <v>12.5</v>
+      </c>
+      <c r="AZ6">
+        <v>18</v>
+      </c>
+      <c r="BA6">
+        <v>40</v>
+      </c>
+      <c r="BB6">
+        <v>42</v>
+      </c>
+      <c r="BC6">
+        <v>20</v>
+      </c>
+      <c r="BD6">
         <v>46</v>
       </c>
-      <c r="AO6">
-        <v>600</v>
-      </c>
-      <c r="AP6">
-        <v>3.35</v>
-      </c>
-      <c r="AQ6">
-        <v>3.55</v>
-      </c>
-      <c r="AR6">
-        <v>4.3</v>
-      </c>
-      <c r="AS6">
-        <v>4.8</v>
-      </c>
-      <c r="AT6">
-        <v>3.15</v>
-      </c>
-      <c r="AU6">
-        <v>3</v>
-      </c>
-      <c r="AV6">
-        <v>3.95</v>
-      </c>
-      <c r="AW6">
-        <v>4.7</v>
-      </c>
-      <c r="AX6">
-        <v>3.85</v>
-      </c>
-      <c r="AY6">
-        <v>3.75</v>
-      </c>
-      <c r="AZ6">
-        <v>4.3</v>
-      </c>
-      <c r="BA6">
-        <v>4.8</v>
-      </c>
-      <c r="BB6">
-        <v>4.5</v>
-      </c>
-      <c r="BC6">
-        <v>4.5</v>
-      </c>
-      <c r="BD6">
-        <v>4.7</v>
-      </c>
       <c r="BE6">
-        <v>4.9</v>
+        <v>65</v>
       </c>
       <c r="BF6">
-        <v>4.5</v>
+        <v>44</v>
       </c>
       <c r="BG6">
-        <v>4.8</v>
+        <v>24</v>
       </c>
       <c r="BH6">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BI6">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BK6">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO6">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="BR6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BU6">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2276,393 +2264,393 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F7">
-        <v>3.1</v>
+        <v>2.22</v>
       </c>
       <c r="G7">
+        <v>2.3</v>
+      </c>
+      <c r="H7">
+        <v>3.6</v>
+      </c>
+      <c r="I7">
+        <v>3.8</v>
+      </c>
+      <c r="J7">
+        <v>3.35</v>
+      </c>
+      <c r="K7">
         <v>3.55</v>
       </c>
-      <c r="H7">
-        <v>2.54</v>
-      </c>
-      <c r="I7">
-        <v>2.76</v>
-      </c>
-      <c r="J7">
-        <v>2.92</v>
-      </c>
-      <c r="K7">
-        <v>3.2</v>
-      </c>
       <c r="L7">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="Q7">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="R7">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="T7">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="U7">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="X7">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="Y7">
+        <v>13.5</v>
+      </c>
+      <c r="Z7">
+        <v>27</v>
+      </c>
+      <c r="AA7">
+        <v>85</v>
+      </c>
+      <c r="AB7">
+        <v>9.6</v>
+      </c>
+      <c r="AC7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>16</v>
+      </c>
+      <c r="AE7">
+        <v>46</v>
+      </c>
+      <c r="AF7">
+        <v>14.5</v>
+      </c>
+      <c r="AG7">
+        <v>11.5</v>
+      </c>
+      <c r="AH7">
+        <v>18.5</v>
+      </c>
+      <c r="AI7">
+        <v>60</v>
+      </c>
+      <c r="AJ7">
+        <v>30</v>
+      </c>
+      <c r="AK7">
+        <v>26</v>
+      </c>
+      <c r="AL7">
+        <v>42</v>
+      </c>
+      <c r="AM7">
+        <v>580</v>
+      </c>
+      <c r="AN7">
+        <v>19.5</v>
+      </c>
+      <c r="AO7">
+        <v>48</v>
+      </c>
+      <c r="AP7">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7">
+        <v>11.5</v>
+      </c>
+      <c r="AR7">
+        <v>20</v>
+      </c>
+      <c r="AS7">
+        <v>50</v>
+      </c>
+      <c r="AT7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>13.5</v>
+      </c>
+      <c r="AW7">
+        <v>32</v>
+      </c>
+      <c r="AX7">
+        <v>12</v>
+      </c>
+      <c r="AY7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>15.5</v>
+      </c>
+      <c r="BA7">
+        <v>38</v>
+      </c>
+      <c r="BB7">
+        <v>21</v>
+      </c>
+      <c r="BC7">
+        <v>21</v>
+      </c>
+      <c r="BD7">
+        <v>29</v>
+      </c>
+      <c r="BE7">
+        <v>75</v>
+      </c>
+      <c r="BF7">
+        <v>16.5</v>
+      </c>
+      <c r="BG7">
+        <v>29</v>
+      </c>
+      <c r="BH7">
+        <v>3.35</v>
+      </c>
+      <c r="BI7">
+        <v>2.96</v>
+      </c>
+      <c r="BJ7">
+        <v>10</v>
+      </c>
+      <c r="BK7">
+        <v>5.4</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>11</v>
+      </c>
+      <c r="BN7">
+        <v>5.1</v>
+      </c>
+      <c r="BO7">
+        <v>4.4</v>
+      </c>
+      <c r="BP7">
+        <v>17.5</v>
+      </c>
+      <c r="BQ7">
+        <v>7</v>
+      </c>
+      <c r="BR7">
+        <v>32</v>
+      </c>
+      <c r="BS7">
         <v>8.6</v>
       </c>
-      <c r="Z7">
-        <v>17</v>
-      </c>
-      <c r="AA7">
-        <v>55</v>
-      </c>
-      <c r="AB7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC7">
-        <v>7.4</v>
-      </c>
-      <c r="AD7">
-        <v>13.5</v>
-      </c>
-      <c r="AE7">
-        <v>48</v>
-      </c>
-      <c r="AF7">
-        <v>22</v>
-      </c>
-      <c r="AG7">
-        <v>15.5</v>
-      </c>
-      <c r="AH7">
-        <v>23</v>
-      </c>
-      <c r="AI7">
-        <v>80</v>
-      </c>
-      <c r="AJ7">
-        <v>160</v>
-      </c>
-      <c r="AK7">
-        <v>60</v>
-      </c>
-      <c r="AL7">
-        <v>90</v>
-      </c>
-      <c r="AM7">
-        <v>500</v>
-      </c>
-      <c r="AN7">
-        <v>80</v>
-      </c>
-      <c r="AO7">
-        <v>55</v>
-      </c>
-      <c r="AP7">
-        <v>4.4</v>
-      </c>
-      <c r="AQ7">
-        <v>4.3</v>
-      </c>
-      <c r="AR7">
-        <v>5.7</v>
-      </c>
-      <c r="AS7">
-        <v>7.4</v>
-      </c>
-      <c r="AT7">
-        <v>4.6</v>
-      </c>
-      <c r="AU7">
-        <v>4</v>
-      </c>
-      <c r="AV7">
-        <v>5.3</v>
-      </c>
-      <c r="AW7">
+      <c r="BT7">
         <v>7.2</v>
       </c>
-      <c r="AX7">
-        <v>6.2</v>
-      </c>
-      <c r="AY7">
-        <v>5.7</v>
-      </c>
-      <c r="AZ7">
-        <v>6.2</v>
-      </c>
-      <c r="BA7">
-        <v>7.8</v>
-      </c>
-      <c r="BB7">
-        <v>7.6</v>
-      </c>
-      <c r="BC7">
-        <v>7.4</v>
-      </c>
-      <c r="BD7">
-        <v>7.8</v>
-      </c>
-      <c r="BE7">
+      <c r="BU7">
+        <v>5.8</v>
+      </c>
+      <c r="BV7">
+        <v>32</v>
+      </c>
+      <c r="BW7">
+        <v>8.6</v>
+      </c>
+      <c r="BX7">
+        <v>44</v>
+      </c>
+      <c r="BY7">
+        <v>9.4</v>
+      </c>
+      <c r="BZ7">
+        <v>30</v>
+      </c>
+      <c r="CA7">
         <v>8.4</v>
       </c>
-      <c r="BF7">
-        <v>7.8</v>
-      </c>
-      <c r="BG7">
-        <v>7.4</v>
-      </c>
-      <c r="BH7">
-        <v>2.82</v>
-      </c>
-      <c r="BI7">
-        <v>2.48</v>
-      </c>
-      <c r="BJ7">
-        <v>11.5</v>
-      </c>
-      <c r="BK7">
-        <v>5.7</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>2.24</v>
-      </c>
-      <c r="BN7">
-        <v>6.4</v>
-      </c>
-      <c r="BO7">
-        <v>4.1</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>2.1</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>2.16</v>
-      </c>
-      <c r="BT7">
-        <v>5.6</v>
-      </c>
-      <c r="BU7">
-        <v>3.75</v>
-      </c>
-      <c r="BV7">
-        <v>25</v>
-      </c>
-      <c r="BW7">
-        <v>2.06</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>2.16</v>
-      </c>
-      <c r="BZ7">
-        <v>1000</v>
-      </c>
-      <c r="CA7">
-        <v>2.16</v>
-      </c>
       <c r="CB7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="H8">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I8">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T8">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="X8">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB8">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE8">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AF8">
         <v>14</v>
       </c>
       <c r="AG8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH8">
         <v>19</v>
       </c>
       <c r="AI8">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL8">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN8">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AO8">
+        <v>65</v>
+      </c>
+      <c r="AP8">
+        <v>12.5</v>
+      </c>
+      <c r="AQ8">
+        <v>12</v>
+      </c>
+      <c r="AR8">
+        <v>22</v>
+      </c>
+      <c r="AS8">
         <v>55</v>
       </c>
-      <c r="AP8">
+      <c r="AT8">
+        <v>8</v>
+      </c>
+      <c r="AU8">
+        <v>7.2</v>
+      </c>
+      <c r="AV8">
+        <v>14</v>
+      </c>
+      <c r="AW8">
+        <v>34</v>
+      </c>
+      <c r="AX8">
         <v>11</v>
-      </c>
-      <c r="AQ8">
-        <v>11.5</v>
-      </c>
-      <c r="AR8">
-        <v>20</v>
-      </c>
-      <c r="AS8">
-        <v>50</v>
-      </c>
-      <c r="AT8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU8">
-        <v>6.8</v>
-      </c>
-      <c r="AV8">
-        <v>13.5</v>
-      </c>
-      <c r="AW8">
-        <v>30</v>
-      </c>
-      <c r="AX8">
-        <v>12</v>
       </c>
       <c r="AY8">
         <v>9.6</v>
@@ -2671,1056 +2659,1056 @@
         <v>16</v>
       </c>
       <c r="BA8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE8">
         <v>75</v>
       </c>
       <c r="BF8">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BG8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH8">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BI8">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="BN8">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BO8">
+        <v>4.2</v>
+      </c>
+      <c r="BP8">
+        <v>18.5</v>
+      </c>
+      <c r="BQ8">
+        <v>3.8</v>
+      </c>
+      <c r="BR8">
+        <v>36</v>
+      </c>
+      <c r="BS8">
+        <v>4.2</v>
+      </c>
+      <c r="BT8">
+        <v>8.6</v>
+      </c>
+      <c r="BU8">
+        <v>6</v>
+      </c>
+      <c r="BV8">
+        <v>40</v>
+      </c>
+      <c r="BW8">
+        <v>4.2</v>
+      </c>
+      <c r="BX8">
+        <v>55</v>
+      </c>
+      <c r="BY8">
         <v>4.4</v>
       </c>
-      <c r="BP8">
-        <v>17</v>
-      </c>
-      <c r="BQ8">
-        <v>7</v>
-      </c>
-      <c r="BR8">
+      <c r="BZ8">
         <v>34</v>
       </c>
-      <c r="BS8">
-        <v>9</v>
-      </c>
-      <c r="BT8">
-        <v>7.2</v>
-      </c>
-      <c r="BU8">
-        <v>5.2</v>
-      </c>
-      <c r="BV8">
-        <v>32</v>
-      </c>
-      <c r="BW8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX8">
-        <v>46</v>
-      </c>
-      <c r="BY8">
-        <v>9.6</v>
-      </c>
-      <c r="BZ8">
-        <v>30</v>
-      </c>
       <c r="CA8">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="CB8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F9">
-        <v>2.04</v>
+        <v>4.3</v>
       </c>
       <c r="G9">
-        <v>2.18</v>
+        <v>5.3</v>
       </c>
       <c r="H9">
-        <v>3.85</v>
+        <v>1.96</v>
       </c>
       <c r="I9">
-        <v>4.2</v>
+        <v>2.14</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K9">
+        <v>3.45</v>
+      </c>
+      <c r="L9">
+        <v>1.53</v>
+      </c>
+      <c r="M9">
+        <v>1.11</v>
+      </c>
+      <c r="N9">
+        <v>2.58</v>
+      </c>
+      <c r="O9">
+        <v>1.51</v>
+      </c>
+      <c r="P9">
+        <v>1.54</v>
+      </c>
+      <c r="Q9">
+        <v>2.44</v>
+      </c>
+      <c r="R9">
+        <v>1.19</v>
+      </c>
+      <c r="S9">
+        <v>4.4</v>
+      </c>
+      <c r="T9">
+        <v>2.08</v>
+      </c>
+      <c r="U9">
+        <v>1.74</v>
+      </c>
+      <c r="V9">
+        <v>1.9</v>
+      </c>
+      <c r="W9">
+        <v>1.23</v>
+      </c>
+      <c r="X9">
+        <v>11</v>
+      </c>
+      <c r="Y9">
+        <v>7</v>
+      </c>
+      <c r="Z9">
+        <v>13.5</v>
+      </c>
+      <c r="AA9">
+        <v>32</v>
+      </c>
+      <c r="AB9">
+        <v>15</v>
+      </c>
+      <c r="AC9">
+        <v>7.8</v>
+      </c>
+      <c r="AD9">
+        <v>13.5</v>
+      </c>
+      <c r="AE9">
+        <v>65</v>
+      </c>
+      <c r="AF9">
+        <v>42</v>
+      </c>
+      <c r="AG9">
+        <v>25</v>
+      </c>
+      <c r="AH9">
+        <v>29</v>
+      </c>
+      <c r="AI9">
+        <v>70</v>
+      </c>
+      <c r="AJ9">
+        <v>900</v>
+      </c>
+      <c r="AK9">
+        <v>240</v>
+      </c>
+      <c r="AL9">
+        <v>500</v>
+      </c>
+      <c r="AM9">
+        <v>500</v>
+      </c>
+      <c r="AN9">
+        <v>600</v>
+      </c>
+      <c r="AO9">
+        <v>29</v>
+      </c>
+      <c r="AP9">
+        <v>3.75</v>
+      </c>
+      <c r="AQ9">
+        <v>3.1</v>
+      </c>
+      <c r="AR9">
+        <v>4</v>
+      </c>
+      <c r="AS9">
+        <v>4.8</v>
+      </c>
+      <c r="AT9">
+        <v>4.1</v>
+      </c>
+      <c r="AU9">
+        <v>3.25</v>
+      </c>
+      <c r="AV9">
+        <v>4</v>
+      </c>
+      <c r="AW9">
+        <v>4.7</v>
+      </c>
+      <c r="AX9">
+        <v>5</v>
+      </c>
+      <c r="AY9">
+        <v>4.6</v>
+      </c>
+      <c r="AZ9">
+        <v>4.7</v>
+      </c>
+      <c r="BA9">
+        <v>5.2</v>
+      </c>
+      <c r="BB9">
+        <v>5.5</v>
+      </c>
+      <c r="BC9">
+        <v>5.4</v>
+      </c>
+      <c r="BD9">
+        <v>5.4</v>
+      </c>
+      <c r="BE9">
+        <v>5.5</v>
+      </c>
+      <c r="BF9">
+        <v>5.5</v>
+      </c>
+      <c r="BG9">
+        <v>4.7</v>
+      </c>
+      <c r="BH9">
+        <v>3.25</v>
+      </c>
+      <c r="BI9">
+        <v>2.3</v>
+      </c>
+      <c r="BJ9">
+        <v>14</v>
+      </c>
+      <c r="BK9">
         <v>3.7</v>
       </c>
-      <c r="L9">
-        <v>1.37</v>
-      </c>
-      <c r="M9">
-        <v>1.08</v>
-      </c>
-      <c r="N9">
-        <v>3.55</v>
-      </c>
-      <c r="O9">
-        <v>1.35</v>
-      </c>
-      <c r="P9">
-        <v>1.87</v>
-      </c>
-      <c r="Q9">
-        <v>2.02</v>
-      </c>
-      <c r="R9">
-        <v>1.33</v>
-      </c>
-      <c r="S9">
-        <v>3.65</v>
-      </c>
-      <c r="T9">
-        <v>1.83</v>
-      </c>
-      <c r="U9">
-        <v>2.06</v>
-      </c>
-      <c r="V9">
-        <v>1.31</v>
-      </c>
-      <c r="W9">
-        <v>1.84</v>
-      </c>
-      <c r="X9">
-        <v>16.5</v>
-      </c>
-      <c r="Y9">
-        <v>15</v>
-      </c>
-      <c r="Z9">
-        <v>30</v>
-      </c>
-      <c r="AA9">
-        <v>500</v>
-      </c>
-      <c r="AB9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD9">
-        <v>18</v>
-      </c>
-      <c r="AE9">
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>4.9</v>
+      </c>
+      <c r="BN9">
+        <v>9.4</v>
+      </c>
+      <c r="BO9">
+        <v>3.25</v>
+      </c>
+      <c r="BP9">
         <v>60</v>
       </c>
-      <c r="AF9">
-        <v>15.5</v>
-      </c>
-      <c r="AG9">
-        <v>11</v>
-      </c>
-      <c r="AH9">
-        <v>19</v>
-      </c>
-      <c r="AI9">
-        <v>85</v>
-      </c>
-      <c r="AJ9">
-        <v>32</v>
-      </c>
-      <c r="AK9">
-        <v>25</v>
-      </c>
-      <c r="AL9">
-        <v>42</v>
-      </c>
-      <c r="AM9">
-        <v>580</v>
-      </c>
-      <c r="AN9">
-        <v>21</v>
-      </c>
-      <c r="AO9">
-        <v>65</v>
-      </c>
-      <c r="AP9">
-        <v>12</v>
-      </c>
-      <c r="AQ9">
-        <v>12</v>
-      </c>
-      <c r="AR9">
-        <v>23</v>
-      </c>
-      <c r="AS9">
-        <v>55</v>
-      </c>
-      <c r="AT9">
-        <v>8</v>
-      </c>
-      <c r="AU9">
-        <v>7</v>
-      </c>
-      <c r="AV9">
-        <v>14</v>
-      </c>
-      <c r="AW9">
-        <v>34</v>
-      </c>
-      <c r="AX9">
-        <v>11</v>
-      </c>
-      <c r="AY9">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9">
-        <v>16</v>
-      </c>
-      <c r="BA9">
-        <v>38</v>
-      </c>
-      <c r="BB9">
-        <v>22</v>
-      </c>
-      <c r="BC9">
+      <c r="BQ9">
+        <v>4.6</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>4.7</v>
+      </c>
+      <c r="BT9">
+        <v>5.3</v>
+      </c>
+      <c r="BU9">
+        <v>2.58</v>
+      </c>
+      <c r="BV9">
         <v>19.5</v>
       </c>
-      <c r="BD9">
-        <v>27</v>
-      </c>
-      <c r="BE9">
-        <v>75</v>
-      </c>
-      <c r="BF9">
-        <v>15</v>
-      </c>
-      <c r="BG9">
-        <v>32</v>
-      </c>
-      <c r="BH9">
-        <v>3.8</v>
-      </c>
-      <c r="BI9">
-        <v>2.98</v>
-      </c>
-      <c r="BJ9">
-        <v>12</v>
-      </c>
-      <c r="BK9">
-        <v>3.5</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>4.7</v>
-      </c>
-      <c r="BN9">
-        <v>5.7</v>
-      </c>
-      <c r="BO9">
-        <v>4.3</v>
-      </c>
-      <c r="BP9">
-        <v>18.5</v>
-      </c>
-      <c r="BQ9">
-        <v>3.8</v>
-      </c>
-      <c r="BR9">
-        <v>38</v>
-      </c>
-      <c r="BS9">
-        <v>4.3</v>
-      </c>
-      <c r="BT9">
-        <v>8.6</v>
-      </c>
-      <c r="BU9">
-        <v>5.4</v>
-      </c>
-      <c r="BV9">
-        <v>42</v>
-      </c>
       <c r="BW9">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BX9">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BY9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ9">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="CA9">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F10">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="G10">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="H10">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="I10">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K10">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L10">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N10">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="O10">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="P10">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Q10">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="R10">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S10">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V10">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="X10">
+        <v>8.4</v>
+      </c>
+      <c r="Y10">
         <v>11</v>
       </c>
-      <c r="Y10">
-        <v>7</v>
-      </c>
       <c r="Z10">
+        <v>28</v>
+      </c>
+      <c r="AA10">
+        <v>900</v>
+      </c>
+      <c r="AB10">
+        <v>7.6</v>
+      </c>
+      <c r="AC10">
+        <v>7.6</v>
+      </c>
+      <c r="AD10">
+        <v>18.5</v>
+      </c>
+      <c r="AE10">
+        <v>75</v>
+      </c>
+      <c r="AF10">
+        <v>15</v>
+      </c>
+      <c r="AG10">
         <v>13.5</v>
       </c>
-      <c r="AA10">
-        <v>32</v>
-      </c>
-      <c r="AB10">
-        <v>15</v>
-      </c>
-      <c r="AC10">
-        <v>7.8</v>
-      </c>
-      <c r="AD10">
-        <v>13.5</v>
-      </c>
-      <c r="AE10">
-        <v>65</v>
-      </c>
-      <c r="AF10">
-        <v>44</v>
-      </c>
-      <c r="AG10">
-        <v>25</v>
-      </c>
       <c r="AH10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI10">
+        <v>260</v>
+      </c>
+      <c r="AJ10">
+        <v>40</v>
+      </c>
+      <c r="AK10">
+        <v>38</v>
+      </c>
+      <c r="AL10">
         <v>75</v>
-      </c>
-      <c r="AJ10">
-        <v>900</v>
-      </c>
-      <c r="AK10">
-        <v>240</v>
-      </c>
-      <c r="AL10">
-        <v>500</v>
       </c>
       <c r="AM10">
         <v>500</v>
       </c>
       <c r="AN10">
+        <v>42</v>
+      </c>
+      <c r="AO10">
         <v>600</v>
       </c>
-      <c r="AO10">
-        <v>32</v>
-      </c>
       <c r="AP10">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="AR10">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AS10">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AU10">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV10">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="AW10">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX10">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY10">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AZ10">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA10">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BB10">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC10">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BD10">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE10">
+        <v>7.8</v>
+      </c>
+      <c r="BF10">
+        <v>6.8</v>
+      </c>
+      <c r="BG10">
+        <v>7.6</v>
+      </c>
+      <c r="BH10">
+        <v>2.76</v>
+      </c>
+      <c r="BI10">
+        <v>2.36</v>
+      </c>
+      <c r="BJ10">
+        <v>12.5</v>
+      </c>
+      <c r="BK10">
+        <v>5.4</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>7.2</v>
+      </c>
+      <c r="BN10">
         <v>5.3</v>
       </c>
-      <c r="BF10">
-        <v>5.2</v>
-      </c>
-      <c r="BG10">
-        <v>4.6</v>
-      </c>
-      <c r="BH10">
-        <v>3.15</v>
-      </c>
-      <c r="BI10">
-        <v>2.26</v>
-      </c>
-      <c r="BJ10">
-        <v>14</v>
-      </c>
-      <c r="BK10">
-        <v>3.8</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>5.1</v>
-      </c>
-      <c r="BN10">
-        <v>9.4</v>
-      </c>
       <c r="BO10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP10">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="BQ10">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS10">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BT10">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BU10">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV10">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="BW10">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BX10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ10">
         <v>55</v>
       </c>
       <c r="CA10">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F11">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H11">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="I11">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J11">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="K11">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="M11">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>2.36</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="P11">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="Q11">
-        <v>2.66</v>
+        <v>1.79</v>
       </c>
       <c r="R11">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="T11">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="U11">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="X11">
-        <v>8.4</v>
+        <v>950</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="Z11">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA11">
         <v>900</v>
       </c>
       <c r="AB11">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="AC11">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AD11">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="AE11">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF11">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="AG11">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="AH11">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI11">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ11">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK11">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL11">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM11">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AO11">
         <v>600</v>
       </c>
       <c r="AP11">
-        <v>4.2</v>
+        <v>1.27</v>
       </c>
       <c r="AQ11">
-        <v>5.8</v>
+        <v>1.25</v>
       </c>
       <c r="AR11">
-        <v>6</v>
+        <v>1.26</v>
       </c>
       <c r="AS11">
-        <v>7</v>
+        <v>1.27</v>
       </c>
       <c r="AT11">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="AU11">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV11">
-        <v>5.4</v>
+        <v>1.26</v>
       </c>
       <c r="AW11">
-        <v>6.8</v>
+        <v>1.27</v>
       </c>
       <c r="AX11">
-        <v>6.2</v>
+        <v>1.25</v>
       </c>
       <c r="AY11">
-        <v>4.9</v>
+        <v>1.25</v>
       </c>
       <c r="AZ11">
-        <v>5.9</v>
+        <v>1.25</v>
       </c>
       <c r="BA11">
-        <v>7</v>
+        <v>1.27</v>
       </c>
       <c r="BB11">
-        <v>6.4</v>
+        <v>1.27</v>
       </c>
       <c r="BC11">
-        <v>6.4</v>
+        <v>1.27</v>
       </c>
       <c r="BD11">
-        <v>6.8</v>
+        <v>1.27</v>
       </c>
       <c r="BE11">
-        <v>7.4</v>
+        <v>1.27</v>
       </c>
       <c r="BF11">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG11">
-        <v>7.2</v>
+        <v>1.55</v>
       </c>
       <c r="BH11">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F12">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="G12">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="H12">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="I12">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="L12">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N12">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="O12">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="P12">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q12">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="R12">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="T12">
+        <v>2.06</v>
+      </c>
+      <c r="U12">
         <v>1.67</v>
       </c>
-      <c r="U12">
-        <v>2.12</v>
-      </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W12">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="X12">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="Y12">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Z12">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA12">
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="AC12">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD12">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE12">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AF12">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AG12">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH12">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI12">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AJ12">
-        <v>900</v>
+        <v>28</v>
       </c>
       <c r="AK12">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AL12">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM12">
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>600</v>
+        <v>26</v>
       </c>
       <c r="AO12">
         <v>600</v>
       </c>
       <c r="AP12">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="AQ12">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="AR12">
-        <v>1.26</v>
+        <v>5.9</v>
       </c>
       <c r="AS12">
-        <v>1.27</v>
+        <v>6.6</v>
       </c>
       <c r="AT12">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="AU12">
         <v>4.9</v>
       </c>
       <c r="AV12">
-        <v>1.26</v>
+        <v>5.2</v>
       </c>
       <c r="AW12">
-        <v>1.27</v>
+        <v>6.4</v>
       </c>
       <c r="AX12">
-        <v>1.25</v>
+        <v>5.1</v>
       </c>
       <c r="AY12">
-        <v>1.25</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12">
-        <v>1.25</v>
+        <v>5.5</v>
       </c>
       <c r="BA12">
-        <v>1.27</v>
+        <v>6.6</v>
       </c>
       <c r="BB12">
-        <v>1.27</v>
+        <v>9</v>
       </c>
       <c r="BC12">
-        <v>1.27</v>
+        <v>7</v>
       </c>
       <c r="BD12">
-        <v>1.27</v>
+        <v>6.2</v>
       </c>
       <c r="BE12">
-        <v>1.27</v>
+        <v>6.8</v>
       </c>
       <c r="BF12">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG12">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3728,725 +3716,725 @@
         <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F13">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="G13">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="H13">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I13">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="J13">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K13">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L13">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M13">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N13">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="O13">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q13">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R13">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="T13">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="U13">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="V13">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="X13">
         <v>11.5</v>
       </c>
       <c r="Y13">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z13">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="AA13">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AE13">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="AF13">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG13">
         <v>12</v>
       </c>
       <c r="AH13">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AI13">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="AJ13">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AK13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL13">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AM13">
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AO13">
         <v>600</v>
       </c>
       <c r="AP13">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ13">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AR13">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AS13">
+        <v>46</v>
+      </c>
+      <c r="AT13">
+        <v>7.8</v>
+      </c>
+      <c r="AU13">
         <v>6.6</v>
       </c>
-      <c r="AT13">
-        <v>4.2</v>
-      </c>
-      <c r="AU13">
-        <v>4.9</v>
-      </c>
       <c r="AV13">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="AW13">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="AX13">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AY13">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA13">
-        <v>6.4</v>
+        <v>42</v>
       </c>
       <c r="BB13">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BC13">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BD13">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BE13">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="BF13">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BG13">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BH13">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BI13">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BN13">
         <v>5.3</v>
       </c>
       <c r="BO13">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="BP13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ13">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="BR13">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT13">
+        <v>6.8</v>
+      </c>
+      <c r="BU13">
+        <v>5.1</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
         <v>9.199999999999999</v>
       </c>
-      <c r="BU13">
-        <v>3.25</v>
-      </c>
-      <c r="BV13">
-        <v>60</v>
-      </c>
-      <c r="BW13">
-        <v>4.6</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>4.7</v>
-      </c>
-      <c r="BZ13">
-        <v>50</v>
-      </c>
-      <c r="CA13">
-        <v>4.6</v>
-      </c>
       <c r="CB13" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F14">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="G14">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="H14">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="I14">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J14">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="K14">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="O14">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="P14">
-        <v>1.73</v>
+        <v>2.34</v>
       </c>
       <c r="Q14">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="S14">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="T14">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="U14">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="X14">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Z14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA14">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB14">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AC14">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AD14">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE14">
         <v>55</v>
       </c>
       <c r="AF14">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG14">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AI14">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AJ14">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AK14">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AL14">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="AM14">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN14">
+        <v>11</v>
+      </c>
+      <c r="AO14">
         <v>34</v>
       </c>
-      <c r="AO14">
-        <v>600</v>
-      </c>
       <c r="AP14">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14">
+        <v>16.5</v>
+      </c>
+      <c r="AR14">
+        <v>24</v>
+      </c>
+      <c r="AS14">
+        <v>50</v>
+      </c>
+      <c r="AT14">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR14">
-        <v>20</v>
-      </c>
-      <c r="AS14">
-        <v>46</v>
-      </c>
-      <c r="AT14">
-        <v>7.6</v>
-      </c>
       <c r="AU14">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AX14">
         <v>12.5</v>
       </c>
       <c r="AY14">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BA14">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BB14">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BC14">
+        <v>17</v>
+      </c>
+      <c r="BD14">
         <v>23</v>
-      </c>
-      <c r="BD14">
-        <v>38</v>
       </c>
       <c r="BE14">
         <v>55</v>
       </c>
       <c r="BF14">
+        <v>9.4</v>
+      </c>
+      <c r="BG14">
         <v>21</v>
       </c>
-      <c r="BG14">
-        <v>32</v>
-      </c>
       <c r="BH14">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BI14">
-        <v>2.72</v>
+        <v>3.65</v>
       </c>
       <c r="BJ14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK14">
+        <v>5.2</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
         <v>10.5</v>
       </c>
-      <c r="BK14">
-        <v>5.3</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>10</v>
-      </c>
       <c r="BN14">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO14">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BQ14">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS14">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT14">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU14">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW14">
         <v>8.199999999999999</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA14">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="G15">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="H15">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="I15">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="J15">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="L15">
+        <v>1.42</v>
+      </c>
+      <c r="M15">
+        <v>1.07</v>
+      </c>
+      <c r="N15">
+        <v>3.7</v>
+      </c>
+      <c r="O15">
         <v>1.34</v>
       </c>
-      <c r="M15">
-        <v>1.05</v>
-      </c>
-      <c r="N15">
-        <v>4.5</v>
-      </c>
-      <c r="O15">
-        <v>1.25</v>
-      </c>
       <c r="P15">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="Q15">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S15">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="T15">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="U15">
-        <v>2.34</v>
+        <v>1.74</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="W15">
-        <v>1.94</v>
+        <v>2.92</v>
       </c>
       <c r="X15">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Z15">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AA15">
-        <v>85</v>
+        <v>370</v>
       </c>
       <c r="AB15">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AC15">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD15">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AE15">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AF15">
-        <v>17</v>
+        <v>8.4</v>
       </c>
       <c r="AG15">
         <v>11</v>
       </c>
       <c r="AH15">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="AI15">
+        <v>470</v>
+      </c>
+      <c r="AJ15">
+        <v>13.5</v>
+      </c>
+      <c r="AK15">
+        <v>18</v>
+      </c>
+      <c r="AL15">
         <v>55</v>
       </c>
-      <c r="AJ15">
-        <v>25</v>
-      </c>
-      <c r="AK15">
-        <v>21</v>
-      </c>
-      <c r="AL15">
-        <v>32</v>
-      </c>
       <c r="AM15">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="AN15">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AO15">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="AP15">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AR15">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AS15">
-        <v>55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT15">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AU15">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AW15">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="AX15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AY15">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB15">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BC15">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BD15">
+        <v>27</v>
+      </c>
+      <c r="BE15">
+        <v>9.6</v>
+      </c>
+      <c r="BF15">
+        <v>8</v>
+      </c>
+      <c r="BG15">
+        <v>15</v>
+      </c>
+      <c r="BH15">
+        <v>4</v>
+      </c>
+      <c r="BI15">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15">
+        <v>15</v>
+      </c>
+      <c r="BK15">
+        <v>4.3</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>5.7</v>
+      </c>
+      <c r="BN15">
+        <v>3.8</v>
+      </c>
+      <c r="BO15">
+        <v>3.35</v>
+      </c>
+      <c r="BP15">
+        <v>11.5</v>
+      </c>
+      <c r="BQ15">
+        <v>4.2</v>
+      </c>
+      <c r="BR15">
+        <v>36</v>
+      </c>
+      <c r="BS15">
+        <v>5</v>
+      </c>
+      <c r="BT15">
+        <v>14.5</v>
+      </c>
+      <c r="BU15">
+        <v>4.3</v>
+      </c>
+      <c r="BV15">
+        <v>110</v>
+      </c>
+      <c r="BW15">
+        <v>5.5</v>
+      </c>
+      <c r="BX15">
+        <v>110</v>
+      </c>
+      <c r="BY15">
+        <v>5.5</v>
+      </c>
+      <c r="BZ15">
         <v>23</v>
       </c>
-      <c r="BE15">
-        <v>55</v>
-      </c>
-      <c r="BF15">
-        <v>10</v>
-      </c>
-      <c r="BG15">
-        <v>23</v>
-      </c>
-      <c r="BH15">
-        <v>3.95</v>
-      </c>
-      <c r="BI15">
-        <v>3.5</v>
-      </c>
-      <c r="BJ15">
-        <v>9.4</v>
-      </c>
-      <c r="BK15">
-        <v>5.2</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>10.5</v>
-      </c>
-      <c r="BN15">
-        <v>5.1</v>
-      </c>
-      <c r="BO15">
-        <v>4.4</v>
-      </c>
-      <c r="BP15">
-        <v>14.5</v>
-      </c>
-      <c r="BQ15">
-        <v>6.4</v>
-      </c>
-      <c r="BR15">
-        <v>25</v>
-      </c>
-      <c r="BS15">
-        <v>7.8</v>
-      </c>
-      <c r="BT15">
-        <v>7.6</v>
-      </c>
-      <c r="BU15">
-        <v>5.5</v>
-      </c>
-      <c r="BV15">
-        <v>30</v>
-      </c>
-      <c r="BW15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX15">
-        <v>36</v>
-      </c>
-      <c r="BY15">
-        <v>8.6</v>
-      </c>
-      <c r="BZ15">
-        <v>21</v>
-      </c>
       <c r="CA15">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4454,241 +4442,241 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16">
+        <v>3.65</v>
+      </c>
+      <c r="G16">
+        <v>4.3</v>
+      </c>
+      <c r="H16">
+        <v>1.93</v>
+      </c>
+      <c r="I16">
+        <v>2.08</v>
+      </c>
+      <c r="J16">
+        <v>3.65</v>
+      </c>
+      <c r="K16">
+        <v>4.4</v>
+      </c>
+      <c r="L16">
+        <v>1.35</v>
+      </c>
+      <c r="M16">
+        <v>1.05</v>
+      </c>
+      <c r="N16">
+        <v>4.3</v>
+      </c>
+      <c r="O16">
+        <v>1.25</v>
+      </c>
+      <c r="P16">
+        <v>2.12</v>
+      </c>
+      <c r="Q16">
+        <v>1.76</v>
+      </c>
+      <c r="R16">
+        <v>1.45</v>
+      </c>
+      <c r="S16">
+        <v>2.88</v>
+      </c>
+      <c r="T16">
+        <v>1.65</v>
+      </c>
+      <c r="U16">
+        <v>2.24</v>
+      </c>
+      <c r="V16">
+        <v>1.92</v>
+      </c>
+      <c r="W16">
+        <v>1.31</v>
+      </c>
+      <c r="X16">
+        <v>21</v>
+      </c>
+      <c r="Y16">
+        <v>12</v>
+      </c>
+      <c r="Z16">
+        <v>15.5</v>
+      </c>
+      <c r="AA16">
+        <v>26</v>
+      </c>
+      <c r="AB16">
+        <v>18</v>
+      </c>
+      <c r="AC16">
+        <v>9.6</v>
+      </c>
+      <c r="AD16">
+        <v>12</v>
+      </c>
+      <c r="AE16">
+        <v>22</v>
+      </c>
+      <c r="AF16">
+        <v>34</v>
+      </c>
+      <c r="AG16">
+        <v>17.5</v>
+      </c>
+      <c r="AH16">
+        <v>19</v>
+      </c>
+      <c r="AI16">
+        <v>36</v>
+      </c>
+      <c r="AJ16">
+        <v>170</v>
+      </c>
+      <c r="AK16">
+        <v>46</v>
+      </c>
+      <c r="AL16">
         <v>120</v>
       </c>
-      <c r="E16" t="s">
-        <v>145</v>
-      </c>
-      <c r="F16">
-        <v>1.45</v>
-      </c>
-      <c r="G16">
-        <v>1.51</v>
-      </c>
-      <c r="H16">
+      <c r="AM16">
+        <v>580</v>
+      </c>
+      <c r="AN16">
+        <v>42</v>
+      </c>
+      <c r="AO16">
+        <v>12.5</v>
+      </c>
+      <c r="AP16">
+        <v>14</v>
+      </c>
+      <c r="AQ16">
         <v>8.800000000000001</v>
       </c>
-      <c r="I16">
+      <c r="AR16">
+        <v>11</v>
+      </c>
+      <c r="AS16">
+        <v>18</v>
+      </c>
+      <c r="AT16">
+        <v>12.5</v>
+      </c>
+      <c r="AU16">
+        <v>7.8</v>
+      </c>
+      <c r="AV16">
+        <v>8</v>
+      </c>
+      <c r="AW16">
+        <v>15</v>
+      </c>
+      <c r="AX16">
+        <v>12</v>
+      </c>
+      <c r="AY16">
+        <v>11.5</v>
+      </c>
+      <c r="AZ16">
+        <v>12.5</v>
+      </c>
+      <c r="BA16">
+        <v>12.5</v>
+      </c>
+      <c r="BB16">
+        <v>6.4</v>
+      </c>
+      <c r="BC16">
+        <v>6</v>
+      </c>
+      <c r="BD16">
+        <v>6</v>
+      </c>
+      <c r="BE16">
+        <v>6.4</v>
+      </c>
+      <c r="BF16">
+        <v>5.9</v>
+      </c>
+      <c r="BG16">
+        <v>9.6</v>
+      </c>
+      <c r="BH16">
+        <v>4.3</v>
+      </c>
+      <c r="BI16">
+        <v>3.15</v>
+      </c>
+      <c r="BJ16">
         <v>10.5</v>
       </c>
-      <c r="J16">
-        <v>4.4</v>
-      </c>
-      <c r="K16">
-        <v>4.8</v>
-      </c>
-      <c r="L16">
-        <v>1.41</v>
-      </c>
-      <c r="M16">
-        <v>1.07</v>
-      </c>
-      <c r="N16">
-        <v>3.55</v>
-      </c>
-      <c r="O16">
-        <v>1.34</v>
-      </c>
-      <c r="P16">
-        <v>1.88</v>
-      </c>
-      <c r="Q16">
-        <v>1.98</v>
-      </c>
-      <c r="R16">
-        <v>1.34</v>
-      </c>
-      <c r="S16">
-        <v>3.55</v>
-      </c>
-      <c r="T16">
-        <v>2.22</v>
-      </c>
-      <c r="U16">
-        <v>1.72</v>
-      </c>
-      <c r="V16">
-        <v>1.11</v>
-      </c>
-      <c r="W16">
-        <v>2.96</v>
-      </c>
-      <c r="X16">
-        <v>17.5</v>
-      </c>
-      <c r="Y16">
-        <v>30</v>
-      </c>
-      <c r="Z16">
-        <v>110</v>
-      </c>
-      <c r="AA16">
-        <v>480</v>
-      </c>
-      <c r="AB16">
-        <v>7.2</v>
-      </c>
-      <c r="AC16">
-        <v>11</v>
-      </c>
-      <c r="AD16">
-        <v>44</v>
-      </c>
-      <c r="AE16">
-        <v>220</v>
-      </c>
-      <c r="AF16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG16">
-        <v>12</v>
-      </c>
-      <c r="AH16">
+      <c r="BK16">
+        <v>3.7</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>5.4</v>
+      </c>
+      <c r="BN16">
+        <v>8.6</v>
+      </c>
+      <c r="BO16">
+        <v>5.8</v>
+      </c>
+      <c r="BP16">
         <v>36</v>
       </c>
-      <c r="AI16">
-        <v>470</v>
-      </c>
-      <c r="AJ16">
-        <v>13</v>
-      </c>
-      <c r="AK16">
-        <v>18</v>
-      </c>
-      <c r="AL16">
-        <v>60</v>
-      </c>
-      <c r="AM16">
-        <v>260</v>
-      </c>
-      <c r="AN16">
-        <v>9</v>
-      </c>
-      <c r="AO16">
-        <v>380</v>
-      </c>
-      <c r="AP16">
-        <v>12.5</v>
-      </c>
-      <c r="AQ16">
-        <v>20</v>
-      </c>
-      <c r="AR16">
-        <v>55</v>
-      </c>
-      <c r="AS16">
-        <v>7.6</v>
-      </c>
-      <c r="AT16">
-        <v>6.2</v>
-      </c>
-      <c r="AU16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV16">
-        <v>25</v>
-      </c>
-      <c r="AW16">
-        <v>7.4</v>
-      </c>
-      <c r="AX16">
-        <v>7</v>
-      </c>
-      <c r="AY16">
-        <v>9</v>
-      </c>
-      <c r="AZ16">
-        <v>21</v>
-      </c>
-      <c r="BA16">
-        <v>29</v>
-      </c>
-      <c r="BB16">
-        <v>11</v>
-      </c>
-      <c r="BC16">
-        <v>15</v>
-      </c>
-      <c r="BD16">
-        <v>26</v>
-      </c>
-      <c r="BE16">
-        <v>36</v>
-      </c>
-      <c r="BF16">
-        <v>7.6</v>
-      </c>
-      <c r="BG16">
-        <v>15</v>
-      </c>
-      <c r="BH16">
+      <c r="BQ16">
+        <v>4.9</v>
+      </c>
+      <c r="BR16">
+        <v>42</v>
+      </c>
+      <c r="BS16">
+        <v>5</v>
+      </c>
+      <c r="BT16">
+        <v>5.6</v>
+      </c>
+      <c r="BU16">
         <v>3.95</v>
       </c>
-      <c r="BI16">
-        <v>3.05</v>
-      </c>
-      <c r="BJ16">
-        <v>15</v>
-      </c>
-      <c r="BK16">
-        <v>3.75</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>4.9</v>
-      </c>
-      <c r="BN16">
-        <v>4.3</v>
-      </c>
-      <c r="BO16">
-        <v>3.35</v>
-      </c>
-      <c r="BP16">
-        <v>11</v>
-      </c>
-      <c r="BQ16">
-        <v>3.45</v>
-      </c>
-      <c r="BR16">
-        <v>36</v>
-      </c>
-      <c r="BS16">
-        <v>4.4</v>
-      </c>
-      <c r="BT16">
-        <v>15</v>
-      </c>
-      <c r="BU16">
-        <v>3.75</v>
-      </c>
       <c r="BV16">
-        <v>120</v>
+        <v>15.5</v>
       </c>
       <c r="BW16">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BX16">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="BY16">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BZ16">
         <v>23</v>
       </c>
       <c r="CA16">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="CB16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4696,241 +4684,241 @@
         <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F17">
+        <v>2.26</v>
+      </c>
+      <c r="G17">
+        <v>2.58</v>
+      </c>
+      <c r="H17">
+        <v>3.05</v>
+      </c>
+      <c r="I17">
+        <v>3.6</v>
+      </c>
+      <c r="J17">
+        <v>3.2</v>
+      </c>
+      <c r="K17">
+        <v>3.85</v>
+      </c>
+      <c r="L17">
+        <v>1.4</v>
+      </c>
+      <c r="M17">
+        <v>1.07</v>
+      </c>
+      <c r="N17">
         <v>3.5</v>
       </c>
-      <c r="G17">
-        <v>4.2</v>
-      </c>
-      <c r="H17">
-        <v>1.95</v>
-      </c>
-      <c r="I17">
-        <v>2.18</v>
-      </c>
-      <c r="J17">
-        <v>3.6</v>
-      </c>
-      <c r="K17">
-        <v>4.1</v>
-      </c>
-      <c r="L17">
-        <v>1.34</v>
-      </c>
-      <c r="M17">
-        <v>1.05</v>
-      </c>
-      <c r="N17">
-        <v>4.2</v>
-      </c>
       <c r="O17">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="P17">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="Q17">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="R17">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S17">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="T17">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="U17">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V17">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="X17">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y17">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z17">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AA17">
-        <v>26</v>
+        <v>230</v>
       </c>
       <c r="AB17">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AC17">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE17">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="AF17">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="AG17">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AJ17">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AK17">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AL17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AM17">
         <v>580</v>
       </c>
       <c r="AN17">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AO17">
-        <v>13.5</v>
+        <v>600</v>
       </c>
       <c r="AP17">
-        <v>14</v>
+        <v>5.1</v>
       </c>
       <c r="AQ17">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR17">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AS17">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="AT17">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU17">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="AV17">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AW17">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AX17">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AY17">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ17">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA17">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC17">
         <v>5.9</v>
       </c>
       <c r="BD17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE17">
+        <v>6.8</v>
+      </c>
+      <c r="BF17">
+        <v>5.6</v>
+      </c>
+      <c r="BG17">
         <v>6.2</v>
       </c>
-      <c r="BF17">
-        <v>5.8</v>
-      </c>
-      <c r="BG17">
-        <v>10.5</v>
-      </c>
       <c r="BH17">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BI17">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK17">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
+        <v>2.52</v>
+      </c>
+      <c r="BN17">
         <v>5.5</v>
       </c>
-      <c r="BN17">
-        <v>8.4</v>
-      </c>
       <c r="BO17">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="BP17">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="BQ17">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BR17">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BT17">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU17">
         <v>4</v>
       </c>
       <c r="BV17">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BW17">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BX17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>4.8</v>
+        <v>2.42</v>
       </c>
       <c r="BZ17">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="CB17" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4938,58 +4926,58 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F18">
+        <v>2.18</v>
+      </c>
+      <c r="G18">
+        <v>13.5</v>
+      </c>
+      <c r="H18">
+        <v>2.04</v>
+      </c>
+      <c r="I18">
+        <v>3.8</v>
+      </c>
+      <c r="J18">
+        <v>2.32</v>
+      </c>
+      <c r="K18">
+        <v>7</v>
+      </c>
+      <c r="L18">
+        <v>1.65</v>
+      </c>
+      <c r="M18">
         <v>1.12</v>
       </c>
-      <c r="G18">
-        <v>990</v>
-      </c>
-      <c r="H18">
+      <c r="N18">
+        <v>2.1</v>
+      </c>
+      <c r="O18">
+        <v>1.6</v>
+      </c>
+      <c r="P18">
+        <v>1.34</v>
+      </c>
+      <c r="Q18">
+        <v>2.84</v>
+      </c>
+      <c r="R18">
         <v>1.12</v>
       </c>
-      <c r="I18">
-        <v>990</v>
-      </c>
-      <c r="J18">
-        <v>1.12</v>
-      </c>
-      <c r="K18">
-        <v>950</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
-        <v>1.01</v>
-      </c>
-      <c r="N18">
-        <v>1.11</v>
-      </c>
-      <c r="O18">
-        <v>1.01</v>
-      </c>
-      <c r="P18">
-        <v>1.1</v>
-      </c>
-      <c r="Q18">
-        <v>1.31</v>
-      </c>
-      <c r="R18">
-        <v>1.08</v>
-      </c>
       <c r="S18">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="T18">
         <v>1.11</v>
@@ -4998,55 +4986,55 @@
         <v>1.11</v>
       </c>
       <c r="V18">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH18">
         <v>1000</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM18">
         <v>1000</v>
@@ -5058,180 +5046,180 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="CB18" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F19">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="G19">
-        <v>600</v>
+        <v>1.88</v>
       </c>
       <c r="H19">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="I19">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="K19">
-        <v>500</v>
+        <v>5.8</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N19">
+        <v>1.79</v>
+      </c>
+      <c r="O19">
         <v>1.1</v>
       </c>
-      <c r="O19">
-        <v>1.02</v>
-      </c>
       <c r="P19">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="Q19">
-        <v>2.52</v>
+        <v>1.41</v>
       </c>
       <c r="R19">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="S19">
-        <v>2.52</v>
+        <v>3.85</v>
       </c>
       <c r="T19">
         <v>1.11</v>
@@ -5240,10 +5228,10 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="W19">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="X19">
         <v>950</v>
@@ -5252,10 +5240,10 @@
         <v>950</v>
       </c>
       <c r="Z19">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA19">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB19">
         <v>950</v>
@@ -5267,10 +5255,10 @@
         <v>950</v>
       </c>
       <c r="AE19">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AF19">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AG19">
         <v>950</v>
@@ -5279,249 +5267,249 @@
         <v>950</v>
       </c>
       <c r="AI19">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ19">
         <v>900</v>
       </c>
       <c r="AK19">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AL19">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP19">
-        <v>4.2</v>
+        <v>1.23</v>
       </c>
       <c r="AQ19">
-        <v>4.4</v>
+        <v>1.23</v>
       </c>
       <c r="AR19">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="AS19">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AT19">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="AU19">
-        <v>3.85</v>
+        <v>1.21</v>
       </c>
       <c r="AV19">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AW19">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AX19">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AY19">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="AZ19">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="BA19">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="BB19">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="BC19">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="BD19">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="BE19">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="BF19">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="BG19">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BH19">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="CA19">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F20">
-        <v>1.63</v>
+        <v>2.28</v>
       </c>
       <c r="G20">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="H20">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="I20">
-        <v>12.5</v>
+        <v>3.55</v>
       </c>
       <c r="J20">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K20">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M20">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N20">
-        <v>1.11</v>
+        <v>3.45</v>
       </c>
       <c r="O20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P20">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="Q20">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="R20">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
-        <v>1.05</v>
+        <v>3.95</v>
       </c>
       <c r="T20">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U20">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V20">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="W20">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="X20">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Y20">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="Z20">
+        <v>910</v>
+      </c>
+      <c r="AA20">
+        <v>910</v>
+      </c>
+      <c r="AB20">
         <v>500</v>
       </c>
-      <c r="AA20">
-        <v>500</v>
-      </c>
-      <c r="AB20">
-        <v>950</v>
-      </c>
       <c r="AC20">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AD20">
         <v>950</v>
       </c>
       <c r="AE20">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="AF20">
-        <v>500</v>
+        <v>860</v>
       </c>
       <c r="AG20">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AH20">
         <v>950</v>
       </c>
       <c r="AI20">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="AJ20">
         <v>900</v>
@@ -5530,70 +5518,70 @@
         <v>500</v>
       </c>
       <c r="AL20">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="AM20">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="AN20">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="AO20">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="AP20">
-        <v>1.23</v>
+        <v>6.2</v>
       </c>
       <c r="AQ20">
-        <v>1.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20">
-        <v>1.23</v>
+        <v>1.86</v>
       </c>
       <c r="AS20">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="AT20">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU20">
-        <v>1.21</v>
+        <v>5.9</v>
       </c>
       <c r="AV20">
-        <v>1.23</v>
+        <v>8.4</v>
       </c>
       <c r="AW20">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="AX20">
-        <v>1.21</v>
+        <v>7</v>
       </c>
       <c r="AY20">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ20">
-        <v>1.22</v>
+        <v>11</v>
       </c>
       <c r="BA20">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="BB20">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="BC20">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="BD20">
-        <v>1.23</v>
+        <v>1.92</v>
       </c>
       <c r="BE20">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="BF20">
-        <v>1.21</v>
+        <v>5</v>
       </c>
       <c r="BG20">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5650,192 +5638,192 @@
         <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F21">
-        <v>2.26</v>
+        <v>1.12</v>
       </c>
       <c r="G21">
-        <v>2.42</v>
+        <v>990</v>
       </c>
       <c r="H21">
-        <v>3.3</v>
+        <v>1.12</v>
       </c>
       <c r="I21">
-        <v>3.7</v>
+        <v>990</v>
       </c>
       <c r="J21">
-        <v>3.45</v>
+        <v>1.15</v>
       </c>
       <c r="K21">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L21">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>1.1</v>
+      </c>
+      <c r="O21">
+        <v>1.01</v>
+      </c>
+      <c r="P21">
+        <v>1.09</v>
+      </c>
+      <c r="Q21">
+        <v>1.29</v>
+      </c>
+      <c r="R21">
+        <v>1.08</v>
+      </c>
+      <c r="S21">
+        <v>2.72</v>
+      </c>
+      <c r="T21">
+        <v>1.11</v>
+      </c>
+      <c r="U21">
+        <v>1.11</v>
+      </c>
+      <c r="V21">
         <v>1.07</v>
       </c>
-      <c r="N21">
-        <v>3.15</v>
-      </c>
-      <c r="O21">
-        <v>1.36</v>
-      </c>
-      <c r="P21">
-        <v>1.84</v>
-      </c>
-      <c r="Q21">
-        <v>2.06</v>
-      </c>
-      <c r="R21">
-        <v>1.31</v>
-      </c>
-      <c r="S21">
-        <v>3.75</v>
-      </c>
-      <c r="T21">
-        <v>1.84</v>
-      </c>
-      <c r="U21">
-        <v>1.92</v>
-      </c>
-      <c r="V21">
-        <v>1.37</v>
-      </c>
       <c r="W21">
-        <v>1.7</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>940</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>860</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5898,186 +5886,186 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F22">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="G22">
-        <v>990</v>
+        <v>1.58</v>
       </c>
       <c r="H22">
-        <v>1.12</v>
+        <v>5.9</v>
       </c>
       <c r="I22">
-        <v>990</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P22">
-        <v>1.09</v>
+        <v>2.64</v>
       </c>
       <c r="Q22">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="R22">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="S22">
+        <v>2.4</v>
+      </c>
+      <c r="T22">
+        <v>1.66</v>
+      </c>
+      <c r="U22">
+        <v>2.22</v>
+      </c>
+      <c r="V22">
+        <v>1.17</v>
+      </c>
+      <c r="W22">
         <v>2.72</v>
       </c>
-      <c r="T22">
-        <v>1.11</v>
-      </c>
-      <c r="U22">
-        <v>1.11</v>
-      </c>
-      <c r="V22">
-        <v>1.06</v>
-      </c>
-      <c r="W22">
-        <v>1.06</v>
-      </c>
       <c r="X22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6140,975 +6128,733 @@
         <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F23">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="G23">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="H23">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="I23">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="J23">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="K23">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M23">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="N23">
-        <v>5.1</v>
+        <v>3.25</v>
       </c>
       <c r="O23">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="P23">
-        <v>2.56</v>
+        <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>1.52</v>
+        <v>2.24</v>
       </c>
       <c r="R23">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="S23">
-        <v>2.28</v>
+        <v>4.2</v>
       </c>
       <c r="T23">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="U23">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="V23">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
-        <v>2.56</v>
+        <v>1.87</v>
       </c>
       <c r="X23">
+        <v>11.5</v>
+      </c>
+      <c r="Y23">
+        <v>14</v>
+      </c>
+      <c r="Z23">
         <v>32</v>
       </c>
-      <c r="Y23">
-        <v>32</v>
-      </c>
-      <c r="Z23">
+      <c r="AA23">
+        <v>900</v>
+      </c>
+      <c r="AB23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC23">
+        <v>7.8</v>
+      </c>
+      <c r="AD23">
+        <v>18.5</v>
+      </c>
+      <c r="AE23">
         <v>65</v>
-      </c>
-      <c r="AA23">
-        <v>700</v>
-      </c>
-      <c r="AB23">
-        <v>14.5</v>
-      </c>
-      <c r="AC23">
-        <v>12.5</v>
-      </c>
-      <c r="AD23">
-        <v>28</v>
-      </c>
-      <c r="AE23">
-        <v>190</v>
       </c>
       <c r="AF23">
         <v>13</v>
       </c>
       <c r="AG23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH23">
         <v>21</v>
       </c>
       <c r="AI23">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AJ23">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AK23">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AL23">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AM23">
-        <v>500</v>
+        <v>640</v>
       </c>
       <c r="AN23">
+        <v>21</v>
+      </c>
+      <c r="AO23">
+        <v>570</v>
+      </c>
+      <c r="AP23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ23">
+        <v>11</v>
+      </c>
+      <c r="AR23">
+        <v>25</v>
+      </c>
+      <c r="AS23">
+        <v>10</v>
+      </c>
+      <c r="AT23">
         <v>7</v>
       </c>
-      <c r="AO23">
-        <v>700</v>
-      </c>
-      <c r="AP23">
+      <c r="AU23">
+        <v>6.6</v>
+      </c>
+      <c r="AV23">
+        <v>15.5</v>
+      </c>
+      <c r="AW23">
+        <v>10</v>
+      </c>
+      <c r="AX23">
+        <v>10.5</v>
+      </c>
+      <c r="AY23">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23">
+        <v>17.5</v>
+      </c>
+      <c r="BA23">
+        <v>10</v>
+      </c>
+      <c r="BB23">
+        <v>21</v>
+      </c>
+      <c r="BC23">
         <v>20</v>
       </c>
-      <c r="AQ23">
-        <v>21</v>
-      </c>
-      <c r="AR23">
-        <v>16</v>
-      </c>
-      <c r="AS23">
-        <v>5</v>
-      </c>
-      <c r="AT23">
-        <v>9.4</v>
-      </c>
-      <c r="AU23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV23">
-        <v>18</v>
-      </c>
-      <c r="AW23">
-        <v>29</v>
-      </c>
-      <c r="AX23">
-        <v>9.4</v>
-      </c>
-      <c r="AY23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ23">
-        <v>15</v>
-      </c>
-      <c r="BA23">
-        <v>27</v>
-      </c>
-      <c r="BB23">
-        <v>12.5</v>
-      </c>
-      <c r="BC23">
-        <v>12</v>
-      </c>
       <c r="BD23">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BE23">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="BF23">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="BG23">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="CB23" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="G24">
+        <v>1.89</v>
+      </c>
+      <c r="H24">
+        <v>4.7</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
+        <v>3.7</v>
+      </c>
+      <c r="K24">
+        <v>3.9</v>
+      </c>
+      <c r="L24">
+        <v>1.42</v>
+      </c>
+      <c r="M24">
+        <v>1.07</v>
+      </c>
+      <c r="N24">
+        <v>3.75</v>
+      </c>
+      <c r="O24">
+        <v>1.34</v>
+      </c>
+      <c r="P24">
+        <v>1.93</v>
+      </c>
+      <c r="Q24">
+        <v>2.02</v>
+      </c>
+      <c r="R24">
+        <v>1.35</v>
+      </c>
+      <c r="S24">
+        <v>3.6</v>
+      </c>
+      <c r="T24">
+        <v>1.86</v>
+      </c>
+      <c r="U24">
+        <v>2.04</v>
+      </c>
+      <c r="V24">
+        <v>1.25</v>
+      </c>
+      <c r="W24">
         <v>2.12</v>
       </c>
-      <c r="H24">
-        <v>4.2</v>
-      </c>
-      <c r="I24">
-        <v>4.7</v>
-      </c>
-      <c r="J24">
-        <v>3.25</v>
-      </c>
-      <c r="K24">
-        <v>3.6</v>
-      </c>
-      <c r="L24">
-        <v>1.01</v>
-      </c>
-      <c r="M24">
-        <v>1.1</v>
-      </c>
-      <c r="N24">
-        <v>3.1</v>
-      </c>
-      <c r="O24">
-        <v>1.41</v>
-      </c>
-      <c r="P24">
-        <v>1.72</v>
-      </c>
-      <c r="Q24">
-        <v>2.2</v>
-      </c>
-      <c r="R24">
-        <v>1.29</v>
-      </c>
-      <c r="S24">
-        <v>4.2</v>
-      </c>
-      <c r="T24">
-        <v>1.93</v>
-      </c>
-      <c r="U24">
-        <v>1.92</v>
-      </c>
-      <c r="V24">
-        <v>1.27</v>
-      </c>
-      <c r="W24">
-        <v>1.89</v>
-      </c>
       <c r="X24">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Y24">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="Z24">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AA24">
         <v>900</v>
       </c>
       <c r="AB24">
+        <v>28</v>
+      </c>
+      <c r="AC24">
+        <v>11.5</v>
+      </c>
+      <c r="AD24">
+        <v>60</v>
+      </c>
+      <c r="AE24">
+        <v>980</v>
+      </c>
+      <c r="AF24">
+        <v>18.5</v>
+      </c>
+      <c r="AG24">
+        <v>11.5</v>
+      </c>
+      <c r="AH24">
+        <v>60</v>
+      </c>
+      <c r="AI24">
+        <v>980</v>
+      </c>
+      <c r="AJ24">
+        <v>65</v>
+      </c>
+      <c r="AK24">
+        <v>130</v>
+      </c>
+      <c r="AL24">
+        <v>980</v>
+      </c>
+      <c r="AM24">
+        <v>580</v>
+      </c>
+      <c r="AN24">
+        <v>85</v>
+      </c>
+      <c r="AO24">
+        <v>500</v>
+      </c>
+      <c r="AP24">
+        <v>10</v>
+      </c>
+      <c r="AQ24">
+        <v>12</v>
+      </c>
+      <c r="AR24">
+        <v>6.8</v>
+      </c>
+      <c r="AS24">
+        <v>2.82</v>
+      </c>
+      <c r="AT24">
+        <v>7.6</v>
+      </c>
+      <c r="AU24">
+        <v>6.8</v>
+      </c>
+      <c r="AV24">
+        <v>10.5</v>
+      </c>
+      <c r="AW24">
+        <v>12</v>
+      </c>
+      <c r="AX24">
+        <v>9</v>
+      </c>
+      <c r="AY24">
+        <v>9</v>
+      </c>
+      <c r="AZ24">
+        <v>12.5</v>
+      </c>
+      <c r="BA24">
+        <v>12.5</v>
+      </c>
+      <c r="BB24">
+        <v>11</v>
+      </c>
+      <c r="BC24">
+        <v>10.5</v>
+      </c>
+      <c r="BD24">
+        <v>9</v>
+      </c>
+      <c r="BE24">
+        <v>2.76</v>
+      </c>
+      <c r="BF24">
+        <v>9</v>
+      </c>
+      <c r="BG24">
+        <v>2.78</v>
+      </c>
+      <c r="BH24">
+        <v>3.4</v>
+      </c>
+      <c r="BI24">
+        <v>3.15</v>
+      </c>
+      <c r="BJ24">
+        <v>10</v>
+      </c>
+      <c r="BK24">
+        <v>6.6</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>17</v>
+      </c>
+      <c r="BN24">
+        <v>4.4</v>
+      </c>
+      <c r="BO24">
+        <v>4</v>
+      </c>
+      <c r="BP24">
+        <v>13</v>
+      </c>
+      <c r="BQ24">
+        <v>7.8</v>
+      </c>
+      <c r="BR24">
+        <v>28</v>
+      </c>
+      <c r="BS24">
+        <v>11.5</v>
+      </c>
+      <c r="BT24">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC24">
-        <v>8</v>
-      </c>
-      <c r="AD24">
-        <v>18.5</v>
-      </c>
-      <c r="AE24">
-        <v>150</v>
-      </c>
-      <c r="AF24">
-        <v>12.5</v>
-      </c>
-      <c r="AG24">
-        <v>11</v>
-      </c>
-      <c r="AH24">
-        <v>22</v>
-      </c>
-      <c r="AI24">
-        <v>80</v>
-      </c>
-      <c r="AJ24">
-        <v>27</v>
-      </c>
-      <c r="AK24">
-        <v>26</v>
-      </c>
-      <c r="AL24">
-        <v>65</v>
-      </c>
-      <c r="AM24">
-        <v>640</v>
-      </c>
-      <c r="AN24">
-        <v>21</v>
-      </c>
-      <c r="AO24">
-        <v>85</v>
-      </c>
-      <c r="AP24">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ24">
-        <v>11.5</v>
-      </c>
-      <c r="AR24">
-        <v>25</v>
-      </c>
-      <c r="AS24">
-        <v>9.6</v>
-      </c>
-      <c r="AT24">
-        <v>6.8</v>
-      </c>
-      <c r="AU24">
-        <v>6.6</v>
-      </c>
-      <c r="AV24">
-        <v>15.5</v>
-      </c>
-      <c r="AW24">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX24">
+      <c r="BU24">
+        <v>7.2</v>
+      </c>
+      <c r="BV24">
+        <v>42</v>
+      </c>
+      <c r="BW24">
+        <v>13</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>14</v>
+      </c>
+      <c r="BZ24">
+        <v>24</v>
+      </c>
+      <c r="CA24">
         <v>10.5</v>
       </c>
-      <c r="AY24">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ24">
-        <v>17.5</v>
-      </c>
-      <c r="BA24">
-        <v>10</v>
-      </c>
-      <c r="BB24">
-        <v>21</v>
-      </c>
-      <c r="BC24">
-        <v>20</v>
-      </c>
-      <c r="BD24">
-        <v>32</v>
-      </c>
-      <c r="BE24">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF24">
-        <v>16.5</v>
-      </c>
-      <c r="BG24">
-        <v>10</v>
-      </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>1.19</v>
-      </c>
-      <c r="BJ24">
-        <v>1000</v>
-      </c>
-      <c r="BK24">
-        <v>1.1</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>1.58</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>1.19</v>
-      </c>
-      <c r="BP24">
-        <v>1000</v>
-      </c>
-      <c r="BQ24">
-        <v>1.44</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>1.69</v>
-      </c>
-      <c r="BT24">
-        <v>1000</v>
-      </c>
-      <c r="BU24">
-        <v>1.38</v>
-      </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
-      <c r="BW24">
-        <v>1.75</v>
-      </c>
-      <c r="BX24">
-        <v>1000</v>
-      </c>
-      <c r="BY24">
-        <v>1.75</v>
-      </c>
-      <c r="BZ24">
-        <v>1000</v>
-      </c>
-      <c r="CA24">
-        <v>1.68</v>
-      </c>
       <c r="CB24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
         <v>88</v>
       </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F25">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H25">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="I25">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="J25">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K25">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="L25">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="M25">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N25">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="O25">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="P25">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Q25">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="R25">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="S25">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="V25">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W25">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X25">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y25">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="Z25">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AA25">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="AB25">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AC25">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AD25">
         <v>23</v>
       </c>
       <c r="AE25">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AF25">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="AG25">
         <v>11.5</v>
       </c>
       <c r="AH25">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AI25">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AJ25">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AK25">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AL25">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AM25">
-        <v>580</v>
+        <v>210</v>
       </c>
       <c r="AN25">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="AO25">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AP25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ25">
         <v>12</v>
       </c>
       <c r="AR25">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS25">
-        <v>2.92</v>
+        <v>10.5</v>
       </c>
       <c r="AT25">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU25">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV25">
+        <v>18</v>
+      </c>
+      <c r="AW25">
         <v>10.5</v>
       </c>
-      <c r="AW25">
-        <v>2.88</v>
-      </c>
       <c r="AX25">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY25">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA25">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="BB25">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BC25">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BD25">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BE25">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="BF25">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BG25">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="BH25">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>3.1</v>
+        <v>1.26</v>
       </c>
       <c r="BJ25">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>6.4</v>
+        <v>1.21</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>16.5</v>
+        <v>1.21</v>
       </c>
       <c r="BN25">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>4.2</v>
+        <v>1.48</v>
       </c>
       <c r="BP25">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>10</v>
+        <v>1.21</v>
       </c>
       <c r="BR25">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>11</v>
+        <v>1.21</v>
       </c>
       <c r="BT25">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="BV25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>12.5</v>
+        <v>1.21</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>13</v>
+        <v>1.21</v>
       </c>
       <c r="BZ25">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>10.5</v>
+        <v>1.21</v>
       </c>
       <c r="CB25" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="26" spans="1:80">
-      <c r="A26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" t="s">
-        <v>155</v>
-      </c>
-      <c r="F26">
-        <v>1.89</v>
-      </c>
-      <c r="G26">
-        <v>1.94</v>
-      </c>
-      <c r="H26">
-        <v>5.1</v>
-      </c>
-      <c r="I26">
-        <v>5.4</v>
-      </c>
-      <c r="J26">
-        <v>3.35</v>
-      </c>
-      <c r="K26">
-        <v>3.55</v>
-      </c>
-      <c r="L26">
-        <v>1.5</v>
-      </c>
-      <c r="M26">
-        <v>1.11</v>
-      </c>
-      <c r="N26">
-        <v>2.96</v>
-      </c>
-      <c r="O26">
-        <v>1.48</v>
-      </c>
-      <c r="P26">
-        <v>1.64</v>
-      </c>
-      <c r="Q26">
-        <v>2.44</v>
-      </c>
-      <c r="R26">
-        <v>1.23</v>
-      </c>
-      <c r="S26">
-        <v>4.9</v>
-      </c>
-      <c r="T26">
-        <v>2.2</v>
-      </c>
-      <c r="U26">
-        <v>1.8</v>
-      </c>
-      <c r="V26">
-        <v>1.22</v>
-      </c>
-      <c r="W26">
-        <v>2.06</v>
-      </c>
-      <c r="X26">
-        <v>10.5</v>
-      </c>
-      <c r="Y26">
-        <v>15</v>
-      </c>
-      <c r="Z26">
-        <v>42</v>
-      </c>
-      <c r="AA26">
-        <v>180</v>
-      </c>
-      <c r="AB26">
-        <v>6.8</v>
-      </c>
-      <c r="AC26">
-        <v>8</v>
-      </c>
-      <c r="AD26">
-        <v>23</v>
-      </c>
-      <c r="AE26">
-        <v>110</v>
-      </c>
-      <c r="AF26">
-        <v>10.5</v>
-      </c>
-      <c r="AG26">
-        <v>11.5</v>
-      </c>
-      <c r="AH26">
-        <v>28</v>
-      </c>
-      <c r="AI26">
-        <v>120</v>
-      </c>
-      <c r="AJ26">
-        <v>23</v>
-      </c>
-      <c r="AK26">
-        <v>26</v>
-      </c>
-      <c r="AL26">
-        <v>55</v>
-      </c>
-      <c r="AM26">
-        <v>210</v>
-      </c>
-      <c r="AN26">
-        <v>970</v>
-      </c>
-      <c r="AO26">
-        <v>170</v>
-      </c>
-      <c r="AP26">
-        <v>9</v>
-      </c>
-      <c r="AQ26">
-        <v>12</v>
-      </c>
-      <c r="AR26">
-        <v>16</v>
-      </c>
-      <c r="AS26">
-        <v>10</v>
-      </c>
-      <c r="AT26">
-        <v>6.2</v>
-      </c>
-      <c r="AU26">
-        <v>7</v>
-      </c>
-      <c r="AV26">
-        <v>18</v>
-      </c>
-      <c r="AW26">
-        <v>10.5</v>
-      </c>
-      <c r="AX26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY26">
-        <v>9.6</v>
-      </c>
-      <c r="AZ26">
-        <v>11</v>
-      </c>
-      <c r="BA26">
-        <v>10.5</v>
-      </c>
-      <c r="BB26">
-        <v>18.5</v>
-      </c>
-      <c r="BC26">
-        <v>20</v>
-      </c>
-      <c r="BD26">
-        <v>22</v>
-      </c>
-      <c r="BE26">
-        <v>10</v>
-      </c>
-      <c r="BF26">
-        <v>16.5</v>
-      </c>
-      <c r="BG26">
-        <v>10</v>
-      </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>1.26</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>1.87</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>1.85</v>
-      </c>
-      <c r="BN26">
-        <v>1000</v>
-      </c>
-      <c r="BO26">
-        <v>1.48</v>
-      </c>
-      <c r="BP26">
-        <v>1000</v>
-      </c>
-      <c r="BQ26">
-        <v>1.85</v>
-      </c>
-      <c r="BR26">
-        <v>1000</v>
-      </c>
-      <c r="BS26">
-        <v>1.85</v>
-      </c>
-      <c r="BT26">
-        <v>1000</v>
-      </c>
-      <c r="BU26">
-        <v>1.21</v>
-      </c>
-      <c r="BV26">
-        <v>1000</v>
-      </c>
-      <c r="BW26">
-        <v>1.87</v>
-      </c>
-      <c r="BX26">
-        <v>1000</v>
-      </c>
-      <c r="BY26">
-        <v>1.87</v>
-      </c>
-      <c r="BZ26">
-        <v>1000</v>
-      </c>
-      <c r="CA26">
-        <v>1.85</v>
-      </c>
-      <c r="CB26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="157">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Argentinian Primera C</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -307,6 +310,9 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>18:15:00</t>
   </si>
   <si>
@@ -352,15 +358,15 @@
     <t>Hangzhou Linping Wuyue</t>
   </si>
   <si>
+    <t>Guizhou Zhucheng Athletic</t>
+  </si>
+  <si>
+    <t>Shenzhen 2028</t>
+  </si>
+  <si>
     <t>Guangdong Mingtu</t>
   </si>
   <si>
-    <t>Shenzhen 2028</t>
-  </si>
-  <si>
-    <t>Guizhou Zhucheng Athletic</t>
-  </si>
-  <si>
     <t>Shijiazhuang Gongfu FC</t>
   </si>
   <si>
@@ -379,6 +385,9 @@
     <t>CA Claypole</t>
   </si>
   <si>
+    <t>Kabylie</t>
+  </si>
+  <si>
     <t>Union Minas</t>
   </si>
   <si>
@@ -424,15 +433,15 @@
     <t>Xian Chongde Ronghai</t>
   </si>
   <si>
+    <t>Shanghai Port B</t>
+  </si>
+  <si>
+    <t>Shandong Taishan B</t>
+  </si>
+  <si>
     <t>Dalian Yingbo II</t>
   </si>
   <si>
-    <t>Shandong Taishan B</t>
-  </si>
-  <si>
-    <t>Shanghai Port B</t>
-  </si>
-  <si>
     <t>Dalian Kun City FC</t>
   </si>
   <si>
@@ -451,6 +460,9 @@
     <t>Deportivo Espanol</t>
   </si>
   <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
     <t>Union Comercio</t>
   </si>
   <si>
@@ -472,7 +484,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-06 01:52:54</t>
+    <t>2026-10-06 04:04:29</t>
   </si>
 </sst>
 </file>
@@ -804,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1054,241 +1066,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F2">
+        <v>1.64</v>
+      </c>
+      <c r="G2">
+        <v>1.71</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
+      </c>
+      <c r="I2">
+        <v>7.2</v>
+      </c>
+      <c r="J2">
+        <v>3.85</v>
+      </c>
+      <c r="K2">
+        <v>4.1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.48</v>
+      </c>
+      <c r="O2">
+        <v>1.57</v>
+      </c>
+      <c r="P2">
+        <v>1.48</v>
+      </c>
+      <c r="Q2">
         <v>2.74</v>
       </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>2.9</v>
-      </c>
-      <c r="I2">
-        <v>3.2</v>
-      </c>
-      <c r="J2">
-        <v>2.92</v>
-      </c>
-      <c r="K2">
-        <v>3.15</v>
-      </c>
-      <c r="L2">
-        <v>1.54</v>
-      </c>
-      <c r="M2">
-        <v>1.12</v>
-      </c>
-      <c r="N2">
-        <v>2.72</v>
-      </c>
-      <c r="O2">
-        <v>1.51</v>
-      </c>
-      <c r="P2">
-        <v>1.55</v>
-      </c>
-      <c r="Q2">
-        <v>2.6</v>
-      </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="S2">
-        <v>5.3</v>
+        <v>2.66</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>1.41</v>
       </c>
       <c r="U2">
-        <v>1.79</v>
+        <v>3.05</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="X2">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y2">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
         <v>48</v>
       </c>
       <c r="AF2">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG2">
+        <v>15</v>
+      </c>
+      <c r="AH2">
+        <v>26</v>
+      </c>
+      <c r="AI2">
+        <v>90</v>
+      </c>
+      <c r="AJ2">
+        <v>70</v>
+      </c>
+      <c r="AK2">
+        <v>55</v>
+      </c>
+      <c r="AL2">
+        <v>95</v>
+      </c>
+      <c r="AM2">
+        <v>250</v>
+      </c>
+      <c r="AN2">
+        <v>80</v>
+      </c>
+      <c r="AO2">
+        <v>70</v>
+      </c>
+      <c r="AP2">
+        <v>7</v>
+      </c>
+      <c r="AQ2">
+        <v>7</v>
+      </c>
+      <c r="AR2">
         <v>14</v>
       </c>
-      <c r="AH2">
-        <v>23</v>
-      </c>
-      <c r="AI2">
-        <v>75</v>
-      </c>
-      <c r="AJ2">
-        <v>50</v>
-      </c>
-      <c r="AK2">
-        <v>42</v>
-      </c>
-      <c r="AL2">
-        <v>120</v>
-      </c>
-      <c r="AM2">
-        <v>220</v>
-      </c>
-      <c r="AN2">
-        <v>48</v>
-      </c>
-      <c r="AO2">
-        <v>60</v>
-      </c>
-      <c r="AP2">
+      <c r="AS2">
+        <v>8</v>
+      </c>
+      <c r="AT2">
         <v>7.6</v>
-      </c>
-      <c r="AQ2">
-        <v>7.6</v>
-      </c>
-      <c r="AR2">
-        <v>16</v>
-      </c>
-      <c r="AS2">
-        <v>7.2</v>
-      </c>
-      <c r="AT2">
-        <v>7.2</v>
       </c>
       <c r="AU2">
         <v>6.2</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="BF2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>4.3</v>
+      </c>
+      <c r="BJ2">
+        <v>5.2</v>
+      </c>
+      <c r="BK2">
+        <v>4.1</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>4.2</v>
+      </c>
+      <c r="BN2">
         <v>2.88</v>
       </c>
-      <c r="BI2">
-        <v>2.44</v>
-      </c>
-      <c r="BJ2">
-        <v>11.5</v>
-      </c>
-      <c r="BK2">
-        <v>5.4</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>170</v>
-      </c>
-      <c r="BN2">
-        <v>5.9</v>
-      </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BR2">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="BS2">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="BX2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="BZ2">
-        <v>50</v>
+        <v>960</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1296,241 +1308,241 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F3">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="G3">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="I3">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="P3">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q3">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="R3">
+        <v>1.35</v>
+      </c>
+      <c r="S3">
+        <v>3.5</v>
+      </c>
+      <c r="T3">
+        <v>1.87</v>
+      </c>
+      <c r="U3">
+        <v>1.96</v>
+      </c>
+      <c r="V3">
+        <v>1.96</v>
+      </c>
+      <c r="W3">
         <v>1.28</v>
       </c>
-      <c r="S3">
-        <v>3.95</v>
-      </c>
-      <c r="T3">
-        <v>2.04</v>
-      </c>
-      <c r="U3">
-        <v>1.81</v>
-      </c>
-      <c r="V3">
-        <v>2.06</v>
-      </c>
-      <c r="W3">
-        <v>1.22</v>
-      </c>
       <c r="X3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y3">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA3">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AB3">
         <v>16.5</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE3">
         <v>24</v>
       </c>
       <c r="AF3">
+        <v>34</v>
+      </c>
+      <c r="AG3">
+        <v>18.5</v>
+      </c>
+      <c r="AH3">
+        <v>23</v>
+      </c>
+      <c r="AI3">
         <v>46</v>
-      </c>
-      <c r="AG3">
-        <v>23</v>
-      </c>
-      <c r="AH3">
-        <v>26</v>
-      </c>
-      <c r="AI3">
-        <v>55</v>
       </c>
       <c r="AJ3">
         <v>900</v>
       </c>
       <c r="AK3">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c r="AL3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AM3">
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="AO3">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AP3">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AQ3">
+        <v>7.6</v>
+      </c>
+      <c r="AR3">
+        <v>10</v>
+      </c>
+      <c r="AS3">
+        <v>18.5</v>
+      </c>
+      <c r="AT3">
+        <v>13</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
+        <v>9</v>
+      </c>
+      <c r="AW3">
+        <v>16.5</v>
+      </c>
+      <c r="AX3">
+        <v>8</v>
+      </c>
+      <c r="AY3">
+        <v>14.5</v>
+      </c>
+      <c r="AZ3">
+        <v>16.5</v>
+      </c>
+      <c r="BA3">
+        <v>30</v>
+      </c>
+      <c r="BB3">
+        <v>9</v>
+      </c>
+      <c r="BC3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD3">
+        <v>8.4</v>
+      </c>
+      <c r="BE3">
+        <v>85</v>
+      </c>
+      <c r="BF3">
+        <v>8.4</v>
+      </c>
+      <c r="BG3">
+        <v>11.5</v>
+      </c>
+      <c r="BH3">
+        <v>3.45</v>
+      </c>
+      <c r="BI3">
+        <v>3.05</v>
+      </c>
+      <c r="BJ3">
+        <v>11</v>
+      </c>
+      <c r="BK3">
+        <v>7.8</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>110</v>
+      </c>
+      <c r="BN3">
+        <v>8.6</v>
+      </c>
+      <c r="BO3">
+        <v>6.6</v>
+      </c>
+      <c r="BP3">
+        <v>46</v>
+      </c>
+      <c r="BQ3">
+        <v>5.9</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
         <v>6</v>
       </c>
-      <c r="AR3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS3">
+      <c r="BT3">
+        <v>5.1</v>
+      </c>
+      <c r="BU3">
+        <v>4</v>
+      </c>
+      <c r="BV3">
         <v>15.5</v>
       </c>
-      <c r="AT3">
-        <v>12</v>
-      </c>
-      <c r="AU3">
-        <v>7</v>
-      </c>
-      <c r="AV3">
-        <v>8.4</v>
-      </c>
-      <c r="AW3">
-        <v>17</v>
-      </c>
-      <c r="AX3">
-        <v>5.7</v>
-      </c>
-      <c r="AY3">
-        <v>16.5</v>
-      </c>
-      <c r="AZ3">
-        <v>18.5</v>
-      </c>
-      <c r="BA3">
-        <v>6.4</v>
-      </c>
-      <c r="BB3">
+      <c r="BW3">
+        <v>10.5</v>
+      </c>
+      <c r="BX3">
+        <v>32</v>
+      </c>
+      <c r="BY3">
+        <v>5.9</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
         <v>6.2</v>
       </c>
-      <c r="BC3">
-        <v>6</v>
-      </c>
-      <c r="BD3">
-        <v>6</v>
-      </c>
-      <c r="BE3">
-        <v>100</v>
-      </c>
-      <c r="BF3">
-        <v>6.2</v>
-      </c>
-      <c r="BG3">
-        <v>12</v>
-      </c>
-      <c r="BH3">
-        <v>3.35</v>
-      </c>
-      <c r="BI3">
-        <v>2.68</v>
-      </c>
-      <c r="BJ3">
-        <v>12.5</v>
-      </c>
-      <c r="BK3">
-        <v>4.6</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>130</v>
-      </c>
-      <c r="BN3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO3">
-        <v>4.2</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>6.6</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>6.6</v>
-      </c>
-      <c r="BT3">
-        <v>4.6</v>
-      </c>
-      <c r="BU3">
-        <v>2.86</v>
-      </c>
-      <c r="BV3">
-        <v>14</v>
-      </c>
-      <c r="BW3">
-        <v>4.8</v>
-      </c>
-      <c r="BX3">
-        <v>34</v>
-      </c>
-      <c r="BY3">
-        <v>6</v>
-      </c>
-      <c r="BZ3">
-        <v>32</v>
-      </c>
-      <c r="CA3">
-        <v>6</v>
-      </c>
       <c r="CB3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1538,241 +1550,241 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G4">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H4">
+        <v>3.25</v>
+      </c>
+      <c r="I4">
         <v>3.4</v>
       </c>
-      <c r="I4">
-        <v>3.95</v>
-      </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="O4">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="Q4">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
         <v>1.58</v>
       </c>
       <c r="X4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y4">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA4">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE4">
+        <v>60</v>
+      </c>
+      <c r="AF4">
+        <v>16</v>
+      </c>
+      <c r="AG4">
+        <v>13.5</v>
+      </c>
+      <c r="AH4">
+        <v>24</v>
+      </c>
+      <c r="AI4">
+        <v>90</v>
+      </c>
+      <c r="AJ4">
+        <v>48</v>
+      </c>
+      <c r="AK4">
+        <v>44</v>
+      </c>
+      <c r="AL4">
+        <v>70</v>
+      </c>
+      <c r="AM4">
+        <v>990</v>
+      </c>
+      <c r="AN4">
+        <v>48</v>
+      </c>
+      <c r="AO4">
         <v>80</v>
       </c>
-      <c r="AF4">
-        <v>15.5</v>
-      </c>
-      <c r="AG4">
-        <v>14</v>
-      </c>
-      <c r="AH4">
-        <v>26</v>
-      </c>
-      <c r="AI4">
-        <v>540</v>
-      </c>
-      <c r="AJ4">
-        <v>50</v>
-      </c>
-      <c r="AK4">
-        <v>48</v>
-      </c>
-      <c r="AL4">
-        <v>90</v>
-      </c>
-      <c r="AM4">
-        <v>500</v>
-      </c>
-      <c r="AN4">
-        <v>55</v>
-      </c>
-      <c r="AO4">
-        <v>600</v>
-      </c>
       <c r="AP4">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4">
         <v>17</v>
       </c>
       <c r="AS4">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="AT4">
+        <v>7.4</v>
+      </c>
+      <c r="AU4">
         <v>6.2</v>
       </c>
-      <c r="AU4">
-        <v>5.9</v>
-      </c>
       <c r="AV4">
+        <v>12.5</v>
+      </c>
+      <c r="AW4">
+        <v>34</v>
+      </c>
+      <c r="AX4">
         <v>13.5</v>
       </c>
-      <c r="AW4">
-        <v>7</v>
-      </c>
-      <c r="AX4">
-        <v>12</v>
-      </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>7.2</v>
+        <v>48</v>
       </c>
       <c r="BB4">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BC4">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BE4">
         <v>140</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BG4">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BH4">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BI4">
-        <v>2.16</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ4">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR4">
+        <v>55</v>
+      </c>
+      <c r="BS4">
+        <v>6</v>
+      </c>
+      <c r="BT4">
+        <v>7.4</v>
+      </c>
+      <c r="BU4">
+        <v>5.6</v>
+      </c>
+      <c r="BV4">
+        <v>36</v>
+      </c>
+      <c r="BW4">
+        <v>5.9</v>
+      </c>
+      <c r="BX4">
         <v>60</v>
       </c>
-      <c r="BS4">
-        <v>4.6</v>
-      </c>
-      <c r="BT4">
-        <v>7.8</v>
-      </c>
-      <c r="BU4">
-        <v>4.9</v>
-      </c>
-      <c r="BV4">
-        <v>44</v>
-      </c>
-      <c r="BW4">
-        <v>4.5</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
       <c r="BY4">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA4">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1780,67 +1792,67 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F5">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="G5">
         <v>2.96</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O5">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="P5">
         <v>1.52</v>
       </c>
       <c r="Q5">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
         <v>1.51</v>
@@ -1852,7 +1864,7 @@
         <v>9.4</v>
       </c>
       <c r="Z5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA5">
         <v>75</v>
@@ -1864,106 +1876,106 @@
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
         <v>60</v>
       </c>
       <c r="AF5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG5">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="AJ5">
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AL5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM5">
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AP5">
         <v>7</v>
       </c>
       <c r="AQ5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR5">
         <v>16</v>
       </c>
       <c r="AS5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AT5">
         <v>7.2</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW5">
         <v>32</v>
       </c>
       <c r="AX5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY5">
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB5">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BC5">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BE5">
         <v>140</v>
       </c>
       <c r="BF5">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BG5">
         <v>44</v>
       </c>
       <c r="BH5">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="BI5">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="BJ5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK5">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1972,49 +1984,49 @@
         <v>170</v>
       </c>
       <c r="BN5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
         <v>29</v>
       </c>
       <c r="BQ5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BR5">
         <v>55</v>
       </c>
       <c r="BS5">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BT5">
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW5">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BX5">
         <v>65</v>
       </c>
       <c r="BY5">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BZ5">
         <v>60</v>
       </c>
       <c r="CA5">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2022,232 +2034,232 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F6">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="G6">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="H6">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I6">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M6">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="P6">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W6">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X6">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA6">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AB6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI6">
         <v>160</v>
       </c>
       <c r="AJ6">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AK6">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AL6">
         <v>190</v>
       </c>
       <c r="AM6">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6">
         <v>600</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP6">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS6">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AT6">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BB6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BC6">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BD6">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BE6">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="BF6">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BG6">
         <v>24</v>
       </c>
       <c r="BH6">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BI6">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="BN6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT6">
         <v>5.5</v>
       </c>
       <c r="BU6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
@@ -2256,7 +2268,7 @@
         <v>9.6</v>
       </c>
       <c r="CB6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2264,46 +2276,46 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F7">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H7">
+        <v>3.5</v>
+      </c>
+      <c r="I7">
+        <v>3.75</v>
+      </c>
+      <c r="J7">
+        <v>3.45</v>
+      </c>
+      <c r="K7">
         <v>3.6</v>
       </c>
-      <c r="I7">
-        <v>3.8</v>
-      </c>
-      <c r="J7">
-        <v>3.35</v>
-      </c>
-      <c r="K7">
-        <v>3.55</v>
-      </c>
       <c r="L7">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
         <v>3.7</v>
       </c>
       <c r="O7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
         <v>1.89</v>
@@ -2312,31 +2324,31 @@
         <v>2.06</v>
       </c>
       <c r="R7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
         <v>3.75</v>
       </c>
       <c r="T7">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V7">
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
         <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA7">
         <v>85</v>
@@ -2348,10 +2360,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF7">
         <v>14.5</v>
@@ -2363,16 +2375,16 @@
         <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM7">
         <v>580</v>
@@ -2390,22 +2402,22 @@
         <v>11.5</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS7">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT7">
         <v>8.199999999999999</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7">
         <v>13.5</v>
       </c>
       <c r="AW7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX7">
         <v>12</v>
@@ -2420,13 +2432,13 @@
         <v>38</v>
       </c>
       <c r="BB7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC7">
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE7">
         <v>75</v>
@@ -2447,16 +2459,16 @@
         <v>10</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO7">
         <v>4.4</v>
@@ -2465,16 +2477,16 @@
         <v>17.5</v>
       </c>
       <c r="BQ7">
+        <v>7.4</v>
+      </c>
+      <c r="BR7">
+        <v>34</v>
+      </c>
+      <c r="BS7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT7">
         <v>7</v>
-      </c>
-      <c r="BR7">
-        <v>32</v>
-      </c>
-      <c r="BS7">
-        <v>8.6</v>
-      </c>
-      <c r="BT7">
-        <v>7.2</v>
       </c>
       <c r="BU7">
         <v>5.8</v>
@@ -2483,22 +2495,22 @@
         <v>32</v>
       </c>
       <c r="BW7">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7">
         <v>44</v>
       </c>
       <c r="BY7">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>30</v>
       </c>
       <c r="CA7">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2506,34 +2518,34 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G8">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
         <v>1.42</v>
@@ -2542,43 +2554,43 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q8">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W8">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA8">
         <v>500</v>
@@ -2596,31 +2608,31 @@
         <v>60</v>
       </c>
       <c r="AF8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG8">
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI8">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL8">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN8">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO8">
         <v>65</v>
@@ -2629,16 +2641,16 @@
         <v>12.5</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS8">
         <v>55</v>
       </c>
       <c r="AT8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU8">
         <v>7.2</v>
@@ -2653,7 +2665,7 @@
         <v>11</v>
       </c>
       <c r="AY8">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
         <v>16</v>
@@ -2662,85 +2674,85 @@
         <v>40</v>
       </c>
       <c r="BB8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC8">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG8">
         <v>32</v>
       </c>
       <c r="BH8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI8">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BN8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BR8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS8">
         <v>4.2</v>
       </c>
       <c r="BT8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BV8">
         <v>40</v>
       </c>
       <c r="BW8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX8">
         <v>55</v>
       </c>
       <c r="BY8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA8">
         <v>4.2</v>
       </c>
       <c r="CB8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2748,70 +2760,70 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F9">
         <v>4.3</v>
       </c>
       <c r="G9">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H9">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J9">
         <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L9">
         <v>1.53</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P9">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q9">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R9">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S9">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U9">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="V9">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X9">
         <v>11</v>
@@ -2820,19 +2832,19 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AA9">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC9">
         <v>7.8</v>
       </c>
       <c r="AD9">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE9">
         <v>65</v>
@@ -2841,10 +2853,10 @@
         <v>42</v>
       </c>
       <c r="AG9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI9">
         <v>70</v>
@@ -2865,61 +2877,61 @@
         <v>600</v>
       </c>
       <c r="AO9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP9">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AR9">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AS9">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AT9">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU9">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AV9">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW9">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AX9">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AY9">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AZ9">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BA9">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BB9">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC9">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD9">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE9">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF9">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG9">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BH9">
         <v>3.25</v>
@@ -2928,7 +2940,7 @@
         <v>2.3</v>
       </c>
       <c r="BJ9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK9">
         <v>3.7</v>
@@ -2943,7 +2955,7 @@
         <v>9.4</v>
       </c>
       <c r="BO9">
-        <v>3.25</v>
+        <v>5.9</v>
       </c>
       <c r="BP9">
         <v>60</v>
@@ -2961,13 +2973,13 @@
         <v>5.3</v>
       </c>
       <c r="BU9">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="BV9">
         <v>19.5</v>
       </c>
       <c r="BW9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX9">
         <v>46</v>
@@ -2979,10 +2991,10 @@
         <v>48</v>
       </c>
       <c r="CA9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2990,241 +3002,241 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F10">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="G10">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="H10">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="J10">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="L10">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="M10">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="P10">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q10">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="W10">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="X10">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y10">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Z10">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="AA10">
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD10">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE10">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="AF10">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AG10">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI10">
         <v>260</v>
       </c>
       <c r="AJ10">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AK10">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AL10">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM10">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AO10">
         <v>600</v>
       </c>
       <c r="AP10">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS10">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT10">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU10">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV10">
+        <v>16</v>
+      </c>
+      <c r="AW10">
+        <v>6.8</v>
+      </c>
+      <c r="AX10">
+        <v>9.4</v>
+      </c>
+      <c r="AY10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10">
         <v>5.6</v>
       </c>
-      <c r="AW10">
-        <v>7.2</v>
-      </c>
-      <c r="AX10">
-        <v>6.2</v>
-      </c>
-      <c r="AY10">
-        <v>5</v>
-      </c>
-      <c r="AZ10">
-        <v>6.2</v>
-      </c>
       <c r="BA10">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB10">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BC10">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BD10">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE10">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BF10">
+        <v>18.5</v>
+      </c>
+      <c r="BG10">
         <v>6.8</v>
       </c>
-      <c r="BG10">
-        <v>7.6</v>
-      </c>
       <c r="BH10">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="BI10">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ10">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BN10">
         <v>5.3</v>
       </c>
       <c r="BO10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP10">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="BR10">
+        <v>46</v>
+      </c>
+      <c r="BS10">
+        <v>4.5</v>
+      </c>
+      <c r="BT10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU10">
+        <v>5.8</v>
+      </c>
+      <c r="BV10">
+        <v>55</v>
+      </c>
+      <c r="BW10">
+        <v>4.6</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>4.7</v>
+      </c>
+      <c r="BZ10">
         <v>48</v>
       </c>
-      <c r="BS10">
-        <v>6.4</v>
-      </c>
-      <c r="BT10">
-        <v>7.2</v>
-      </c>
-      <c r="BU10">
-        <v>4.1</v>
-      </c>
-      <c r="BV10">
-        <v>42</v>
-      </c>
-      <c r="BW10">
-        <v>6.2</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>6.6</v>
-      </c>
-      <c r="BZ10">
-        <v>55</v>
-      </c>
       <c r="CA10">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3232,241 +3244,241 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F11">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="G11">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="H11">
         <v>3.05</v>
       </c>
       <c r="I11">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="J11">
+        <v>3.4</v>
+      </c>
+      <c r="K11">
+        <v>3.95</v>
+      </c>
+      <c r="L11">
+        <v>1.38</v>
+      </c>
+      <c r="M11">
+        <v>1.06</v>
+      </c>
+      <c r="N11">
         <v>3.3</v>
-      </c>
-      <c r="K11">
-        <v>4.5</v>
-      </c>
-      <c r="L11">
-        <v>1.36</v>
-      </c>
-      <c r="M11">
-        <v>1.05</v>
-      </c>
-      <c r="N11">
-        <v>3.6</v>
       </c>
       <c r="O11">
         <v>1.31</v>
       </c>
       <c r="P11">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q11">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="R11">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T11">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U11">
         <v>2.16</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X11">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="Y11">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="Z11">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AA11">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB11">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AC11">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="AD11">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AE11">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AF11">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AG11">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AI11">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ11">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK11">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AL11">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>600</v>
+        <v>19</v>
       </c>
       <c r="AO11">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AP11">
-        <v>1.27</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
-        <v>1.25</v>
+        <v>9.6</v>
       </c>
       <c r="AR11">
-        <v>1.26</v>
+        <v>16</v>
       </c>
       <c r="AS11">
-        <v>1.27</v>
+        <v>25</v>
       </c>
       <c r="AT11">
-        <v>1.25</v>
+        <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>1.26</v>
+        <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>1.27</v>
+        <v>15</v>
       </c>
       <c r="AX11">
-        <v>1.25</v>
+        <v>10.5</v>
       </c>
       <c r="AY11">
-        <v>1.25</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11">
-        <v>1.25</v>
+        <v>13</v>
       </c>
       <c r="BA11">
-        <v>1.27</v>
+        <v>18</v>
       </c>
       <c r="BB11">
-        <v>1.27</v>
+        <v>13.5</v>
       </c>
       <c r="BC11">
-        <v>1.27</v>
+        <v>16.5</v>
       </c>
       <c r="BD11">
-        <v>1.27</v>
+        <v>15.5</v>
       </c>
       <c r="BE11">
-        <v>1.27</v>
+        <v>38</v>
       </c>
       <c r="BF11">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BG11">
-        <v>1.55</v>
+        <v>12</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3474,241 +3486,241 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F12">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="H12">
+        <v>3.5</v>
+      </c>
+      <c r="I12">
         <v>4.2</v>
       </c>
-      <c r="I12">
-        <v>5.3</v>
-      </c>
       <c r="J12">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="K12">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="L12">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="M12">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N12">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="O12">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="P12">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="Q12">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="R12">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S12">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="T12">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U12">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V12">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="W12">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="X12">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y12">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="AA12">
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE12">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="AF12">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
         <v>26</v>
       </c>
       <c r="AI12">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="AJ12">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AK12">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AL12">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AM12">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN12">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AO12">
         <v>600</v>
       </c>
       <c r="AP12">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR12">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS12">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT12">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AU12">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AV12">
+        <v>5.7</v>
+      </c>
+      <c r="AW12">
+        <v>7.4</v>
+      </c>
+      <c r="AX12">
+        <v>6.2</v>
+      </c>
+      <c r="AY12">
         <v>5.2</v>
       </c>
-      <c r="AW12">
-        <v>6.4</v>
-      </c>
-      <c r="AX12">
-        <v>5.1</v>
-      </c>
-      <c r="AY12">
+      <c r="AZ12">
+        <v>6.2</v>
+      </c>
+      <c r="BA12">
         <v>7.6</v>
       </c>
-      <c r="AZ12">
-        <v>5.5</v>
-      </c>
-      <c r="BA12">
-        <v>6.6</v>
-      </c>
       <c r="BB12">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BC12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BD12">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE12">
+        <v>8</v>
+      </c>
+      <c r="BF12">
         <v>6.8</v>
       </c>
-      <c r="BF12">
-        <v>5.5</v>
-      </c>
       <c r="BG12">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH12">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="BI12">
         <v>2.34</v>
       </c>
       <c r="BJ12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK12">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BN12">
         <v>5.3</v>
       </c>
       <c r="BO12">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="BP12">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BQ12">
+        <v>6.6</v>
+      </c>
+      <c r="BR12">
+        <v>50</v>
+      </c>
+      <c r="BS12">
+        <v>7.8</v>
+      </c>
+      <c r="BT12">
+        <v>7.2</v>
+      </c>
+      <c r="BU12">
         <v>4</v>
       </c>
-      <c r="BR12">
-        <v>46</v>
-      </c>
-      <c r="BS12">
-        <v>4.5</v>
-      </c>
-      <c r="BT12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU12">
-        <v>3.25</v>
-      </c>
       <c r="BV12">
+        <v>42</v>
+      </c>
+      <c r="BW12">
+        <v>7.6</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ12">
         <v>55</v>
       </c>
-      <c r="BW12">
-        <v>4.6</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>4.8</v>
-      </c>
-      <c r="BZ12">
-        <v>46</v>
-      </c>
       <c r="CA12">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3716,25 +3728,25 @@
         <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F13">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G13">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I13">
         <v>3.65</v>
@@ -3746,7 +3758,7 @@
         <v>3.4</v>
       </c>
       <c r="L13">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M13">
         <v>1.09</v>
@@ -3758,7 +3770,7 @@
         <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q13">
         <v>2.28</v>
@@ -3770,16 +3782,16 @@
         <v>4.3</v>
       </c>
       <c r="T13">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U13">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X13">
         <v>11.5</v>
@@ -3788,10 +3800,10 @@
         <v>12</v>
       </c>
       <c r="Z13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA13">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -3803,10 +3815,10 @@
         <v>15.5</v>
       </c>
       <c r="AE13">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AF13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -3821,7 +3833,7 @@
         <v>40</v>
       </c>
       <c r="AK13">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL13">
         <v>130</v>
@@ -3830,7 +3842,7 @@
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO13">
         <v>600</v>
@@ -3848,7 +3860,7 @@
         <v>46</v>
       </c>
       <c r="AT13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU13">
         <v>6.6</v>
@@ -3866,7 +3878,7 @@
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA13">
         <v>42</v>
@@ -3875,10 +3887,10 @@
         <v>27</v>
       </c>
       <c r="BC13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD13">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE13">
         <v>55</v>
@@ -3887,7 +3899,7 @@
         <v>21</v>
       </c>
       <c r="BG13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH13">
         <v>3.1</v>
@@ -3899,13 +3911,13 @@
         <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN13">
         <v>5.3</v>
@@ -3917,19 +3929,19 @@
         <v>19.5</v>
       </c>
       <c r="BQ13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13">
         <v>6.8</v>
       </c>
       <c r="BU13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -3941,16 +3953,16 @@
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3958,25 +3970,25 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F14">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G14">
         <v>2.08</v>
       </c>
       <c r="H14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I14">
         <v>4.1</v>
@@ -3994,28 +4006,28 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O14">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
         <v>2.34</v>
       </c>
       <c r="Q14">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R14">
         <v>1.53</v>
       </c>
       <c r="S14">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T14">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U14">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
         <v>1.32</v>
@@ -4033,7 +4045,7 @@
         <v>32</v>
       </c>
       <c r="AA14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB14">
         <v>12.5</v>
@@ -4042,7 +4054,7 @@
         <v>9.4</v>
       </c>
       <c r="AD14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE14">
         <v>55</v>
@@ -4057,10 +4069,10 @@
         <v>16.5</v>
       </c>
       <c r="AI14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK14">
         <v>20</v>
@@ -4069,7 +4081,7 @@
         <v>30</v>
       </c>
       <c r="AM14">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN14">
         <v>11</v>
@@ -4084,13 +4096,13 @@
         <v>16.5</v>
       </c>
       <c r="AR14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS14">
         <v>50</v>
       </c>
       <c r="AT14">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU14">
         <v>8.199999999999999</v>
@@ -4111,7 +4123,7 @@
         <v>14</v>
       </c>
       <c r="BA14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB14">
         <v>20</v>
@@ -4120,7 +4132,7 @@
         <v>17</v>
       </c>
       <c r="BD14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE14">
         <v>55</v>
@@ -4129,7 +4141,7 @@
         <v>9.4</v>
       </c>
       <c r="BG14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BH14">
         <v>4.1</v>
@@ -4147,10 +4159,10 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN14">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO14">
         <v>4.4</v>
@@ -4159,13 +4171,13 @@
         <v>14</v>
       </c>
       <c r="BQ14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR14">
         <v>24</v>
       </c>
       <c r="BS14">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT14">
         <v>7.6</v>
@@ -4177,22 +4189,22 @@
         <v>28</v>
       </c>
       <c r="BW14">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX14">
         <v>34</v>
       </c>
       <c r="BY14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ14">
         <v>19.5</v>
       </c>
       <c r="CA14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4200,34 +4212,34 @@
         <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F15">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G15">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H15">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L15">
         <v>1.42</v>
@@ -4242,28 +4254,28 @@
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q15">
         <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S15">
         <v>3.65</v>
       </c>
       <c r="T15">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U15">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V15">
         <v>1.11</v>
       </c>
       <c r="W15">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X15">
         <v>18</v>
@@ -4272,28 +4284,28 @@
         <v>26</v>
       </c>
       <c r="Z15">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AA15">
         <v>370</v>
       </c>
       <c r="AB15">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD15">
         <v>36</v>
       </c>
       <c r="AE15">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AF15">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AG15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15">
         <v>36</v>
@@ -4302,7 +4314,7 @@
         <v>470</v>
       </c>
       <c r="AJ15">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK15">
         <v>18</v>
@@ -4314,10 +4326,10 @@
         <v>230</v>
       </c>
       <c r="AN15">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO15">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AP15">
         <v>12.5</v>
@@ -4329,19 +4341,19 @@
         <v>50</v>
       </c>
       <c r="AS15">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT15">
         <v>6.4</v>
       </c>
       <c r="AU15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV15">
         <v>23</v>
       </c>
       <c r="AW15">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX15">
         <v>7</v>
@@ -4362,19 +4374,19 @@
         <v>15.5</v>
       </c>
       <c r="BD15">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BE15">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF15">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG15">
         <v>15</v>
       </c>
       <c r="BH15">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI15">
         <v>3.1</v>
@@ -4383,58 +4395,58 @@
         <v>15</v>
       </c>
       <c r="BK15">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BN15">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BO15">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ15">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BR15">
         <v>36</v>
       </c>
       <c r="BS15">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BT15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU15">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BV15">
         <v>110</v>
       </c>
       <c r="BW15">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BX15">
         <v>110</v>
       </c>
       <c r="BY15">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BZ15">
         <v>23</v>
       </c>
       <c r="CA15">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="CB15" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4442,112 +4454,112 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F16">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G16">
         <v>4.3</v>
       </c>
       <c r="H16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J16">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K16">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M16">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="O16">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q16">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="R16">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S16">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="T16">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="U16">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="V16">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="W16">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X16">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA16">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AB16">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AC16">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE16">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AF16">
         <v>34</v>
       </c>
       <c r="AG16">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH16">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI16">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AJ16">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AK16">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AL16">
         <v>120</v>
@@ -4556,127 +4568,127 @@
         <v>580</v>
       </c>
       <c r="AN16">
-        <v>42</v>
+        <v>240</v>
       </c>
       <c r="AO16">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AP16">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR16">
         <v>11</v>
       </c>
       <c r="AS16">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU16">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW16">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AX16">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AY16">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ16">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA16">
         <v>12.5</v>
       </c>
       <c r="BB16">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC16">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BD16">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE16">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF16">
+        <v>5.1</v>
+      </c>
+      <c r="BG16">
+        <v>13</v>
+      </c>
+      <c r="BH16">
+        <v>3.9</v>
+      </c>
+      <c r="BI16">
+        <v>3</v>
+      </c>
+      <c r="BJ16">
+        <v>11</v>
+      </c>
+      <c r="BK16">
+        <v>3.95</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
         <v>5.9</v>
       </c>
-      <c r="BG16">
-        <v>9.6</v>
-      </c>
-      <c r="BH16">
-        <v>4.3</v>
-      </c>
-      <c r="BI16">
-        <v>3.15</v>
-      </c>
-      <c r="BJ16">
-        <v>10.5</v>
-      </c>
-      <c r="BK16">
-        <v>3.7</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
+      <c r="BN16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO16">
+        <v>5.7</v>
+      </c>
+      <c r="BP16">
+        <v>34</v>
+      </c>
+      <c r="BQ16">
+        <v>5.2</v>
+      </c>
+      <c r="BR16">
+        <v>44</v>
+      </c>
+      <c r="BS16">
         <v>5.4</v>
       </c>
-      <c r="BN16">
-        <v>8.6</v>
-      </c>
-      <c r="BO16">
-        <v>5.8</v>
-      </c>
-      <c r="BP16">
-        <v>36</v>
-      </c>
-      <c r="BQ16">
-        <v>4.9</v>
-      </c>
-      <c r="BR16">
-        <v>42</v>
-      </c>
-      <c r="BS16">
+      <c r="BT16">
+        <v>5.5</v>
+      </c>
+      <c r="BU16">
+        <v>4</v>
+      </c>
+      <c r="BV16">
+        <v>17</v>
+      </c>
+      <c r="BW16">
+        <v>4.5</v>
+      </c>
+      <c r="BX16">
+        <v>32</v>
+      </c>
+      <c r="BY16">
+        <v>5.2</v>
+      </c>
+      <c r="BZ16">
+        <v>26</v>
+      </c>
+      <c r="CA16">
         <v>5</v>
       </c>
-      <c r="BT16">
-        <v>5.6</v>
-      </c>
-      <c r="BU16">
-        <v>3.95</v>
-      </c>
-      <c r="BV16">
-        <v>15.5</v>
-      </c>
-      <c r="BW16">
-        <v>4.2</v>
-      </c>
-      <c r="BX16">
-        <v>28</v>
-      </c>
-      <c r="BY16">
-        <v>4.7</v>
-      </c>
-      <c r="BZ16">
-        <v>23</v>
-      </c>
-      <c r="CA16">
-        <v>4.6</v>
-      </c>
       <c r="CB16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4684,16 +4696,16 @@
         <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F17">
         <v>2.26</v>
@@ -4708,10 +4720,10 @@
         <v>3.6</v>
       </c>
       <c r="J17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L17">
         <v>1.4</v>
@@ -4720,22 +4732,22 @@
         <v>1.07</v>
       </c>
       <c r="N17">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P17">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q17">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R17">
         <v>1.32</v>
       </c>
       <c r="S17">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T17">
         <v>1.74</v>
@@ -4804,7 +4816,7 @@
         <v>600</v>
       </c>
       <c r="AP17">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AQ17">
         <v>4.7</v>
@@ -4816,10 +4828,10 @@
         <v>6.6</v>
       </c>
       <c r="AT17">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU17">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV17">
         <v>4.9</v>
@@ -4831,10 +4843,10 @@
         <v>5.1</v>
       </c>
       <c r="AY17">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ17">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA17">
         <v>6.4</v>
@@ -4852,7 +4864,7 @@
         <v>6.8</v>
       </c>
       <c r="BF17">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BG17">
         <v>6.2</v>
@@ -4918,7 +4930,7 @@
         <v>7.4</v>
       </c>
       <c r="CB17" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4926,1155 +4938,1155 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F18">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="G18">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="H18">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="I18">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="J18">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="L18">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M18">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="O18">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="P18">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Q18">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="R18">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S18">
-        <v>1.05</v>
+        <v>6.8</v>
       </c>
       <c r="T18">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="U18">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="W18">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X18">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="Y18">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="Z18">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="AA18">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="AB18">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="AC18">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="AD18">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AE18">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="AF18">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="AG18">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI18">
-        <v>460</v>
+        <v>240</v>
       </c>
       <c r="AJ18">
         <v>900</v>
       </c>
       <c r="AK18">
-        <v>290</v>
+        <v>170</v>
       </c>
       <c r="AL18">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP18">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ18">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AR18">
-        <v>1.37</v>
+        <v>11.5</v>
       </c>
       <c r="AS18">
-        <v>1.41</v>
+        <v>6.2</v>
       </c>
       <c r="AT18">
+        <v>7</v>
+      </c>
+      <c r="AU18">
+        <v>5.8</v>
+      </c>
+      <c r="AV18">
+        <v>11</v>
+      </c>
+      <c r="AW18">
+        <v>34</v>
+      </c>
+      <c r="AX18">
+        <v>18</v>
+      </c>
+      <c r="AY18">
+        <v>13.5</v>
+      </c>
+      <c r="AZ18">
+        <v>5.9</v>
+      </c>
+      <c r="BA18">
+        <v>6.6</v>
+      </c>
+      <c r="BB18">
+        <v>6.6</v>
+      </c>
+      <c r="BC18">
+        <v>6.6</v>
+      </c>
+      <c r="BD18">
+        <v>6.8</v>
+      </c>
+      <c r="BE18">
+        <v>7</v>
+      </c>
+      <c r="BF18">
+        <v>6.8</v>
+      </c>
+      <c r="BG18">
+        <v>6.4</v>
+      </c>
+      <c r="BH18">
+        <v>2.52</v>
+      </c>
+      <c r="BI18">
+        <v>2.1</v>
+      </c>
+      <c r="BJ18">
+        <v>13.5</v>
+      </c>
+      <c r="BK18">
+        <v>5.6</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN18">
+        <v>7</v>
+      </c>
+      <c r="BO18">
         <v>5.1</v>
       </c>
-      <c r="AU18">
-        <v>1.37</v>
-      </c>
-      <c r="AV18">
-        <v>1.36</v>
-      </c>
-      <c r="AW18">
-        <v>1.41</v>
-      </c>
-      <c r="AX18">
-        <v>1.38</v>
-      </c>
-      <c r="AY18">
-        <v>1.37</v>
-      </c>
-      <c r="AZ18">
-        <v>1.42</v>
-      </c>
-      <c r="BA18">
-        <v>1.41</v>
-      </c>
-      <c r="BB18">
-        <v>1.41</v>
-      </c>
-      <c r="BC18">
-        <v>1.41</v>
-      </c>
-      <c r="BD18">
-        <v>1.41</v>
-      </c>
-      <c r="BE18">
-        <v>1.42</v>
-      </c>
-      <c r="BF18">
-        <v>1.55</v>
-      </c>
-      <c r="BG18">
-        <v>1.55</v>
-      </c>
-      <c r="BH18">
-        <v>2.62</v>
-      </c>
-      <c r="BI18">
-        <v>2.08</v>
-      </c>
-      <c r="BJ18">
-        <v>14</v>
-      </c>
-      <c r="BK18">
-        <v>4.8</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.92</v>
-      </c>
-      <c r="BN18">
-        <v>7.2</v>
-      </c>
-      <c r="BO18">
-        <v>3.65</v>
-      </c>
       <c r="BP18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BQ18">
-        <v>1.85</v>
+        <v>7.8</v>
       </c>
       <c r="BR18">
         <v>80</v>
       </c>
       <c r="BS18">
-        <v>1.89</v>
+        <v>8.6</v>
       </c>
       <c r="BT18">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BU18">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="BV18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW18">
-        <v>1.81</v>
+        <v>7</v>
       </c>
       <c r="BX18">
         <v>65</v>
       </c>
       <c r="BY18">
-        <v>1.88</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.89</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F19">
-        <v>1.72</v>
+        <v>1.1</v>
       </c>
       <c r="G19">
-        <v>1.88</v>
+        <v>1000</v>
       </c>
       <c r="H19">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="I19">
-        <v>8.199999999999999</v>
+        <v>110</v>
       </c>
       <c r="J19">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="K19">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.79</v>
+        <v>1.02</v>
       </c>
       <c r="O19">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P19">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Q19">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="S19">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="T19">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20">
+        <v>1.82</v>
+      </c>
+      <c r="G20">
+        <v>1.88</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>6.6</v>
+      </c>
+      <c r="J20">
+        <v>3.3</v>
+      </c>
+      <c r="K20">
+        <v>3.7</v>
+      </c>
+      <c r="L20">
+        <v>1.41</v>
+      </c>
+      <c r="M20">
+        <v>1.09</v>
+      </c>
+      <c r="N20">
+        <v>2.8</v>
+      </c>
+      <c r="O20">
+        <v>1.41</v>
+      </c>
+      <c r="P20">
+        <v>1.62</v>
+      </c>
+      <c r="Q20">
+        <v>2.2</v>
+      </c>
+      <c r="R20">
+        <v>1.21</v>
+      </c>
+      <c r="S20">
+        <v>4.2</v>
+      </c>
+      <c r="T20">
+        <v>2</v>
+      </c>
+      <c r="U20">
+        <v>1.66</v>
+      </c>
+      <c r="V20">
+        <v>1.21</v>
+      </c>
+      <c r="W20">
+        <v>2.12</v>
+      </c>
+      <c r="X20">
+        <v>11.5</v>
+      </c>
+      <c r="Y20">
+        <v>18.5</v>
+      </c>
+      <c r="Z20">
+        <v>46</v>
+      </c>
+      <c r="AA20">
+        <v>900</v>
+      </c>
+      <c r="AB20">
+        <v>7.6</v>
+      </c>
+      <c r="AC20">
+        <v>9</v>
+      </c>
+      <c r="AD20">
+        <v>25</v>
+      </c>
+      <c r="AE20">
+        <v>110</v>
+      </c>
+      <c r="AF20">
+        <v>11</v>
+      </c>
+      <c r="AG20">
+        <v>11.5</v>
+      </c>
+      <c r="AH20">
+        <v>27</v>
+      </c>
+      <c r="AI20">
+        <v>130</v>
+      </c>
+      <c r="AJ20">
+        <v>25</v>
+      </c>
+      <c r="AK20">
+        <v>25</v>
+      </c>
+      <c r="AL20">
+        <v>55</v>
+      </c>
+      <c r="AM20">
+        <v>580</v>
+      </c>
+      <c r="AN20">
+        <v>19</v>
+      </c>
+      <c r="AO20">
+        <v>600</v>
+      </c>
+      <c r="AP20">
+        <v>4.7</v>
+      </c>
+      <c r="AQ20">
+        <v>12</v>
+      </c>
+      <c r="AR20">
+        <v>32</v>
+      </c>
+      <c r="AS20">
+        <v>6.6</v>
+      </c>
+      <c r="AT20">
+        <v>5.6</v>
+      </c>
+      <c r="AU20">
+        <v>6.6</v>
+      </c>
+      <c r="AV20">
+        <v>18.5</v>
+      </c>
+      <c r="AW20">
+        <v>6.8</v>
+      </c>
+      <c r="AX20">
+        <v>4.5</v>
+      </c>
+      <c r="AY20">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20">
+        <v>20</v>
+      </c>
+      <c r="BA20">
+        <v>6.6</v>
+      </c>
+      <c r="BB20">
+        <v>17</v>
+      </c>
+      <c r="BC20">
+        <v>6.2</v>
+      </c>
+      <c r="BD20">
+        <v>38</v>
+      </c>
+      <c r="BE20">
+        <v>6.6</v>
+      </c>
+      <c r="BF20">
+        <v>5.8</v>
+      </c>
+      <c r="BG20">
+        <v>6.6</v>
+      </c>
+      <c r="BH20">
+        <v>3.45</v>
+      </c>
+      <c r="BI20">
+        <v>2.42</v>
+      </c>
+      <c r="BJ20">
+        <v>14</v>
+      </c>
+      <c r="BK20">
+        <v>3.65</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>4.9</v>
+      </c>
+      <c r="BN20">
+        <v>4.9</v>
+      </c>
+      <c r="BO20">
+        <v>3.3</v>
+      </c>
+      <c r="BP20">
+        <v>16.5</v>
+      </c>
+      <c r="BQ20">
+        <v>3.8</v>
+      </c>
+      <c r="BR20">
+        <v>42</v>
+      </c>
+      <c r="BS20">
+        <v>4.4</v>
+      </c>
+      <c r="BT20">
+        <v>10.5</v>
+      </c>
+      <c r="BU20">
+        <v>3.35</v>
+      </c>
+      <c r="BV20">
+        <v>70</v>
+      </c>
+      <c r="BW20">
+        <v>4.6</v>
+      </c>
+      <c r="BX20">
         <v>85</v>
       </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>146</v>
-      </c>
-      <c r="F20">
-        <v>2.28</v>
-      </c>
-      <c r="G20">
-        <v>2.42</v>
-      </c>
-      <c r="H20">
-        <v>3.35</v>
-      </c>
-      <c r="I20">
-        <v>3.55</v>
-      </c>
-      <c r="J20">
-        <v>3.45</v>
-      </c>
-      <c r="K20">
-        <v>3.6</v>
-      </c>
-      <c r="L20">
-        <v>1.44</v>
-      </c>
-      <c r="M20">
-        <v>1.07</v>
-      </c>
-      <c r="N20">
-        <v>3.45</v>
-      </c>
-      <c r="O20">
-        <v>1.36</v>
-      </c>
-      <c r="P20">
-        <v>1.81</v>
-      </c>
-      <c r="Q20">
-        <v>2.14</v>
-      </c>
-      <c r="R20">
-        <v>1.3</v>
-      </c>
-      <c r="S20">
-        <v>3.95</v>
-      </c>
-      <c r="T20">
-        <v>1.84</v>
-      </c>
-      <c r="U20">
-        <v>1.92</v>
-      </c>
-      <c r="V20">
-        <v>1.39</v>
-      </c>
-      <c r="W20">
-        <v>1.7</v>
-      </c>
-      <c r="X20">
-        <v>34</v>
-      </c>
-      <c r="Y20">
-        <v>940</v>
-      </c>
-      <c r="Z20">
-        <v>910</v>
-      </c>
-      <c r="AA20">
-        <v>910</v>
-      </c>
-      <c r="AB20">
-        <v>500</v>
-      </c>
-      <c r="AC20">
-        <v>14</v>
-      </c>
-      <c r="AD20">
-        <v>950</v>
-      </c>
-      <c r="AE20">
-        <v>910</v>
-      </c>
-      <c r="AF20">
-        <v>860</v>
-      </c>
-      <c r="AG20">
-        <v>34</v>
-      </c>
-      <c r="AH20">
-        <v>950</v>
-      </c>
-      <c r="AI20">
-        <v>910</v>
-      </c>
-      <c r="AJ20">
-        <v>900</v>
-      </c>
-      <c r="AK20">
-        <v>500</v>
-      </c>
-      <c r="AL20">
-        <v>910</v>
-      </c>
-      <c r="AM20">
-        <v>910</v>
-      </c>
-      <c r="AN20">
-        <v>910</v>
-      </c>
-      <c r="AO20">
-        <v>910</v>
-      </c>
-      <c r="AP20">
-        <v>6.2</v>
-      </c>
-      <c r="AQ20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR20">
-        <v>1.86</v>
-      </c>
-      <c r="AS20">
-        <v>1.91</v>
-      </c>
-      <c r="AT20">
-        <v>5.1</v>
-      </c>
-      <c r="AU20">
-        <v>5.9</v>
-      </c>
-      <c r="AV20">
-        <v>8.4</v>
-      </c>
-      <c r="AW20">
-        <v>1.9</v>
-      </c>
-      <c r="AX20">
-        <v>7</v>
-      </c>
-      <c r="AY20">
-        <v>6.4</v>
-      </c>
-      <c r="AZ20">
-        <v>11</v>
-      </c>
-      <c r="BA20">
-        <v>1.93</v>
-      </c>
-      <c r="BB20">
-        <v>1.89</v>
-      </c>
-      <c r="BC20">
-        <v>1.87</v>
-      </c>
-      <c r="BD20">
-        <v>1.92</v>
-      </c>
-      <c r="BE20">
-        <v>1.93</v>
-      </c>
-      <c r="BF20">
-        <v>5</v>
-      </c>
-      <c r="BG20">
-        <v>1.87</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.04</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.04</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.04</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.04</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.04</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.04</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.04</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F21">
-        <v>1.12</v>
+        <v>2.28</v>
       </c>
       <c r="G21">
-        <v>990</v>
+        <v>2.36</v>
       </c>
       <c r="H21">
-        <v>1.12</v>
+        <v>3.35</v>
       </c>
       <c r="I21">
-        <v>990</v>
+        <v>3.55</v>
       </c>
       <c r="J21">
-        <v>1.15</v>
+        <v>3.45</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="O21">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P21">
-        <v>1.09</v>
+        <v>1.8</v>
       </c>
       <c r="Q21">
-        <v>1.29</v>
+        <v>2.14</v>
       </c>
       <c r="R21">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="S21">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="T21">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U21">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V21">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.73</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB21" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22">
+        <v>2.24</v>
+      </c>
+      <c r="G22">
+        <v>2.58</v>
+      </c>
+      <c r="H22">
+        <v>3.05</v>
+      </c>
+      <c r="I22">
+        <v>3.6</v>
+      </c>
+      <c r="J22">
+        <v>3.4</v>
+      </c>
+      <c r="K22">
+        <v>3.9</v>
+      </c>
+      <c r="L22">
+        <v>1.38</v>
+      </c>
+      <c r="M22">
+        <v>1.06</v>
+      </c>
+      <c r="N22">
+        <v>3.65</v>
+      </c>
+      <c r="O22">
+        <v>1.3</v>
+      </c>
+      <c r="P22">
+        <v>1.89</v>
+      </c>
+      <c r="Q22">
+        <v>1.88</v>
+      </c>
+      <c r="R22">
+        <v>1.37</v>
+      </c>
+      <c r="S22">
+        <v>3.2</v>
+      </c>
+      <c r="T22">
+        <v>1.7</v>
+      </c>
+      <c r="U22">
+        <v>2.1</v>
+      </c>
+      <c r="V22">
+        <v>1.38</v>
+      </c>
+      <c r="W22">
+        <v>1.64</v>
+      </c>
+      <c r="X22">
+        <v>17</v>
+      </c>
+      <c r="Y22">
+        <v>14</v>
+      </c>
+      <c r="Z22">
+        <v>25</v>
+      </c>
+      <c r="AA22">
+        <v>900</v>
+      </c>
+      <c r="AB22">
+        <v>11.5</v>
+      </c>
+      <c r="AC22">
+        <v>8.6</v>
+      </c>
+      <c r="AD22">
+        <v>15</v>
+      </c>
+      <c r="AE22">
+        <v>500</v>
+      </c>
+      <c r="AF22">
+        <v>17</v>
+      </c>
+      <c r="AG22">
+        <v>12.5</v>
+      </c>
+      <c r="AH22">
+        <v>19.5</v>
+      </c>
+      <c r="AI22">
+        <v>500</v>
+      </c>
+      <c r="AJ22">
+        <v>36</v>
+      </c>
+      <c r="AK22">
+        <v>28</v>
+      </c>
+      <c r="AL22">
         <v>100</v>
       </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>148</v>
-      </c>
-      <c r="F22">
-        <v>1.54</v>
-      </c>
-      <c r="G22">
-        <v>1.58</v>
-      </c>
-      <c r="H22">
+      <c r="AM22">
+        <v>580</v>
+      </c>
+      <c r="AN22">
+        <v>23</v>
+      </c>
+      <c r="AO22">
+        <v>40</v>
+      </c>
+      <c r="AP22">
+        <v>4.9</v>
+      </c>
+      <c r="AQ22">
+        <v>4.6</v>
+      </c>
+      <c r="AR22">
+        <v>5.5</v>
+      </c>
+      <c r="AS22">
+        <v>6.2</v>
+      </c>
+      <c r="AT22">
+        <v>4.3</v>
+      </c>
+      <c r="AU22">
+        <v>3.85</v>
+      </c>
+      <c r="AV22">
+        <v>4.7</v>
+      </c>
+      <c r="AW22">
         <v>5.9</v>
       </c>
-      <c r="I22">
-        <v>7</v>
-      </c>
-      <c r="J22">
-        <v>4.7</v>
-      </c>
-      <c r="K22">
-        <v>5.2</v>
-      </c>
-      <c r="L22">
-        <v>1.28</v>
-      </c>
-      <c r="M22">
-        <v>1.03</v>
-      </c>
-      <c r="N22">
-        <v>5.7</v>
-      </c>
-      <c r="O22">
-        <v>1.18</v>
-      </c>
-      <c r="P22">
-        <v>2.64</v>
-      </c>
-      <c r="Q22">
-        <v>1.55</v>
-      </c>
-      <c r="R22">
-        <v>1.65</v>
-      </c>
-      <c r="S22">
-        <v>2.4</v>
-      </c>
-      <c r="T22">
-        <v>1.66</v>
-      </c>
-      <c r="U22">
-        <v>2.22</v>
-      </c>
-      <c r="V22">
-        <v>1.17</v>
-      </c>
-      <c r="W22">
-        <v>2.72</v>
-      </c>
-      <c r="X22">
-        <v>32</v>
-      </c>
-      <c r="Y22">
-        <v>60</v>
-      </c>
-      <c r="Z22">
-        <v>65</v>
-      </c>
-      <c r="AA22">
-        <v>700</v>
-      </c>
-      <c r="AB22">
-        <v>13</v>
-      </c>
-      <c r="AC22">
-        <v>12.5</v>
-      </c>
-      <c r="AD22">
-        <v>26</v>
-      </c>
-      <c r="AE22">
-        <v>80</v>
-      </c>
-      <c r="AF22">
-        <v>12</v>
-      </c>
-      <c r="AG22">
-        <v>11</v>
-      </c>
-      <c r="AH22">
-        <v>20</v>
-      </c>
-      <c r="AI22">
-        <v>160</v>
-      </c>
-      <c r="AJ22">
-        <v>16</v>
-      </c>
-      <c r="AK22">
-        <v>15.5</v>
-      </c>
-      <c r="AL22">
-        <v>34</v>
-      </c>
-      <c r="AM22">
-        <v>500</v>
-      </c>
-      <c r="AN22">
-        <v>6.2</v>
-      </c>
-      <c r="AO22">
-        <v>700</v>
-      </c>
-      <c r="AP22">
-        <v>18</v>
-      </c>
-      <c r="AQ22">
-        <v>17</v>
-      </c>
-      <c r="AR22">
-        <v>24</v>
-      </c>
-      <c r="AS22">
-        <v>7.8</v>
-      </c>
-      <c r="AT22">
-        <v>10</v>
-      </c>
-      <c r="AU22">
-        <v>10</v>
-      </c>
-      <c r="AV22">
-        <v>20</v>
-      </c>
-      <c r="AW22">
-        <v>30</v>
-      </c>
       <c r="AX22">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="AY22">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="AZ22">
-        <v>16</v>
+        <v>5.1</v>
       </c>
       <c r="BA22">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="BB22">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC22">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD22">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BE22">
-        <v>38</v>
+        <v>6.4</v>
       </c>
       <c r="BF22">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG22">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK22">
         <v>1.04</v>
@@ -6086,13 +6098,13 @@
         <v>1.04</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO22">
         <v>1.04</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ22">
         <v>1.04</v>
@@ -6104,7 +6116,7 @@
         <v>1.04</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU22">
         <v>1.04</v>
@@ -6122,739 +6134,981 @@
         <v>1.04</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA22">
         <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F23">
-        <v>2.06</v>
+        <v>1.54</v>
       </c>
       <c r="G23">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="H23">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="I23">
+        <v>7</v>
+      </c>
+      <c r="J23">
         <v>4.6</v>
       </c>
-      <c r="J23">
-        <v>3.3</v>
-      </c>
       <c r="K23">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="L23">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="M23">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N23">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="O23">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="P23">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="Q23">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="R23">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="S23">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="T23">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="U23">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="V23">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="W23">
-        <v>1.87</v>
+        <v>2.72</v>
       </c>
       <c r="X23">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="Y23">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="Z23">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AA23">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB23">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AC23">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AE23">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AF23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG23">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH23">
         <v>21</v>
       </c>
       <c r="AI23">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AJ23">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="AK23">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="AL23">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AM23">
-        <v>640</v>
+        <v>580</v>
       </c>
       <c r="AN23">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AO23">
-        <v>570</v>
+        <v>700</v>
       </c>
       <c r="AP23">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AR23">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="AS23">
+        <v>7.4</v>
+      </c>
+      <c r="AT23">
         <v>10</v>
       </c>
-      <c r="AT23">
+      <c r="AU23">
+        <v>10</v>
+      </c>
+      <c r="AV23">
+        <v>20</v>
+      </c>
+      <c r="AW23">
         <v>7</v>
       </c>
-      <c r="AU23">
-        <v>6.6</v>
-      </c>
-      <c r="AV23">
-        <v>15.5</v>
-      </c>
-      <c r="AW23">
-        <v>10</v>
-      </c>
       <c r="AX23">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY23">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ23">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA23">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BB23">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BC23">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BD23">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BE23">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BF23">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="BG23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI23">
-        <v>1.19</v>
+        <v>3.55</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK23">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO23">
-        <v>1.19</v>
+        <v>3.5</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ23">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS23">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU23">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW23">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY23">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA23">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F24">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="G24">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="H24">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J24">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="K24">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="L24">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M24">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O24">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="P24">
+        <v>1.73</v>
+      </c>
+      <c r="Q24">
+        <v>2.24</v>
+      </c>
+      <c r="R24">
+        <v>1.29</v>
+      </c>
+      <c r="S24">
+        <v>4.2</v>
+      </c>
+      <c r="T24">
         <v>1.93</v>
       </c>
-      <c r="Q24">
-        <v>2.02</v>
-      </c>
-      <c r="R24">
-        <v>1.35</v>
-      </c>
-      <c r="S24">
-        <v>3.6</v>
-      </c>
-      <c r="T24">
-        <v>1.86</v>
-      </c>
       <c r="U24">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="V24">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W24">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="X24">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="Y24">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="Z24">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AA24">
         <v>900</v>
       </c>
       <c r="AB24">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC24">
+        <v>7.8</v>
+      </c>
+      <c r="AD24">
+        <v>18.5</v>
+      </c>
+      <c r="AE24">
+        <v>150</v>
+      </c>
+      <c r="AF24">
+        <v>13</v>
+      </c>
+      <c r="AG24">
+        <v>11</v>
+      </c>
+      <c r="AH24">
+        <v>21</v>
+      </c>
+      <c r="AI24">
+        <v>190</v>
+      </c>
+      <c r="AJ24">
+        <v>27</v>
+      </c>
+      <c r="AK24">
+        <v>26</v>
+      </c>
+      <c r="AL24">
+        <v>65</v>
+      </c>
+      <c r="AM24">
+        <v>640</v>
+      </c>
+      <c r="AN24">
+        <v>21</v>
+      </c>
+      <c r="AO24">
+        <v>570</v>
+      </c>
+      <c r="AP24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ24">
         <v>11.5</v>
       </c>
-      <c r="AD24">
-        <v>60</v>
-      </c>
-      <c r="AE24">
-        <v>980</v>
-      </c>
-      <c r="AF24">
-        <v>18.5</v>
-      </c>
-      <c r="AG24">
-        <v>11.5</v>
-      </c>
-      <c r="AH24">
-        <v>60</v>
-      </c>
-      <c r="AI24">
-        <v>980</v>
-      </c>
-      <c r="AJ24">
-        <v>65</v>
-      </c>
-      <c r="AK24">
-        <v>130</v>
-      </c>
-      <c r="AL24">
-        <v>980</v>
-      </c>
-      <c r="AM24">
-        <v>580</v>
-      </c>
-      <c r="AN24">
-        <v>85</v>
-      </c>
-      <c r="AO24">
-        <v>500</v>
-      </c>
-      <c r="AP24">
+      <c r="AR24">
+        <v>8.6</v>
+      </c>
+      <c r="AS24">
         <v>10</v>
       </c>
-      <c r="AQ24">
-        <v>12</v>
-      </c>
-      <c r="AR24">
-        <v>6.8</v>
-      </c>
-      <c r="AS24">
-        <v>2.82</v>
-      </c>
       <c r="AT24">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV24">
+        <v>15.5</v>
+      </c>
+      <c r="AW24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX24">
         <v>10.5</v>
       </c>
-      <c r="AW24">
-        <v>12</v>
-      </c>
-      <c r="AX24">
-        <v>9</v>
-      </c>
       <c r="AY24">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ24">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA24">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BB24">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BC24">
+        <v>20</v>
+      </c>
+      <c r="BD24">
+        <v>32</v>
+      </c>
+      <c r="BE24">
         <v>10.5</v>
       </c>
-      <c r="BD24">
-        <v>9</v>
-      </c>
-      <c r="BE24">
-        <v>2.76</v>
-      </c>
       <c r="BF24">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="BG24">
-        <v>2.78</v>
+        <v>10</v>
       </c>
       <c r="BH24">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>3.15</v>
+        <v>1.19</v>
       </c>
       <c r="BJ24">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>6.6</v>
+        <v>1.44</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>17</v>
+        <v>1.58</v>
       </c>
       <c r="BN24">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>4</v>
+        <v>1.19</v>
       </c>
       <c r="BP24">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>7.8</v>
+        <v>1.48</v>
       </c>
       <c r="BR24">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>11.5</v>
+        <v>1.69</v>
       </c>
       <c r="BT24">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>7.2</v>
+        <v>1.38</v>
       </c>
       <c r="BV24">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>13</v>
+        <v>1.75</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>14</v>
+        <v>1.75</v>
       </c>
       <c r="BZ24">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>10.5</v>
+        <v>1.68</v>
       </c>
       <c r="CB24" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F25">
+        <v>1.86</v>
+      </c>
+      <c r="G25">
         <v>1.89</v>
       </c>
-      <c r="G25">
-        <v>1.94</v>
-      </c>
       <c r="H25">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I25">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J25">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K25">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="L25">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="M25">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N25">
-        <v>2.96</v>
+        <v>3.75</v>
       </c>
       <c r="O25">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="P25">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="Q25">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="R25">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="S25">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="T25">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="U25">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="V25">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X25">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="Y25">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="Z25">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AA25">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB25">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD25">
         <v>23</v>
       </c>
       <c r="AE25">
-        <v>110</v>
+        <v>980</v>
       </c>
       <c r="AF25">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG25">
         <v>11.5</v>
       </c>
       <c r="AH25">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AI25">
-        <v>120</v>
+        <v>980</v>
       </c>
       <c r="AJ25">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AK25">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="AL25">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM25">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="AN25">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AO25">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AP25">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AQ25">
         <v>12</v>
       </c>
       <c r="AR25">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AS25">
+        <v>3.35</v>
+      </c>
+      <c r="AT25">
+        <v>7.6</v>
+      </c>
+      <c r="AU25">
+        <v>6.4</v>
+      </c>
+      <c r="AV25">
         <v>10.5</v>
       </c>
-      <c r="AT25">
+      <c r="AW25">
+        <v>13</v>
+      </c>
+      <c r="AX25">
+        <v>8</v>
+      </c>
+      <c r="AY25">
+        <v>7.2</v>
+      </c>
+      <c r="AZ25">
+        <v>16</v>
+      </c>
+      <c r="BA25">
+        <v>23</v>
+      </c>
+      <c r="BB25">
+        <v>10.5</v>
+      </c>
+      <c r="BC25">
+        <v>10.5</v>
+      </c>
+      <c r="BD25">
+        <v>9.4</v>
+      </c>
+      <c r="BE25">
+        <v>3.3</v>
+      </c>
+      <c r="BF25">
+        <v>9</v>
+      </c>
+      <c r="BG25">
+        <v>3.3</v>
+      </c>
+      <c r="BH25">
+        <v>3.4</v>
+      </c>
+      <c r="BI25">
+        <v>3.15</v>
+      </c>
+      <c r="BJ25">
+        <v>10</v>
+      </c>
+      <c r="BK25">
+        <v>6.6</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>17</v>
+      </c>
+      <c r="BN25">
+        <v>4.4</v>
+      </c>
+      <c r="BO25">
+        <v>4</v>
+      </c>
+      <c r="BP25">
+        <v>13</v>
+      </c>
+      <c r="BQ25">
+        <v>7.8</v>
+      </c>
+      <c r="BR25">
+        <v>28</v>
+      </c>
+      <c r="BS25">
+        <v>11.5</v>
+      </c>
+      <c r="BT25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU25">
+        <v>7.2</v>
+      </c>
+      <c r="BV25">
+        <v>42</v>
+      </c>
+      <c r="BW25">
+        <v>13</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>14</v>
+      </c>
+      <c r="BZ25">
+        <v>24</v>
+      </c>
+      <c r="CA25">
+        <v>10.5</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26">
+        <v>1.89</v>
+      </c>
+      <c r="G26">
+        <v>1.94</v>
+      </c>
+      <c r="H26">
+        <v>5.1</v>
+      </c>
+      <c r="I26">
+        <v>5.4</v>
+      </c>
+      <c r="J26">
+        <v>3.4</v>
+      </c>
+      <c r="K26">
+        <v>3.55</v>
+      </c>
+      <c r="L26">
+        <v>1.54</v>
+      </c>
+      <c r="M26">
+        <v>1.11</v>
+      </c>
+      <c r="N26">
+        <v>2.96</v>
+      </c>
+      <c r="O26">
+        <v>1.48</v>
+      </c>
+      <c r="P26">
+        <v>1.64</v>
+      </c>
+      <c r="Q26">
+        <v>2.48</v>
+      </c>
+      <c r="R26">
+        <v>1.23</v>
+      </c>
+      <c r="S26">
+        <v>5</v>
+      </c>
+      <c r="T26">
+        <v>2.2</v>
+      </c>
+      <c r="U26">
+        <v>1.79</v>
+      </c>
+      <c r="V26">
+        <v>1.23</v>
+      </c>
+      <c r="W26">
+        <v>2.06</v>
+      </c>
+      <c r="X26">
+        <v>10.5</v>
+      </c>
+      <c r="Y26">
+        <v>14</v>
+      </c>
+      <c r="Z26">
+        <v>42</v>
+      </c>
+      <c r="AA26">
+        <v>170</v>
+      </c>
+      <c r="AB26">
+        <v>6.8</v>
+      </c>
+      <c r="AC26">
+        <v>7.8</v>
+      </c>
+      <c r="AD26">
+        <v>22</v>
+      </c>
+      <c r="AE26">
+        <v>100</v>
+      </c>
+      <c r="AF26">
+        <v>10.5</v>
+      </c>
+      <c r="AG26">
+        <v>11.5</v>
+      </c>
+      <c r="AH26">
+        <v>28</v>
+      </c>
+      <c r="AI26">
+        <v>120</v>
+      </c>
+      <c r="AJ26">
+        <v>23</v>
+      </c>
+      <c r="AK26">
+        <v>25</v>
+      </c>
+      <c r="AL26">
+        <v>55</v>
+      </c>
+      <c r="AM26">
+        <v>200</v>
+      </c>
+      <c r="AN26">
+        <v>21</v>
+      </c>
+      <c r="AO26">
+        <v>160</v>
+      </c>
+      <c r="AP26">
+        <v>9</v>
+      </c>
+      <c r="AQ26">
+        <v>12</v>
+      </c>
+      <c r="AR26">
+        <v>32</v>
+      </c>
+      <c r="AS26">
+        <v>11</v>
+      </c>
+      <c r="AT26">
         <v>6.2</v>
       </c>
-      <c r="AU25">
+      <c r="AU26">
         <v>7</v>
       </c>
-      <c r="AV25">
+      <c r="AV26">
         <v>18</v>
       </c>
-      <c r="AW25">
-        <v>10.5</v>
-      </c>
-      <c r="AX25">
+      <c r="AW26">
+        <v>40</v>
+      </c>
+      <c r="AX26">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY25">
+      <c r="AY26">
         <v>9.6</v>
       </c>
-      <c r="AZ25">
+      <c r="AZ26">
+        <v>11.5</v>
+      </c>
+      <c r="BA26">
         <v>11</v>
       </c>
-      <c r="BA25">
-        <v>10.5</v>
-      </c>
-      <c r="BB25">
+      <c r="BB26">
         <v>18.5</v>
       </c>
-      <c r="BC25">
+      <c r="BC26">
         <v>20</v>
       </c>
-      <c r="BD25">
+      <c r="BD26">
         <v>23</v>
       </c>
-      <c r="BE25">
-        <v>10.5</v>
-      </c>
-      <c r="BF25">
+      <c r="BE26">
+        <v>11</v>
+      </c>
+      <c r="BF26">
         <v>16.5</v>
       </c>
-      <c r="BG25">
-        <v>10.5</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.26</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.21</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.21</v>
-      </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
-        <v>1.48</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.21</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>1.21</v>
-      </c>
-      <c r="BT25">
-        <v>1000</v>
-      </c>
-      <c r="BU25">
-        <v>2.1</v>
-      </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
-        <v>1.21</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
-        <v>1.21</v>
-      </c>
-      <c r="BZ25">
-        <v>1000</v>
-      </c>
-      <c r="CA25">
-        <v>1.21</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>152</v>
+      <c r="BG26">
+        <v>11</v>
+      </c>
+      <c r="BH26">
+        <v>2.88</v>
+      </c>
+      <c r="BI26">
+        <v>2.66</v>
+      </c>
+      <c r="BJ26">
+        <v>12</v>
+      </c>
+      <c r="BK26">
+        <v>9</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>13</v>
+      </c>
+      <c r="BN26">
+        <v>4.3</v>
+      </c>
+      <c r="BO26">
+        <v>3.9</v>
+      </c>
+      <c r="BP26">
+        <v>15.5</v>
+      </c>
+      <c r="BQ26">
+        <v>7.4</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>10</v>
+      </c>
+      <c r="BT26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU26">
+        <v>5.4</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>11</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>12</v>
+      </c>
+      <c r="BZ26">
+        <v>38</v>
+      </c>
+      <c r="CA26">
+        <v>10</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -379,7 +379,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-06 10:38:39</t>
+    <t>2026-10-06 12:50:18</t>
   </si>
 </sst>
 </file>
@@ -973,226 +973,226 @@
         <v>110</v>
       </c>
       <c r="F2">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="G2">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="H2">
-        <v>2.62</v>
+        <v>55</v>
       </c>
       <c r="I2">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>700</v>
       </c>
       <c r="L2">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1.51</v>
+      </c>
+      <c r="Q2">
+        <v>2.2</v>
+      </c>
+      <c r="R2">
+        <v>1.03</v>
+      </c>
+      <c r="S2">
+        <v>17.5</v>
+      </c>
+      <c r="T2">
+        <v>3.7</v>
+      </c>
+      <c r="U2">
         <v>1.19</v>
       </c>
-      <c r="P2">
-        <v>2.58</v>
-      </c>
-      <c r="Q2">
-        <v>1.58</v>
-      </c>
-      <c r="R2">
-        <v>1.64</v>
-      </c>
-      <c r="S2">
-        <v>2.38</v>
-      </c>
-      <c r="T2">
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>50</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
         <v>1.53</v>
       </c>
-      <c r="U2">
-        <v>2.58</v>
-      </c>
-      <c r="V2">
-        <v>1.55</v>
-      </c>
-      <c r="W2">
-        <v>1.6</v>
-      </c>
-      <c r="X2">
-        <v>27</v>
-      </c>
-      <c r="Y2">
-        <v>19</v>
-      </c>
-      <c r="Z2">
-        <v>23</v>
-      </c>
-      <c r="AA2">
+      <c r="AG2">
+        <v>6.8</v>
+      </c>
+      <c r="AH2">
+        <v>970</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>11</v>
+      </c>
+      <c r="AK2">
+        <v>970</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>970</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2">
+        <v>10.5</v>
+      </c>
+      <c r="AR2">
+        <v>10.5</v>
+      </c>
+      <c r="AS2">
+        <v>10.5</v>
+      </c>
+      <c r="AT2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU2">
+        <v>11.5</v>
+      </c>
+      <c r="AV2">
+        <v>10.5</v>
+      </c>
+      <c r="AW2">
+        <v>10.5</v>
+      </c>
+      <c r="AX2">
+        <v>1.42</v>
+      </c>
+      <c r="AY2">
+        <v>4.5</v>
+      </c>
+      <c r="AZ2">
+        <v>38</v>
+      </c>
+      <c r="BA2">
+        <v>120</v>
+      </c>
+      <c r="BB2">
+        <v>6.6</v>
+      </c>
+      <c r="BC2">
+        <v>22</v>
+      </c>
+      <c r="BD2">
+        <v>11.5</v>
+      </c>
+      <c r="BE2">
+        <v>110</v>
+      </c>
+      <c r="BF2">
         <v>44</v>
       </c>
-      <c r="AB2">
-        <v>18.5</v>
-      </c>
-      <c r="AC2">
-        <v>11</v>
-      </c>
-      <c r="AD2">
-        <v>13</v>
-      </c>
-      <c r="AE2">
-        <v>36</v>
-      </c>
-      <c r="AF2">
-        <v>23</v>
-      </c>
-      <c r="AG2">
-        <v>13</v>
-      </c>
-      <c r="AH2">
-        <v>15</v>
-      </c>
-      <c r="AI2">
-        <v>32</v>
-      </c>
-      <c r="AJ2">
-        <v>40</v>
-      </c>
-      <c r="AK2">
-        <v>29</v>
-      </c>
-      <c r="AL2">
-        <v>42</v>
-      </c>
-      <c r="AM2">
-        <v>75</v>
-      </c>
-      <c r="AN2">
-        <v>14.5</v>
-      </c>
-      <c r="AO2">
-        <v>50</v>
-      </c>
-      <c r="AP2">
-        <v>21</v>
-      </c>
-      <c r="AQ2">
-        <v>15</v>
-      </c>
-      <c r="AR2">
-        <v>18.5</v>
-      </c>
-      <c r="AS2">
-        <v>29</v>
-      </c>
-      <c r="AT2">
-        <v>13.5</v>
-      </c>
-      <c r="AU2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV2">
-        <v>11</v>
-      </c>
-      <c r="AW2">
-        <v>20</v>
-      </c>
-      <c r="AX2">
-        <v>18.5</v>
-      </c>
-      <c r="AY2">
+      <c r="BG2">
         <v>10.5</v>
       </c>
-      <c r="AZ2">
-        <v>13</v>
-      </c>
-      <c r="BA2">
-        <v>24</v>
-      </c>
-      <c r="BB2">
-        <v>29</v>
-      </c>
-      <c r="BC2">
-        <v>20</v>
-      </c>
-      <c r="BD2">
-        <v>23</v>
-      </c>
-      <c r="BE2">
-        <v>44</v>
-      </c>
-      <c r="BF2">
-        <v>11.5</v>
-      </c>
-      <c r="BG2">
-        <v>12.5</v>
-      </c>
       <c r="BH2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>121</v>
@@ -1215,226 +1215,226 @@
         <v>111</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G3">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K3">
         <v>3.65</v>
       </c>
       <c r="L3">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P3">
         <v>1.86</v>
       </c>
       <c r="Q3">
+        <v>2.1</v>
+      </c>
+      <c r="R3">
+        <v>1.34</v>
+      </c>
+      <c r="S3">
+        <v>3.75</v>
+      </c>
+      <c r="T3">
+        <v>1.88</v>
+      </c>
+      <c r="U3">
         <v>2.04</v>
       </c>
-      <c r="R3">
-        <v>1.33</v>
-      </c>
-      <c r="S3">
-        <v>3.6</v>
-      </c>
-      <c r="T3">
-        <v>1.78</v>
-      </c>
-      <c r="U3">
-        <v>2.02</v>
-      </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="X3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y3">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA3">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC3">
         <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
+        <v>11</v>
+      </c>
+      <c r="AH3">
+        <v>19.5</v>
+      </c>
+      <c r="AI3">
+        <v>70</v>
+      </c>
+      <c r="AJ3">
+        <v>26</v>
+      </c>
+      <c r="AK3">
+        <v>23</v>
+      </c>
+      <c r="AL3">
+        <v>42</v>
+      </c>
+      <c r="AM3">
+        <v>140</v>
+      </c>
+      <c r="AN3">
+        <v>18</v>
+      </c>
+      <c r="AO3">
+        <v>70</v>
+      </c>
+      <c r="AP3">
+        <v>11.5</v>
+      </c>
+      <c r="AQ3">
         <v>12.5</v>
       </c>
-      <c r="AH3">
-        <v>18.5</v>
-      </c>
-      <c r="AI3">
-        <v>120</v>
-      </c>
-      <c r="AJ3">
-        <v>60</v>
-      </c>
-      <c r="AK3">
-        <v>46</v>
-      </c>
-      <c r="AL3">
-        <v>100</v>
-      </c>
-      <c r="AM3">
-        <v>580</v>
-      </c>
-      <c r="AN3">
-        <v>23</v>
-      </c>
-      <c r="AO3">
-        <v>600</v>
-      </c>
-      <c r="AP3">
+      <c r="AR3">
+        <v>28</v>
+      </c>
+      <c r="AS3">
+        <v>70</v>
+      </c>
+      <c r="AT3">
+        <v>8</v>
+      </c>
+      <c r="AU3">
+        <v>7.4</v>
+      </c>
+      <c r="AV3">
+        <v>14.5</v>
+      </c>
+      <c r="AW3">
+        <v>48</v>
+      </c>
+      <c r="AX3">
         <v>11</v>
       </c>
-      <c r="AQ3">
-        <v>10</v>
-      </c>
-      <c r="AR3">
+      <c r="AY3">
+        <v>9.6</v>
+      </c>
+      <c r="AZ3">
+        <v>17.5</v>
+      </c>
+      <c r="BA3">
+        <v>50</v>
+      </c>
+      <c r="BB3">
+        <v>22</v>
+      </c>
+      <c r="BC3">
         <v>19</v>
       </c>
-      <c r="AS3">
-        <v>26</v>
-      </c>
-      <c r="AT3">
-        <v>8.4</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
-      </c>
-      <c r="AV3">
-        <v>11.5</v>
-      </c>
-      <c r="AW3">
-        <v>21</v>
-      </c>
-      <c r="AX3">
-        <v>13</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
-      <c r="AZ3">
-        <v>15</v>
-      </c>
-      <c r="BA3">
-        <v>22</v>
-      </c>
-      <c r="BB3">
-        <v>18.5</v>
-      </c>
-      <c r="BC3">
-        <v>13.5</v>
-      </c>
       <c r="BD3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BE3">
-        <v>8.800000000000001</v>
+        <v>85</v>
       </c>
       <c r="BF3">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BH3">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI3">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="BJ3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
+        <v>4.1</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>6.4</v>
+      </c>
+      <c r="BN3">
         <v>4.9</v>
       </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN3">
+      <c r="BO3">
+        <v>4.2</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>6.8</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>5.6</v>
+      </c>
+      <c r="BT3">
+        <v>7.4</v>
+      </c>
+      <c r="BU3">
+        <v>6</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>5.8</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>6</v>
+      </c>
+      <c r="BZ3">
+        <v>29</v>
+      </c>
+      <c r="CA3">
         <v>5.5</v>
-      </c>
-      <c r="BO3">
-        <v>4</v>
-      </c>
-      <c r="BP3">
-        <v>19</v>
-      </c>
-      <c r="BQ3">
-        <v>6.4</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>7.6</v>
-      </c>
-      <c r="BT3">
-        <v>6.8</v>
-      </c>
-      <c r="BU3">
-        <v>4.8</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>7.2</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>7.8</v>
-      </c>
-      <c r="BZ3">
-        <v>1000</v>
-      </c>
-      <c r="CA3">
-        <v>7.4</v>
       </c>
       <c r="CB3" t="s">
         <v>121</v>
@@ -1457,37 +1457,37 @@
         <v>112</v>
       </c>
       <c r="F4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I4">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="J4">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K4">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="L4">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="M4">
         <v>1.16</v>
       </c>
       <c r="N4">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q4">
         <v>3.05</v>
@@ -1502,10 +1502,10 @@
         <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W4">
         <v>1.34</v>
@@ -1514,25 +1514,25 @@
         <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF4">
         <v>26</v>
@@ -1541,7 +1541,7 @@
         <v>19</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI4">
         <v>260</v>
@@ -1565,10 +1565,10 @@
         <v>65</v>
       </c>
       <c r="AP4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR4">
         <v>12</v>
@@ -1577,10 +1577,10 @@
         <v>18</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV4">
         <v>11</v>
@@ -1598,85 +1598,85 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH4">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BI4">
         <v>2</v>
       </c>
       <c r="BJ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4">
         <v>7.2</v>
       </c>
       <c r="BO4">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BP4">
         <v>46</v>
       </c>
       <c r="BQ4">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BT4">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
         <v>121</v>
@@ -1941,220 +1941,220 @@
         <v>114</v>
       </c>
       <c r="F6">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="G6">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I6">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="Q6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R6">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="V6">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X6">
         <v>13</v>
       </c>
       <c r="Y6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z6">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AA6">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB6">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AE6">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AF6">
         <v>10.5</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AJ6">
         <v>18</v>
       </c>
       <c r="AK6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM6">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO6">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="AP6">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AR6">
-        <v>5.9</v>
+        <v>40</v>
       </c>
       <c r="AS6">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU6">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
         <v>20</v>
       </c>
       <c r="AW6">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX6">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="BB6">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BC6">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BE6">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG6">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
+        <v>4.7</v>
+      </c>
+      <c r="BN6">
         <v>4.8</v>
       </c>
-      <c r="BN6">
-        <v>4.5</v>
-      </c>
       <c r="BO6">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BP6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ6">
         <v>3.6</v>
       </c>
       <c r="BR6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BT6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BU6">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="BV6">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="BW6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX6">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="BY6">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2183,85 +2183,85 @@
         <v>115</v>
       </c>
       <c r="F7">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="G7">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H7">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I7">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M7">
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y7">
         <v>12</v>
       </c>
       <c r="Z7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA7">
         <v>80</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG7">
         <v>12</v>
@@ -2273,43 +2273,43 @@
         <v>70</v>
       </c>
       <c r="AJ7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM7">
         <v>450</v>
       </c>
       <c r="AN7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO7">
         <v>60</v>
       </c>
       <c r="AP7">
+        <v>10</v>
+      </c>
+      <c r="AQ7">
         <v>10.5</v>
-      </c>
-      <c r="AQ7">
-        <v>10</v>
       </c>
       <c r="AR7">
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AT7">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU7">
         <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW7">
         <v>36</v>
@@ -2321,10 +2321,10 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA7">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7">
         <v>14.5</v>
@@ -2336,19 +2336,19 @@
         <v>36</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF7">
         <v>20</v>
       </c>
       <c r="BG7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BH7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI7">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
@@ -2360,49 +2360,49 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BR7">
         <v>36</v>
       </c>
       <c r="BS7">
+        <v>7.2</v>
+      </c>
+      <c r="BT7">
         <v>7</v>
       </c>
-      <c r="BT7">
-        <v>6.8</v>
-      </c>
       <c r="BU7">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BY7">
+        <v>7.6</v>
+      </c>
+      <c r="BZ7">
+        <v>36</v>
+      </c>
+      <c r="CA7">
         <v>7.2</v>
-      </c>
-      <c r="BZ7">
-        <v>34</v>
-      </c>
-      <c r="CA7">
-        <v>6.8</v>
       </c>
       <c r="CB7" t="s">
         <v>121</v>
@@ -2425,22 +2425,22 @@
         <v>116</v>
       </c>
       <c r="F8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G8">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J8">
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
         <v>1.37</v>
@@ -2449,46 +2449,46 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>1.27</v>
       </c>
       <c r="P8">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q8">
         <v>1.79</v>
       </c>
       <c r="R8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T8">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U8">
         <v>2.22</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W8">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X8">
         <v>17</v>
       </c>
       <c r="Y8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z8">
         <v>26</v>
       </c>
       <c r="AA8">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="AB8">
         <v>12</v>
@@ -2512,16 +2512,16 @@
         <v>17</v>
       </c>
       <c r="AI8">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="AJ8">
         <v>34</v>
       </c>
       <c r="AK8">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AM8">
         <v>580</v>
@@ -2530,7 +2530,7 @@
         <v>19</v>
       </c>
       <c r="AO8">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AP8">
         <v>12.5</v>
@@ -2542,7 +2542,7 @@
         <v>20</v>
       </c>
       <c r="AS8">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="AT8">
         <v>9.6</v>
@@ -2554,7 +2554,7 @@
         <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
@@ -2566,25 +2566,25 @@
         <v>13.5</v>
       </c>
       <c r="BA8">
-        <v>26</v>
+        <v>7.2</v>
       </c>
       <c r="BB8">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BC8">
         <v>18.5</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BE8">
-        <v>55</v>
+        <v>7.8</v>
       </c>
       <c r="BF8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG8">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BH8">
         <v>3.7</v>
@@ -2667,10 +2667,10 @@
         <v>117</v>
       </c>
       <c r="F9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H9">
         <v>6.2</v>
@@ -2682,10 +2682,10 @@
         <v>4.9</v>
       </c>
       <c r="K9">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M9">
         <v>1.03</v>
@@ -2694,10 +2694,10 @@
         <v>5.7</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P9">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q9">
         <v>1.55</v>
@@ -2706,25 +2706,25 @@
         <v>1.65</v>
       </c>
       <c r="S9">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T9">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
         <v>1.17</v>
       </c>
       <c r="W9">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X9">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Y9">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z9">
         <v>85</v>
@@ -2736,7 +2736,7 @@
         <v>12</v>
       </c>
       <c r="AC9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD9">
         <v>32</v>
@@ -2745,10 +2745,10 @@
         <v>190</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9">
         <v>21</v>
@@ -2760,7 +2760,7 @@
         <v>16.5</v>
       </c>
       <c r="AK9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
         <v>34</v>
@@ -2769,7 +2769,7 @@
         <v>320</v>
       </c>
       <c r="AN9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO9">
         <v>85</v>
@@ -2778,25 +2778,25 @@
         <v>21</v>
       </c>
       <c r="AQ9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR9">
         <v>46</v>
       </c>
       <c r="AS9">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AT9">
         <v>9.6</v>
       </c>
       <c r="AU9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW9">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX9">
         <v>9.6</v>
@@ -2805,10 +2805,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB9">
         <v>12.5</v>
@@ -2817,28 +2817,28 @@
         <v>12.5</v>
       </c>
       <c r="BD9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE9">
         <v>55</v>
       </c>
       <c r="BF9">
+        <v>5.1</v>
+      </c>
+      <c r="BG9">
+        <v>40</v>
+      </c>
+      <c r="BH9">
         <v>5.2</v>
       </c>
-      <c r="BG9">
-        <v>38</v>
-      </c>
-      <c r="BH9">
-        <v>5.3</v>
-      </c>
       <c r="BI9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2856,7 +2856,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BR9">
         <v>25</v>
@@ -2868,7 +2868,7 @@
         <v>12</v>
       </c>
       <c r="BU9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV9">
         <v>55</v>
@@ -2883,7 +2883,7 @@
         <v>4.3</v>
       </c>
       <c r="BZ9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA9">
         <v>3.6</v>
@@ -2909,124 +2909,124 @@
         <v>118</v>
       </c>
       <c r="F10">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="G10">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="H10">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L10">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P10">
+        <v>1.65</v>
+      </c>
+      <c r="Q10">
+        <v>2.42</v>
+      </c>
+      <c r="R10">
+        <v>1.24</v>
+      </c>
+      <c r="S10">
+        <v>4.7</v>
+      </c>
+      <c r="T10">
+        <v>1.99</v>
+      </c>
+      <c r="U10">
+        <v>1.88</v>
+      </c>
+      <c r="V10">
+        <v>1.34</v>
+      </c>
+      <c r="W10">
         <v>1.71</v>
       </c>
-      <c r="Q10">
-        <v>2.32</v>
-      </c>
-      <c r="R10">
-        <v>1.26</v>
-      </c>
-      <c r="S10">
-        <v>4.4</v>
-      </c>
-      <c r="T10">
-        <v>1.94</v>
-      </c>
-      <c r="U10">
-        <v>1.92</v>
-      </c>
-      <c r="V10">
-        <v>1.31</v>
-      </c>
-      <c r="W10">
-        <v>1.78</v>
-      </c>
       <c r="X10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA10">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB10">
         <v>8.4</v>
       </c>
       <c r="AC10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE10">
         <v>60</v>
       </c>
       <c r="AF10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI10">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
+        <v>36</v>
+      </c>
+      <c r="AK10">
         <v>32</v>
       </c>
-      <c r="AK10">
+      <c r="AL10">
+        <v>65</v>
+      </c>
+      <c r="AM10">
+        <v>580</v>
+      </c>
+      <c r="AN10">
         <v>29</v>
       </c>
-      <c r="AL10">
-        <v>50</v>
-      </c>
-      <c r="AM10">
-        <v>640</v>
-      </c>
-      <c r="AN10">
-        <v>25</v>
-      </c>
       <c r="AO10">
-        <v>80</v>
+        <v>570</v>
       </c>
       <c r="AP10">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ10">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR10">
         <v>12</v>
       </c>
       <c r="AS10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT10">
         <v>7</v>
@@ -3035,22 +3035,22 @@
         <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX10">
         <v>11.5</v>
       </c>
       <c r="AY10">
+        <v>10</v>
+      </c>
+      <c r="AZ10">
+        <v>18</v>
+      </c>
+      <c r="BA10">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10">
-        <v>17.5</v>
-      </c>
-      <c r="BA10">
-        <v>9.6</v>
       </c>
       <c r="BB10">
         <v>13.5</v>
@@ -3059,76 +3059,76 @@
         <v>12.5</v>
       </c>
       <c r="BD10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE10">
         <v>10</v>
       </c>
       <c r="BF10">
+        <v>8.4</v>
+      </c>
+      <c r="BG10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH10">
+        <v>2.94</v>
+      </c>
+      <c r="BI10">
+        <v>2.64</v>
+      </c>
+      <c r="BJ10">
+        <v>11</v>
+      </c>
+      <c r="BK10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>11</v>
+      </c>
+      <c r="BN10">
+        <v>5.2</v>
+      </c>
+      <c r="BO10">
+        <v>4.3</v>
+      </c>
+      <c r="BP10">
         <v>20</v>
       </c>
-      <c r="BG10">
-        <v>9.6</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.19</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.1</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.19</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>1.19</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
       <c r="BQ10">
-        <v>1.13</v>
+        <v>7.4</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS10">
-        <v>1.69</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU10">
-        <v>1.19</v>
+        <v>5.7</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW10">
-        <v>1.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10">
-        <v>1.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA10">
-        <v>1.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>121</v>
@@ -3151,13 +3151,13 @@
         <v>119</v>
       </c>
       <c r="F11">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G11">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>5.2</v>
@@ -3169,34 +3169,34 @@
         <v>3.9</v>
       </c>
       <c r="L11">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M11">
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O11">
+        <v>1.34</v>
+      </c>
+      <c r="P11">
+        <v>1.97</v>
+      </c>
+      <c r="Q11">
+        <v>2</v>
+      </c>
+      <c r="R11">
         <v>1.36</v>
       </c>
-      <c r="P11">
-        <v>1.94</v>
-      </c>
-      <c r="Q11">
-        <v>2.04</v>
-      </c>
-      <c r="R11">
-        <v>1.35</v>
-      </c>
       <c r="S11">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T11">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
         <v>1.23</v>
@@ -3211,16 +3211,16 @@
         <v>16.5</v>
       </c>
       <c r="Z11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA11">
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="AB11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11">
         <v>19.5</v>
@@ -3235,7 +3235,7 @@
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11">
         <v>160</v>
@@ -3268,10 +3268,10 @@
         <v>29</v>
       </c>
       <c r="AS11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
         <v>7.8</v>
@@ -3280,7 +3280,7 @@
         <v>17</v>
       </c>
       <c r="AW11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3292,43 +3292,43 @@
         <v>18.5</v>
       </c>
       <c r="BA11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD11">
         <v>28</v>
       </c>
       <c r="BE11">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BH11">
         <v>3.35</v>
       </c>
       <c r="BI11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL11">
         <v>140</v>
       </c>
       <c r="BM11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BN11">
         <v>4.4</v>
@@ -3340,7 +3340,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ11">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR11">
         <v>28</v>
@@ -3349,7 +3349,7 @@
         <v>11</v>
       </c>
       <c r="BT11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU11">
         <v>7.4</v>
@@ -3367,10 +3367,10 @@
         <v>14</v>
       </c>
       <c r="BZ11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="s">
         <v>121</v>
@@ -3393,16 +3393,16 @@
         <v>120</v>
       </c>
       <c r="F12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G12">
         <v>1.96</v>
       </c>
       <c r="H12">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J12">
         <v>3.35</v>
@@ -3414,13 +3414,13 @@
         <v>1.55</v>
       </c>
       <c r="M12">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N12">
         <v>2.92</v>
       </c>
       <c r="O12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P12">
         <v>1.62</v>
@@ -3429,10 +3429,10 @@
         <v>2.54</v>
       </c>
       <c r="R12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T12">
         <v>2.22</v>
@@ -3447,16 +3447,16 @@
         <v>2.04</v>
       </c>
       <c r="X12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y12">
         <v>14</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AA12">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB12">
         <v>6.8</v>
@@ -3489,16 +3489,16 @@
         <v>26</v>
       </c>
       <c r="AL12">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AM12">
         <v>220</v>
       </c>
       <c r="AN12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO12">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AP12">
         <v>8.800000000000001</v>
@@ -3507,7 +3507,7 @@
         <v>12</v>
       </c>
       <c r="AR12">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="AS12">
         <v>12.5</v>
@@ -3528,7 +3528,7 @@
         <v>9</v>
       </c>
       <c r="AY12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
         <v>20</v>
@@ -3543,7 +3543,7 @@
         <v>20</v>
       </c>
       <c r="BD12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE12">
         <v>12.5</v>
@@ -3555,7 +3555,7 @@
         <v>12.5</v>
       </c>
       <c r="BH12">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI12">
         <v>2.64</v>
@@ -3564,13 +3564,13 @@
         <v>12</v>
       </c>
       <c r="BK12">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN12">
         <v>4.3</v>
@@ -3582,7 +3582,7 @@
         <v>16</v>
       </c>
       <c r="BQ12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR12">
         <v>40</v>
@@ -3606,7 +3606,7 @@
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ12">
         <v>40</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
   <si>
     <t>League</t>
   </si>
@@ -256,18 +256,15 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Slovenian 2 SNL</t>
+    <t>Argentinian Primera C</t>
+  </si>
+  <si>
+    <t>Algerian Ligue 1</t>
   </si>
   <si>
     <t>Peruvian Segunda Division</t>
   </si>
   <si>
-    <t>Argentinian Primera C</t>
-  </si>
-  <si>
-    <t>Algerian Ligue 1</t>
-  </si>
-  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -280,12 +277,6 @@
     <t>2026-10-06</t>
   </si>
   <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>16:00:00</t>
-  </si>
-  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -313,12 +304,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>NK Bilje</t>
-  </si>
-  <si>
-    <t>Pirata FC</t>
-  </si>
-  <si>
     <t>CA Claypole</t>
   </si>
   <si>
@@ -346,12 +331,6 @@
     <t>Goias</t>
   </si>
   <si>
-    <t>NK Jadran Dekani</t>
-  </si>
-  <si>
-    <t>Ayacucho Futbol Club</t>
-  </si>
-  <si>
     <t>Deportivo Espanol</t>
   </si>
   <si>
@@ -379,7 +358,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-06 12:50:18</t>
+    <t>2026-10-06 15:02:08</t>
   </si>
 </sst>
 </file>
@@ -711,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -961,34 +940,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F2">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="G2">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="H2">
-        <v>55</v>
+        <v>3.45</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>2.24</v>
       </c>
       <c r="K2">
-        <v>700</v>
+        <v>2.32</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1003,28 +982,28 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>1.51</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="R2">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="S2">
-        <v>17.5</v>
+        <v>2.96</v>
       </c>
       <c r="T2">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>50</v>
+        <v>1.37</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1042,97 +1021,97 @@
         <v>1000</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF2">
-        <v>1.53</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AH2">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>970</v>
+        <v>75</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP2">
+        <v>13.5</v>
+      </c>
+      <c r="AQ2">
+        <v>13.5</v>
+      </c>
+      <c r="AR2">
+        <v>13.5</v>
+      </c>
+      <c r="AS2">
+        <v>13.5</v>
+      </c>
+      <c r="AT2">
+        <v>13.5</v>
+      </c>
+      <c r="AU2">
+        <v>3.05</v>
+      </c>
+      <c r="AV2">
+        <v>5.1</v>
+      </c>
+      <c r="AW2">
+        <v>18.5</v>
+      </c>
+      <c r="AX2">
+        <v>13.5</v>
+      </c>
+      <c r="AY2">
+        <v>5.2</v>
+      </c>
+      <c r="AZ2">
+        <v>7.8</v>
+      </c>
+      <c r="BA2">
+        <v>26</v>
+      </c>
+      <c r="BB2">
+        <v>13.5</v>
+      </c>
+      <c r="BC2">
+        <v>18</v>
+      </c>
+      <c r="BD2">
+        <v>26</v>
+      </c>
+      <c r="BE2">
+        <v>12</v>
+      </c>
+      <c r="BF2">
         <v>11.5</v>
       </c>
-      <c r="AQ2">
-        <v>10.5</v>
-      </c>
-      <c r="AR2">
-        <v>10.5</v>
-      </c>
-      <c r="AS2">
-        <v>10.5</v>
-      </c>
-      <c r="AT2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU2">
+      <c r="BG2">
         <v>11.5</v>
-      </c>
-      <c r="AV2">
-        <v>10.5</v>
-      </c>
-      <c r="AW2">
-        <v>10.5</v>
-      </c>
-      <c r="AX2">
-        <v>1.42</v>
-      </c>
-      <c r="AY2">
-        <v>4.5</v>
-      </c>
-      <c r="AZ2">
-        <v>38</v>
-      </c>
-      <c r="BA2">
-        <v>120</v>
-      </c>
-      <c r="BB2">
-        <v>6.6</v>
-      </c>
-      <c r="BC2">
-        <v>22</v>
-      </c>
-      <c r="BD2">
-        <v>11.5</v>
-      </c>
-      <c r="BE2">
-        <v>110</v>
-      </c>
-      <c r="BF2">
-        <v>44</v>
-      </c>
-      <c r="BG2">
-        <v>10.5</v>
       </c>
       <c r="BH2">
         <v>0</v>
@@ -1195,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1203,241 +1182,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F3">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="G3">
-        <v>2.16</v>
+        <v>600</v>
       </c>
       <c r="H3">
-        <v>3.9</v>
+        <v>1.12</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>870</v>
       </c>
       <c r="J3">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="K3">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L3">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="O3">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P3">
-        <v>1.86</v>
+        <v>1.02</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R3">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="S3">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="T3">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>15.5</v>
+        <v>1.55</v>
       </c>
       <c r="BG3">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1445,241 +1424,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F4">
+        <v>1.72</v>
+      </c>
+      <c r="G4">
+        <v>1.74</v>
+      </c>
+      <c r="H4">
+        <v>5.4</v>
+      </c>
+      <c r="I4">
+        <v>5.7</v>
+      </c>
+      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4">
+        <v>4.3</v>
+      </c>
+      <c r="L4">
+        <v>1.43</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>3.35</v>
+      </c>
+      <c r="O4">
+        <v>1.37</v>
+      </c>
+      <c r="P4">
+        <v>1.84</v>
+      </c>
+      <c r="Q4">
+        <v>2.06</v>
+      </c>
+      <c r="R4">
+        <v>1.31</v>
+      </c>
+      <c r="S4">
+        <v>3.9</v>
+      </c>
+      <c r="T4">
+        <v>2.08</v>
+      </c>
+      <c r="U4">
+        <v>1.83</v>
+      </c>
+      <c r="V4">
+        <v>1.21</v>
+      </c>
+      <c r="W4">
+        <v>2.32</v>
+      </c>
+      <c r="X4">
+        <v>14</v>
+      </c>
+      <c r="Y4">
+        <v>18</v>
+      </c>
+      <c r="Z4">
+        <v>55</v>
+      </c>
+      <c r="AA4">
+        <v>180</v>
+      </c>
+      <c r="AB4">
+        <v>8</v>
+      </c>
+      <c r="AC4">
+        <v>9</v>
+      </c>
+      <c r="AD4">
+        <v>24</v>
+      </c>
+      <c r="AE4">
+        <v>110</v>
+      </c>
+      <c r="AF4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG4">
+        <v>11</v>
+      </c>
+      <c r="AH4">
+        <v>26</v>
+      </c>
+      <c r="AI4">
+        <v>110</v>
+      </c>
+      <c r="AJ4">
+        <v>18.5</v>
+      </c>
+      <c r="AK4">
+        <v>21</v>
+      </c>
+      <c r="AL4">
+        <v>50</v>
+      </c>
+      <c r="AM4">
+        <v>580</v>
+      </c>
+      <c r="AN4">
+        <v>12.5</v>
+      </c>
+      <c r="AO4">
+        <v>160</v>
+      </c>
+      <c r="AP4">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4">
+        <v>15</v>
+      </c>
+      <c r="AR4">
+        <v>42</v>
+      </c>
+      <c r="AS4">
+        <v>80</v>
+      </c>
+      <c r="AT4">
+        <v>7</v>
+      </c>
+      <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>20</v>
+      </c>
+      <c r="AW4">
+        <v>65</v>
+      </c>
+      <c r="AX4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY4">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4">
+        <v>21</v>
+      </c>
+      <c r="BA4">
+        <v>50</v>
+      </c>
+      <c r="BB4">
+        <v>15</v>
+      </c>
+      <c r="BC4">
+        <v>17</v>
+      </c>
+      <c r="BD4">
+        <v>36</v>
+      </c>
+      <c r="BE4">
+        <v>70</v>
+      </c>
+      <c r="BF4">
+        <v>10.5</v>
+      </c>
+      <c r="BG4">
+        <v>11</v>
+      </c>
+      <c r="BH4">
+        <v>3.75</v>
+      </c>
+      <c r="BI4">
+        <v>2.82</v>
+      </c>
+      <c r="BJ4">
+        <v>13.5</v>
+      </c>
+      <c r="BK4">
+        <v>4.1</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>4.8</v>
+      </c>
+      <c r="BN4">
+        <v>4.7</v>
+      </c>
+      <c r="BO4">
         <v>3.45</v>
       </c>
-      <c r="G4">
-        <v>3.9</v>
-      </c>
-      <c r="H4">
-        <v>2.52</v>
-      </c>
-      <c r="I4">
-        <v>2.72</v>
-      </c>
-      <c r="J4">
-        <v>2.74</v>
-      </c>
-      <c r="K4">
-        <v>2.92</v>
-      </c>
-      <c r="L4">
-        <v>1.75</v>
-      </c>
-      <c r="M4">
-        <v>1.16</v>
-      </c>
-      <c r="N4">
-        <v>2.32</v>
-      </c>
-      <c r="O4">
-        <v>1.67</v>
-      </c>
-      <c r="P4">
-        <v>1.41</v>
-      </c>
-      <c r="Q4">
-        <v>3.05</v>
-      </c>
-      <c r="R4">
-        <v>1.13</v>
-      </c>
-      <c r="S4">
-        <v>6.8</v>
-      </c>
-      <c r="T4">
-        <v>2.28</v>
-      </c>
-      <c r="U4">
-        <v>1.65</v>
-      </c>
-      <c r="V4">
-        <v>1.58</v>
-      </c>
-      <c r="W4">
-        <v>1.34</v>
-      </c>
-      <c r="X4">
-        <v>7.4</v>
-      </c>
-      <c r="Y4">
-        <v>7.4</v>
-      </c>
-      <c r="Z4">
-        <v>15.5</v>
-      </c>
-      <c r="AA4">
-        <v>46</v>
-      </c>
-      <c r="AB4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC4">
-        <v>7.6</v>
-      </c>
-      <c r="AD4">
-        <v>14.5</v>
-      </c>
-      <c r="AE4">
-        <v>48</v>
-      </c>
-      <c r="AF4">
-        <v>26</v>
-      </c>
-      <c r="AG4">
-        <v>19</v>
-      </c>
-      <c r="AH4">
-        <v>30</v>
-      </c>
-      <c r="AI4">
-        <v>260</v>
-      </c>
-      <c r="AJ4">
-        <v>260</v>
-      </c>
-      <c r="AK4">
-        <v>170</v>
-      </c>
-      <c r="AL4">
-        <v>350</v>
-      </c>
-      <c r="AM4">
-        <v>500</v>
-      </c>
-      <c r="AN4">
-        <v>600</v>
-      </c>
-      <c r="AO4">
-        <v>65</v>
-      </c>
-      <c r="AP4">
-        <v>5.7</v>
-      </c>
-      <c r="AQ4">
-        <v>5.8</v>
-      </c>
-      <c r="AR4">
-        <v>12</v>
-      </c>
-      <c r="AS4">
-        <v>18</v>
-      </c>
-      <c r="AT4">
-        <v>7.6</v>
-      </c>
-      <c r="AU4">
-        <v>5.9</v>
-      </c>
-      <c r="AV4">
-        <v>11</v>
-      </c>
-      <c r="AW4">
-        <v>6.8</v>
-      </c>
-      <c r="AX4">
-        <v>18.5</v>
-      </c>
-      <c r="AY4">
+      <c r="BP4">
         <v>14</v>
       </c>
-      <c r="AZ4">
-        <v>15</v>
-      </c>
-      <c r="BA4">
-        <v>7.2</v>
-      </c>
-      <c r="BB4">
-        <v>7.2</v>
-      </c>
-      <c r="BC4">
-        <v>7</v>
-      </c>
-      <c r="BD4">
-        <v>7.2</v>
-      </c>
-      <c r="BE4">
-        <v>7.6</v>
-      </c>
-      <c r="BF4">
-        <v>7.4</v>
-      </c>
-      <c r="BG4">
-        <v>7</v>
-      </c>
-      <c r="BH4">
-        <v>2.42</v>
-      </c>
-      <c r="BI4">
-        <v>2</v>
-      </c>
-      <c r="BJ4">
-        <v>14.5</v>
-      </c>
-      <c r="BK4">
-        <v>6</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN4">
-        <v>7.2</v>
-      </c>
-      <c r="BO4">
-        <v>5.6</v>
-      </c>
-      <c r="BP4">
-        <v>46</v>
-      </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="BT4">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU4">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BV4">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1687,483 +1666,483 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="G5">
-        <v>600</v>
+        <v>2.36</v>
       </c>
       <c r="H5">
-        <v>1.12</v>
+        <v>3.5</v>
       </c>
       <c r="I5">
-        <v>870</v>
+        <v>3.65</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P5">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R5">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO5">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>1.55</v>
+        <v>20</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F6">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="G6">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="H6">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="I6">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
         <v>1.4</v>
       </c>
       <c r="M6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
+        <v>3.85</v>
+      </c>
+      <c r="O6">
+        <v>1.3</v>
+      </c>
+      <c r="P6">
+        <v>2.02</v>
+      </c>
+      <c r="Q6">
+        <v>1.87</v>
+      </c>
+      <c r="R6">
+        <v>1.38</v>
+      </c>
+      <c r="S6">
         <v>3.25</v>
       </c>
-      <c r="O6">
-        <v>1.38</v>
-      </c>
-      <c r="P6">
-        <v>1.72</v>
-      </c>
-      <c r="Q6">
-        <v>2.08</v>
-      </c>
-      <c r="R6">
-        <v>1.28</v>
-      </c>
-      <c r="S6">
-        <v>3.95</v>
-      </c>
       <c r="T6">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="U6">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="V6">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>2.26</v>
+        <v>1.67</v>
       </c>
       <c r="X6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y6">
+        <v>14.5</v>
+      </c>
+      <c r="Z6">
+        <v>26</v>
+      </c>
+      <c r="AA6">
+        <v>130</v>
+      </c>
+      <c r="AB6">
+        <v>11.5</v>
+      </c>
+      <c r="AC6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>14.5</v>
+      </c>
+      <c r="AE6">
+        <v>46</v>
+      </c>
+      <c r="AF6">
+        <v>17.5</v>
+      </c>
+      <c r="AG6">
+        <v>11.5</v>
+      </c>
+      <c r="AH6">
+        <v>17</v>
+      </c>
+      <c r="AI6">
+        <v>120</v>
+      </c>
+      <c r="AJ6">
+        <v>38</v>
+      </c>
+      <c r="AK6">
+        <v>36</v>
+      </c>
+      <c r="AL6">
+        <v>65</v>
+      </c>
+      <c r="AM6">
+        <v>580</v>
+      </c>
+      <c r="AN6">
+        <v>20</v>
+      </c>
+      <c r="AO6">
+        <v>500</v>
+      </c>
+      <c r="AP6">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6">
+        <v>11.5</v>
+      </c>
+      <c r="AR6">
+        <v>20</v>
+      </c>
+      <c r="AS6">
+        <v>36</v>
+      </c>
+      <c r="AT6">
+        <v>9.6</v>
+      </c>
+      <c r="AU6">
+        <v>7</v>
+      </c>
+      <c r="AV6">
+        <v>11.5</v>
+      </c>
+      <c r="AW6">
+        <v>23</v>
+      </c>
+      <c r="AX6">
+        <v>12.5</v>
+      </c>
+      <c r="AY6">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6">
+        <v>13.5</v>
+      </c>
+      <c r="BA6">
+        <v>30</v>
+      </c>
+      <c r="BB6">
+        <v>23</v>
+      </c>
+      <c r="BC6">
+        <v>20</v>
+      </c>
+      <c r="BD6">
+        <v>27</v>
+      </c>
+      <c r="BE6">
+        <v>60</v>
+      </c>
+      <c r="BF6">
+        <v>14.5</v>
+      </c>
+      <c r="BG6">
         <v>19</v>
       </c>
-      <c r="Z6">
-        <v>60</v>
-      </c>
-      <c r="AA6">
-        <v>180</v>
-      </c>
-      <c r="AB6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC6">
+      <c r="BH6">
+        <v>3.6</v>
+      </c>
+      <c r="BI6">
+        <v>2.86</v>
+      </c>
+      <c r="BJ6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK6">
+        <v>5</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
         <v>9.4</v>
       </c>
-      <c r="AD6">
-        <v>26</v>
-      </c>
-      <c r="AE6">
-        <v>100</v>
-      </c>
-      <c r="AF6">
-        <v>10.5</v>
-      </c>
-      <c r="AG6">
-        <v>10.5</v>
-      </c>
-      <c r="AH6">
-        <v>28</v>
-      </c>
-      <c r="AI6">
-        <v>260</v>
-      </c>
-      <c r="AJ6">
-        <v>18</v>
-      </c>
-      <c r="AK6">
-        <v>22</v>
-      </c>
-      <c r="AL6">
-        <v>48</v>
-      </c>
-      <c r="AM6">
-        <v>500</v>
-      </c>
-      <c r="AN6">
-        <v>14</v>
-      </c>
-      <c r="AO6">
-        <v>150</v>
-      </c>
-      <c r="AP6">
-        <v>10.5</v>
-      </c>
-      <c r="AQ6">
-        <v>15.5</v>
-      </c>
-      <c r="AR6">
-        <v>40</v>
-      </c>
-      <c r="AS6">
-        <v>9</v>
-      </c>
-      <c r="AT6">
+      <c r="BN6">
+        <v>5.5</v>
+      </c>
+      <c r="BO6">
+        <v>4.2</v>
+      </c>
+      <c r="BP6">
+        <v>18.5</v>
+      </c>
+      <c r="BQ6">
         <v>6.6</v>
       </c>
-      <c r="AU6">
-        <v>7.8</v>
-      </c>
-      <c r="AV6">
-        <v>20</v>
-      </c>
-      <c r="AW6">
-        <v>9.6</v>
-      </c>
-      <c r="AX6">
-        <v>7.8</v>
-      </c>
-      <c r="AY6">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6">
-        <v>18.5</v>
-      </c>
-      <c r="BA6">
-        <v>44</v>
-      </c>
-      <c r="BB6">
-        <v>15</v>
-      </c>
-      <c r="BC6">
-        <v>16</v>
-      </c>
-      <c r="BD6">
-        <v>38</v>
-      </c>
-      <c r="BE6">
-        <v>65</v>
-      </c>
-      <c r="BF6">
-        <v>11</v>
-      </c>
-      <c r="BG6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH6">
-        <v>3.75</v>
-      </c>
-      <c r="BI6">
-        <v>2.78</v>
-      </c>
-      <c r="BJ6">
-        <v>13.5</v>
-      </c>
-      <c r="BK6">
-        <v>3.8</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>4.7</v>
-      </c>
-      <c r="BN6">
-        <v>4.8</v>
-      </c>
-      <c r="BO6">
-        <v>3.5</v>
-      </c>
-      <c r="BP6">
-        <v>14.5</v>
-      </c>
-      <c r="BQ6">
-        <v>3.6</v>
-      </c>
       <c r="BR6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS6">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT6">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="BU6">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV6">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="BW6">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BX6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2171,483 +2150,483 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F7">
-        <v>2.26</v>
+        <v>1.52</v>
       </c>
       <c r="G7">
+        <v>1.55</v>
+      </c>
+      <c r="H7">
+        <v>6.2</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>4.8</v>
+      </c>
+      <c r="K7">
+        <v>5.2</v>
+      </c>
+      <c r="L7">
+        <v>1.27</v>
+      </c>
+      <c r="M7">
+        <v>1.03</v>
+      </c>
+      <c r="N7">
+        <v>6</v>
+      </c>
+      <c r="O7">
+        <v>1.18</v>
+      </c>
+      <c r="P7">
+        <v>2.68</v>
+      </c>
+      <c r="Q7">
+        <v>1.54</v>
+      </c>
+      <c r="R7">
+        <v>1.67</v>
+      </c>
+      <c r="S7">
         <v>2.36</v>
       </c>
-      <c r="H7">
-        <v>3.55</v>
-      </c>
-      <c r="I7">
-        <v>3.75</v>
-      </c>
-      <c r="J7">
-        <v>3.3</v>
-      </c>
-      <c r="K7">
-        <v>3.55</v>
-      </c>
-      <c r="L7">
-        <v>1.48</v>
-      </c>
-      <c r="M7">
-        <v>1.09</v>
-      </c>
-      <c r="N7">
-        <v>3.2</v>
-      </c>
-      <c r="O7">
-        <v>1.41</v>
-      </c>
-      <c r="P7">
-        <v>1.75</v>
-      </c>
-      <c r="Q7">
-        <v>2.24</v>
-      </c>
-      <c r="R7">
-        <v>1.28</v>
-      </c>
-      <c r="S7">
-        <v>4.2</v>
-      </c>
       <c r="T7">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="U7">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
-        <v>1.74</v>
+        <v>2.78</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="Y7">
+        <v>36</v>
+      </c>
+      <c r="Z7">
+        <v>80</v>
+      </c>
+      <c r="AA7">
+        <v>700</v>
+      </c>
+      <c r="AB7">
         <v>12</v>
       </c>
-      <c r="Z7">
-        <v>26</v>
-      </c>
-      <c r="AA7">
+      <c r="AC7">
+        <v>12.5</v>
+      </c>
+      <c r="AD7">
+        <v>32</v>
+      </c>
+      <c r="AE7">
+        <v>190</v>
+      </c>
+      <c r="AF7">
+        <v>12</v>
+      </c>
+      <c r="AG7">
+        <v>11</v>
+      </c>
+      <c r="AH7">
+        <v>21</v>
+      </c>
+      <c r="AI7">
         <v>80</v>
       </c>
-      <c r="AB7">
+      <c r="AJ7">
+        <v>16.5</v>
+      </c>
+      <c r="AK7">
+        <v>15.5</v>
+      </c>
+      <c r="AL7">
+        <v>34</v>
+      </c>
+      <c r="AM7">
+        <v>320</v>
+      </c>
+      <c r="AN7">
+        <v>6.2</v>
+      </c>
+      <c r="AO7">
+        <v>85</v>
+      </c>
+      <c r="AP7">
+        <v>21</v>
+      </c>
+      <c r="AQ7">
+        <v>24</v>
+      </c>
+      <c r="AR7">
+        <v>46</v>
+      </c>
+      <c r="AS7">
+        <v>70</v>
+      </c>
+      <c r="AT7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU7">
+        <v>10</v>
+      </c>
+      <c r="AV7">
+        <v>21</v>
+      </c>
+      <c r="AW7">
+        <v>50</v>
+      </c>
+      <c r="AX7">
+        <v>9.6</v>
+      </c>
+      <c r="AY7">
         <v>8.6</v>
       </c>
-      <c r="AC7">
-        <v>7.8</v>
-      </c>
-      <c r="AD7">
+      <c r="AZ7">
         <v>16</v>
       </c>
-      <c r="AE7">
-        <v>60</v>
-      </c>
-      <c r="AF7">
-        <v>14.5</v>
-      </c>
-      <c r="AG7">
+      <c r="BA7">
+        <v>40</v>
+      </c>
+      <c r="BB7">
+        <v>12.5</v>
+      </c>
+      <c r="BC7">
+        <v>12.5</v>
+      </c>
+      <c r="BD7">
+        <v>22</v>
+      </c>
+      <c r="BE7">
+        <v>55</v>
+      </c>
+      <c r="BF7">
+        <v>5</v>
+      </c>
+      <c r="BG7">
+        <v>40</v>
+      </c>
+      <c r="BH7">
+        <v>5.2</v>
+      </c>
+      <c r="BI7">
+        <v>3.5</v>
+      </c>
+      <c r="BJ7">
         <v>12</v>
       </c>
-      <c r="AH7">
-        <v>20</v>
-      </c>
-      <c r="AI7">
-        <v>70</v>
-      </c>
-      <c r="AJ7">
-        <v>38</v>
-      </c>
-      <c r="AK7">
-        <v>32</v>
-      </c>
-      <c r="AL7">
-        <v>46</v>
-      </c>
-      <c r="AM7">
-        <v>450</v>
-      </c>
-      <c r="AN7">
-        <v>24</v>
-      </c>
-      <c r="AO7">
-        <v>60</v>
-      </c>
-      <c r="AP7">
-        <v>10</v>
-      </c>
-      <c r="AQ7">
-        <v>10.5</v>
-      </c>
-      <c r="AR7">
-        <v>20</v>
-      </c>
-      <c r="AS7">
-        <v>30</v>
-      </c>
-      <c r="AT7">
-        <v>7.6</v>
-      </c>
-      <c r="AU7">
-        <v>6.8</v>
-      </c>
-      <c r="AV7">
-        <v>13</v>
-      </c>
-      <c r="AW7">
-        <v>36</v>
-      </c>
-      <c r="AX7">
-        <v>12</v>
-      </c>
-      <c r="AY7">
-        <v>10</v>
-      </c>
-      <c r="AZ7">
-        <v>17</v>
-      </c>
-      <c r="BA7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB7">
-        <v>14.5</v>
-      </c>
-      <c r="BC7">
-        <v>15.5</v>
-      </c>
-      <c r="BD7">
-        <v>36</v>
-      </c>
-      <c r="BE7">
-        <v>10</v>
-      </c>
-      <c r="BF7">
-        <v>20</v>
-      </c>
-      <c r="BG7">
-        <v>9</v>
-      </c>
-      <c r="BH7">
-        <v>3.4</v>
-      </c>
-      <c r="BI7">
-        <v>2.82</v>
-      </c>
-      <c r="BJ7">
-        <v>10.5</v>
-      </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="BN7">
         <v>5.2</v>
       </c>
       <c r="BO7">
+        <v>3.45</v>
+      </c>
+      <c r="BP7">
+        <v>11</v>
+      </c>
+      <c r="BQ7">
+        <v>3.35</v>
+      </c>
+      <c r="BR7">
+        <v>24</v>
+      </c>
+      <c r="BS7">
+        <v>4</v>
+      </c>
+      <c r="BT7">
+        <v>12</v>
+      </c>
+      <c r="BU7">
+        <v>3.45</v>
+      </c>
+      <c r="BV7">
+        <v>55</v>
+      </c>
+      <c r="BW7">
         <v>4.5</v>
       </c>
-      <c r="BP7">
-        <v>18.5</v>
-      </c>
-      <c r="BQ7">
-        <v>6</v>
-      </c>
-      <c r="BR7">
-        <v>36</v>
-      </c>
-      <c r="BS7">
-        <v>7.2</v>
-      </c>
-      <c r="BT7">
-        <v>7</v>
-      </c>
-      <c r="BU7">
-        <v>6</v>
-      </c>
-      <c r="BV7">
-        <v>34</v>
-      </c>
-      <c r="BW7">
-        <v>7</v>
-      </c>
       <c r="BX7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY7">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ7">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="CA7">
-        <v>7.2</v>
+        <v>3.65</v>
       </c>
       <c r="CB7" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F8">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G8">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="H8">
+        <v>3.7</v>
+      </c>
+      <c r="I8">
+        <v>3.9</v>
+      </c>
+      <c r="J8">
+        <v>3.1</v>
+      </c>
+      <c r="K8">
+        <v>3.3</v>
+      </c>
+      <c r="L8">
+        <v>1.52</v>
+      </c>
+      <c r="M8">
+        <v>1.11</v>
+      </c>
+      <c r="N8">
         <v>3</v>
       </c>
-      <c r="I8">
-        <v>3.4</v>
-      </c>
-      <c r="J8">
-        <v>3.35</v>
-      </c>
-      <c r="K8">
-        <v>3.9</v>
-      </c>
-      <c r="L8">
-        <v>1.37</v>
-      </c>
-      <c r="M8">
-        <v>1.06</v>
-      </c>
-      <c r="N8">
-        <v>4</v>
-      </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="P8">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="Q8">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="R8">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="V8">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W8">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="X8">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="Y8">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Z8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA8">
-        <v>310</v>
+        <v>80</v>
       </c>
       <c r="AB8">
+        <v>8.4</v>
+      </c>
+      <c r="AC8">
+        <v>7.6</v>
+      </c>
+      <c r="AD8">
+        <v>16</v>
+      </c>
+      <c r="AE8">
+        <v>55</v>
+      </c>
+      <c r="AF8">
+        <v>14</v>
+      </c>
+      <c r="AG8">
         <v>12</v>
       </c>
-      <c r="AC8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8">
-        <v>14.5</v>
-      </c>
-      <c r="AE8">
-        <v>85</v>
-      </c>
-      <c r="AF8">
-        <v>17.5</v>
-      </c>
-      <c r="AG8">
-        <v>11.5</v>
-      </c>
       <c r="AH8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>420</v>
+        <v>75</v>
       </c>
       <c r="AJ8">
         <v>34</v>
       </c>
       <c r="AK8">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AL8">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN8">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AP8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ8">
+        <v>10</v>
+      </c>
+      <c r="AR8">
+        <v>21</v>
+      </c>
+      <c r="AS8">
+        <v>48</v>
+      </c>
+      <c r="AT8">
+        <v>7.4</v>
+      </c>
+      <c r="AU8">
+        <v>6.8</v>
+      </c>
+      <c r="AV8">
+        <v>13.5</v>
+      </c>
+      <c r="AW8">
+        <v>46</v>
+      </c>
+      <c r="AX8">
+        <v>12</v>
+      </c>
+      <c r="AY8">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8">
+        <v>18.5</v>
+      </c>
+      <c r="BA8">
+        <v>40</v>
+      </c>
+      <c r="BB8">
+        <v>23</v>
+      </c>
+      <c r="BC8">
+        <v>26</v>
+      </c>
+      <c r="BD8">
+        <v>42</v>
+      </c>
+      <c r="BE8">
         <v>12.5</v>
       </c>
-      <c r="AQ8">
-        <v>11.5</v>
-      </c>
-      <c r="AR8">
+      <c r="BF8">
+        <v>23</v>
+      </c>
+      <c r="BG8">
+        <v>28</v>
+      </c>
+      <c r="BH8">
+        <v>2.94</v>
+      </c>
+      <c r="BI8">
+        <v>2.64</v>
+      </c>
+      <c r="BJ8">
+        <v>11</v>
+      </c>
+      <c r="BK8">
+        <v>5.7</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>11</v>
+      </c>
+      <c r="BN8">
+        <v>5.2</v>
+      </c>
+      <c r="BO8">
+        <v>4.3</v>
+      </c>
+      <c r="BP8">
         <v>20</v>
       </c>
-      <c r="AS8">
-        <v>7.6</v>
-      </c>
-      <c r="AT8">
-        <v>9.6</v>
-      </c>
-      <c r="AU8">
+      <c r="BQ8">
+        <v>7.4</v>
+      </c>
+      <c r="BR8">
+        <v>40</v>
+      </c>
+      <c r="BS8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT8">
         <v>7</v>
       </c>
-      <c r="AV8">
-        <v>11.5</v>
-      </c>
-      <c r="AW8">
-        <v>13.5</v>
-      </c>
-      <c r="AX8">
-        <v>12.5</v>
-      </c>
-      <c r="AY8">
-        <v>8.4</v>
-      </c>
-      <c r="AZ8">
-        <v>13.5</v>
-      </c>
-      <c r="BA8">
-        <v>7.2</v>
-      </c>
-      <c r="BB8">
-        <v>12.5</v>
-      </c>
-      <c r="BC8">
-        <v>18.5</v>
-      </c>
-      <c r="BD8">
-        <v>14.5</v>
-      </c>
-      <c r="BE8">
-        <v>7.8</v>
-      </c>
-      <c r="BF8">
-        <v>14.5</v>
-      </c>
-      <c r="BG8">
-        <v>6.8</v>
-      </c>
-      <c r="BH8">
-        <v>3.7</v>
-      </c>
-      <c r="BI8">
-        <v>2.92</v>
-      </c>
-      <c r="BJ8">
+      <c r="BU8">
+        <v>5.7</v>
+      </c>
+      <c r="BV8">
+        <v>36</v>
+      </c>
+      <c r="BW8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX8">
+        <v>55</v>
+      </c>
+      <c r="BY8">
         <v>9.800000000000001</v>
       </c>
-      <c r="BK8">
-        <v>4.8</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN8">
-        <v>5.6</v>
-      </c>
-      <c r="BO8">
-        <v>4.2</v>
-      </c>
-      <c r="BP8">
-        <v>18</v>
-      </c>
-      <c r="BQ8">
-        <v>6.2</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>7.4</v>
-      </c>
-      <c r="BT8">
-        <v>6.8</v>
-      </c>
-      <c r="BU8">
-        <v>5.1</v>
-      </c>
-      <c r="BV8">
-        <v>1000</v>
-      </c>
-      <c r="BW8">
-        <v>7</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>7.6</v>
-      </c>
       <c r="BZ8">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB8" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2655,967 +2634,483 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F9">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="H9">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="J9">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="K9">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="O9">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="P9">
-        <v>2.66</v>
+        <v>1.97</v>
       </c>
       <c r="Q9">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="T9">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="U9">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="V9">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="W9">
-        <v>2.78</v>
+        <v>2.16</v>
       </c>
       <c r="X9">
-        <v>40</v>
+        <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>36</v>
+        <v>16.5</v>
       </c>
       <c r="Z9">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AA9">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AB9">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AC9">
+        <v>8.6</v>
+      </c>
+      <c r="AD9">
+        <v>19.5</v>
+      </c>
+      <c r="AE9">
+        <v>70</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+      <c r="AH9">
+        <v>20</v>
+      </c>
+      <c r="AI9">
+        <v>75</v>
+      </c>
+      <c r="AJ9">
+        <v>19.5</v>
+      </c>
+      <c r="AK9">
+        <v>19.5</v>
+      </c>
+      <c r="AL9">
+        <v>38</v>
+      </c>
+      <c r="AM9">
+        <v>120</v>
+      </c>
+      <c r="AN9">
         <v>12.5</v>
       </c>
-      <c r="AD9">
+      <c r="AO9">
+        <v>90</v>
+      </c>
+      <c r="AP9">
+        <v>12.5</v>
+      </c>
+      <c r="AQ9">
+        <v>15</v>
+      </c>
+      <c r="AR9">
+        <v>30</v>
+      </c>
+      <c r="AS9">
+        <v>55</v>
+      </c>
+      <c r="AT9">
+        <v>8</v>
+      </c>
+      <c r="AU9">
+        <v>8</v>
+      </c>
+      <c r="AV9">
+        <v>17.5</v>
+      </c>
+      <c r="AW9">
+        <v>55</v>
+      </c>
+      <c r="AX9">
+        <v>10.5</v>
+      </c>
+      <c r="AY9">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9">
+        <v>18.5</v>
+      </c>
+      <c r="BA9">
+        <v>46</v>
+      </c>
+      <c r="BB9">
+        <v>17.5</v>
+      </c>
+      <c r="BC9">
+        <v>17.5</v>
+      </c>
+      <c r="BD9">
         <v>32</v>
       </c>
-      <c r="AE9">
-        <v>190</v>
-      </c>
-      <c r="AF9">
-        <v>12</v>
-      </c>
-      <c r="AG9">
+      <c r="BE9">
+        <v>50</v>
+      </c>
+      <c r="BF9">
+        <v>10.5</v>
+      </c>
+      <c r="BG9">
+        <v>60</v>
+      </c>
+      <c r="BH9">
+        <v>3.35</v>
+      </c>
+      <c r="BI9">
+        <v>3.15</v>
+      </c>
+      <c r="BJ9">
+        <v>10.5</v>
+      </c>
+      <c r="BK9">
+        <v>9</v>
+      </c>
+      <c r="BL9">
+        <v>140</v>
+      </c>
+      <c r="BM9">
+        <v>16.5</v>
+      </c>
+      <c r="BN9">
+        <v>4.4</v>
+      </c>
+      <c r="BO9">
+        <v>4</v>
+      </c>
+      <c r="BP9">
+        <v>12.5</v>
+      </c>
+      <c r="BQ9">
+        <v>7.4</v>
+      </c>
+      <c r="BR9">
+        <v>28</v>
+      </c>
+      <c r="BS9">
         <v>11</v>
       </c>
-      <c r="AH9">
-        <v>21</v>
-      </c>
-      <c r="AI9">
-        <v>160</v>
-      </c>
-      <c r="AJ9">
-        <v>16.5</v>
-      </c>
-      <c r="AK9">
-        <v>15.5</v>
-      </c>
-      <c r="AL9">
-        <v>34</v>
-      </c>
-      <c r="AM9">
-        <v>320</v>
-      </c>
-      <c r="AN9">
-        <v>6.2</v>
-      </c>
-      <c r="AO9">
-        <v>85</v>
-      </c>
-      <c r="AP9">
-        <v>21</v>
-      </c>
-      <c r="AQ9">
-        <v>24</v>
-      </c>
-      <c r="AR9">
-        <v>46</v>
-      </c>
-      <c r="AS9">
-        <v>100</v>
-      </c>
-      <c r="AT9">
-        <v>9.6</v>
-      </c>
-      <c r="AU9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV9">
-        <v>21</v>
-      </c>
-      <c r="AW9">
-        <v>50</v>
-      </c>
-      <c r="AX9">
-        <v>9.6</v>
-      </c>
-      <c r="AY9">
-        <v>8.6</v>
-      </c>
-      <c r="AZ9">
-        <v>16</v>
-      </c>
-      <c r="BA9">
-        <v>38</v>
-      </c>
-      <c r="BB9">
-        <v>12.5</v>
-      </c>
-      <c r="BC9">
-        <v>12.5</v>
-      </c>
-      <c r="BD9">
-        <v>22</v>
-      </c>
-      <c r="BE9">
-        <v>55</v>
-      </c>
-      <c r="BF9">
-        <v>5.1</v>
-      </c>
-      <c r="BG9">
-        <v>40</v>
-      </c>
-      <c r="BH9">
-        <v>5.2</v>
-      </c>
-      <c r="BI9">
-        <v>3.5</v>
-      </c>
-      <c r="BJ9">
-        <v>12</v>
-      </c>
-      <c r="BK9">
-        <v>3.4</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>4.5</v>
-      </c>
-      <c r="BN9">
-        <v>5.2</v>
-      </c>
-      <c r="BO9">
-        <v>3.45</v>
-      </c>
-      <c r="BP9">
-        <v>11.5</v>
-      </c>
-      <c r="BQ9">
-        <v>3.35</v>
-      </c>
-      <c r="BR9">
-        <v>25</v>
-      </c>
-      <c r="BS9">
-        <v>3.95</v>
-      </c>
       <c r="BT9">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV9">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BW9">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BX9">
         <v>55</v>
       </c>
       <c r="BY9">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="BZ9">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="CA9">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F10">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="G10">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="H10">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L10">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O10">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q10">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="R10">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T10">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="U10">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="V10">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="W10">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="X10">
+        <v>9.6</v>
+      </c>
+      <c r="Y10">
+        <v>14</v>
+      </c>
+      <c r="Z10">
+        <v>70</v>
+      </c>
+      <c r="AA10">
+        <v>170</v>
+      </c>
+      <c r="AB10">
+        <v>6.8</v>
+      </c>
+      <c r="AC10">
+        <v>7.8</v>
+      </c>
+      <c r="AD10">
+        <v>23</v>
+      </c>
+      <c r="AE10">
+        <v>170</v>
+      </c>
+      <c r="AF10">
         <v>10.5</v>
       </c>
-      <c r="Y10">
-        <v>11.5</v>
-      </c>
-      <c r="Z10">
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
         <v>26</v>
       </c>
-      <c r="AA10">
-        <v>500</v>
-      </c>
-      <c r="AB10">
-        <v>8.4</v>
-      </c>
-      <c r="AC10">
-        <v>7.4</v>
-      </c>
-      <c r="AD10">
-        <v>16.5</v>
-      </c>
-      <c r="AE10">
-        <v>60</v>
-      </c>
-      <c r="AF10">
-        <v>14</v>
-      </c>
-      <c r="AG10">
-        <v>12</v>
-      </c>
-      <c r="AH10">
+      <c r="AI10">
+        <v>130</v>
+      </c>
+      <c r="AJ10">
         <v>22</v>
       </c>
-      <c r="AI10">
-        <v>75</v>
-      </c>
-      <c r="AJ10">
-        <v>36</v>
-      </c>
       <c r="AK10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL10">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AM10">
-        <v>580</v>
+        <v>220</v>
       </c>
       <c r="AN10">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AO10">
-        <v>570</v>
+        <v>150</v>
       </c>
       <c r="AP10">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ10">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AR10">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AS10">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AT10">
+        <v>6.2</v>
+      </c>
+      <c r="AU10">
         <v>7</v>
       </c>
-      <c r="AU10">
-        <v>6.6</v>
-      </c>
       <c r="AV10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AW10">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="AX10">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AY10">
         <v>10</v>
       </c>
       <c r="AZ10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA10">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BB10">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC10">
+        <v>20</v>
+      </c>
+      <c r="BD10">
+        <v>11.5</v>
+      </c>
+      <c r="BE10">
+        <v>13</v>
+      </c>
+      <c r="BF10">
+        <v>17</v>
+      </c>
+      <c r="BG10">
         <v>12.5</v>
       </c>
-      <c r="BD10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE10">
-        <v>10</v>
-      </c>
-      <c r="BF10">
-        <v>8.4</v>
-      </c>
-      <c r="BG10">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH10">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="BI10">
         <v>2.64</v>
       </c>
       <c r="BJ10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK10">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BN10">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BQ10">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR10">
         <v>40</v>
       </c>
       <c r="BS10">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BT10">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BU10">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BV10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BX10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA10">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:80">
-      <c r="A11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11">
-        <v>1.83</v>
-      </c>
-      <c r="G11">
-        <v>1.85</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>5.2</v>
-      </c>
-      <c r="J11">
-        <v>3.8</v>
-      </c>
-      <c r="K11">
-        <v>3.9</v>
-      </c>
-      <c r="L11">
-        <v>1.42</v>
-      </c>
-      <c r="M11">
-        <v>1.08</v>
-      </c>
-      <c r="N11">
-        <v>3.8</v>
-      </c>
-      <c r="O11">
-        <v>1.34</v>
-      </c>
-      <c r="P11">
-        <v>1.97</v>
-      </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
-      <c r="R11">
-        <v>1.36</v>
-      </c>
-      <c r="S11">
-        <v>3.6</v>
-      </c>
-      <c r="T11">
-        <v>1.9</v>
-      </c>
-      <c r="U11">
-        <v>2.08</v>
-      </c>
-      <c r="V11">
-        <v>1.23</v>
-      </c>
-      <c r="W11">
-        <v>2.16</v>
-      </c>
-      <c r="X11">
-        <v>13.5</v>
-      </c>
-      <c r="Y11">
-        <v>16.5</v>
-      </c>
-      <c r="Z11">
-        <v>40</v>
-      </c>
-      <c r="AA11">
-        <v>190</v>
-      </c>
-      <c r="AB11">
-        <v>8.4</v>
-      </c>
-      <c r="AC11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD11">
-        <v>19.5</v>
-      </c>
-      <c r="AE11">
-        <v>70</v>
-      </c>
-      <c r="AF11">
-        <v>11.5</v>
-      </c>
-      <c r="AG11">
-        <v>10.5</v>
-      </c>
-      <c r="AH11">
-        <v>20</v>
-      </c>
-      <c r="AI11">
-        <v>160</v>
-      </c>
-      <c r="AJ11">
-        <v>20</v>
-      </c>
-      <c r="AK11">
-        <v>20</v>
-      </c>
-      <c r="AL11">
-        <v>38</v>
-      </c>
-      <c r="AM11">
-        <v>200</v>
-      </c>
-      <c r="AN11">
-        <v>12.5</v>
-      </c>
-      <c r="AO11">
-        <v>95</v>
-      </c>
-      <c r="AP11">
-        <v>12.5</v>
-      </c>
-      <c r="AQ11">
-        <v>14.5</v>
-      </c>
-      <c r="AR11">
-        <v>29</v>
-      </c>
-      <c r="AS11">
-        <v>16.5</v>
-      </c>
-      <c r="AT11">
-        <v>7.8</v>
-      </c>
-      <c r="AU11">
-        <v>7.8</v>
-      </c>
-      <c r="AV11">
-        <v>17</v>
-      </c>
-      <c r="AW11">
-        <v>34</v>
-      </c>
-      <c r="AX11">
-        <v>10.5</v>
-      </c>
-      <c r="AY11">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11">
-        <v>18.5</v>
-      </c>
-      <c r="BA11">
-        <v>38</v>
-      </c>
-      <c r="BB11">
-        <v>17.5</v>
-      </c>
-      <c r="BC11">
-        <v>17.5</v>
-      </c>
-      <c r="BD11">
-        <v>28</v>
-      </c>
-      <c r="BE11">
-        <v>16.5</v>
-      </c>
-      <c r="BF11">
-        <v>10.5</v>
-      </c>
-      <c r="BG11">
-        <v>50</v>
-      </c>
-      <c r="BH11">
-        <v>3.35</v>
-      </c>
-      <c r="BI11">
-        <v>3.15</v>
-      </c>
-      <c r="BJ11">
-        <v>10.5</v>
-      </c>
-      <c r="BK11">
-        <v>9</v>
-      </c>
-      <c r="BL11">
-        <v>140</v>
-      </c>
-      <c r="BM11">
-        <v>16.5</v>
-      </c>
-      <c r="BN11">
-        <v>4.4</v>
-      </c>
-      <c r="BO11">
-        <v>4</v>
-      </c>
-      <c r="BP11">
-        <v>12.5</v>
-      </c>
-      <c r="BQ11">
-        <v>7.4</v>
-      </c>
-      <c r="BR11">
-        <v>28</v>
-      </c>
-      <c r="BS11">
-        <v>11</v>
-      </c>
-      <c r="BT11">
-        <v>8.4</v>
-      </c>
-      <c r="BU11">
-        <v>7.4</v>
-      </c>
-      <c r="BV11">
-        <v>44</v>
-      </c>
-      <c r="BW11">
-        <v>13</v>
-      </c>
-      <c r="BX11">
-        <v>55</v>
-      </c>
-      <c r="BY11">
-        <v>14</v>
-      </c>
-      <c r="BZ11">
-        <v>23</v>
-      </c>
-      <c r="CA11">
-        <v>10</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:80">
-      <c r="A12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>120</v>
-      </c>
-      <c r="F12">
-        <v>1.93</v>
-      </c>
-      <c r="G12">
-        <v>1.96</v>
-      </c>
-      <c r="H12">
-        <v>5</v>
-      </c>
-      <c r="I12">
-        <v>5.2</v>
-      </c>
-      <c r="J12">
-        <v>3.35</v>
-      </c>
-      <c r="K12">
-        <v>3.5</v>
-      </c>
-      <c r="L12">
-        <v>1.55</v>
-      </c>
-      <c r="M12">
-        <v>1.12</v>
-      </c>
-      <c r="N12">
-        <v>2.92</v>
-      </c>
-      <c r="O12">
-        <v>1.5</v>
-      </c>
-      <c r="P12">
-        <v>1.62</v>
-      </c>
-      <c r="Q12">
-        <v>2.54</v>
-      </c>
-      <c r="R12">
-        <v>1.22</v>
-      </c>
-      <c r="S12">
-        <v>5.2</v>
-      </c>
-      <c r="T12">
-        <v>2.22</v>
-      </c>
-      <c r="U12">
-        <v>1.79</v>
-      </c>
-      <c r="V12">
-        <v>1.23</v>
-      </c>
-      <c r="W12">
-        <v>2.04</v>
-      </c>
-      <c r="X12">
-        <v>9.6</v>
-      </c>
-      <c r="Y12">
-        <v>14</v>
-      </c>
-      <c r="Z12">
-        <v>70</v>
-      </c>
-      <c r="AA12">
-        <v>170</v>
-      </c>
-      <c r="AB12">
-        <v>6.8</v>
-      </c>
-      <c r="AC12">
-        <v>7.8</v>
-      </c>
-      <c r="AD12">
-        <v>23</v>
-      </c>
-      <c r="AE12">
-        <v>110</v>
-      </c>
-      <c r="AF12">
-        <v>10.5</v>
-      </c>
-      <c r="AG12">
-        <v>11</v>
-      </c>
-      <c r="AH12">
-        <v>26</v>
-      </c>
-      <c r="AI12">
-        <v>130</v>
-      </c>
-      <c r="AJ12">
-        <v>22</v>
-      </c>
-      <c r="AK12">
-        <v>26</v>
-      </c>
-      <c r="AL12">
-        <v>95</v>
-      </c>
-      <c r="AM12">
-        <v>220</v>
-      </c>
-      <c r="AN12">
-        <v>21</v>
-      </c>
-      <c r="AO12">
-        <v>200</v>
-      </c>
-      <c r="AP12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ12">
-        <v>12</v>
-      </c>
-      <c r="AR12">
-        <v>10</v>
-      </c>
-      <c r="AS12">
-        <v>12.5</v>
-      </c>
-      <c r="AT12">
-        <v>6.2</v>
-      </c>
-      <c r="AU12">
-        <v>7</v>
-      </c>
-      <c r="AV12">
-        <v>18</v>
-      </c>
-      <c r="AW12">
-        <v>12</v>
-      </c>
-      <c r="AX12">
-        <v>9</v>
-      </c>
-      <c r="AY12">
-        <v>10</v>
-      </c>
-      <c r="AZ12">
-        <v>20</v>
-      </c>
-      <c r="BA12">
-        <v>12</v>
-      </c>
-      <c r="BB12">
-        <v>18.5</v>
-      </c>
-      <c r="BC12">
-        <v>20</v>
-      </c>
-      <c r="BD12">
-        <v>11.5</v>
-      </c>
-      <c r="BE12">
-        <v>12.5</v>
-      </c>
-      <c r="BF12">
-        <v>17</v>
-      </c>
-      <c r="BG12">
-        <v>12.5</v>
-      </c>
-      <c r="BH12">
-        <v>2.8</v>
-      </c>
-      <c r="BI12">
-        <v>2.64</v>
-      </c>
-      <c r="BJ12">
-        <v>12</v>
-      </c>
-      <c r="BK12">
-        <v>9</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>14.5</v>
-      </c>
-      <c r="BN12">
-        <v>4.3</v>
-      </c>
-      <c r="BO12">
-        <v>3.8</v>
-      </c>
-      <c r="BP12">
-        <v>16</v>
-      </c>
-      <c r="BQ12">
-        <v>8</v>
-      </c>
-      <c r="BR12">
-        <v>40</v>
-      </c>
-      <c r="BS12">
-        <v>11</v>
-      </c>
-      <c r="BT12">
-        <v>8.6</v>
-      </c>
-      <c r="BU12">
-        <v>6.2</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>12</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>13</v>
-      </c>
-      <c r="BZ12">
-        <v>40</v>
-      </c>
-      <c r="CA12">
-        <v>11</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Argentinian Primera C</t>
-  </si>
-  <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
@@ -277,9 +274,6 @@
     <t>2026-10-06</t>
   </si>
   <si>
-    <t>17:00:00</t>
-  </si>
-  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -304,9 +298,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>CA Claypole</t>
-  </si>
-  <si>
     <t>Kabylie</t>
   </si>
   <si>
@@ -331,9 +322,6 @@
     <t>Goias</t>
   </si>
   <si>
-    <t>Deportivo Espanol</t>
-  </si>
-  <si>
     <t>MC Alger</t>
   </si>
   <si>
@@ -358,7 +346,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-10-06 15:02:08</t>
+    <t>2026-10-06 17:13:21</t>
   </si>
 </sst>
 </file>
@@ -690,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -940,70 +928,70 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F2">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="G2">
-        <v>3.7</v>
+        <v>600</v>
       </c>
       <c r="H2">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>870</v>
       </c>
       <c r="J2">
-        <v>2.24</v>
+        <v>1.1</v>
       </c>
       <c r="K2">
-        <v>2.32</v>
+        <v>950</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="Q2">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R2">
-        <v>1.47</v>
+        <v>1.03</v>
       </c>
       <c r="S2">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1021,160 +1009,160 @@
         <v>1000</v>
       </c>
       <c r="AC2">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
         <v>1000</v>
       </c>
       <c r="AG2">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>1000</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1182,184 +1170,184 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F3">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="G3">
-        <v>600</v>
+        <v>1.91</v>
       </c>
       <c r="H3">
-        <v>1.12</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>870</v>
+        <v>4.6</v>
       </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
         <v>1.1</v>
       </c>
       <c r="O3">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P3">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Q3">
         <v>1.01</v>
       </c>
       <c r="R3">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="S3">
         <v>1.01</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V3">
         <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO3">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BF3">
-        <v>1.55</v>
+        <v>9</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1377,7 +1365,7 @@
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1410,13 +1398,13 @@
         <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1424,1693 +1412,1451 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F4">
-        <v>1.72</v>
+        <v>2.66</v>
       </c>
       <c r="G4">
-        <v>1.74</v>
+        <v>2.76</v>
       </c>
       <c r="H4">
-        <v>5.4</v>
+        <v>2.98</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
-        <v>2.32</v>
+        <v>1.54</v>
       </c>
       <c r="X4">
+        <v>11</v>
+      </c>
+      <c r="Y4">
+        <v>10.5</v>
+      </c>
+      <c r="Z4">
+        <v>20</v>
+      </c>
+      <c r="AA4">
+        <v>55</v>
+      </c>
+      <c r="AB4">
+        <v>9.4</v>
+      </c>
+      <c r="AC4">
+        <v>7.4</v>
+      </c>
+      <c r="AD4">
         <v>14</v>
       </c>
-      <c r="Y4">
+      <c r="AE4">
+        <v>48</v>
+      </c>
+      <c r="AF4">
+        <v>17</v>
+      </c>
+      <c r="AG4">
+        <v>13</v>
+      </c>
+      <c r="AH4">
+        <v>21</v>
+      </c>
+      <c r="AI4">
+        <v>75</v>
+      </c>
+      <c r="AJ4">
+        <v>46</v>
+      </c>
+      <c r="AK4">
+        <v>44</v>
+      </c>
+      <c r="AL4">
+        <v>70</v>
+      </c>
+      <c r="AM4">
+        <v>150</v>
+      </c>
+      <c r="AN4">
+        <v>40</v>
+      </c>
+      <c r="AO4">
+        <v>48</v>
+      </c>
+      <c r="AP4">
+        <v>9.4</v>
+      </c>
+      <c r="AQ4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR4">
+        <v>16</v>
+      </c>
+      <c r="AS4">
+        <v>40</v>
+      </c>
+      <c r="AT4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU4">
+        <v>6.4</v>
+      </c>
+      <c r="AV4">
+        <v>12</v>
+      </c>
+      <c r="AW4">
+        <v>32</v>
+      </c>
+      <c r="AX4">
+        <v>14</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
         <v>18</v>
-      </c>
-      <c r="Z4">
-        <v>55</v>
-      </c>
-      <c r="AA4">
-        <v>180</v>
-      </c>
-      <c r="AB4">
-        <v>8</v>
-      </c>
-      <c r="AC4">
-        <v>9</v>
-      </c>
-      <c r="AD4">
-        <v>24</v>
-      </c>
-      <c r="AE4">
-        <v>110</v>
-      </c>
-      <c r="AF4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG4">
-        <v>11</v>
-      </c>
-      <c r="AH4">
-        <v>26</v>
-      </c>
-      <c r="AI4">
-        <v>110</v>
-      </c>
-      <c r="AJ4">
-        <v>18.5</v>
-      </c>
-      <c r="AK4">
-        <v>21</v>
-      </c>
-      <c r="AL4">
-        <v>50</v>
-      </c>
-      <c r="AM4">
-        <v>580</v>
-      </c>
-      <c r="AN4">
-        <v>12.5</v>
-      </c>
-      <c r="AO4">
-        <v>160</v>
-      </c>
-      <c r="AP4">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4">
-        <v>15</v>
-      </c>
-      <c r="AR4">
-        <v>42</v>
-      </c>
-      <c r="AS4">
-        <v>80</v>
-      </c>
-      <c r="AT4">
-        <v>7</v>
-      </c>
-      <c r="AU4">
-        <v>8</v>
-      </c>
-      <c r="AV4">
-        <v>20</v>
-      </c>
-      <c r="AW4">
-        <v>65</v>
-      </c>
-      <c r="AX4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY4">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4">
-        <v>21</v>
       </c>
       <c r="BA4">
         <v>50</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="BC4">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BE4">
+        <v>110</v>
+      </c>
+      <c r="BF4">
+        <v>32</v>
+      </c>
+      <c r="BG4">
+        <v>34</v>
+      </c>
+      <c r="BH4">
+        <v>2.58</v>
+      </c>
+      <c r="BI4">
+        <v>2.44</v>
+      </c>
+      <c r="BJ4">
+        <v>11.5</v>
+      </c>
+      <c r="BK4">
+        <v>10.5</v>
+      </c>
+      <c r="BL4">
+        <v>290</v>
+      </c>
+      <c r="BM4">
+        <v>13</v>
+      </c>
+      <c r="BN4">
+        <v>5.6</v>
+      </c>
+      <c r="BO4">
+        <v>5</v>
+      </c>
+      <c r="BP4">
+        <v>29</v>
+      </c>
+      <c r="BQ4">
+        <v>21</v>
+      </c>
+      <c r="BR4">
+        <v>65</v>
+      </c>
+      <c r="BS4">
+        <v>44</v>
+      </c>
+      <c r="BT4">
+        <v>5.8</v>
+      </c>
+      <c r="BU4">
+        <v>5.3</v>
+      </c>
+      <c r="BV4">
+        <v>34</v>
+      </c>
+      <c r="BW4">
+        <v>23</v>
+      </c>
+      <c r="BX4">
         <v>70</v>
       </c>
-      <c r="BF4">
-        <v>10.5</v>
-      </c>
-      <c r="BG4">
-        <v>11</v>
-      </c>
-      <c r="BH4">
-        <v>3.75</v>
-      </c>
-      <c r="BI4">
-        <v>2.82</v>
-      </c>
-      <c r="BJ4">
-        <v>13.5</v>
-      </c>
-      <c r="BK4">
-        <v>4.1</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>4.8</v>
-      </c>
-      <c r="BN4">
-        <v>4.7</v>
-      </c>
-      <c r="BO4">
-        <v>3.45</v>
-      </c>
-      <c r="BP4">
-        <v>14</v>
-      </c>
-      <c r="BQ4">
-        <v>4.1</v>
-      </c>
-      <c r="BR4">
-        <v>38</v>
-      </c>
-      <c r="BS4">
-        <v>4.4</v>
-      </c>
-      <c r="BT4">
-        <v>11.5</v>
-      </c>
-      <c r="BU4">
-        <v>7.8</v>
-      </c>
-      <c r="BV4">
-        <v>75</v>
-      </c>
-      <c r="BW4">
-        <v>4.6</v>
-      </c>
-      <c r="BX4">
-        <v>85</v>
-      </c>
       <c r="BY4">
-        <v>4.9</v>
+        <v>48</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CB4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F5">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G5">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="J5">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5">
+        <v>1.29</v>
+      </c>
+      <c r="P5">
+        <v>2.04</v>
+      </c>
+      <c r="Q5">
+        <v>1.9</v>
+      </c>
+      <c r="R5">
+        <v>1.39</v>
+      </c>
+      <c r="S5">
         <v>3.25</v>
       </c>
-      <c r="O5">
-        <v>1.41</v>
-      </c>
-      <c r="P5">
+      <c r="T5">
         <v>1.75</v>
       </c>
-      <c r="Q5">
-        <v>2.28</v>
-      </c>
-      <c r="R5">
-        <v>1.28</v>
-      </c>
-      <c r="S5">
-        <v>4.2</v>
-      </c>
-      <c r="T5">
-        <v>1.92</v>
-      </c>
       <c r="U5">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="X5">
+        <v>16.5</v>
+      </c>
+      <c r="Y5">
+        <v>14</v>
+      </c>
+      <c r="Z5">
+        <v>25</v>
+      </c>
+      <c r="AA5">
+        <v>95</v>
+      </c>
+      <c r="AB5">
+        <v>12</v>
+      </c>
+      <c r="AC5">
+        <v>8.6</v>
+      </c>
+      <c r="AD5">
+        <v>14</v>
+      </c>
+      <c r="AE5">
+        <v>46</v>
+      </c>
+      <c r="AF5">
+        <v>17.5</v>
+      </c>
+      <c r="AG5">
         <v>11.5</v>
       </c>
-      <c r="Y5">
-        <v>12</v>
-      </c>
-      <c r="Z5">
-        <v>26</v>
-      </c>
-      <c r="AA5">
-        <v>80</v>
-      </c>
-      <c r="AB5">
-        <v>8.6</v>
-      </c>
-      <c r="AC5">
-        <v>7.8</v>
-      </c>
-      <c r="AD5">
-        <v>16</v>
-      </c>
-      <c r="AE5">
-        <v>60</v>
-      </c>
-      <c r="AF5">
-        <v>14.5</v>
-      </c>
-      <c r="AG5">
-        <v>12</v>
-      </c>
       <c r="AH5">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>38</v>
       </c>
       <c r="AK5">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AL5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM5">
         <v>200</v>
       </c>
       <c r="AN5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT5">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AX5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA5">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BB5">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BC5">
+        <v>20</v>
+      </c>
+      <c r="BD5">
+        <v>28</v>
+      </c>
+      <c r="BE5">
+        <v>42</v>
+      </c>
+      <c r="BF5">
         <v>15.5</v>
       </c>
-      <c r="BD5">
-        <v>36</v>
-      </c>
-      <c r="BE5">
-        <v>10</v>
-      </c>
-      <c r="BF5">
-        <v>20</v>
-      </c>
       <c r="BG5">
+        <v>24</v>
+      </c>
+      <c r="BH5">
+        <v>3.6</v>
+      </c>
+      <c r="BI5">
+        <v>3.1</v>
+      </c>
+      <c r="BJ5">
         <v>9.4</v>
       </c>
-      <c r="BH5">
-        <v>3.45</v>
-      </c>
-      <c r="BI5">
-        <v>2.84</v>
-      </c>
-      <c r="BJ5">
+      <c r="BK5">
+        <v>7.6</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>10.5</v>
       </c>
-      <c r="BK5">
+      <c r="BN5">
+        <v>5.5</v>
+      </c>
+      <c r="BO5">
+        <v>4.7</v>
+      </c>
+      <c r="BP5">
+        <v>17.5</v>
+      </c>
+      <c r="BQ5">
+        <v>7</v>
+      </c>
+      <c r="BR5">
+        <v>32</v>
+      </c>
+      <c r="BS5">
+        <v>8.6</v>
+      </c>
+      <c r="BT5">
         <v>6.8</v>
       </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
+      <c r="BU5">
+        <v>5.5</v>
+      </c>
+      <c r="BV5">
+        <v>970</v>
+      </c>
+      <c r="BW5">
+        <v>8</v>
+      </c>
+      <c r="BX5">
+        <v>990</v>
+      </c>
+      <c r="BY5">
+        <v>9</v>
+      </c>
+      <c r="BZ5">
+        <v>26</v>
+      </c>
+      <c r="CA5">
         <v>8.199999999999999</v>
       </c>
-      <c r="BN5">
-        <v>5.2</v>
-      </c>
-      <c r="BO5">
-        <v>4.5</v>
-      </c>
-      <c r="BP5">
-        <v>18.5</v>
-      </c>
-      <c r="BQ5">
-        <v>6</v>
-      </c>
-      <c r="BR5">
-        <v>36</v>
-      </c>
-      <c r="BS5">
-        <v>7</v>
-      </c>
-      <c r="BT5">
-        <v>7</v>
-      </c>
-      <c r="BU5">
-        <v>6</v>
-      </c>
-      <c r="BV5">
-        <v>34</v>
-      </c>
-      <c r="BW5">
-        <v>6.8</v>
-      </c>
-      <c r="BX5">
-        <v>48</v>
-      </c>
-      <c r="BY5">
-        <v>7.4</v>
-      </c>
-      <c r="BZ5">
-        <v>36</v>
-      </c>
-      <c r="CA5">
-        <v>7</v>
-      </c>
       <c r="CB5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F6">
+        <v>1.51</v>
+      </c>
+      <c r="G6">
+        <v>1.55</v>
+      </c>
+      <c r="H6">
+        <v>6.4</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4.9</v>
+      </c>
+      <c r="K6">
+        <v>5.3</v>
+      </c>
+      <c r="L6">
+        <v>1.27</v>
+      </c>
+      <c r="M6">
+        <v>1.03</v>
+      </c>
+      <c r="N6">
+        <v>6</v>
+      </c>
+      <c r="O6">
+        <v>1.18</v>
+      </c>
+      <c r="P6">
+        <v>2.7</v>
+      </c>
+      <c r="Q6">
+        <v>1.54</v>
+      </c>
+      <c r="R6">
+        <v>1.69</v>
+      </c>
+      <c r="S6">
         <v>2.36</v>
       </c>
-      <c r="G6">
-        <v>2.48</v>
-      </c>
-      <c r="H6">
-        <v>3.05</v>
-      </c>
-      <c r="I6">
-        <v>3.35</v>
-      </c>
-      <c r="J6">
-        <v>3.55</v>
-      </c>
-      <c r="K6">
-        <v>3.7</v>
-      </c>
-      <c r="L6">
-        <v>1.4</v>
-      </c>
-      <c r="M6">
-        <v>1.06</v>
-      </c>
-      <c r="N6">
-        <v>3.85</v>
-      </c>
-      <c r="O6">
-        <v>1.3</v>
-      </c>
-      <c r="P6">
-        <v>2.02</v>
-      </c>
-      <c r="Q6">
-        <v>1.87</v>
-      </c>
-      <c r="R6">
-        <v>1.38</v>
-      </c>
-      <c r="S6">
-        <v>3.25</v>
-      </c>
       <c r="T6">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U6">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="X6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Y6">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AA6">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AB6">
+        <v>13</v>
+      </c>
+      <c r="AC6">
+        <v>12</v>
+      </c>
+      <c r="AD6">
+        <v>27</v>
+      </c>
+      <c r="AE6">
+        <v>90</v>
+      </c>
+      <c r="AF6">
+        <v>12</v>
+      </c>
+      <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>21</v>
+      </c>
+      <c r="AI6">
+        <v>80</v>
+      </c>
+      <c r="AJ6">
+        <v>15.5</v>
+      </c>
+      <c r="AK6">
+        <v>15</v>
+      </c>
+      <c r="AL6">
+        <v>29</v>
+      </c>
+      <c r="AM6">
+        <v>95</v>
+      </c>
+      <c r="AN6">
+        <v>5.7</v>
+      </c>
+      <c r="AO6">
+        <v>65</v>
+      </c>
+      <c r="AP6">
+        <v>22</v>
+      </c>
+      <c r="AQ6">
+        <v>27</v>
+      </c>
+      <c r="AR6">
+        <v>30</v>
+      </c>
+      <c r="AS6">
+        <v>12</v>
+      </c>
+      <c r="AT6">
+        <v>10.5</v>
+      </c>
+      <c r="AU6">
+        <v>10.5</v>
+      </c>
+      <c r="AV6">
+        <v>22</v>
+      </c>
+      <c r="AW6">
+        <v>30</v>
+      </c>
+      <c r="AX6">
+        <v>10</v>
+      </c>
+      <c r="AY6">
+        <v>9</v>
+      </c>
+      <c r="AZ6">
+        <v>17</v>
+      </c>
+      <c r="BA6">
+        <v>27</v>
+      </c>
+      <c r="BB6">
+        <v>13</v>
+      </c>
+      <c r="BC6">
+        <v>12.5</v>
+      </c>
+      <c r="BD6">
+        <v>22</v>
+      </c>
+      <c r="BE6">
+        <v>42</v>
+      </c>
+      <c r="BF6">
+        <v>5.2</v>
+      </c>
+      <c r="BG6">
+        <v>11</v>
+      </c>
+      <c r="BH6">
+        <v>4.9</v>
+      </c>
+      <c r="BI6">
+        <v>4.1</v>
+      </c>
+      <c r="BJ6">
         <v>11.5</v>
       </c>
-      <c r="AC6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6">
-        <v>14.5</v>
-      </c>
-      <c r="AE6">
-        <v>46</v>
-      </c>
-      <c r="AF6">
-        <v>17.5</v>
-      </c>
-      <c r="AG6">
-        <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>17</v>
-      </c>
-      <c r="AI6">
-        <v>120</v>
-      </c>
-      <c r="AJ6">
-        <v>38</v>
-      </c>
-      <c r="AK6">
-        <v>36</v>
-      </c>
-      <c r="AL6">
-        <v>65</v>
-      </c>
-      <c r="AM6">
-        <v>580</v>
-      </c>
-      <c r="AN6">
-        <v>20</v>
-      </c>
-      <c r="AO6">
-        <v>500</v>
-      </c>
-      <c r="AP6">
-        <v>12.5</v>
-      </c>
-      <c r="AQ6">
-        <v>11.5</v>
-      </c>
-      <c r="AR6">
-        <v>20</v>
-      </c>
-      <c r="AS6">
-        <v>36</v>
-      </c>
-      <c r="AT6">
-        <v>9.6</v>
-      </c>
-      <c r="AU6">
-        <v>7</v>
-      </c>
-      <c r="AV6">
-        <v>11.5</v>
-      </c>
-      <c r="AW6">
-        <v>23</v>
-      </c>
-      <c r="AX6">
-        <v>12.5</v>
-      </c>
-      <c r="AY6">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6">
-        <v>13.5</v>
-      </c>
-      <c r="BA6">
-        <v>30</v>
-      </c>
-      <c r="BB6">
-        <v>23</v>
-      </c>
-      <c r="BC6">
-        <v>20</v>
-      </c>
-      <c r="BD6">
-        <v>27</v>
-      </c>
-      <c r="BE6">
-        <v>60</v>
-      </c>
-      <c r="BF6">
-        <v>14.5</v>
-      </c>
-      <c r="BG6">
-        <v>19</v>
-      </c>
-      <c r="BH6">
-        <v>3.6</v>
-      </c>
-      <c r="BI6">
-        <v>2.86</v>
-      </c>
-      <c r="BJ6">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BK6">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BN6">
+        <v>4.7</v>
+      </c>
+      <c r="BO6">
+        <v>3.95</v>
+      </c>
+      <c r="BP6">
+        <v>11</v>
+      </c>
+      <c r="BQ6">
+        <v>3.9</v>
+      </c>
+      <c r="BR6">
+        <v>24</v>
+      </c>
+      <c r="BS6">
+        <v>4.8</v>
+      </c>
+      <c r="BT6">
+        <v>12</v>
+      </c>
+      <c r="BU6">
+        <v>4</v>
+      </c>
+      <c r="BV6">
+        <v>55</v>
+      </c>
+      <c r="BW6">
         <v>5.5</v>
       </c>
-      <c r="BO6">
+      <c r="BX6">
+        <v>55</v>
+      </c>
+      <c r="BY6">
+        <v>5.5</v>
+      </c>
+      <c r="BZ6">
+        <v>14</v>
+      </c>
+      <c r="CA6">
         <v>4.2</v>
       </c>
-      <c r="BP6">
-        <v>18.5</v>
-      </c>
-      <c r="BQ6">
-        <v>6.6</v>
-      </c>
-      <c r="BR6">
-        <v>32</v>
-      </c>
-      <c r="BS6">
-        <v>7.6</v>
-      </c>
-      <c r="BT6">
-        <v>6.8</v>
-      </c>
-      <c r="BU6">
-        <v>5.1</v>
-      </c>
-      <c r="BV6">
-        <v>27</v>
-      </c>
-      <c r="BW6">
-        <v>7.4</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>8</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>7.4</v>
-      </c>
       <c r="CB6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="G7">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="J7">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="L7">
+        <v>1.53</v>
+      </c>
+      <c r="M7">
+        <v>1.11</v>
+      </c>
+      <c r="N7">
+        <v>3.1</v>
+      </c>
+      <c r="O7">
+        <v>1.45</v>
+      </c>
+      <c r="P7">
+        <v>1.69</v>
+      </c>
+      <c r="Q7">
+        <v>2.36</v>
+      </c>
+      <c r="R7">
         <v>1.27</v>
       </c>
-      <c r="M7">
-        <v>1.03</v>
-      </c>
-      <c r="N7">
-        <v>6</v>
-      </c>
-      <c r="O7">
-        <v>1.18</v>
-      </c>
-      <c r="P7">
-        <v>2.68</v>
-      </c>
-      <c r="Q7">
-        <v>1.54</v>
-      </c>
-      <c r="R7">
-        <v>1.67</v>
-      </c>
       <c r="S7">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="T7">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="U7">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="V7">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>2.78</v>
+        <v>1.72</v>
       </c>
       <c r="X7">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AA7">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="AB7">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="AE7">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="AF7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ7">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AK7">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="AL7">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AM7">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AN7">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="AO7">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP7">
+        <v>9</v>
+      </c>
+      <c r="AQ7">
+        <v>10</v>
+      </c>
+      <c r="AR7">
         <v>21</v>
       </c>
-      <c r="AQ7">
-        <v>24</v>
-      </c>
-      <c r="AR7">
-        <v>46</v>
-      </c>
       <c r="AS7">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AT7">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>14</v>
+      </c>
+      <c r="AW7">
+        <v>44</v>
+      </c>
+      <c r="AX7">
+        <v>12</v>
+      </c>
+      <c r="AY7">
         <v>10</v>
       </c>
-      <c r="AV7">
-        <v>21</v>
-      </c>
-      <c r="AW7">
-        <v>50</v>
-      </c>
-      <c r="AX7">
-        <v>9.6</v>
-      </c>
-      <c r="AY7">
-        <v>8.6</v>
-      </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
         <v>40</v>
       </c>
       <c r="BB7">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BD7">
+        <v>40</v>
+      </c>
+      <c r="BE7">
+        <v>12</v>
+      </c>
+      <c r="BF7">
         <v>22</v>
       </c>
-      <c r="BE7">
-        <v>55</v>
-      </c>
-      <c r="BF7">
-        <v>5</v>
-      </c>
       <c r="BG7">
+        <v>28</v>
+      </c>
+      <c r="BH7">
+        <v>2.94</v>
+      </c>
+      <c r="BI7">
+        <v>2.64</v>
+      </c>
+      <c r="BJ7">
+        <v>11</v>
+      </c>
+      <c r="BK7">
+        <v>9</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>11.5</v>
+      </c>
+      <c r="BN7">
+        <v>5.1</v>
+      </c>
+      <c r="BO7">
+        <v>4.4</v>
+      </c>
+      <c r="BP7">
+        <v>20</v>
+      </c>
+      <c r="BQ7">
+        <v>13.5</v>
+      </c>
+      <c r="BR7">
         <v>40</v>
       </c>
-      <c r="BH7">
-        <v>5.2</v>
-      </c>
-      <c r="BI7">
-        <v>3.5</v>
-      </c>
-      <c r="BJ7">
-        <v>12</v>
-      </c>
-      <c r="BK7">
-        <v>3.45</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>4.6</v>
-      </c>
-      <c r="BN7">
-        <v>5.2</v>
-      </c>
-      <c r="BO7">
-        <v>3.45</v>
-      </c>
-      <c r="BP7">
-        <v>11</v>
-      </c>
-      <c r="BQ7">
-        <v>3.35</v>
-      </c>
-      <c r="BR7">
-        <v>24</v>
-      </c>
       <c r="BS7">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="BT7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="BV7">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BW7">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7">
         <v>55</v>
       </c>
       <c r="BY7">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="CA7">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="CB7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>2.32</v>
+        <v>1.82</v>
       </c>
       <c r="G8">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="H8">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="I8">
+        <v>5.3</v>
+      </c>
+      <c r="J8">
+        <v>3.75</v>
+      </c>
+      <c r="K8">
         <v>3.9</v>
       </c>
-      <c r="J8">
-        <v>3.1</v>
-      </c>
-      <c r="K8">
-        <v>3.3</v>
-      </c>
       <c r="L8">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O8">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="Q8">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="R8">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="U8">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="W8">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="X8">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="Z8">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AB8">
         <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF8">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI8">
         <v>75</v>
       </c>
       <c r="AJ8">
+        <v>19.5</v>
+      </c>
+      <c r="AK8">
+        <v>19.5</v>
+      </c>
+      <c r="AL8">
+        <v>38</v>
+      </c>
+      <c r="AM8">
+        <v>120</v>
+      </c>
+      <c r="AN8">
+        <v>12.5</v>
+      </c>
+      <c r="AO8">
+        <v>90</v>
+      </c>
+      <c r="AP8">
+        <v>12.5</v>
+      </c>
+      <c r="AQ8">
+        <v>15</v>
+      </c>
+      <c r="AR8">
         <v>34</v>
       </c>
-      <c r="AK8">
-        <v>30</v>
-      </c>
-      <c r="AL8">
+      <c r="AS8">
         <v>55</v>
       </c>
-      <c r="AM8">
-        <v>150</v>
-      </c>
-      <c r="AN8">
-        <v>29</v>
-      </c>
-      <c r="AO8">
-        <v>70</v>
-      </c>
-      <c r="AP8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ8">
+      <c r="AT8">
+        <v>8</v>
+      </c>
+      <c r="AU8">
+        <v>7.8</v>
+      </c>
+      <c r="AV8">
+        <v>17.5</v>
+      </c>
+      <c r="AW8">
+        <v>42</v>
+      </c>
+      <c r="AX8">
         <v>10</v>
       </c>
-      <c r="AR8">
-        <v>21</v>
-      </c>
-      <c r="AS8">
-        <v>48</v>
-      </c>
-      <c r="AT8">
-        <v>7.4</v>
-      </c>
-      <c r="AU8">
-        <v>6.8</v>
-      </c>
-      <c r="AV8">
-        <v>13.5</v>
-      </c>
-      <c r="AW8">
-        <v>46</v>
-      </c>
-      <c r="AX8">
-        <v>12</v>
-      </c>
       <c r="AY8">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
         <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB8">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BC8">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="BD8">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BE8">
+        <v>50</v>
+      </c>
+      <c r="BF8">
+        <v>12</v>
+      </c>
+      <c r="BG8">
+        <v>60</v>
+      </c>
+      <c r="BH8">
+        <v>3.35</v>
+      </c>
+      <c r="BI8">
+        <v>3.15</v>
+      </c>
+      <c r="BJ8">
+        <v>10.5</v>
+      </c>
+      <c r="BK8">
+        <v>9</v>
+      </c>
+      <c r="BL8">
+        <v>140</v>
+      </c>
+      <c r="BM8">
+        <v>16.5</v>
+      </c>
+      <c r="BN8">
+        <v>4.4</v>
+      </c>
+      <c r="BO8">
+        <v>4</v>
+      </c>
+      <c r="BP8">
         <v>12.5</v>
-      </c>
-      <c r="BF8">
-        <v>23</v>
-      </c>
-      <c r="BG8">
-        <v>28</v>
-      </c>
-      <c r="BH8">
-        <v>2.94</v>
-      </c>
-      <c r="BI8">
-        <v>2.64</v>
-      </c>
-      <c r="BJ8">
-        <v>11</v>
-      </c>
-      <c r="BK8">
-        <v>5.7</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>11</v>
-      </c>
-      <c r="BN8">
-        <v>5.2</v>
-      </c>
-      <c r="BO8">
-        <v>4.3</v>
-      </c>
-      <c r="BP8">
-        <v>20</v>
       </c>
       <c r="BQ8">
         <v>7.4</v>
       </c>
       <c r="BR8">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BS8">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT8">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BU8">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BV8">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BW8">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BX8">
         <v>55</v>
       </c>
       <c r="BY8">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="CA8">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
         <v>85</v>
       </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F9">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="G9">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="H9">
         <v>4.9</v>
       </c>
       <c r="I9">
+        <v>5.1</v>
+      </c>
+      <c r="J9">
+        <v>3.4</v>
+      </c>
+      <c r="K9">
+        <v>3.5</v>
+      </c>
+      <c r="L9">
+        <v>1.56</v>
+      </c>
+      <c r="M9">
+        <v>1.11</v>
+      </c>
+      <c r="N9">
+        <v>2.92</v>
+      </c>
+      <c r="O9">
+        <v>1.5</v>
+      </c>
+      <c r="P9">
+        <v>1.63</v>
+      </c>
+      <c r="Q9">
+        <v>2.56</v>
+      </c>
+      <c r="R9">
+        <v>1.22</v>
+      </c>
+      <c r="S9">
         <v>5.2</v>
       </c>
-      <c r="J9">
-        <v>3.75</v>
-      </c>
-      <c r="K9">
-        <v>3.9</v>
-      </c>
-      <c r="L9">
-        <v>1.42</v>
-      </c>
-      <c r="M9">
-        <v>1.08</v>
-      </c>
-      <c r="N9">
-        <v>3.8</v>
-      </c>
-      <c r="O9">
-        <v>1.34</v>
-      </c>
-      <c r="P9">
-        <v>1.97</v>
-      </c>
-      <c r="Q9">
-        <v>2</v>
-      </c>
-      <c r="R9">
-        <v>1.36</v>
-      </c>
-      <c r="S9">
-        <v>3.6</v>
-      </c>
       <c r="T9">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="U9">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="V9">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="X9">
+        <v>9.4</v>
+      </c>
+      <c r="Y9">
         <v>13.5</v>
       </c>
-      <c r="Y9">
-        <v>16.5</v>
-      </c>
       <c r="Z9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA9">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB9">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE9">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH9">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AI9">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AJ9">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AK9">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AL9">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AM9">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN9">
+        <v>21</v>
+      </c>
+      <c r="AO9">
+        <v>140</v>
+      </c>
+      <c r="AP9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ9">
         <v>12.5</v>
-      </c>
-      <c r="AO9">
-        <v>90</v>
-      </c>
-      <c r="AP9">
-        <v>12.5</v>
-      </c>
-      <c r="AQ9">
-        <v>15</v>
       </c>
       <c r="AR9">
         <v>30</v>
       </c>
       <c r="AS9">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="AT9">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AU9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV9">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW9">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AX9">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
+        <v>23</v>
+      </c>
+      <c r="BA9">
+        <v>15.5</v>
+      </c>
+      <c r="BB9">
+        <v>20</v>
+      </c>
+      <c r="BC9">
+        <v>23</v>
+      </c>
+      <c r="BD9">
+        <v>19.5</v>
+      </c>
+      <c r="BE9">
+        <v>15</v>
+      </c>
+      <c r="BF9">
         <v>18.5</v>
       </c>
-      <c r="BA9">
-        <v>46</v>
-      </c>
-      <c r="BB9">
-        <v>17.5</v>
-      </c>
-      <c r="BC9">
-        <v>17.5</v>
-      </c>
-      <c r="BD9">
-        <v>32</v>
-      </c>
-      <c r="BE9">
-        <v>50</v>
-      </c>
-      <c r="BF9">
-        <v>10.5</v>
-      </c>
       <c r="BG9">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="BH9">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="BI9">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK9">
         <v>9</v>
       </c>
       <c r="BL9">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO9">
         <v>4</v>
       </c>
       <c r="BP9">
+        <v>16</v>
+      </c>
+      <c r="BQ9">
+        <v>11.5</v>
+      </c>
+      <c r="BR9">
+        <v>40</v>
+      </c>
+      <c r="BS9">
         <v>12.5</v>
       </c>
-      <c r="BQ9">
-        <v>7.4</v>
-      </c>
-      <c r="BR9">
-        <v>28</v>
-      </c>
-      <c r="BS9">
-        <v>11</v>
-      </c>
       <c r="BT9">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV9">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ9">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="CA9">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:80">
-      <c r="A10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10">
-        <v>1.94</v>
-      </c>
-      <c r="G10">
-        <v>1.96</v>
-      </c>
-      <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10">
-        <v>5.2</v>
-      </c>
-      <c r="J10">
-        <v>3.35</v>
-      </c>
-      <c r="K10">
-        <v>3.5</v>
-      </c>
-      <c r="L10">
-        <v>1.55</v>
-      </c>
-      <c r="M10">
-        <v>1.12</v>
-      </c>
-      <c r="N10">
-        <v>2.92</v>
-      </c>
-      <c r="O10">
-        <v>1.5</v>
-      </c>
-      <c r="P10">
-        <v>1.63</v>
-      </c>
-      <c r="Q10">
-        <v>2.56</v>
-      </c>
-      <c r="R10">
-        <v>1.22</v>
-      </c>
-      <c r="S10">
-        <v>5.2</v>
-      </c>
-      <c r="T10">
-        <v>2.22</v>
-      </c>
-      <c r="U10">
-        <v>1.79</v>
-      </c>
-      <c r="V10">
-        <v>1.23</v>
-      </c>
-      <c r="W10">
-        <v>2.02</v>
-      </c>
-      <c r="X10">
-        <v>9.6</v>
-      </c>
-      <c r="Y10">
-        <v>14</v>
-      </c>
-      <c r="Z10">
-        <v>70</v>
-      </c>
-      <c r="AA10">
-        <v>170</v>
-      </c>
-      <c r="AB10">
-        <v>6.8</v>
-      </c>
-      <c r="AC10">
-        <v>7.8</v>
-      </c>
-      <c r="AD10">
-        <v>23</v>
-      </c>
-      <c r="AE10">
-        <v>170</v>
-      </c>
-      <c r="AF10">
-        <v>10.5</v>
-      </c>
-      <c r="AG10">
-        <v>11</v>
-      </c>
-      <c r="AH10">
-        <v>26</v>
-      </c>
-      <c r="AI10">
-        <v>130</v>
-      </c>
-      <c r="AJ10">
-        <v>22</v>
-      </c>
-      <c r="AK10">
-        <v>26</v>
-      </c>
-      <c r="AL10">
-        <v>95</v>
-      </c>
-      <c r="AM10">
-        <v>220</v>
-      </c>
-      <c r="AN10">
-        <v>21</v>
-      </c>
-      <c r="AO10">
-        <v>150</v>
-      </c>
-      <c r="AP10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ10">
-        <v>12</v>
-      </c>
-      <c r="AR10">
-        <v>10.5</v>
-      </c>
-      <c r="AS10">
-        <v>12.5</v>
-      </c>
-      <c r="AT10">
-        <v>6.2</v>
-      </c>
-      <c r="AU10">
-        <v>7</v>
-      </c>
-      <c r="AV10">
-        <v>18</v>
-      </c>
-      <c r="AW10">
-        <v>28</v>
-      </c>
-      <c r="AX10">
-        <v>9</v>
-      </c>
-      <c r="AY10">
-        <v>10</v>
-      </c>
-      <c r="AZ10">
-        <v>20</v>
-      </c>
-      <c r="BA10">
-        <v>12.5</v>
-      </c>
-      <c r="BB10">
-        <v>18.5</v>
-      </c>
-      <c r="BC10">
-        <v>20</v>
-      </c>
-      <c r="BD10">
-        <v>11.5</v>
-      </c>
-      <c r="BE10">
-        <v>13</v>
-      </c>
-      <c r="BF10">
-        <v>17</v>
-      </c>
-      <c r="BG10">
-        <v>12.5</v>
-      </c>
-      <c r="BH10">
-        <v>2.8</v>
-      </c>
-      <c r="BI10">
-        <v>2.64</v>
-      </c>
-      <c r="BJ10">
-        <v>12</v>
-      </c>
-      <c r="BK10">
-        <v>9</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>15.5</v>
-      </c>
-      <c r="BN10">
-        <v>4.3</v>
-      </c>
-      <c r="BO10">
-        <v>4</v>
-      </c>
-      <c r="BP10">
-        <v>16</v>
-      </c>
-      <c r="BQ10">
-        <v>9.6</v>
-      </c>
-      <c r="BR10">
-        <v>40</v>
-      </c>
-      <c r="BS10">
-        <v>11.5</v>
-      </c>
-      <c r="BT10">
-        <v>8.4</v>
-      </c>
-      <c r="BU10">
-        <v>6.2</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>12.5</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>13.5</v>
-      </c>
-      <c r="BZ10">
-        <v>40</v>
-      </c>
-      <c r="CA10">
-        <v>11.5</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
